--- a/output/profile_1_civil_vias_sst_tracker.xlsx
+++ b/output/profile_1_civil_vias_sst_tracker.xlsx
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K417"/>
+  <dimension ref="A1:K424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8065,26 +8065,26 @@
     <row r="161" ht="22" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>3cbe044b124adb25</t>
+          <t>0a8a903505ae1d9a</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 05:09</t>
+          <t>2026-09-27 15:38</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>Coordinador/a Plan estratégico de seguridad vial</t>
+          <t>Psicólogo especialista SST</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>EMPRESA TRANSPORTADORA SAN GABRIEL SAS</t>
+          <t>Importante empresa del sector</t>
         </is>
       </c>
       <c r="E161" s="7" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -8092,17 +8092,13 @@
         </is>
       </c>
       <c r="G161" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinadora-plan-estrategico-de-seguridad-vial-pesv-bogota-en-bogota-dc-2AE9BF94CB16F8FA61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H161" s="6" t="inlineStr">
-        <is>
-          <t>$ 3.710.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-psicologo-especialista-sst-medellin-en-medellin-A6F5DECAB8956D1061373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H161" s="6" t="inlineStr"/>
       <c r="I161" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 55/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
@@ -8115,7 +8111,7 @@
     <row r="162" ht="22" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>f93c2e5eedb2fde7</t>
+          <t>3cbe044b124adb25</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -8125,12 +8121,12 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Coordinador seguridad industrial y sst - plantas de producción</t>
+          <t>Coordinador/a Plan estratégico de seguridad vial</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>EMPRESA TRANSPORTADORA SAN GABRIEL SAS</t>
         </is>
       </c>
       <c r="E162" s="7" t="n">
@@ -8142,13 +8138,17 @@
         </is>
       </c>
       <c r="G162" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-seguridad-industrial-y-sst-plantas-de-produccion-1886745985", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H162" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinadora-plan-estrategico-de-seguridad-vial-pesv-bogota-en-bogota-dc-2AE9BF94CB16F8FA61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H162" s="6" t="inlineStr">
+        <is>
+          <t>$ 3.710.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -8161,7 +8161,7 @@
     <row r="163" ht="22" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>a1c66287744c7791</t>
+          <t>f93c2e5eedb2fde7</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -8171,12 +8171,12 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Coordinador/a Plan estratégico de seguridad vial</t>
+          <t>Coordinador seguridad industrial y sst - plantas de producción</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Empresa Transportadora San Gabriel S.A.S.</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E163" s="7" t="n">
@@ -8188,13 +8188,13 @@
         </is>
       </c>
       <c r="G163" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-plan-estrat%C3%A9gico-de-seguridad-vial-pesv-at-empresa-transportadora-san-gabriel-s-a-s-4469263436", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-seguridad-industrial-y-sst-plantas-de-produccion-1886745985", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H163" s="6" t="inlineStr"/>
       <c r="I163" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
@@ -8207,22 +8207,22 @@
     <row r="164" ht="22" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>336177464dac0014</t>
+          <t>a1c66287744c7791</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 10:17</t>
+          <t>2026-09-22 05:09</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Coordinador/a PESV / Plan estratégico de seguridad vial</t>
+          <t>Coordinador/a Plan estratégico de seguridad vial</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO COMFAMA</t>
+          <t>Empresa Transportadora San Gabriel S.A.S.</t>
         </is>
       </c>
       <c r="E164" s="7" t="n">
@@ -8234,14 +8234,10 @@
         </is>
       </c>
       <c r="G164" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinadora-pesv-plan-estrategico-de-seguridad-vial-seguridad-y-salud-en-el-trabajo-en-medellin-5081CD2DD6E3583F61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H164" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.800.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-plan-estrat%C3%A9gico-de-seguridad-vial-pesv-at-empresa-transportadora-san-gabriel-s-a-s-4469263436", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H164" s="6" t="inlineStr"/>
       <c r="I164" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -8257,22 +8253,22 @@
     <row r="165" ht="22" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>0f38d72fbe51d491</t>
+          <t>336177464dac0014</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:49</t>
+          <t>2026-09-23 10:17</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Coordinador PESV Plan Estratégico de Seguridad Vial/ Cubrimiento Licencia de Maternidad</t>
+          <t>Coordinador/a PESV / Plan estratégico de seguridad vial</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Eulen Colombia S.A</t>
+          <t>AGENCIA DE EMPLEO COMFAMA</t>
         </is>
       </c>
       <c r="E165" s="7" t="n">
@@ -8284,12 +8280,12 @@
         </is>
       </c>
       <c r="G165" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-pesv-plan-estrategico-de-seguridad-vial-cubrimiento-licencia-de-maternidad-en-bogota-dc-2BC3B40C1B36AB5561373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinadora-pesv-plan-estrategico-de-seguridad-vial-seguridad-y-salud-en-el-trabajo-en-medellin-5081CD2DD6E3583F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H165" s="6" t="inlineStr">
         <is>
-          <t>$ 2.105.000,00 (Mensual)</t>
+          <t>$ 2.800.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I165" s="3" t="inlineStr">
@@ -8307,22 +8303,22 @@
     <row r="166" ht="22" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>fb215e5097ec76c6</t>
+          <t>0f38d72fbe51d491</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:50</t>
+          <t>2026-09-24 15:49</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Coordinador(a) de Seguridad y Salud en el Trabajo</t>
+          <t>Coordinador PESV Plan Estratégico de Seguridad Vial/ Cubrimiento Licencia de Maternidad</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Importante empresa del sector LOGISTICO</t>
+          <t>Eulen Colombia S.A</t>
         </is>
       </c>
       <c r="E166" s="7" t="n">
@@ -8334,13 +8330,17 @@
         </is>
       </c>
       <c r="G166" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinadora-de-seguridad-y-salud-en-el-trabajo-sst-barranquilla-en-barranquilla-C2287C727D6B7D0A61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H166" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-pesv-plan-estrategico-de-seguridad-vial-cubrimiento-licencia-de-maternidad-en-bogota-dc-2BC3B40C1B36AB5561373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H166" s="6" t="inlineStr">
+        <is>
+          <t>$ 2.105.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I166" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -8353,26 +8353,26 @@
     <row r="167" ht="22" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>aab045c9be9eca86</t>
+          <t>fb215e5097ec76c6</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 03:17</t>
+          <t>2026-09-25 15:50</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero infraestructura - bilingue - remoto</t>
+          <t>Coordinador(a) de Seguridad y Salud en el Trabajo</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>MICHAEL PAGE INTERNATIONAL</t>
+          <t>Importante empresa del sector LOGISTICO</t>
         </is>
       </c>
       <c r="E167" s="7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
@@ -8380,13 +8380,13 @@
         </is>
       </c>
       <c r="G167" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-infraestructura-bilingue-remoto-1886744267", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinadora-de-seguridad-y-salud-en-el-trabajo-sst-barranquilla-en-barranquilla-C2287C727D6B7D0A61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H167" s="6" t="inlineStr"/>
       <c r="I167" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
@@ -8399,7 +8399,7 @@
     <row r="168" ht="22" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>1a61ce5041122a0a</t>
+          <t>aab045c9be9eca86</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -8409,12 +8409,12 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero de infraestructura (servidores/aws) - remoto</t>
+          <t>Ingeniero infraestructura - bilingue - remoto</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>Cinte Colombia SAS</t>
+          <t>MICHAEL PAGE INTERNATIONAL</t>
         </is>
       </c>
       <c r="E168" s="7" t="n">
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="G168" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-de-infraestructura-servidores-aws-remoto-1886744007", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-infraestructura-bilingue-remoto-1886744267", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H168" s="6" t="inlineStr"/>
@@ -8445,7 +8445,7 @@
     <row r="169" ht="22" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>1c3cc968f8905c3e</t>
+          <t>1a61ce5041122a0a</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero/a de infraestructura y conectividad cloud remoto</t>
+          <t>Ingeniero de infraestructura (servidores/aws) - remoto</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>TALYCAP GLOBAL SAS</t>
+          <t>Cinte Colombia SAS</t>
         </is>
       </c>
       <c r="E169" s="7" t="n">
@@ -8472,7 +8472,7 @@
         </is>
       </c>
       <c r="G169" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-a-de-infraestructura-y-conectividad-cloud-remoto-1886768627", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-de-infraestructura-servidores-aws-remoto-1886744007", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H169" s="6" t="inlineStr"/>
@@ -8491,7 +8491,7 @@
     <row r="170" ht="22" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>d1d0c6736a34b513</t>
+          <t>1c3cc968f8905c3e</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero/a de infraestructura y conectividad cloud 100% remoto</t>
+          <t>Ingeniero/a de infraestructura y conectividad cloud remoto</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
@@ -8518,7 +8518,7 @@
         </is>
       </c>
       <c r="G170" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-a-de-infraestructura-y-conectividad-cloud-100-remoto-1886768625", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-a-de-infraestructura-y-conectividad-cloud-remoto-1886768627", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H170" s="6" t="inlineStr"/>
@@ -8537,7 +8537,7 @@
     <row r="171" ht="22" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>ec4f785d321ad6f2</t>
+          <t>d1d0c6736a34b513</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero de infraestructura</t>
+          <t>Ingeniero/a de infraestructura y conectividad cloud 100% remoto</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>TALYCAP GLOBAL SAS</t>
         </is>
       </c>
       <c r="E171" s="7" t="n">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="G171" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-de-infraestructura-1886755031", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-a-de-infraestructura-y-conectividad-cloud-100-remoto-1886768625", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H171" s="6" t="inlineStr"/>
@@ -8583,7 +8583,7 @@
     <row r="172" ht="22" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>0948ea95da6f92b1</t>
+          <t>ec4f785d321ad6f2</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Director de interventoría concesión</t>
+          <t>Ingeniero de infraestructura</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="G172" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-de-interventoria-concesion-1886746971", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-de-infraestructura-1886755031", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H172" s="6" t="inlineStr"/>
       <c r="I172" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
@@ -8629,7 +8629,7 @@
     <row r="173" ht="22" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>c9f286b043467fde</t>
+          <t>0948ea95da6f92b1</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>Director de interventoría proyectos de tecnología</t>
+          <t>Director de interventoría concesión</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="G173" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-de-interventoria-proyectos-de-tecnologia-1886751669", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-de-interventoria-concesion-1886746971", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H173" s="6" t="inlineStr"/>
@@ -8675,7 +8675,7 @@
     <row r="174" ht="22" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>1a624bde0aabf417</t>
+          <t>c9f286b043467fde</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -8685,12 +8685,12 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Director de interventoria civil | yumbo - valle del cauca</t>
+          <t>Director de interventoría proyectos de tecnología</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>INP PROYECTOS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E174" s="7" t="n">
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="G174" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-de-interventoria-civil-yumbo-valle-del-cauca-1886761247", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-de-interventoria-proyectos-de-tecnologia-1886751669", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H174" s="6" t="inlineStr"/>
@@ -8721,7 +8721,7 @@
     <row r="175" ht="22" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>5a15c71034d6360d</t>
+          <t>1a624bde0aabf417</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>Director de interventoría / mosquera, cundinamarca</t>
+          <t>Director de interventoria civil | yumbo - valle del cauca</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>INP PROYECTOS</t>
         </is>
       </c>
       <c r="E175" s="7" t="n">
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="G175" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-de-interventoria-mosquera-cundinamarca-1886761828", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-de-interventoria-civil-yumbo-valle-del-cauca-1886761247", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H175" s="6" t="inlineStr"/>
@@ -8767,7 +8767,7 @@
     <row r="176" ht="22" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>deca148c608f5071</t>
+          <t>5a15c71034d6360d</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Director hseq - chia</t>
+          <t>Director de interventoría / mosquera, cundinamarca</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
@@ -8794,13 +8794,13 @@
         </is>
       </c>
       <c r="G176" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-hseq-chia-1886755279", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-de-interventoria-mosquera-cundinamarca-1886761828", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H176" s="6" t="inlineStr"/>
       <c r="I176" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
@@ -8813,7 +8813,7 @@
     <row r="177" ht="22" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>158a5b888f4835d9</t>
+          <t>deca148c608f5071</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero Civil Senior Estructural Obras Hidráulicas</t>
+          <t>Director hseq - chia</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>IDOM Consulting, Engineering, Architecture</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E177" s="7" t="n">
@@ -8840,13 +8840,13 @@
         </is>
       </c>
       <c r="G177" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-civil-senior-estructural-obras-hidr%C3%A1ulicas-at-idom-consulting-engineering-architecture-4449786446", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-hseq-chia-1886755279", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H177" s="6" t="inlineStr"/>
       <c r="I177" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
@@ -8859,22 +8859,22 @@
     <row r="178" ht="22" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>f1bdba926234f67e</t>
+          <t>158a5b888f4835d9</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 03:27</t>
+          <t>2026-09-22 03:17</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Director (a) Comercial ARL y SST</t>
+          <t>Ingeniero Civil Senior Estructural Obras Hidráulicas</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>MASTER SST</t>
+          <t>IDOM Consulting, Engineering, Architecture</t>
         </is>
       </c>
       <c r="E178" s="7" t="n">
@@ -8886,17 +8886,13 @@
         </is>
       </c>
       <c r="G178" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-director-a-comercial-arl-y-sst-bogota-y-zonas-aledanas-en-bogota-dc-AD10DBD96F164F8C61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H178" s="6" t="inlineStr">
-        <is>
-          <t>$ 3.000.000,00 (Mensual) + Comisiones</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-civil-senior-estructural-obras-hidr%C3%A1ulicas-at-idom-consulting-engineering-architecture-4449786446", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H178" s="6" t="inlineStr"/>
       <c r="I178" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
@@ -8909,22 +8905,22 @@
     <row r="179" ht="22" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>90c3670c335038e4</t>
+          <t>f1bdba926234f67e</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 05:09</t>
+          <t>2026-09-22 03:27</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>Director de Proyecto</t>
+          <t>Director (a) Comercial ARL y SST</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>ADRIAN MAFIOLI Y CIA S.A.S</t>
+          <t>MASTER SST</t>
         </is>
       </c>
       <c r="E179" s="7" t="n">
@@ -8936,13 +8932,17 @@
         </is>
       </c>
       <c r="G179" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-director-de-proyecto-ingeniero-en-transporte-y-vias-ingeniero-civil-en-lebrija-04F373EC97EDC4CB61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H179" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-director-a-comercial-arl-y-sst-bogota-y-zonas-aledanas-en-bogota-dc-AD10DBD96F164F8C61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H179" s="6" t="inlineStr">
+        <is>
+          <t>$ 3.000.000,00 (Mensual) + Comisiones</t>
+        </is>
+      </c>
       <c r="I179" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
@@ -8955,7 +8955,7 @@
     <row r="180" ht="22" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>1af0455db2f829b8</t>
+          <t>90c3670c335038e4</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>Consultora en Seguridad y Salud en el trabajo</t>
+          <t>Director de Proyecto</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>MEZZA Y CIA LTDA</t>
+          <t>ADRIAN MAFIOLI Y CIA S.A.S</t>
         </is>
       </c>
       <c r="E180" s="7" t="n">
@@ -8982,17 +8982,13 @@
         </is>
       </c>
       <c r="G180" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-consultora-en-seguridad-y-salud-en-el-trabajo-en-bogota-dc-07E9BF3B6742F79361373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H180" s="6" t="inlineStr">
-        <is>
-          <t>Presencial y remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-director-de-proyecto-ingeniero-en-transporte-y-vias-ingeniero-civil-en-lebrija-04F373EC97EDC4CB61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H180" s="6" t="inlineStr"/>
       <c r="I180" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
@@ -9005,7 +9001,7 @@
     <row r="181" ht="22" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>1feadbd74bd9bfbe</t>
+          <t>1af0455db2f829b8</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -9015,12 +9011,12 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>Director de interventoría</t>
+          <t>Consultora en Seguridad y Salud en el trabajo</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>AMERICAS GBS SAS</t>
+          <t>MEZZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="E181" s="7" t="n">
@@ -9032,13 +9028,17 @@
         </is>
       </c>
       <c r="G181" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-director-de-interventoria-director-de-obra-en--643E1A399D2C177561373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H181" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-consultora-en-seguridad-y-salud-en-el-trabajo-en-bogota-dc-07E9BF3B6742F79361373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H181" s="6" t="inlineStr">
+        <is>
+          <t>Presencial y remoto</t>
+        </is>
+      </c>
       <c r="I181" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
@@ -9051,7 +9051,7 @@
     <row r="182" ht="22" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>58e1b7cc06edffaf</t>
+          <t>1feadbd74bd9bfbe</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -9061,12 +9061,12 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>Gerente de proyecto sector inmobiliario</t>
+          <t>Director de interventoría</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO COMFAMA</t>
+          <t>AMERICAS GBS SAS</t>
         </is>
       </c>
       <c r="E182" s="7" t="n">
@@ -9078,14 +9078,10 @@
         </is>
       </c>
       <c r="G182" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-gerente-de-proyecto-sector-inmobiliario-en-medellin-1D6BC514AC61985761373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H182" s="6" t="inlineStr">
-        <is>
-          <t>$ 12.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-director-de-interventoria-director-de-obra-en--643E1A399D2C177561373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H182" s="6" t="inlineStr"/>
       <c r="I182" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -9101,7 +9097,7 @@
     <row r="183" ht="22" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>511ca640d20d7c32</t>
+          <t>58e1b7cc06edffaf</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -9111,12 +9107,12 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero infraestructura - bilingue - remoto</t>
+          <t>Gerente de proyecto sector inmobiliario</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>MICHAEL PAGE INTERNATIONAL</t>
+          <t>AGENCIA DE EMPLEO COMFAMA</t>
         </is>
       </c>
       <c r="E183" s="7" t="n">
@@ -9128,13 +9124,17 @@
         </is>
       </c>
       <c r="G183" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-infraestructura-bilingue-remoto-1886744267", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H183" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-gerente-de-proyecto-sector-inmobiliario-en-medellin-1D6BC514AC61985761373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H183" s="6" t="inlineStr">
+        <is>
+          <t>$ 12.000.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I183" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
     <row r="184" ht="22" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>c4c55096ea3e18ec</t>
+          <t>511ca640d20d7c32</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero de infraestructura (servidores/aws) - remoto</t>
+          <t>Ingeniero infraestructura - bilingue - remoto</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>Cinte Colombia SAS</t>
+          <t>MICHAEL PAGE INTERNATIONAL</t>
         </is>
       </c>
       <c r="E184" s="7" t="n">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="G184" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-de-infraestructura-servidores-aws-remoto-1886744007", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-infraestructura-bilingue-remoto-1886744267", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H184" s="6" t="inlineStr"/>
@@ -9193,7 +9193,7 @@
     <row r="185" ht="22" customHeight="1">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>9bf756e884703fa1</t>
+          <t>c4c55096ea3e18ec</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
@@ -9203,12 +9203,12 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero/a de infraestructura y conectividad cloud remoto</t>
+          <t>Ingeniero de infraestructura (servidores/aws) - remoto</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>TALYCAP GLOBAL SAS</t>
+          <t>Cinte Colombia SAS</t>
         </is>
       </c>
       <c r="E185" s="7" t="n">
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="G185" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-a-de-infraestructura-y-conectividad-cloud-remoto-1886768627", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-de-infraestructura-servidores-aws-remoto-1886744007", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H185" s="6" t="inlineStr"/>
@@ -9239,7 +9239,7 @@
     <row r="186" ht="22" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>6f66992aface828b</t>
+          <t>9bf756e884703fa1</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero/a de infraestructura y conectividad cloud 100% remoto</t>
+          <t>Ingeniero/a de infraestructura y conectividad cloud remoto</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
@@ -9266,7 +9266,7 @@
         </is>
       </c>
       <c r="G186" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-a-de-infraestructura-y-conectividad-cloud-100-remoto-1886768625", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-a-de-infraestructura-y-conectividad-cloud-remoto-1886768627", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H186" s="6" t="inlineStr"/>
@@ -9285,7 +9285,7 @@
     <row r="187" ht="22" customHeight="1">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>aa9466dfe7d6ea2b</t>
+          <t>6f66992aface828b</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero de infraestructura</t>
+          <t>Ingeniero/a de infraestructura y conectividad cloud 100% remoto</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>TALYCAP GLOBAL SAS</t>
         </is>
       </c>
       <c r="E187" s="7" t="n">
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="G187" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-de-infraestructura-1886755031", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-a-de-infraestructura-y-conectividad-cloud-100-remoto-1886768625", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H187" s="6" t="inlineStr"/>
@@ -9331,7 +9331,7 @@
     <row r="188" ht="22" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>b6b37cabc98817e3</t>
+          <t>aa9466dfe7d6ea2b</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>Director de interventoría concesión</t>
+          <t>Ingeniero de infraestructura</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
@@ -9358,13 +9358,13 @@
         </is>
       </c>
       <c r="G188" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-de-interventoria-concesion-1886746971", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-de-infraestructura-1886755031", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H188" s="6" t="inlineStr"/>
       <c r="I188" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
@@ -9377,7 +9377,7 @@
     <row r="189" ht="22" customHeight="1">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>ce17946994d038a1</t>
+          <t>b6b37cabc98817e3</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>Director de interventoría proyectos de tecnología</t>
+          <t>Director de interventoría concesión</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="G189" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-de-interventoria-proyectos-de-tecnologia-1886751669", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-de-interventoria-concesion-1886746971", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H189" s="6" t="inlineStr"/>
@@ -9423,7 +9423,7 @@
     <row r="190" ht="22" customHeight="1">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>bda13b98253a2a50</t>
+          <t>ce17946994d038a1</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -9433,12 +9433,12 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>Director de interventoria civil | yumbo - valle del cauca</t>
+          <t>Director de interventoría proyectos de tecnología</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>INP PROYECTOS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E190" s="7" t="n">
@@ -9450,7 +9450,7 @@
         </is>
       </c>
       <c r="G190" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-de-interventoria-civil-yumbo-valle-del-cauca-1886761247", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-de-interventoria-proyectos-de-tecnologia-1886751669", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H190" s="6" t="inlineStr"/>
@@ -9469,7 +9469,7 @@
     <row r="191" ht="22" customHeight="1">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>5f9ea780b98f8c1e</t>
+          <t>bda13b98253a2a50</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>Director de interventoría / mosquera, cundinamarca</t>
+          <t>Director de interventoria civil | yumbo - valle del cauca</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>INP PROYECTOS</t>
         </is>
       </c>
       <c r="E191" s="7" t="n">
@@ -9496,7 +9496,7 @@
         </is>
       </c>
       <c r="G191" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-de-interventoria-mosquera-cundinamarca-1886761828", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-de-interventoria-civil-yumbo-valle-del-cauca-1886761247", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H191" s="6" t="inlineStr"/>
@@ -9515,7 +9515,7 @@
     <row r="192" ht="22" customHeight="1">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>fc3b5b2ce1bd6c85</t>
+          <t>5f9ea780b98f8c1e</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>Director hseq - chia</t>
+          <t>Director de interventoría / mosquera, cundinamarca</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
@@ -9542,13 +9542,13 @@
         </is>
       </c>
       <c r="G192" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-hseq-chia-1886755279", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-de-interventoria-mosquera-cundinamarca-1886761828", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H192" s="6" t="inlineStr"/>
       <c r="I192" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
@@ -9561,7 +9561,7 @@
     <row r="193" ht="22" customHeight="1">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>7d9a8688b4af9ac9</t>
+          <t>fc3b5b2ce1bd6c85</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero hseq - neiva</t>
+          <t>Director hseq - chia</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>ICONTEC</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E193" s="7" t="n">
@@ -9588,7 +9588,7 @@
         </is>
       </c>
       <c r="G193" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-hseq-neiva-1886744084", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-hseq-chia-1886755279", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H193" s="6" t="inlineStr"/>
@@ -9607,7 +9607,7 @@
     <row r="194" ht="22" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>9672c07df7f7c273</t>
+          <t>7d9a8688b4af9ac9</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>Bogota - consultor de sistemas de gestion - hseq</t>
+          <t>Ingeniero hseq - neiva</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ICONTEC</t>
         </is>
       </c>
       <c r="E194" s="7" t="n">
@@ -9634,7 +9634,7 @@
         </is>
       </c>
       <c r="G194" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/bogota-consultor-de-sistemas-de-gestion-hseq-1886769154", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-hseq-neiva-1886744084", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H194" s="6" t="inlineStr"/>
@@ -9653,7 +9653,7 @@
     <row r="195" ht="22" customHeight="1">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>0a1acb8adf7421ab</t>
+          <t>9672c07df7f7c273</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>Medellin - consultor de sistemas de gestion - hseq</t>
+          <t>Bogota - consultor de sistemas de gestion - hseq</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
@@ -9680,7 +9680,7 @@
         </is>
       </c>
       <c r="G195" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/medellin-consultor-de-sistemas-de-gestion-hseq-1886769144", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/bogota-consultor-de-sistemas-de-gestion-hseq-1886769154", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H195" s="6" t="inlineStr"/>
@@ -9699,7 +9699,7 @@
     <row r="196" ht="22" customHeight="1">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>df96de49b7d10c23</t>
+          <t>0a1acb8adf7421ab</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>Consultor(a) sistema de gestión hseq - bucaramanga</t>
+          <t>Medellin - consultor de sistemas de gestion - hseq</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
@@ -9726,7 +9726,7 @@
         </is>
       </c>
       <c r="G196" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultora-sistema-de-gestion-hseq-bucaramanga-1886759378", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/medellin-consultor-de-sistemas-de-gestion-hseq-1886769144", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H196" s="6" t="inlineStr"/>
@@ -9745,7 +9745,7 @@
     <row r="197" ht="22" customHeight="1">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>40659dd2e41fd444</t>
+          <t>df96de49b7d10c23</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero topográfico - especialista senior</t>
+          <t>Consultor(a) sistema de gestión hseq - bucaramanga</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -9772,13 +9772,13 @@
         </is>
       </c>
       <c r="G197" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-topografico-especialista-senior-1886765054", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultora-sistema-de-gestion-hseq-bucaramanga-1886759378", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H197" s="6" t="inlineStr"/>
       <c r="I197" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
@@ -9791,7 +9791,7 @@
     <row r="198" ht="22" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>7b0f7c3850ec6f61</t>
+          <t>40659dd2e41fd444</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>Coordinador (a) senior - especialista en bioequivalencias</t>
+          <t>Ingeniero topográfico - especialista senior</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>LABORATORIOS BUSSIE</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E198" s="7" t="n">
@@ -9818,7 +9818,7 @@
         </is>
       </c>
       <c r="G198" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-a-senior-especialista-en-bioequivalencias-1886769840", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-topografico-especialista-senior-1886765054", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H198" s="6" t="inlineStr"/>
@@ -9837,7 +9837,7 @@
     <row r="199" ht="22" customHeight="1">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>aeaf42aeea186cb0</t>
+          <t>7b0f7c3850ec6f61</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>Profesional en sst o ingeniero esp en sst - rio negro</t>
+          <t>Coordinador (a) senior - especialista en bioequivalencias</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>LABORATORIOS BUSSIE</t>
         </is>
       </c>
       <c r="E199" s="7" t="n">
@@ -9864,13 +9864,13 @@
         </is>
       </c>
       <c r="G199" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/profesional-en-sst-o-ingeniero-esp-en-sst-rio-negro-1886758412", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-a-senior-especialista-en-bioequivalencias-1886769840", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H199" s="6" t="inlineStr"/>
       <c r="I199" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
@@ -9883,7 +9883,7 @@
     <row r="200" ht="22" customHeight="1">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>07f1ee6c04e40269</t>
+          <t>aeaf42aeea186cb0</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -9910,7 +9910,7 @@
         </is>
       </c>
       <c r="G200" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/profesional-en-sst-o-ingeniero-esp-en-sst-rio-negro-1886752068", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/profesional-en-sst-o-ingeniero-esp-en-sst-rio-negro-1886758412", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H200" s="6" t="inlineStr"/>
@@ -9929,7 +9929,7 @@
     <row r="201" ht="22" customHeight="1">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>09443eef5570ce96</t>
+          <t>07f1ee6c04e40269</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>Director de proyecto movilidad</t>
+          <t>Profesional en sst o ingeniero esp en sst - rio negro</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>JAHV MC GREGOR S.A.S</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E201" s="7" t="n">
@@ -9956,13 +9956,13 @@
         </is>
       </c>
       <c r="G201" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-de-proyecto-movilidad-1886766486", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/profesional-en-sst-o-ingeniero-esp-en-sst-rio-negro-1886752068", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H201" s="6" t="inlineStr"/>
       <c r="I201" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
@@ -9975,7 +9975,7 @@
     <row r="202" ht="22" customHeight="1">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>b54c3610b3497128</t>
+          <t>09443eef5570ce96</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -9985,12 +9985,12 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>Líder proyectos e ingeniería</t>
+          <t>Director de proyecto movilidad</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>SinapSer</t>
+          <t>JAHV MC GREGOR S.A.S</t>
         </is>
       </c>
       <c r="E202" s="7" t="n">
@@ -10002,7 +10002,7 @@
         </is>
       </c>
       <c r="G202" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/lider-proyectos-e-ingenieria-1886749715", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-de-proyecto-movilidad-1886766486", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H202" s="6" t="inlineStr"/>
@@ -10021,7 +10021,7 @@
     <row r="203" ht="22" customHeight="1">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>d554349d14476076</t>
+          <t>b54c3610b3497128</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>Director de proyecto</t>
+          <t>Líder proyectos e ingeniería</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>SinapSer</t>
         </is>
       </c>
       <c r="E203" s="7" t="n">
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="G203" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-de-proyecto-1886769375", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/lider-proyectos-e-ingenieria-1886749715", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H203" s="6" t="inlineStr"/>
@@ -10067,7 +10067,7 @@
     <row r="204" ht="22" customHeight="1">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>772da76a91611419</t>
+          <t>d554349d14476076</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>Gerente de proyectos</t>
+          <t>Director de proyecto</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>SUMMAR PRODUCTIVIDAD S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E204" s="7" t="n">
@@ -10094,7 +10094,7 @@
         </is>
       </c>
       <c r="G204" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/gerente-de-proyectos-1886767600", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-de-proyecto-1886769375", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H204" s="6" t="inlineStr"/>
@@ -10113,7 +10113,7 @@
     <row r="205" ht="22" customHeight="1">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>2fb7132270011cb4</t>
+          <t>772da76a91611419</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>Gerente de proyecto tic</t>
+          <t>Gerente de proyectos</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>MANPOWER</t>
+          <t>SUMMAR PRODUCTIVIDAD S.A.S</t>
         </is>
       </c>
       <c r="E205" s="7" t="n">
@@ -10140,7 +10140,7 @@
         </is>
       </c>
       <c r="G205" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/gerente-de-proyecto-tic-1886743669", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/gerente-de-proyectos-1886767600", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H205" s="6" t="inlineStr"/>
@@ -10159,7 +10159,7 @@
     <row r="206" ht="22" customHeight="1">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>3f55a2f61ab57bc3</t>
+          <t>2fb7132270011cb4</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -10169,12 +10169,12 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>Gerente de proyectos para empresa de tecnología</t>
+          <t>Gerente de proyecto tic</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>Gattaca Outsourcing S.A.S.</t>
+          <t>MANPOWER</t>
         </is>
       </c>
       <c r="E206" s="7" t="n">
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="G206" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/gerente-de-proyectos-para-empresa-de-tecnologia-1886747783", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/gerente-de-proyecto-tic-1886743669", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H206" s="6" t="inlineStr"/>
@@ -10205,7 +10205,7 @@
     <row r="207" ht="22" customHeight="1">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>66e63adcbcc1d616</t>
+          <t>3f55a2f61ab57bc3</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -10215,12 +10215,12 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>Consultor de soporte gestión humana y sst</t>
+          <t>Gerente de proyectos para empresa de tecnología</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Gattaca Outsourcing S.A.S.</t>
         </is>
       </c>
       <c r="E207" s="7" t="n">
@@ -10232,13 +10232,13 @@
         </is>
       </c>
       <c r="G207" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultor-de-soporte-gestion-humana-y-sst-1886759036", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/gerente-de-proyectos-para-empresa-de-tecnologia-1886747783", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H207" s="6" t="inlineStr"/>
       <c r="I207" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
     <row r="208" ht="22" customHeight="1">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>4b86da36a8f7b158</t>
+          <t>66e63adcbcc1d616</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero esp en sst - palmira</t>
+          <t>Consultor de soporte gestión humana y sst</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E208" s="7" t="n">
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="G208" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-esp-en-sst-palmira-1886743728", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultor-de-soporte-gestion-humana-y-sst-1886759036", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H208" s="6" t="inlineStr"/>
@@ -10297,7 +10297,7 @@
     <row r="209" ht="22" customHeight="1">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>0a9344b068ffdb17</t>
+          <t>4b86da36a8f7b158</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -10324,7 +10324,7 @@
         </is>
       </c>
       <c r="G209" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-esp-en-sst-palmira-1886760865", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-esp-en-sst-palmira-1886743728", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H209" s="6" t="inlineStr"/>
@@ -10343,7 +10343,7 @@
     <row r="210" ht="22" customHeight="1">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>193cfde3b5dfbfaa</t>
+          <t>0a9344b068ffdb17</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>Director(a) de talento humano y sst</t>
+          <t>Ingeniero esp en sst - palmira</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E210" s="7" t="n">
@@ -10370,7 +10370,7 @@
         </is>
       </c>
       <c r="G210" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/directora-de-talento-humano-y-sst-1886746502", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-esp-en-sst-palmira-1886760865", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H210" s="6" t="inlineStr"/>
@@ -10389,7 +10389,7 @@
     <row r="211" ht="22" customHeight="1">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>6386ae2cdd0ca648</t>
+          <t>193cfde3b5dfbfaa</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -10399,12 +10399,12 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero hseq - hidrocarburos</t>
+          <t>Director(a) de talento humano y sst</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E211" s="7" t="n">
@@ -10416,7 +10416,7 @@
         </is>
       </c>
       <c r="G211" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-hseq-hidrocarburos-1886757090", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/directora-de-talento-humano-y-sst-1886746502", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H211" s="6" t="inlineStr"/>
@@ -10435,7 +10435,7 @@
     <row r="212" ht="22" customHeight="1">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>7e3a819c5137691c</t>
+          <t>6386ae2cdd0ca648</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -10445,12 +10445,12 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>Bogota - consultor sistemas de gestión sst- con licencia en sst</t>
+          <t>Ingeniero hseq - hidrocarburos</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E212" s="7" t="n">
@@ -10462,13 +10462,13 @@
         </is>
       </c>
       <c r="G212" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/bogota-consultor-sistemas-de-gestion-sst-con-licencia-en-sst-1886759829", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-hseq-hidrocarburos-1886757090", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H212" s="6" t="inlineStr"/>
       <c r="I212" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado. Observación: Requiere Licencia en Seguridad y Salud en el Trabajo (SST) vigente.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J212" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
     <row r="213" ht="22" customHeight="1">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>8a9cbfc1b1d76c90</t>
+          <t>7e3a819c5137691c</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -10508,7 +10508,7 @@
         </is>
       </c>
       <c r="G213" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/bogota-consultor-sistemas-de-gestion-sst-con-licencia-en-sst-1886764895", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/bogota-consultor-sistemas-de-gestion-sst-con-licencia-en-sst-1886759829", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H213" s="6" t="inlineStr"/>
@@ -10527,7 +10527,7 @@
     <row r="214" ht="22" customHeight="1">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>654baa524215581d</t>
+          <t>8a9cbfc1b1d76c90</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>Medellín - consultor sistemas de gestión sst- con licencia en sst</t>
+          <t>Bogota - consultor sistemas de gestión sst- con licencia en sst</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="G214" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/medellin-consultor-sistemas-de-gestion-sst-con-licencia-en-sst-1886764969", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/bogota-consultor-sistemas-de-gestion-sst-con-licencia-en-sst-1886764895", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H214" s="6" t="inlineStr"/>
@@ -10573,7 +10573,7 @@
     <row r="215" ht="22" customHeight="1">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>cfad72f86eb60cd6</t>
+          <t>654baa524215581d</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>Consultor sst freelance</t>
+          <t>Medellín - consultor sistemas de gestión sst- con licencia en sst</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>SELECTED HR</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E215" s="7" t="n">
@@ -10600,13 +10600,13 @@
         </is>
       </c>
       <c r="G215" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultor-sst-freelance-1886758665", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/medellin-consultor-sistemas-de-gestion-sst-con-licencia-en-sst-1886764969", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H215" s="6" t="inlineStr"/>
       <c r="I215" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado. Observación: Requiere Licencia en Seguridad y Salud en el Trabajo (SST) vigente.</t>
         </is>
       </c>
       <c r="J215" s="2" t="inlineStr">
@@ -10619,7 +10619,7 @@
     <row r="216" ht="22" customHeight="1">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>b7e5ecf9972019b8</t>
+          <t>cfad72f86eb60cd6</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>Cali - consultor de sistemas de gestion sst independiente</t>
+          <t>Consultor sst freelance</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>SELECTED HR</t>
         </is>
       </c>
       <c r="E216" s="7" t="n">
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="G216" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-consultor-de-sistemas-de-gestion-sst-independiente-1886766615", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultor-sst-freelance-1886758665", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H216" s="6" t="inlineStr"/>
@@ -10665,7 +10665,7 @@
     <row r="217" ht="22" customHeight="1">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>45156e9fe504104c</t>
+          <t>b7e5ecf9972019b8</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>Barranquilla - consultor de sistemas de gestion sst independiente</t>
+          <t>Cali - consultor de sistemas de gestion sst independiente</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
@@ -10692,7 +10692,7 @@
         </is>
       </c>
       <c r="G217" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/barranquilla-consultor-de-sistemas-de-gestion-sst-independiente-1886765182", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-consultor-de-sistemas-de-gestion-sst-independiente-1886766615", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H217" s="6" t="inlineStr"/>
@@ -10711,7 +10711,7 @@
     <row r="218" ht="22" customHeight="1">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>2414c05d0c98b4bf</t>
+          <t>45156e9fe504104c</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>Consultor(a) sst - gestión del riesgo químico - barrancabermeja</t>
+          <t>Barranquilla - consultor de sistemas de gestion sst independiente</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
@@ -10738,7 +10738,7 @@
         </is>
       </c>
       <c r="G218" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultora-sst-gestion-del-riesgo-quimico-barrancabermeja-1886746280", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/barranquilla-consultor-de-sistemas-de-gestion-sst-independiente-1886765182", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H218" s="6" t="inlineStr"/>
@@ -10757,7 +10757,7 @@
     <row r="219" ht="22" customHeight="1">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>3d360078771e726a</t>
+          <t>2414c05d0c98b4bf</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -10767,12 +10767,12 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero hseq</t>
+          <t>Consultor(a) sst - gestión del riesgo químico - barrancabermeja</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>CONCONCRETO S.A.</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E219" s="7" t="n">
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="G219" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-hseq-1886755671", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultora-sst-gestion-del-riesgo-quimico-barrancabermeja-1886746280", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H219" s="6" t="inlineStr"/>
@@ -10803,7 +10803,7 @@
     <row r="220" ht="22" customHeight="1">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>596e039a845e32eb</t>
+          <t>3d360078771e726a</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -10813,12 +10813,12 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero de infraestructura ti</t>
+          <t>Ingeniero hseq</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>CONCONCRETO S.A.</t>
         </is>
       </c>
       <c r="E220" s="7" t="n">
@@ -10830,13 +10830,13 @@
         </is>
       </c>
       <c r="G220" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-de-infraestructura-ti-1886762110", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-hseq-1886755671", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H220" s="6" t="inlineStr"/>
       <c r="I220" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J220" s="2" t="inlineStr">
@@ -10849,7 +10849,7 @@
     <row r="221" ht="22" customHeight="1">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>eff7bc9185d1d6d6</t>
+          <t>596e039a845e32eb</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>Avaluador - especialista senior en seguimiento, control e interventoría de obra.</t>
+          <t>Ingeniero de infraestructura ti</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
@@ -10876,13 +10876,13 @@
         </is>
       </c>
       <c r="G221" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/avaluador-especialista-senior-en-seguimiento-control-e-interventoria-de-obra-1886733468", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-de-infraestructura-ti-1886762110", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H221" s="6" t="inlineStr"/>
       <c r="I221" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J221" s="2" t="inlineStr">
@@ -10895,7 +10895,7 @@
     <row r="222" ht="22" customHeight="1">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>4628b75d3c64d84f</t>
+          <t>eff7bc9185d1d6d6</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -10905,12 +10905,12 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>Analista senior de control de proyectos sector inmobiliario, obra civil, construcción en bogota</t>
+          <t>Avaluador - especialista senior en seguimiento, control e interventoría de obra.</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>MANPOWER</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E222" s="7" t="n">
@@ -10922,7 +10922,7 @@
         </is>
       </c>
       <c r="G222" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-senior-de-control-de-proyectos-sector-inmobiliario-obra-civil-construccion-en-bogota-1886762627", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/avaluador-especialista-senior-en-seguimiento-control-e-interventoria-de-obra-1886733468", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H222" s="6" t="inlineStr"/>
@@ -10941,7 +10941,7 @@
     <row r="223" ht="22" customHeight="1">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>a3bdfbb53c8050bc</t>
+          <t>4628b75d3c64d84f</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -10951,12 +10951,12 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>Líder Técnico - Colombia</t>
+          <t>Analista senior de control de proyectos sector inmobiliario, obra civil, construcción en bogota</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
-          <t>SETI S.A.S</t>
+          <t>MANPOWER</t>
         </is>
       </c>
       <c r="E223" s="7" t="n">
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="G223" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/l%C3%ADder-t%C3%A9cnico-colombia-at-seti-s-a-s-4464254507", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-senior-de-control-de-proyectos-sector-inmobiliario-obra-civil-construccion-en-bogota-1886762627", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H223" s="6" t="inlineStr"/>
@@ -10987,7 +10987,7 @@
     <row r="224" ht="22" customHeight="1">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>9876a1d7b57c2e9d</t>
+          <t>a3bdfbb53c8050bc</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -10997,12 +10997,12 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>Diseñador Civil Senior/Senior Civil Designer</t>
+          <t>Líder Técnico - Colombia</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>Pond &amp; Company</t>
+          <t>SETI S.A.S</t>
         </is>
       </c>
       <c r="E224" s="7" t="n">
@@ -11014,7 +11014,7 @@
         </is>
       </c>
       <c r="G224" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/dise%C3%B1ador-civil-senior-senior-civil-designer-at-pond-company-4448248118", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/l%C3%ADder-t%C3%A9cnico-colombia-at-seti-s-a-s-4464254507", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H224" s="6" t="inlineStr"/>
@@ -11033,7 +11033,7 @@
     <row r="225" ht="22" customHeight="1">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>c5c945234866a1f1</t>
+          <t>9876a1d7b57c2e9d</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -11043,12 +11043,12 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>Gerente HSE - Barranquilla</t>
+          <t>Diseñador Civil Senior/Senior Civil Designer</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>ADAMA Ltd.</t>
+          <t>Pond &amp; Company</t>
         </is>
       </c>
       <c r="E225" s="7" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="G225" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gerente-hse-barranquilla-colombia-at-adama-ltd-4468291249", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/dise%C3%B1ador-civil-senior-senior-civil-designer-at-pond-company-4448248118", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H225" s="6" t="inlineStr"/>
       <c r="I225" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J225" s="2" t="inlineStr">
@@ -11079,22 +11079,22 @@
     <row r="226" ht="22" customHeight="1">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>mock_nonmatch_008</t>
+          <t>c5c945234866a1f1</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 09:45</t>
+          <t>2026-09-22 05:09</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>Especialista Hidráulico y Sanitario para Plantas de Tratamiento de Aguas Residuales</t>
+          <t>Gerente HSE - Barranquilla</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>Aguas y Cuencas Ambientales S.A.S. E.S.P.</t>
+          <t>ADAMA Ltd.</t>
         </is>
       </c>
       <c r="E226" s="7" t="n">
@@ -11106,17 +11106,13 @@
         </is>
       </c>
       <c r="G226" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/mock-nonmatch-008", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H226" s="6" t="inlineStr">
-        <is>
-          <t>$ 7.500.000 COP</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gerente-hse-barranquilla-colombia-at-adama-ltd-4468291249", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H226" s="6" t="inlineStr"/>
       <c r="I226" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J226" s="2" t="inlineStr">
@@ -11129,22 +11125,22 @@
     <row r="227" ht="22" customHeight="1">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>7fb7d18d4b7e2f15</t>
+          <t>mock_nonmatch_008</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 10:17</t>
+          <t>2026-09-23 09:45</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>Gerente de Proyectos de redes secas eléctricas en sector inmobiliarios vivienda</t>
+          <t>Especialista Hidráulico y Sanitario para Plantas de Tratamiento de Aguas Residuales</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>Soluciones Inmediatas</t>
+          <t>Aguas y Cuencas Ambientales S.A.S. E.S.P.</t>
         </is>
       </c>
       <c r="E227" s="7" t="n">
@@ -11156,12 +11152,12 @@
         </is>
       </c>
       <c r="G227" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-gerente-de-proyectos-de-redes-secas-electricas-en-sector-inmobiliarios-vivienda-en-barranquilla-1D8CA2C26D08E95B61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/mock-nonmatch-008", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H227" s="6" t="inlineStr">
         <is>
-          <t>$ 7.000.000,00 (Mensual)</t>
+          <t>$ 7.500.000 COP</t>
         </is>
       </c>
       <c r="I227" s="3" t="inlineStr">
@@ -11179,7 +11175,7 @@
     <row r="228" ht="22" customHeight="1">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>f46574832270c441</t>
+          <t>7fb7d18d4b7e2f15</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -11189,12 +11185,12 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>Director de proyectos construcción/impermeabilización</t>
+          <t>Gerente de Proyectos de redes secas eléctricas en sector inmobiliarios vivienda</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Soluciones Inmediatas</t>
         </is>
       </c>
       <c r="E228" s="7" t="n">
@@ -11206,10 +11202,14 @@
         </is>
       </c>
       <c r="G228" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-de-proyectos-construccion-impermeabilizacion-1886757649", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H228" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-gerente-de-proyectos-de-redes-secas-electricas-en-sector-inmobiliarios-vivienda-en-barranquilla-1D8CA2C26D08E95B61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H228" s="6" t="inlineStr">
+        <is>
+          <t>$ 7.000.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I228" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -11225,7 +11225,7 @@
     <row r="229" ht="22" customHeight="1">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>3723b2e178098779</t>
+          <t>f46574832270c441</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero de infraestructura</t>
+          <t>Director de proyectos construcción/impermeabilización</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E229" s="7" t="n">
@@ -11252,13 +11252,13 @@
         </is>
       </c>
       <c r="G229" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-de-infraestructura-1886762657", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-de-proyectos-construccion-impermeabilizacion-1886757649", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H229" s="6" t="inlineStr"/>
       <c r="I229" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J229" s="2" t="inlineStr">
@@ -11271,7 +11271,7 @@
     <row r="230" ht="22" customHeight="1">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>bf21ac0878b65435</t>
+          <t>3723b2e178098779</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero industrial esp en sst - exp en sector construcción - barranquilla</t>
+          <t>Ingeniero de infraestructura</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E230" s="7" t="n">
@@ -11298,13 +11298,13 @@
         </is>
       </c>
       <c r="G230" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-industrial-esp-en-sst-exp-en-sector-construccion-barranquilla-1886766331", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-de-infraestructura-1886762657", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H230" s="6" t="inlineStr"/>
       <c r="I230" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J230" s="2" t="inlineStr">
@@ -11317,7 +11317,7 @@
     <row r="231" ht="22" customHeight="1">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>3a03aae1fae2698b</t>
+          <t>bf21ac0878b65435</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -11327,12 +11327,12 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero(a) Sr Obras Civiles</t>
+          <t>Ingeniero industrial esp en sst - exp en sector construcción - barranquilla</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>Parex Resources</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E231" s="7" t="n">
@@ -11344,13 +11344,13 @@
         </is>
       </c>
       <c r="G231" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-sr-obras-civiles-at-parex-resources-4436029487", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-industrial-esp-en-sst-exp-en-sector-construccion-barranquilla-1886766331", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H231" s="6" t="inlineStr"/>
       <c r="I231" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J231" s="2" t="inlineStr">
@@ -11363,22 +11363,22 @@
     <row r="232" ht="22" customHeight="1">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>32f893fe802cdb50</t>
+          <t>3a03aae1fae2698b</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:49</t>
+          <t>2026-09-23 10:17</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>Director de Proyectos Construcción/impermeabilización</t>
+          <t>Ingeniero(a) Sr Obras Civiles</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>Adecco Colombia S.A.</t>
+          <t>Parex Resources</t>
         </is>
       </c>
       <c r="E232" s="7" t="n">
@@ -11390,7 +11390,7 @@
         </is>
       </c>
       <c r="G232" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-director-de-proyectos-construccionimpermeabilizacion-en-bogota-dc-362312C315753AF861373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-sr-obras-civiles-at-parex-resources-4436029487", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H232" s="6" t="inlineStr"/>
@@ -11409,7 +11409,7 @@
     <row r="233" ht="22" customHeight="1">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>c9aa3304763a1c02</t>
+          <t>32f893fe802cdb50</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>Gerente de proyecto de implementación erp siesa</t>
+          <t>Director de Proyectos Construcción/impermeabilización</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Adecco Colombia S.A.</t>
         </is>
       </c>
       <c r="E233" s="7" t="n">
@@ -11436,7 +11436,7 @@
         </is>
       </c>
       <c r="G233" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/gerente-de-proyecto-de-implementacion-erp-siesa-1886759247", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-director-de-proyectos-construccionimpermeabilizacion-en-bogota-dc-362312C315753AF861373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H233" s="6" t="inlineStr"/>
@@ -11455,7 +11455,7 @@
     <row r="234" ht="22" customHeight="1">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>5d33b91bceb27cc7</t>
+          <t>c9aa3304763a1c02</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>Asesor en prevención sst</t>
+          <t>Gerente de proyecto de implementación erp siesa</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>SONDA</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E234" s="7" t="n">
@@ -11482,13 +11482,13 @@
         </is>
       </c>
       <c r="G234" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asesor-en-prevencion-sst-1886748210", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/gerente-de-proyecto-de-implementacion-erp-siesa-1886759247", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H234" s="6" t="inlineStr"/>
       <c r="I234" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J234" s="2" t="inlineStr">
@@ -11501,22 +11501,22 @@
     <row r="235" ht="22" customHeight="1">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>a8091ac7ae978c56</t>
+          <t>5d33b91bceb27cc7</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:50</t>
+          <t>2026-09-24 15:49</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>Senior Engineer/Specialist - Structural/Civil</t>
+          <t>Asesor en prevención sst</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>SONDA</t>
         </is>
       </c>
       <c r="E235" s="7" t="n">
@@ -11528,13 +11528,13 @@
         </is>
       </c>
       <c r="G235" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/senior-engineer-specialist-structural-civil-at-kent-4448228012", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asesor-en-prevencion-sst-1886748210", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H235" s="6" t="inlineStr"/>
       <c r="I235" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J235" s="2" t="inlineStr">
@@ -11547,7 +11547,7 @@
     <row r="236" ht="22" customHeight="1">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>f3a1b7629bfb5091</t>
+          <t>a8091ac7ae978c56</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -11557,12 +11557,12 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero de Infraestructura Física y Mantenimiento / Galapa</t>
+          <t>Senior Engineer/Specialist - Structural/Civil</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>Coopidrogas</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="E236" s="7" t="n">
@@ -11574,13 +11574,13 @@
         </is>
       </c>
       <c r="G236" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-de-infraestructura-f%C3%ADsica-y-mantenimiento-galapa-at-coopidrogas-4447216390", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/senior-engineer-specialist-structural-civil-at-kent-4448228012", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H236" s="6" t="inlineStr"/>
       <c r="I236" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J236" s="2" t="inlineStr">
@@ -11593,22 +11593,22 @@
     <row r="237" ht="22" customHeight="1">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>7cc53930dd68fddd</t>
+          <t>f3a1b7629bfb5091</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 05:09</t>
+          <t>2026-09-24 15:50</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>Líder de Seguridad y salud en el trabajo</t>
+          <t>Ingeniero de Infraestructura Física y Mantenimiento / Galapa</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
-          <t>Importante empresa del sector</t>
+          <t>Coopidrogas</t>
         </is>
       </c>
       <c r="E237" s="7" t="n">
@@ -11620,13 +11620,13 @@
         </is>
       </c>
       <c r="G237" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-lider-de-seguridad-y-salud-en-el-trabajo-en-bogota-dc-1FA3664D15D5571061373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-de-infraestructura-f%C3%ADsica-y-mantenimiento-galapa-at-coopidrogas-4447216390", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H237" s="6" t="inlineStr"/>
       <c r="I237" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J237" s="2" t="inlineStr">
@@ -11639,7 +11639,7 @@
     <row r="238" ht="22" customHeight="1">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>8f2604180c4175aa</t>
+          <t>7cc53930dd68fddd</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -11649,12 +11649,12 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>Líder hseq</t>
+          <t>Líder de Seguridad y salud en el trabajo</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>Grupo Good</t>
+          <t>Importante empresa del sector</t>
         </is>
       </c>
       <c r="E238" s="7" t="n">
@@ -11666,7 +11666,7 @@
         </is>
       </c>
       <c r="G238" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/lider-hseq-1886758267", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-lider-de-seguridad-y-salud-en-el-trabajo-en-bogota-dc-1FA3664D15D5571061373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H238" s="6" t="inlineStr"/>
@@ -11685,7 +11685,7 @@
     <row r="239" ht="22" customHeight="1">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>c996b309ea31c398</t>
+          <t>8f2604180c4175aa</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -11695,12 +11695,12 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>Lider hseq</t>
+          <t>Líder hseq</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Grupo Good</t>
         </is>
       </c>
       <c r="E239" s="7" t="n">
@@ -11712,7 +11712,7 @@
         </is>
       </c>
       <c r="G239" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/lider-hseq-1886767416", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/lider-hseq-1886758267", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H239" s="6" t="inlineStr"/>
@@ -11731,7 +11731,7 @@
     <row r="240" ht="22" customHeight="1">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>1a35e87760c6acbe</t>
+          <t>c996b309ea31c398</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>Líder hseq</t>
+          <t>Lider hseq</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
@@ -11758,7 +11758,7 @@
         </is>
       </c>
       <c r="G240" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/lider-hseq-1886761912", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/lider-hseq-1886767416", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H240" s="6" t="inlineStr"/>
@@ -11777,7 +11777,7 @@
     <row r="241" ht="22" customHeight="1">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>ddd0530c3b22efe7</t>
+          <t>1a35e87760c6acbe</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>Lider sst para la guajira</t>
+          <t>Líder hseq</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
@@ -11804,7 +11804,7 @@
         </is>
       </c>
       <c r="G241" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/lider-sst-para-la-guajira-1886764349", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/lider-hseq-1886761912", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H241" s="6" t="inlineStr"/>
@@ -11823,7 +11823,7 @@
     <row r="242" ht="22" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>5890db86961c728a</t>
+          <t>ddd0530c3b22efe7</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>Lider de proyectos de infraestructura</t>
+          <t>Lider sst para la guajira</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
@@ -11850,13 +11850,13 @@
         </is>
       </c>
       <c r="G242" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/lider-de-proyectos-de-infraestructura-1886763250", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/lider-sst-para-la-guajira-1886764349", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H242" s="6" t="inlineStr"/>
       <c r="I242" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J242" s="2" t="inlineStr">
@@ -11869,7 +11869,7 @@
     <row r="243" ht="22" customHeight="1">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>0b3307883dd9e76d</t>
+          <t>5890db86961c728a</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>Líder de Infraestructura y Estructuración de Proyectos</t>
+          <t>Lider de proyectos de infraestructura</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>Innova Schools Colombia</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E243" s="7" t="n">
@@ -11896,7 +11896,7 @@
         </is>
       </c>
       <c r="G243" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/l%C3%ADder-de-infraestructura-y-estructuraci%C3%B3n-de-proyectos-at-innova-schools-colombia-4462807966", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/lider-de-proyectos-de-infraestructura-1886763250", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H243" s="6" t="inlineStr"/>
@@ -11915,7 +11915,7 @@
     <row r="244" ht="22" customHeight="1">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>b16bf21d94be490a</t>
+          <t>0b3307883dd9e76d</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -11925,12 +11925,12 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>Líder HSEQ</t>
+          <t>Líder de Infraestructura y Estructuración de Proyectos</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>RH Group</t>
+          <t>Innova Schools Colombia</t>
         </is>
       </c>
       <c r="E244" s="7" t="n">
@@ -11942,13 +11942,13 @@
         </is>
       </c>
       <c r="G244" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/l%C3%ADder-hseq-at-rh-group-4468612641", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/l%C3%ADder-de-infraestructura-y-estructuraci%C3%B3n-de-proyectos-at-innova-schools-colombia-4462807966", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H244" s="6" t="inlineStr"/>
       <c r="I244" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J244" s="2" t="inlineStr">
@@ -11961,22 +11961,22 @@
     <row r="245" ht="22" customHeight="1">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>cd1ed0c7003820f9</t>
+          <t>b16bf21d94be490a</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:50</t>
+          <t>2026-09-22 05:09</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>Analista técnico HSEQ</t>
+          <t>Líder HSEQ</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>Importante empresa del sector</t>
+          <t>RH Group</t>
         </is>
       </c>
       <c r="E245" s="7" t="n">
@@ -11988,7 +11988,7 @@
         </is>
       </c>
       <c r="G245" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-tecnico-hseq-auxiliar-siso-en-bucaramanga-D61BC02E1336822161373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/l%C3%ADder-hseq-at-rh-group-4468612641", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H245" s="6" t="inlineStr"/>
@@ -12007,7 +12007,7 @@
     <row r="246" ht="22" customHeight="1">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>2a1cbfdbed03a387</t>
+          <t>cd1ed0c7003820f9</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>Analista SST/ Con Licencia Vigente</t>
+          <t>Analista técnico HSEQ</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
@@ -12034,14 +12034,10 @@
         </is>
       </c>
       <c r="G246" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-sst-con-licencia-vigente-en-bogota-dc-427AA507B61CAF9061373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H246" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.908.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-tecnico-hseq-auxiliar-siso-en-bucaramanga-D61BC02E1336822161373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H246" s="6" t="inlineStr"/>
       <c r="I246" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -12057,7 +12053,7 @@
     <row r="247" ht="22" customHeight="1">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>bb3f6db46a6887f1</t>
+          <t>2a1cbfdbed03a387</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
@@ -12067,12 +12063,12 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>Analista seguridad y salud en el trabajo</t>
+          <t>Analista SST/ Con Licencia Vigente</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
-          <t>GENTE UTIL S.A.</t>
+          <t>Importante empresa del sector</t>
         </is>
       </c>
       <c r="E247" s="7" t="n">
@@ -12084,12 +12080,12 @@
         </is>
       </c>
       <c r="G247" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-seguridad-y-salud-en-el-trabajo-en-bucaramanga-217BC88A60F8BD9261373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-sst-con-licencia-vigente-en-bogota-dc-427AA507B61CAF9061373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H247" s="6" t="inlineStr">
         <is>
-          <t>$ 2.700.000,00 (Mensual)</t>
+          <t>$ 1.908.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I247" s="3" t="inlineStr">
@@ -12107,7 +12103,7 @@
     <row r="248" ht="22" customHeight="1">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>1ead4f148498c379</t>
+          <t>bb3f6db46a6887f1</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
@@ -12117,12 +12113,12 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>Analista HSEQ</t>
+          <t>Analista seguridad y salud en el trabajo</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>TNC SOLUCIONES</t>
+          <t>GENTE UTIL S.A.</t>
         </is>
       </c>
       <c r="E248" s="7" t="n">
@@ -12134,12 +12130,12 @@
         </is>
       </c>
       <c r="G248" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-hseq-guarne-en-guarne-E886A61EC9E5D90B61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-seguridad-y-salud-en-el-trabajo-en-bucaramanga-217BC88A60F8BD9261373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H248" s="6" t="inlineStr">
         <is>
-          <t>$ 2.400.000,00 (Mensual)</t>
+          <t>$ 2.700.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I248" s="3" t="inlineStr">
@@ -12157,7 +12153,7 @@
     <row r="249" ht="22" customHeight="1">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>9ff1e568afbe6452</t>
+          <t>1ead4f148498c379</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
@@ -12172,7 +12168,7 @@
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>ELIS COLOMBIA SAS</t>
+          <t>TNC SOLUCIONES</t>
         </is>
       </c>
       <c r="E249" s="7" t="n">
@@ -12184,12 +12180,12 @@
         </is>
       </c>
       <c r="G249" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-hseq-medellin-en-medellin-B43CB6F9EBA28A8161373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-hseq-guarne-en-guarne-E886A61EC9E5D90B61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H249" s="6" t="inlineStr">
         <is>
-          <t>$ 1.951.000,00 (Mensual)</t>
+          <t>$ 2.400.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I249" s="3" t="inlineStr">
@@ -12207,7 +12203,7 @@
     <row r="250" ht="22" customHeight="1">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>8b0ee5de6334b5ca</t>
+          <t>9ff1e568afbe6452</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
@@ -12217,12 +12213,12 @@
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>Analista Ambiental HSEQ</t>
+          <t>Analista HSEQ</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>Importante empresa del sector</t>
+          <t>ELIS COLOMBIA SAS</t>
         </is>
       </c>
       <c r="E250" s="7" t="n">
@@ -12234,10 +12230,14 @@
         </is>
       </c>
       <c r="G250" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-ambiental-hseq-lider-de-sostenibilidad-ambiental-ingeniero-en-bogota-dc-BB1D9E72E010F26D61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H250" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-hseq-medellin-en-medellin-B43CB6F9EBA28A8161373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H250" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.951.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I250" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -12253,7 +12253,7 @@
     <row r="251" ht="22" customHeight="1">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>cf943e439e7fa597</t>
+          <t>8b0ee5de6334b5ca</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -12263,12 +12263,12 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>Analista de SST sector alimentos</t>
+          <t>Analista Ambiental HSEQ</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
-          <t>GENTE UTIL S.A.</t>
+          <t>Importante empresa del sector</t>
         </is>
       </c>
       <c r="E251" s="7" t="n">
@@ -12280,14 +12280,10 @@
         </is>
       </c>
       <c r="G251" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-sst-sector-alimentos-en-bucaramanga-03C3091ADF2940A061373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H251" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.700.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-ambiental-hseq-lider-de-sostenibilidad-ambiental-ingeniero-en-bogota-dc-BB1D9E72E010F26D61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H251" s="6" t="inlineStr"/>
       <c r="I251" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -12303,7 +12299,7 @@
     <row r="252" ht="22" customHeight="1">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>d447a89ce66534d3</t>
+          <t>cf943e439e7fa597</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
@@ -12313,12 +12309,12 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>Analista pesv</t>
+          <t>Analista de SST sector alimentos</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>GYP BOGOTA S.A.S.</t>
+          <t>GENTE UTIL S.A.</t>
         </is>
       </c>
       <c r="E252" s="7" t="n">
@@ -12330,17 +12326,17 @@
         </is>
       </c>
       <c r="G252" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-pesv-junior-en-bogota-dc-BCB0395C3C5D8A2F61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-sst-sector-alimentos-en-bucaramanga-03C3091ADF2940A061373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H252" s="6" t="inlineStr">
         <is>
-          <t>$ 2.200.000,00 (Mensual)</t>
+          <t>$ 2.700.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I252" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J252" s="2" t="inlineStr">
@@ -12353,7 +12349,7 @@
     <row r="253" ht="22" customHeight="1">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>8e20d357d678b79d</t>
+          <t>d447a89ce66534d3</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
@@ -12363,12 +12359,12 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>Analista HSEQ</t>
+          <t>Analista pesv</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
         <is>
-          <t>Alianza Temporal S.A.S</t>
+          <t>GYP BOGOTA S.A.S.</t>
         </is>
       </c>
       <c r="E253" s="7" t="n">
@@ -12380,17 +12376,17 @@
         </is>
       </c>
       <c r="G253" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-hseq-en-bogota-dc-1C936FC8891CA02A61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-pesv-junior-en-bogota-dc-BCB0395C3C5D8A2F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H253" s="6" t="inlineStr">
         <is>
-          <t>$ 2.800.000,00 (Mensual)</t>
+          <t>$ 2.200.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I253" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J253" s="2" t="inlineStr">
@@ -12403,7 +12399,7 @@
     <row r="254" ht="22" customHeight="1">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>9d2ac9f3d7cb9acd</t>
+          <t>8e20d357d678b79d</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
@@ -12413,7 +12409,7 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>Analista HSEQ / SGI</t>
+          <t>Analista HSEQ</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
@@ -12430,7 +12426,7 @@
         </is>
       </c>
       <c r="G254" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-hseq-sgi-en-bogota-dc-0CE6D56C083ABD1961373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-hseq-en-bogota-dc-1C936FC8891CA02A61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H254" s="6" t="inlineStr">
@@ -12453,7 +12449,7 @@
     <row r="255" ht="22" customHeight="1">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>4deabccd5a9cdc25</t>
+          <t>9d2ac9f3d7cb9acd</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
@@ -12463,7 +12459,7 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>Analista HSEQ</t>
+          <t>Analista HSEQ / SGI</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
@@ -12480,7 +12476,7 @@
         </is>
       </c>
       <c r="G255" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-hseq-en-bogota-dc-448326405347581761373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-hseq-sgi-en-bogota-dc-0CE6D56C083ABD1961373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H255" s="6" t="inlineStr">
@@ -12503,7 +12499,7 @@
     <row r="256" ht="22" customHeight="1">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>04a62710351898c7</t>
+          <t>4deabccd5a9cdc25</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -12513,12 +12509,12 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>Profesional en SST analista SIG</t>
+          <t>Analista HSEQ</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>MULTISOLUCIONES A&amp;A SAS</t>
+          <t>Alianza Temporal S.A.S</t>
         </is>
       </c>
       <c r="E256" s="7" t="n">
@@ -12530,12 +12526,12 @@
         </is>
       </c>
       <c r="G256" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-profesional-en-sst-analista-sig-lunes-a-viernes-zona-alcazares-en-bogota-dc-44FDC591768D6E7361373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-hseq-en-bogota-dc-448326405347581761373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H256" s="6" t="inlineStr">
         <is>
-          <t>$ 2.500.000,00 (Mensual)</t>
+          <t>$ 2.800.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I256" s="3" t="inlineStr">
@@ -12553,7 +12549,7 @@
     <row r="257" ht="22" customHeight="1">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>c7446dc528c6d347</t>
+          <t>04a62710351898c7</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -12580,7 +12576,7 @@
         </is>
       </c>
       <c r="G257" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-profesional-en-sst-analista-sig-lunes-a-viernes-zona-alcazares-en-bogota-dc-1B88E58AD1C7CC5061373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-profesional-en-sst-analista-sig-lunes-a-viernes-zona-alcazares-en-bogota-dc-44FDC591768D6E7361373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H257" s="6" t="inlineStr">
@@ -12603,7 +12599,7 @@
     <row r="258" ht="22" customHeight="1">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>fbadbced248d18e1</t>
+          <t>c7446dc528c6d347</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
@@ -12613,12 +12609,12 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>Consultor en Seguridad Vial</t>
+          <t>Profesional en SST analista SIG</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>CORPORACION SIGMA SAS</t>
+          <t>MULTISOLUCIONES A&amp;A SAS</t>
         </is>
       </c>
       <c r="E258" s="7" t="n">
@@ -12630,13 +12626,17 @@
         </is>
       </c>
       <c r="G258" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-consultor-en-seguridad-vial-pesv-y-gestion-del-riego-vial-en-bogota-dc-A22BEA7B6CD0ECAF61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H258" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-profesional-en-sst-analista-sig-lunes-a-viernes-zona-alcazares-en-bogota-dc-1B88E58AD1C7CC5061373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H258" s="6" t="inlineStr">
+        <is>
+          <t>$ 2.500.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I258" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J258" s="2" t="inlineStr">
@@ -12649,7 +12649,7 @@
     <row r="259" ht="22" customHeight="1">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>f5f6fb5fa69e5858</t>
+          <t>fbadbced248d18e1</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
@@ -12659,12 +12659,12 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>Analista SST</t>
+          <t>Consultor en Seguridad Vial</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
-          <t>S&amp;A Servicios y Asesorias</t>
+          <t>CORPORACION SIGMA SAS</t>
         </is>
       </c>
       <c r="E259" s="7" t="n">
@@ -12676,17 +12676,13 @@
         </is>
       </c>
       <c r="G259" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-sst-medellin-en-medellin-08A3D3F6FA52C2AC61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H259" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.700.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-consultor-en-seguridad-vial-pesv-y-gestion-del-riego-vial-en-bogota-dc-A22BEA7B6CD0ECAF61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H259" s="6" t="inlineStr"/>
       <c r="I259" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J259" s="2" t="inlineStr">
@@ -12699,7 +12695,7 @@
     <row r="260" ht="22" customHeight="1">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>6fd98edb1903dcca</t>
+          <t>f5f6fb5fa69e5858</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
@@ -12709,12 +12705,12 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>Analista SST para incapacidad</t>
+          <t>Analista SST</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>PQP. Productos Quimicos Panamericanos S.A</t>
+          <t>S&amp;A Servicios y Asesorias</t>
         </is>
       </c>
       <c r="E260" s="7" t="n">
@@ -12726,10 +12722,14 @@
         </is>
       </c>
       <c r="G260" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-sst-para-incapacidad-barranquilla-en-barranquilla-2ADE011329ECD43761373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H260" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-sst-medellin-en-medellin-08A3D3F6FA52C2AC61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H260" s="6" t="inlineStr">
+        <is>
+          <t>$ 2.700.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I260" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -12745,7 +12745,7 @@
     <row r="261" ht="22" customHeight="1">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>541d99c3c6e9a353</t>
+          <t>6fd98edb1903dcca</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
@@ -12755,12 +12755,12 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>Analista de infraestructura i (redes/firewall) - presencial en bogotá</t>
+          <t>Analista SST para incapacidad</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>Cinte Colombia SAS</t>
+          <t>PQP. Productos Quimicos Panamericanos S.A</t>
         </is>
       </c>
       <c r="E261" s="7" t="n">
@@ -12772,13 +12772,13 @@
         </is>
       </c>
       <c r="G261" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-infraestructura-i-redes-firewall-presencial-en-bogota-1886756899", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-sst-para-incapacidad-barranquilla-en-barranquilla-2ADE011329ECD43761373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H261" s="6" t="inlineStr"/>
       <c r="I261" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J261" s="2" t="inlineStr">
@@ -12791,7 +12791,7 @@
     <row r="262" ht="22" customHeight="1">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>03a8ea34d80e8a34</t>
+          <t>541d99c3c6e9a353</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -12801,12 +12801,12 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>Analista de seguridad y salud en el trabajo funza presencial</t>
+          <t>Analista de infraestructura i (redes/firewall) - presencial en bogotá</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Cinte Colombia SAS</t>
         </is>
       </c>
       <c r="E262" s="7" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="G262" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-seguridad-y-salud-en-el-trabajo-funza-presencial-1886725219", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-infraestructura-i-redes-firewall-presencial-en-bogota-1886756899", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H262" s="6" t="inlineStr"/>
       <c r="I262" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J262" s="2" t="inlineStr">
@@ -12837,7 +12837,7 @@
     <row r="263" ht="22" customHeight="1">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>540178b2a701337c</t>
+          <t>03a8ea34d80e8a34</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -12847,7 +12847,7 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>Analista de seguridad y salud en el trabajo</t>
+          <t>Analista de seguridad y salud en el trabajo funza presencial</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
@@ -12864,7 +12864,7 @@
         </is>
       </c>
       <c r="G263" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-seguridad-y-salud-en-el-trabajo-1886770263", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-seguridad-y-salud-en-el-trabajo-funza-presencial-1886725219", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H263" s="6" t="inlineStr"/>
@@ -12883,7 +12883,7 @@
     <row r="264" ht="22" customHeight="1">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>e11ebdd67cc774e6</t>
+          <t>540178b2a701337c</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
@@ -12910,7 +12910,7 @@
         </is>
       </c>
       <c r="G264" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-seguridad-y-salud-en-el-trabajo-1886767319", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-seguridad-y-salud-en-el-trabajo-1886770263", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H264" s="6" t="inlineStr"/>
@@ -12929,7 +12929,7 @@
     <row r="265" ht="22" customHeight="1">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>bcff69a50f54e5a9</t>
+          <t>e11ebdd67cc774e6</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
-          <t>FLEXO SPRING</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E265" s="7" t="n">
@@ -12956,7 +12956,7 @@
         </is>
       </c>
       <c r="G265" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-seguridad-y-salud-en-el-trabajo-1886763294", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-seguridad-y-salud-en-el-trabajo-1886767319", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H265" s="6" t="inlineStr"/>
@@ -12975,7 +12975,7 @@
     <row r="266" ht="22" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>7b7be0e160fd697a</t>
+          <t>bcff69a50f54e5a9</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>DAVITA SAS</t>
+          <t>FLEXO SPRING</t>
         </is>
       </c>
       <c r="E266" s="7" t="n">
@@ -13002,7 +13002,7 @@
         </is>
       </c>
       <c r="G266" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-seguridad-y-salud-en-el-trabajo-1886744905", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-seguridad-y-salud-en-el-trabajo-1886763294", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H266" s="6" t="inlineStr"/>
@@ -13021,7 +13021,7 @@
     <row r="267" ht="22" customHeight="1">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>953a9dbdeb50a536</t>
+          <t>7b7be0e160fd697a</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
@@ -13031,12 +13031,12 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>Líder de seguridad y salud en el trabajo-maní, casanare</t>
+          <t>Analista de seguridad y salud en el trabajo</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>DAVITA SAS</t>
         </is>
       </c>
       <c r="E267" s="7" t="n">
@@ -13048,7 +13048,7 @@
         </is>
       </c>
       <c r="G267" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/lider-de-seguridad-y-salud-en-el-trabajomani-casanare-1886766966", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-seguridad-y-salud-en-el-trabajo-1886744905", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H267" s="6" t="inlineStr"/>
@@ -13067,7 +13067,7 @@
     <row r="268" ht="22" customHeight="1">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>1077a52c358d103c</t>
+          <t>953a9dbdeb50a536</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
@@ -13077,12 +13077,12 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>Analista de seguridad y salud en el trabajo</t>
+          <t>Líder de seguridad y salud en el trabajo-maní, casanare</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>FLEXO SPRING</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E268" s="7" t="n">
@@ -13094,7 +13094,7 @@
         </is>
       </c>
       <c r="G268" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-seguridad-y-salud-en-el-trabajo-1886762820", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/lider-de-seguridad-y-salud-en-el-trabajomani-casanare-1886766966", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H268" s="6" t="inlineStr"/>
@@ -13113,7 +13113,7 @@
     <row r="269" ht="22" customHeight="1">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>49485c38f90564f4</t>
+          <t>1077a52c358d103c</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>Analista sst seguridad y salud den el trabajo // villavicencio meta</t>
+          <t>Analista de seguridad y salud en el trabajo</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FLEXO SPRING</t>
         </is>
       </c>
       <c r="E269" s="7" t="n">
@@ -13140,7 +13140,7 @@
         </is>
       </c>
       <c r="G269" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-sst-seguridad-y-salud-den-el-trabajo-villavicencio-meta-1886739263", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-seguridad-y-salud-en-el-trabajo-1886762820", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H269" s="6" t="inlineStr"/>
@@ -13159,7 +13159,7 @@
     <row r="270" ht="22" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>3996788779b0f367</t>
+          <t>49485c38f90564f4</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
@@ -13169,7 +13169,7 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>Analista de sst</t>
+          <t>Analista sst seguridad y salud den el trabajo // villavicencio meta</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="G270" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-sst-1886750073", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-sst-seguridad-y-salud-den-el-trabajo-villavicencio-meta-1886739263", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H270" s="6" t="inlineStr"/>
@@ -13205,7 +13205,7 @@
     <row r="271" ht="22" customHeight="1">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>a7b8c286017a1279</t>
+          <t>3996788779b0f367</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
@@ -13215,12 +13215,12 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>Analista de medicina preventiva-sst</t>
+          <t>Analista de sst</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
-          <t>ORGANIZACION GEN</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E271" s="7" t="n">
@@ -13232,7 +13232,7 @@
         </is>
       </c>
       <c r="G271" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-medicina-preventivasst-1886767891", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-sst-1886750073", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H271" s="6" t="inlineStr"/>
@@ -13251,7 +13251,7 @@
     <row r="272" ht="22" customHeight="1">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>cb5259b3fda206ce</t>
+          <t>a7b8c286017a1279</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>Analista hseq</t>
+          <t>Analista de medicina preventiva-sst</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ORGANIZACION GEN</t>
         </is>
       </c>
       <c r="E272" s="7" t="n">
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="G272" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-hseq-1886768704", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-medicina-preventivasst-1886767891", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H272" s="6" t="inlineStr"/>
@@ -13297,7 +13297,7 @@
     <row r="273" ht="22" customHeight="1">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>2833e263103c1333</t>
+          <t>cb5259b3fda206ce</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>Analista hseq tocancipa</t>
+          <t>Analista hseq</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
@@ -13324,7 +13324,7 @@
         </is>
       </c>
       <c r="G273" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-hseq-tocancipa-1886712233", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-hseq-1886768704", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H273" s="6" t="inlineStr"/>
@@ -13343,7 +13343,7 @@
     <row r="274" ht="22" customHeight="1">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>dac638d1bd51c678</t>
+          <t>2833e263103c1333</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>Director proyectos e ingeniería</t>
+          <t>Analista hseq tocancipa</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>SinapSer</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E274" s="7" t="n">
@@ -13370,13 +13370,13 @@
         </is>
       </c>
       <c r="G274" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-proyectos-e-ingenieria-1886749724", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-hseq-tocancipa-1886712233", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H274" s="6" t="inlineStr"/>
       <c r="I274" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr">
@@ -13389,7 +13389,7 @@
     <row r="275" ht="22" customHeight="1">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>6b6e8ba8ffb749b7</t>
+          <t>dac638d1bd51c678</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
@@ -13399,12 +13399,12 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>Analista de seguridad vial</t>
+          <t>Director proyectos e ingeniería</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
         <is>
-          <t>FLEXITEMP</t>
+          <t>SinapSer</t>
         </is>
       </c>
       <c r="E275" s="7" t="n">
@@ -13416,13 +13416,13 @@
         </is>
       </c>
       <c r="G275" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-seguridad-vial-1886767093", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/director-proyectos-e-ingenieria-1886749724", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H275" s="6" t="inlineStr"/>
       <c r="I275" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J275" s="2" t="inlineStr">
@@ -13435,7 +13435,7 @@
     <row r="276" ht="22" customHeight="1">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>c58d8d2ab06afb3e</t>
+          <t>6b6e8ba8ffb749b7</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
@@ -13445,12 +13445,12 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>Lider corporativo de sst latam</t>
+          <t>Analista de seguridad vial</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>DISAN COLOMBIA S.A.S</t>
+          <t>FLEXITEMP</t>
         </is>
       </c>
       <c r="E276" s="7" t="n">
@@ -13462,13 +13462,13 @@
         </is>
       </c>
       <c r="G276" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/lider-corporativo-de-sst-latam-1886770796", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-seguridad-vial-1886767093", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H276" s="6" t="inlineStr"/>
       <c r="I276" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J276" s="2" t="inlineStr">
@@ -13481,7 +13481,7 @@
     <row r="277" ht="22" customHeight="1">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>d9a45ecb5a281054</t>
+          <t>c58d8d2ab06afb3e</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>Analista sst sector floricultor</t>
+          <t>Lider corporativo de sst latam</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO CAFAM</t>
+          <t>DISAN COLOMBIA S.A.S</t>
         </is>
       </c>
       <c r="E277" s="7" t="n">
@@ -13508,7 +13508,7 @@
         </is>
       </c>
       <c r="G277" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-sst-sector-floricultor-1886753404", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/lider-corporativo-de-sst-latam-1886770796", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H277" s="6" t="inlineStr"/>
@@ -13527,7 +13527,7 @@
     <row r="278" ht="22" customHeight="1">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>4d7fa5b437ae0bb5</t>
+          <t>d9a45ecb5a281054</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
@@ -13537,12 +13537,12 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>Analista sst - santa marta</t>
+          <t>Analista sst sector floricultor</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>AGENCIA DE EMPLEO CAFAM</t>
         </is>
       </c>
       <c r="E278" s="7" t="n">
@@ -13554,7 +13554,7 @@
         </is>
       </c>
       <c r="G278" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-sst-santa-marta-1886765312", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-sst-sector-floricultor-1886753404", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H278" s="6" t="inlineStr"/>
@@ -13573,7 +13573,7 @@
     <row r="279" ht="22" customHeight="1">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>0924285e67d45615</t>
+          <t>4d7fa5b437ae0bb5</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>Analista de sst- tabio</t>
+          <t>Analista sst - santa marta</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
@@ -13600,7 +13600,7 @@
         </is>
       </c>
       <c r="G279" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-sst-tabio-1886757209", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-sst-santa-marta-1886765312", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H279" s="6" t="inlineStr"/>
@@ -13619,7 +13619,7 @@
     <row r="280" ht="22" customHeight="1">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>a0b1ddd1068c41b6</t>
+          <t>0924285e67d45615</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>Analista de sst</t>
+          <t>Analista de sst- tabio</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>ALCIAUTOS SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E280" s="7" t="n">
@@ -13646,7 +13646,7 @@
         </is>
       </c>
       <c r="G280" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-sst-1886755902", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-sst-tabio-1886757209", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H280" s="6" t="inlineStr"/>
@@ -13665,7 +13665,7 @@
     <row r="281" ht="22" customHeight="1">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>0e8e9e5f8fd1279f</t>
+          <t>a0b1ddd1068c41b6</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
@@ -13675,12 +13675,12 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>Analista de seguridad y salud en el trabajo</t>
+          <t>Analista de sst</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ALCIAUTOS SAS</t>
         </is>
       </c>
       <c r="E281" s="7" t="n">
@@ -13692,7 +13692,7 @@
         </is>
       </c>
       <c r="G281" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-seguridad-y-salud-en-el-trabajo-1886745959", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-sst-1886755902", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H281" s="6" t="inlineStr"/>
@@ -13711,7 +13711,7 @@
     <row r="282" ht="22" customHeight="1">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>3f516439681196e6</t>
+          <t>0e8e9e5f8fd1279f</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
@@ -13721,12 +13721,12 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>Analista de sst</t>
+          <t>Analista de seguridad y salud en el trabajo</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>ALCIAUTOS SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E282" s="7" t="n">
@@ -13738,7 +13738,7 @@
         </is>
       </c>
       <c r="G282" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-sst-1886766524", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-seguridad-y-salud-en-el-trabajo-1886745959", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H282" s="6" t="inlineStr"/>
@@ -13757,7 +13757,7 @@
     <row r="283" ht="22" customHeight="1">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>431b016f24a1f2e7</t>
+          <t>3f516439681196e6</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
@@ -13767,12 +13767,12 @@
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>Analista de hseq</t>
+          <t>Analista de sst</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
         <is>
-          <t>DHL SUPPLY CHAIN COLOMBIA</t>
+          <t>ALCIAUTOS SAS</t>
         </is>
       </c>
       <c r="E283" s="7" t="n">
@@ -13784,7 +13784,7 @@
         </is>
       </c>
       <c r="G283" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-hseq-1886756771", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-sst-1886766524", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H283" s="6" t="inlineStr"/>
@@ -13803,7 +13803,7 @@
     <row r="284" ht="22" customHeight="1">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>a3bc4d60e4d02902</t>
+          <t>431b016f24a1f2e7</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
@@ -13813,12 +13813,12 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>Cali - consultor integral sistemas de gestion sst - con licencia en sst</t>
+          <t>Analista de hseq</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>DHL SUPPLY CHAIN COLOMBIA</t>
         </is>
       </c>
       <c r="E284" s="7" t="n">
@@ -13830,13 +13830,13 @@
         </is>
       </c>
       <c r="G284" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-consultor-integral-sistemas-de-gestion-sst-con-licencia-en-sst-1886771972", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-hseq-1886756771", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H284" s="6" t="inlineStr"/>
       <c r="I284" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado. Observación: Requiere Licencia en Seguridad y Salud en el Trabajo (SST) vigente.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
@@ -13849,7 +13849,7 @@
     <row r="285" ht="22" customHeight="1">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>5a6dfbb47030360b</t>
+          <t>a3bc4d60e4d02902</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
@@ -13859,7 +13859,7 @@
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>Analista sst</t>
+          <t>Cali - consultor integral sistemas de gestion sst - con licencia en sst</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
@@ -13876,13 +13876,13 @@
         </is>
       </c>
       <c r="G285" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-sst-1886749305", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-consultor-integral-sistemas-de-gestion-sst-con-licencia-en-sst-1886771972", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H285" s="6" t="inlineStr"/>
       <c r="I285" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado. Observación: Requiere Licencia en Seguridad y Salud en el Trabajo (SST) vigente.</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
@@ -13895,7 +13895,7 @@
     <row r="286" ht="22" customHeight="1">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>d9cfb72d0a715a59</t>
+          <t>5a6dfbb47030360b</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
@@ -13905,12 +13905,12 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>Analista hse</t>
+          <t>Analista sst</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>MTS Administración total S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E286" s="7" t="n">
@@ -13922,7 +13922,7 @@
         </is>
       </c>
       <c r="G286" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-hse-1886746749", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-sst-1886749305", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H286" s="6" t="inlineStr"/>
@@ -13941,7 +13941,7 @@
     <row r="287" ht="22" customHeight="1">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>40841d71c43f1222</t>
+          <t>d9cfb72d0a715a59</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>Analista hse / bogotá</t>
+          <t>Analista hse</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
@@ -13968,7 +13968,7 @@
         </is>
       </c>
       <c r="G287" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-hse-bogota-1886747171", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-hse-1886746749", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H287" s="6" t="inlineStr"/>
@@ -13987,7 +13987,7 @@
     <row r="288" ht="22" customHeight="1">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>c3ac919add19223e</t>
+          <t>40841d71c43f1222</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
@@ -13997,12 +13997,12 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar hseq / obra vivienda técnicos y/o tecnólogos fusagasuga y al rededores</t>
+          <t>Analista hse / bogotá</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>OIKOS S.A.</t>
+          <t>MTS Administración total S.A.S</t>
         </is>
       </c>
       <c r="E288" s="7" t="n">
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="G288" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-hseq-obra-vivienda-tecnicos-y-o-tecnologos-fusagasuga-y-al-rededores-1886755940", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-hse-bogota-1886747171", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H288" s="6" t="inlineStr"/>
@@ -14033,7 +14033,7 @@
     <row r="289" ht="22" customHeight="1">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>081f1cdd6c603c67</t>
+          <t>c3ac919add19223e</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>Coordinado/a de hseq tecnico / tecnologo</t>
+          <t>Auxiliar hseq / obra vivienda técnicos y/o tecnólogos fusagasuga y al rededores</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
         <is>
-          <t>GI GROUP STAFFING S.A.S</t>
+          <t>OIKOS S.A.</t>
         </is>
       </c>
       <c r="E289" s="7" t="n">
@@ -14060,7 +14060,7 @@
         </is>
       </c>
       <c r="G289" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinado-a-de-hseq-tecnico-tecnologo-1886753906", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-hseq-obra-vivienda-tecnicos-y-o-tecnologos-fusagasuga-y-al-rededores-1886755940", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H289" s="6" t="inlineStr"/>
@@ -14079,7 +14079,7 @@
     <row r="290" ht="22" customHeight="1">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>fda7dd0065c71794</t>
+          <t>081f1cdd6c603c67</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
@@ -14089,12 +14089,12 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>Analista de logística e infraestructura</t>
+          <t>Coordinado/a de hseq tecnico / tecnologo</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>Compañía Aseguradora de Fianzas - Seguros Confianza S.A.</t>
+          <t>GI GROUP STAFFING S.A.S</t>
         </is>
       </c>
       <c r="E290" s="7" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="G290" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-logistica-e-infraestructura-1886755686", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinado-a-de-hseq-tecnico-tecnologo-1886753906", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H290" s="6" t="inlineStr"/>
       <c r="I290" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J290" s="2" t="inlineStr">
@@ -14125,7 +14125,7 @@
     <row r="291" ht="22" customHeight="1">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>06ac12af82c8f553</t>
+          <t>fda7dd0065c71794</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
@@ -14135,12 +14135,12 @@
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>Analista de seguridad y salud en el trabajo</t>
+          <t>Analista de logística e infraestructura</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
         <is>
-          <t>Agaval S.A.</t>
+          <t>Compañía Aseguradora de Fianzas - Seguros Confianza S.A.</t>
         </is>
       </c>
       <c r="E291" s="7" t="n">
@@ -14152,13 +14152,13 @@
         </is>
       </c>
       <c r="G291" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-seguridad-y-salud-en-el-trabajo-at-agaval-s-a-4470416741", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-logistica-e-infraestructura-1886755686", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H291" s="6" t="inlineStr"/>
       <c r="I291" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J291" s="2" t="inlineStr">
@@ -14171,7 +14171,7 @@
     <row r="292" ht="22" customHeight="1">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>dbdcc9c937f7fac0</t>
+          <t>06ac12af82c8f553</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
@@ -14181,12 +14181,12 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>Técnico/Analista HSE - Vacante Inclusiva PCD</t>
+          <t>Analista de seguridad y salud en el trabajo</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>Unisys</t>
+          <t>Agaval S.A.</t>
         </is>
       </c>
       <c r="E292" s="7" t="n">
@@ -14198,7 +14198,7 @@
         </is>
       </c>
       <c r="G292" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/t%C3%A9cnico-analista-hse-vacante-inclusiva-pcd-at-unisys-4460766616", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-seguridad-y-salud-en-el-trabajo-at-agaval-s-a-4470416741", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H292" s="6" t="inlineStr"/>
@@ -14217,7 +14217,7 @@
     <row r="293" ht="22" customHeight="1">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>dc76c168bb90e870</t>
+          <t>dbdcc9c937f7fac0</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>Analista SST</t>
+          <t>Técnico/Analista HSE - Vacante Inclusiva PCD</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
         <is>
-          <t>Constructora Las Galias</t>
+          <t>Unisys</t>
         </is>
       </c>
       <c r="E293" s="7" t="n">
@@ -14244,7 +14244,7 @@
         </is>
       </c>
       <c r="G293" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-sst-at-constructora-las-galias-4456720035", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/t%C3%A9cnico-analista-hse-vacante-inclusiva-pcd-at-unisys-4460766616", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H293" s="6" t="inlineStr"/>
@@ -14263,7 +14263,7 @@
     <row r="294" ht="22" customHeight="1">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>ab0b8a02ee89c538</t>
+          <t>dc76c168bb90e870</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
@@ -14273,12 +14273,12 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>Analista de seguridad y salud en el trabajo</t>
+          <t>Analista SST</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>DaVita Colombia</t>
+          <t>Constructora Las Galias</t>
         </is>
       </c>
       <c r="E294" s="7" t="n">
@@ -14290,7 +14290,7 @@
         </is>
       </c>
       <c r="G294" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-seguridad-y-salud-en-el-trabajo-at-davita-colombia-4453103338", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-sst-at-constructora-las-galias-4456720035", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H294" s="6" t="inlineStr"/>
@@ -14309,7 +14309,7 @@
     <row r="295" ht="22" customHeight="1">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>461d2d2e2c8db03a</t>
+          <t>ab0b8a02ee89c538</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
@@ -14319,12 +14319,12 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>Analista Sst Y Sg</t>
+          <t>Analista de seguridad y salud en el trabajo</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
         <is>
-          <t>GLOBAL LOGÍSTICA DE TRANSPORTE S.A.S</t>
+          <t>DaVita Colombia</t>
         </is>
       </c>
       <c r="E295" s="7" t="n">
@@ -14336,7 +14336,7 @@
         </is>
       </c>
       <c r="G295" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-sst-y-sg-at-global-log%C3%ADstica-de-transporte-s-a-s-4467897164", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-seguridad-y-salud-en-el-trabajo-at-davita-colombia-4453103338", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H295" s="6" t="inlineStr"/>
@@ -14355,7 +14355,7 @@
     <row r="296" ht="22" customHeight="1">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>c39a6537e6eea06b</t>
+          <t>461d2d2e2c8db03a</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
@@ -14365,7 +14365,7 @@
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>Analista SST y SG</t>
+          <t>Analista Sst Y Sg</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
@@ -14382,7 +14382,7 @@
         </is>
       </c>
       <c r="G296" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-sst-y-sg-at-global-log%C3%ADstica-de-transporte-s-a-s-4468342327", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-sst-y-sg-at-global-log%C3%ADstica-de-transporte-s-a-s-4467897164", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H296" s="6" t="inlineStr"/>
@@ -14401,7 +14401,7 @@
     <row r="297" ht="22" customHeight="1">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>a084c2779add376e</t>
+          <t>c39a6537e6eea06b</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
@@ -14411,12 +14411,12 @@
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>ANALISTA SST</t>
+          <t>Analista SST y SG</t>
         </is>
       </c>
       <c r="D297" s="3" t="inlineStr">
         <is>
-          <t>DHL Supply Chain</t>
+          <t>GLOBAL LOGÍSTICA DE TRANSPORTE S.A.S</t>
         </is>
       </c>
       <c r="E297" s="7" t="n">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="G297" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-sst-at-dhl-supply-chain-4464420416", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-sst-y-sg-at-global-log%C3%ADstica-de-transporte-s-a-s-4468342327", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H297" s="6" t="inlineStr"/>
@@ -14447,7 +14447,7 @@
     <row r="298" ht="22" customHeight="1">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>b346821234375c6b</t>
+          <t>a084c2779add376e</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>Tecnologo o tecnico en salud ocupacional</t>
+          <t>ANALISTA SST</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>Llanopozos sa</t>
+          <t>DHL Supply Chain</t>
         </is>
       </c>
       <c r="E298" s="7" t="n">
@@ -14474,7 +14474,7 @@
         </is>
       </c>
       <c r="G298" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/tecnologo-o-tecnico-en-salud-ocupacional-4471620635", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-sst-at-dhl-supply-chain-4464420416", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H298" s="6" t="inlineStr"/>
@@ -14493,7 +14493,7 @@
     <row r="299" ht="22" customHeight="1">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>18698a98a0559ee4</t>
+          <t>b346821234375c6b</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
@@ -14503,12 +14503,12 @@
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>ANALISTA - SST</t>
+          <t>Tecnologo o tecnico en salud ocupacional</t>
         </is>
       </c>
       <c r="D299" s="3" t="inlineStr">
         <is>
-          <t>Gerleinco SAS</t>
+          <t>Llanopozos sa</t>
         </is>
       </c>
       <c r="E299" s="7" t="n">
@@ -14520,7 +14520,7 @@
         </is>
       </c>
       <c r="G299" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-sst-at-gerleinco-sas-4468331526", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/tecnologo-o-tecnico-en-salud-ocupacional-4471620635", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H299" s="6" t="inlineStr"/>
@@ -14539,7 +14539,7 @@
     <row r="300" ht="22" customHeight="1">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>61d593970cdc1eb0</t>
+          <t>18698a98a0559ee4</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
@@ -14549,12 +14549,12 @@
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>Analista Seguridad Vial</t>
+          <t>ANALISTA - SST</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>Improve Solutions S.A.S.</t>
+          <t>Gerleinco SAS</t>
         </is>
       </c>
       <c r="E300" s="7" t="n">
@@ -14566,13 +14566,13 @@
         </is>
       </c>
       <c r="G300" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-seguridad-vial-at-improve-solutions-s-a-s-4463145618", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-sst-at-gerleinco-sas-4468331526", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H300" s="6" t="inlineStr"/>
       <c r="I300" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J300" s="2" t="inlineStr">
@@ -14585,7 +14585,7 @@
     <row r="301" ht="22" customHeight="1">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>7b3bcbac47723cda</t>
+          <t>61d593970cdc1eb0</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
@@ -14595,12 +14595,12 @@
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>Analista de SST Bogotá</t>
+          <t>Analista Seguridad Vial</t>
         </is>
       </c>
       <c r="D301" s="3" t="inlineStr">
         <is>
-          <t>X-Cargo</t>
+          <t>Improve Solutions S.A.S.</t>
         </is>
       </c>
       <c r="E301" s="7" t="n">
@@ -14612,13 +14612,13 @@
         </is>
       </c>
       <c r="G301" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-sst-bogot%C3%A1-at-x-cargo-4470414820", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-seguridad-vial-at-improve-solutions-s-a-s-4463145618", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H301" s="6" t="inlineStr"/>
       <c r="I301" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr">
@@ -14631,7 +14631,7 @@
     <row r="302" ht="22" customHeight="1">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>76e9e10e6636e900</t>
+          <t>7b3bcbac47723cda</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
@@ -14641,12 +14641,12 @@
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>Líder de Interventoría Civil</t>
+          <t>Analista de SST Bogotá</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>Erco Energía</t>
+          <t>X-Cargo</t>
         </is>
       </c>
       <c r="E302" s="7" t="n">
@@ -14658,13 +14658,13 @@
         </is>
       </c>
       <c r="G302" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/l%C3%ADder-de-interventor%C3%ADa-civil-at-erco-energ%C3%ADa-4471619395", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-sst-bogot%C3%A1-at-x-cargo-4470414820", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H302" s="6" t="inlineStr"/>
       <c r="I302" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr">
@@ -14677,22 +14677,22 @@
     <row r="303" ht="22" customHeight="1">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>6f437a27b6511e2d</t>
+          <t>76e9e10e6636e900</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:00</t>
+          <t>2026-09-25 15:50</t>
         </is>
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>Analista HSEQ</t>
+          <t>Líder de Interventoría Civil</t>
         </is>
       </c>
       <c r="D303" s="3" t="inlineStr">
         <is>
-          <t>Alianza Temporal S.A.S</t>
+          <t>Erco Energía</t>
         </is>
       </c>
       <c r="E303" s="7" t="n">
@@ -14704,17 +14704,13 @@
         </is>
       </c>
       <c r="G303" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-hseq-en-bogota-dc-E4BED3252AF449C661373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H303" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.800.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/l%C3%ADder-de-interventor%C3%ADa-civil-at-erco-energ%C3%ADa-4471619395", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H303" s="6" t="inlineStr"/>
       <c r="I303" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J303" s="2" t="inlineStr">
@@ -14727,7 +14723,7 @@
     <row r="304" ht="22" customHeight="1">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>8e91529f2772c72c</t>
+          <t>6f437a27b6511e2d</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
@@ -14737,12 +14733,12 @@
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>Analista SST</t>
+          <t>Analista HSEQ</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr">
         <is>
-          <t>Importante empresa del sector</t>
+          <t>Alianza Temporal S.A.S</t>
         </is>
       </c>
       <c r="E304" s="7" t="n">
@@ -14754,12 +14750,12 @@
         </is>
       </c>
       <c r="G304" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-sst-con-experiencia-en-barranquilla-6CA31CFAD0482DD661373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-hseq-en-bogota-dc-E4BED3252AF449C661373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H304" s="6" t="inlineStr">
         <is>
-          <t>$ 2.200.000,00 (Mensual)</t>
+          <t>$ 2.800.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I304" s="3" t="inlineStr">
@@ -14777,7 +14773,7 @@
     <row r="305" ht="22" customHeight="1">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>13f03ff01ddce4a7</t>
+          <t>8e91529f2772c72c</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
@@ -14792,7 +14788,7 @@
       </c>
       <c r="D305" s="3" t="inlineStr">
         <is>
-          <t>TECNO FUEGO S.A.S.</t>
+          <t>Importante empresa del sector</t>
         </is>
       </c>
       <c r="E305" s="7" t="n">
@@ -14804,12 +14800,12 @@
         </is>
       </c>
       <c r="G305" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-sst-barranquilla-en-barranquilla-32BBEEDAA6E18BE461373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-sst-con-experiencia-en-barranquilla-6CA31CFAD0482DD661373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H305" s="6" t="inlineStr">
         <is>
-          <t>$ 1.939.999,00 (Mensual)</t>
+          <t>$ 2.200.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I305" s="3" t="inlineStr">
@@ -14827,7 +14823,7 @@
     <row r="306" ht="22" customHeight="1">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>28b598355a120cb3</t>
+          <t>13f03ff01ddce4a7</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
@@ -14837,12 +14833,12 @@
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>Tecnico o tecnologo en seguridad y salud en el trabajo</t>
+          <t>Analista SST</t>
         </is>
       </c>
       <c r="D306" s="3" t="inlineStr">
         <is>
-          <t>ABOGADOS TRIANA SAS</t>
+          <t>TECNO FUEGO S.A.S.</t>
         </is>
       </c>
       <c r="E306" s="7" t="n">
@@ -14854,10 +14850,14 @@
         </is>
       </c>
       <c r="G306" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/tecnico-o-tecnologo-en-seguridad-y-salud-en-el-trabajo-1886771946", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H306" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-sst-barranquilla-en-barranquilla-32BBEEDAA6E18BE461373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H306" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.939.999,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I306" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -14873,7 +14873,7 @@
     <row r="307" ht="22" customHeight="1">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>617d4224f3e92d29</t>
+          <t>28b598355a120cb3</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
@@ -14883,12 +14883,12 @@
       </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
-          <t>Cali - consultor de sistemas de gestion sst independiente</t>
+          <t>Tecnico o tecnologo en seguridad y salud en el trabajo</t>
         </is>
       </c>
       <c r="D307" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ABOGADOS TRIANA SAS</t>
         </is>
       </c>
       <c r="E307" s="7" t="n">
@@ -14900,7 +14900,7 @@
         </is>
       </c>
       <c r="G307" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-consultor-de-sistemas-de-gestion-sst-independiente-1886772687", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/tecnico-o-tecnologo-en-seguridad-y-salud-en-el-trabajo-1886771946", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H307" s="6" t="inlineStr"/>
@@ -14919,7 +14919,7 @@
     <row r="308" ht="22" customHeight="1">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>8bd71be8a3c31a17</t>
+          <t>617d4224f3e92d29</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
@@ -14929,12 +14929,12 @@
       </c>
       <c r="C308" s="3" t="inlineStr">
         <is>
-          <t>Coordinado/a de hseq tecnico / tecnologo</t>
+          <t>Cali - consultor de sistemas de gestion sst independiente</t>
         </is>
       </c>
       <c r="D308" s="3" t="inlineStr">
         <is>
-          <t>GI GROUP STAFFING S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E308" s="7" t="n">
@@ -14946,7 +14946,7 @@
         </is>
       </c>
       <c r="G308" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinado-a-de-hseq-tecnico-tecnologo-licencia-de-maternidad-1886755960", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-consultor-de-sistemas-de-gestion-sst-independiente-1886772687", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H308" s="6" t="inlineStr"/>
@@ -14965,7 +14965,7 @@
     <row r="309" ht="22" customHeight="1">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>48a32ee00e933602</t>
+          <t>8bd71be8a3c31a17</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
@@ -14975,12 +14975,12 @@
       </c>
       <c r="C309" s="3" t="inlineStr">
         <is>
-          <t>Líder de HSE Funza</t>
+          <t>Coordinado/a de hseq tecnico / tecnologo</t>
         </is>
       </c>
       <c r="D309" s="3" t="inlineStr">
         <is>
-          <t>Coaspharma</t>
+          <t>GI GROUP STAFFING S.A.S</t>
         </is>
       </c>
       <c r="E309" s="7" t="n">
@@ -14992,7 +14992,7 @@
         </is>
       </c>
       <c r="G309" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/l%C3%ADder-de-hse-funza-at-coaspharma-4472206802", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinado-a-de-hseq-tecnico-tecnologo-licencia-de-maternidad-1886755960", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H309" s="6" t="inlineStr"/>
@@ -15011,26 +15011,26 @@
     <row r="310" ht="22" customHeight="1">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>4426b2c17306f519</t>
+          <t>48a32ee00e933602</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 05:09</t>
+          <t>2026-09-26 15:00</t>
         </is>
       </c>
       <c r="C310" s="3" t="inlineStr">
         <is>
-          <t>Residente de Seguridad y Salud en el trabajo</t>
+          <t>Líder de HSE Funza</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
         <is>
-          <t>Cal y Mayor y Asociados S.C</t>
-        </is>
-      </c>
-      <c r="E310" s="8" t="n">
-        <v>0.48</v>
+          <t>Coaspharma</t>
+        </is>
+      </c>
+      <c r="E310" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="F310" s="2" t="inlineStr">
         <is>
@@ -15038,17 +15038,13 @@
         </is>
       </c>
       <c r="G310" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-residente-de-seguridad-y-salud-en-el-trabajo-sst-sst-en-bogota-dc-D67E64C3D53E0D6961373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H310" s="6" t="inlineStr">
-        <is>
-          <t>$ 4.200.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/l%C3%ADder-de-hse-funza-at-coaspharma-4472206802", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H310" s="6" t="inlineStr"/>
       <c r="I310" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J310" s="2" t="inlineStr">
@@ -15061,26 +15057,26 @@
     <row r="311" ht="22" customHeight="1">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>83015d6afb890f1d</t>
+          <t>158d52d234c03ea0</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 05:09</t>
+          <t>2026-09-27 15:38</t>
         </is>
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t>Analista/profesional HSEQ / SST Sesquile o Alrededores</t>
+          <t>Analista HSEQ</t>
         </is>
       </c>
       <c r="D311" s="3" t="inlineStr">
         <is>
-          <t>ACTIVOS S A S</t>
-        </is>
-      </c>
-      <c r="E311" s="8" t="n">
-        <v>0.48</v>
+          <t>Adecco Colombia S.A.</t>
+        </is>
+      </c>
+      <c r="E311" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="F311" s="2" t="inlineStr">
         <is>
@@ -15088,17 +15084,17 @@
         </is>
       </c>
       <c r="G311" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analistaprofesional-hseq-sst-sesquile-o-alrededores-sector-consumo-masivo-en-sesquile-632A9566338A59E361373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-hseq-bogota-en-bogota-dc-0AD6A8A7D12FF6DE61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H311" s="6" t="inlineStr">
         <is>
-          <t>$ 4.000.000,00 (Mensual)</t>
+          <t>$ 2.320.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I311" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J311" s="2" t="inlineStr">
@@ -15111,26 +15107,26 @@
     <row r="312" ht="22" customHeight="1">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>bc0b38b5129e0905</t>
+          <t>182f0845a966ef19</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 05:09</t>
+          <t>2026-09-27 15:38</t>
         </is>
       </c>
       <c r="C312" s="3" t="inlineStr">
         <is>
-          <t>Profesional en seguridad y salud en el trabajo SST</t>
+          <t>Analista Seguridad Vial</t>
         </is>
       </c>
       <c r="D312" s="3" t="inlineStr">
         <is>
-          <t>Seguridad y Vigilancia Exito de Colombia</t>
-        </is>
-      </c>
-      <c r="E312" s="8" t="n">
-        <v>0.48</v>
+          <t>IMPROVE SOLUTIONS S.A.S</t>
+        </is>
+      </c>
+      <c r="E312" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="F312" s="2" t="inlineStr">
         <is>
@@ -15138,17 +15134,13 @@
         </is>
       </c>
       <c r="G312" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-profesional-en-seguridad-y-salud-en-el-trabajo-sst-con-experiencia-y-conocimiento-en-pesv-en-bogota-dc-A7CA6F8805D1C53B61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H312" s="6" t="inlineStr">
-        <is>
-          <t>$ 3.200.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-seguridad-vial-en-cucuta-8D0599AAE93B7BDB61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H312" s="6" t="inlineStr"/>
       <c r="I312" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J312" s="2" t="inlineStr">
@@ -15161,26 +15153,26 @@
     <row r="313" ht="22" customHeight="1">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>e15ce00dbe5c21b5</t>
+          <t>a7b55fd269df3a50</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 05:09</t>
+          <t>2026-09-27 15:38</t>
         </is>
       </c>
       <c r="C313" s="3" t="inlineStr">
         <is>
-          <t>Tecnólogo HSEQ / Seguridad y Salud en el Trabajo</t>
+          <t>Analista de Seguridad y Salud en el Trabajo</t>
         </is>
       </c>
       <c r="D313" s="3" t="inlineStr">
         <is>
-          <t>Lighgen Ingeniería Ltda</t>
-        </is>
-      </c>
-      <c r="E313" s="8" t="n">
-        <v>0.48</v>
+          <t>Importante empresa del sector</t>
+        </is>
+      </c>
+      <c r="E313" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="F313" s="2" t="inlineStr">
         <is>
@@ -15188,13 +15180,17 @@
         </is>
       </c>
       <c r="G313" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-tecnologo-hseq-seguridad-y-salud-en-el-trabajo-con-experiencia-2-anos-en-bogota-dc-87DB3FCAFEA8E12861373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H313" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-seguridad-y-salud-en-el-trabajo-en-girardota-FCB0DBA2EE5A9F3C61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H313" s="6" t="inlineStr">
+        <is>
+          <t>$ 2.800.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I313" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J313" s="2" t="inlineStr">
@@ -15207,26 +15203,26 @@
     <row r="314" ht="22" customHeight="1">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>1f3bf8b16a58f0b4</t>
+          <t>665bd61e41f51bda</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 05:09</t>
+          <t>2026-09-27 15:38</t>
         </is>
       </c>
       <c r="C314" s="3" t="inlineStr">
         <is>
-          <t>Inspector (a) de vias y urbanismo</t>
+          <t>Director de interventoría / Mosquera, Cundinamarca</t>
         </is>
       </c>
       <c r="D314" s="3" t="inlineStr">
         <is>
-          <t>METRO LINEA 1 S.A.S.</t>
-        </is>
-      </c>
-      <c r="E314" s="8" t="n">
-        <v>0.48</v>
+          <t>Importante empresa del sector</t>
+        </is>
+      </c>
+      <c r="E314" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="F314" s="2" t="inlineStr">
         <is>
@@ -15234,13 +15230,17 @@
         </is>
       </c>
       <c r="G314" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/inspector-a-de-vias-y-urbanismo-1886728733", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H314" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-director-de-interventoria-mosquera-cundinamarca-en-mosquera-097873138F684A0161373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H314" s="6" t="inlineStr">
+        <is>
+          <t>$ 7.300.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I314" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J314" s="2" t="inlineStr">
@@ -15253,26 +15253,26 @@
     <row r="315" ht="22" customHeight="1">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>8fd843a922654d9e</t>
+          <t>2d7943b278e48a1f</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 05:09</t>
+          <t>2026-09-27 15:38</t>
         </is>
       </c>
       <c r="C315" s="3" t="inlineStr">
         <is>
-          <t>Oficial de obra</t>
+          <t>Analista de seguridad y salud en el trabajo</t>
         </is>
       </c>
       <c r="D315" s="3" t="inlineStr">
         <is>
-          <t>TERMOTECNICA COINDUSTRIAL SAS</t>
-        </is>
-      </c>
-      <c r="E315" s="8" t="n">
-        <v>0.48</v>
+          <t>Fundación Santa Fe de Bogotá</t>
+        </is>
+      </c>
+      <c r="E315" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="F315" s="2" t="inlineStr">
         <is>
@@ -15280,13 +15280,13 @@
         </is>
       </c>
       <c r="G315" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/oficial-de-obra-puentevias-1886766237", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-seguridad-y-salud-en-el-trabajo-1886761626", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H315" s="6" t="inlineStr"/>
       <c r="I315" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J315" s="2" t="inlineStr">
@@ -15299,26 +15299,26 @@
     <row r="316" ht="22" customHeight="1">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>03eab73111095faa</t>
+          <t>56bbeddd14532a1d</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 05:09</t>
+          <t>2026-09-27 15:38</t>
         </is>
       </c>
       <c r="C316" s="3" t="inlineStr">
         <is>
-          <t>Residente estructuras</t>
+          <t>Ingeniero de infraestructura ti / siberia - tenjo</t>
         </is>
       </c>
       <c r="D316" s="3" t="inlineStr">
         <is>
-          <t>CONCONCRETO S.A.</t>
-        </is>
-      </c>
-      <c r="E316" s="8" t="n">
-        <v>0.48</v>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E316" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="F316" s="2" t="inlineStr">
         <is>
@@ -15326,13 +15326,13 @@
         </is>
       </c>
       <c r="G316" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/residente-estructuras-experiencia-en-infraestructura-vial-y-talud-1886757305", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-de-infraestructura-ti-siberia-tenjo-1886757026", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H316" s="6" t="inlineStr"/>
       <c r="I316" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J316" s="2" t="inlineStr">
@@ -15345,7 +15345,7 @@
     <row r="317" ht="22" customHeight="1">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>c5911c7562546e3c</t>
+          <t>4426b2c17306f519</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
@@ -15355,12 +15355,12 @@
       </c>
       <c r="C317" s="3" t="inlineStr">
         <is>
-          <t>Profesional con experiencia en el sector de transporte marítimo y/o por vías navegables</t>
+          <t>Residente de Seguridad y Salud en el trabajo</t>
         </is>
       </c>
       <c r="D317" s="3" t="inlineStr">
         <is>
-          <t>ICONTEC</t>
+          <t>Cal y Mayor y Asociados S.C</t>
         </is>
       </c>
       <c r="E317" s="8" t="n">
@@ -15372,13 +15372,17 @@
         </is>
       </c>
       <c r="G317" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/profesional-con-experiencia-en-el-sector-de-transporte-maritimo-y-o-por-vias-navegables-1886761682", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H317" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-residente-de-seguridad-y-salud-en-el-trabajo-sst-sst-en-bogota-dc-D67E64C3D53E0D6961373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H317" s="6" t="inlineStr">
+        <is>
+          <t>$ 4.200.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I317" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J317" s="2" t="inlineStr">
@@ -15391,7 +15395,7 @@
     <row r="318" ht="22" customHeight="1">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>c2903e245a44de39</t>
+          <t>83015d6afb890f1d</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
@@ -15401,12 +15405,12 @@
       </c>
       <c r="C318" s="3" t="inlineStr">
         <is>
-          <t>Encargado de obra</t>
+          <t>Analista/profesional HSEQ / SST Sesquile o Alrededores</t>
         </is>
       </c>
       <c r="D318" s="3" t="inlineStr">
         <is>
-          <t>TERMOTECNICA COINDUSTRIAL SAS</t>
+          <t>ACTIVOS S A S</t>
         </is>
       </c>
       <c r="E318" s="8" t="n">
@@ -15418,13 +15422,17 @@
         </is>
       </c>
       <c r="G318" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/encargado-de-obra-puentes-vias-1886762620", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H318" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analistaprofesional-hseq-sst-sesquile-o-alrededores-sector-consumo-masivo-en-sesquile-632A9566338A59E361373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H318" s="6" t="inlineStr">
+        <is>
+          <t>$ 4.000.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I318" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J318" s="2" t="inlineStr">
@@ -15437,7 +15445,7 @@
     <row r="319" ht="22" customHeight="1">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>a5bd833e8b837d34</t>
+          <t>bc0b38b5129e0905</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
@@ -15447,12 +15455,12 @@
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>Residente en seguridad y salud en el trabajo</t>
+          <t>Profesional en seguridad y salud en el trabajo SST</t>
         </is>
       </c>
       <c r="D319" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Seguridad y Vigilancia Exito de Colombia</t>
         </is>
       </c>
       <c r="E319" s="8" t="n">
@@ -15464,10 +15472,14 @@
         </is>
       </c>
       <c r="G319" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/residente-en-seguridad-y-salud-en-el-trabajo-sst-1886762728", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H319" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-profesional-en-seguridad-y-salud-en-el-trabajo-sst-con-experiencia-y-conocimiento-en-pesv-en-bogota-dc-A7CA6F8805D1C53B61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H319" s="6" t="inlineStr">
+        <is>
+          <t>$ 3.200.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I319" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -15483,7 +15495,7 @@
     <row r="320" ht="22" customHeight="1">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>55e7967f3b4afa02</t>
+          <t>e15ce00dbe5c21b5</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
@@ -15493,12 +15505,12 @@
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>Tecnólogo/a en Seguridad y Salud en el Trabajo</t>
+          <t>Tecnólogo HSEQ / Seguridad y Salud en el Trabajo</t>
         </is>
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>EOSOL</t>
+          <t>Lighgen Ingeniería Ltda</t>
         </is>
       </c>
       <c r="E320" s="8" t="n">
@@ -15510,7 +15522,7 @@
         </is>
       </c>
       <c r="G320" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/tecn%C3%B3logo-a-en-seguridad-y-salud-en-el-trabajo-sst-at-eosol-4464868638", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-tecnologo-hseq-seguridad-y-salud-en-el-trabajo-con-experiencia-2-anos-en-bogota-dc-87DB3FCAFEA8E12861373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H320" s="6" t="inlineStr"/>
@@ -15529,7 +15541,7 @@
     <row r="321" ht="22" customHeight="1">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>6df905e482fe09b1</t>
+          <t>1f3bf8b16a58f0b4</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
@@ -15539,12 +15551,12 @@
       </c>
       <c r="C321" s="3" t="inlineStr">
         <is>
-          <t>Aprendiz SENA - Técnico(a) de Salud Ocupacional o Seguridad y Salud en el Trabajo - Ginebra</t>
+          <t>Inspector (a) de vias y urbanismo</t>
         </is>
       </c>
       <c r="D321" s="3" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>METRO LINEA 1 S.A.S.</t>
         </is>
       </c>
       <c r="E321" s="8" t="n">
@@ -15556,13 +15568,13 @@
         </is>
       </c>
       <c r="G321" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-sena-t%C3%A9cnico-a-de-salud-ocupacional-o-seguridad-y-salud-en-el-trabajo-ginebra-at-cargill-4466994159", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/inspector-a-de-vias-y-urbanismo-1886728733", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H321" s="6" t="inlineStr"/>
       <c r="I321" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J321" s="2" t="inlineStr">
@@ -15575,7 +15587,7 @@
     <row r="322" ht="22" customHeight="1">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>06656fbb2d452086</t>
+          <t>8fd843a922654d9e</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
@@ -15585,12 +15597,12 @@
       </c>
       <c r="C322" s="3" t="inlineStr">
         <is>
-          <t>Residente de Seguridad y Salud en el trabajo</t>
+          <t>Oficial de obra</t>
         </is>
       </c>
       <c r="D322" s="3" t="inlineStr">
         <is>
-          <t>Grupo Cal y Mayor</t>
+          <t>TERMOTECNICA COINDUSTRIAL SAS</t>
         </is>
       </c>
       <c r="E322" s="8" t="n">
@@ -15602,13 +15614,13 @@
         </is>
       </c>
       <c r="G322" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/residente-de-seguridad-y-salud-en-el-trabajo-sst-at-cal-y-mayor-4468610572", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/oficial-de-obra-puentevias-1886766237", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H322" s="6" t="inlineStr"/>
       <c r="I322" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J322" s="2" t="inlineStr">
@@ -15621,7 +15633,7 @@
     <row r="323" ht="22" customHeight="1">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>7796e088dce85b5a</t>
+          <t>03eab73111095faa</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
@@ -15631,16 +15643,16 @@
       </c>
       <c r="C323" s="3" t="inlineStr">
         <is>
-          <t>Civil Engineer (Fire Sprinkler Design))</t>
+          <t>Residente estructuras</t>
         </is>
       </c>
       <c r="D323" s="3" t="inlineStr">
         <is>
-          <t>Hyremote</t>
+          <t>CONCONCRETO S.A.</t>
         </is>
       </c>
       <c r="E323" s="8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="F323" s="2" t="inlineStr">
         <is>
@@ -15648,17 +15660,13 @@
         </is>
       </c>
       <c r="G323" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-civil-engineer-fire-sprinkler-design-english-c1-remote-en-bogota-dc-A2EE61A321FC0D3361373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H323" s="6" t="inlineStr">
-        <is>
-          <t>$ 4.499.993,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/residente-estructuras-experiencia-en-infraestructura-vial-y-talud-1886757305", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H323" s="6" t="inlineStr"/>
       <c r="I323" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J323" s="2" t="inlineStr">
@@ -15671,7 +15679,7 @@
     <row r="324" ht="22" customHeight="1">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>48463526ca7c8ada</t>
+          <t>c5911c7562546e3c</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
@@ -15681,16 +15689,16 @@
       </c>
       <c r="C324" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero Civil Especialista en Hidrología e Hidráulica</t>
+          <t>Profesional con experiencia en el sector de transporte marítimo y/o por vías navegables</t>
         </is>
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>ATLAS INFRASTRUCTURE DESIGN LIMITED</t>
+          <t>ICONTEC</t>
         </is>
       </c>
       <c r="E324" s="8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="F324" s="2" t="inlineStr">
         <is>
@@ -15698,17 +15706,13 @@
         </is>
       </c>
       <c r="G324" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-especialista-en-hidrologia-e-hidraulica-tiempo-completo-en-remoto-y-de-larga-duracion-en-colombia-027FB718364F4C7761373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H324" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/profesional-con-experiencia-en-el-sector-de-transporte-maritimo-y-o-por-vias-navegables-1886761682", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H324" s="6" t="inlineStr"/>
       <c r="I324" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J324" s="2" t="inlineStr">
@@ -15721,7 +15725,7 @@
     <row r="325" ht="22" customHeight="1">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>2d406567ceb21bf8</t>
+          <t>c2903e245a44de39</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
@@ -15731,16 +15735,16 @@
       </c>
       <c r="C325" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero Civil de Diseño</t>
+          <t>Encargado de obra</t>
         </is>
       </c>
       <c r="D325" s="3" t="inlineStr">
         <is>
-          <t>ATLAS INFRASTRUCTURE DESIGN LIMITED</t>
+          <t>TERMOTECNICA COINDUSTRIAL SAS</t>
         </is>
       </c>
       <c r="E325" s="8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="F325" s="2" t="inlineStr">
         <is>
@@ -15748,17 +15752,13 @@
         </is>
       </c>
       <c r="G325" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-de-diseno-tiempo-completo-en-remoto-en-colombia-4CB8F30B6D8FBF7261373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H325" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/encargado-de-obra-puentes-vias-1886762620", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H325" s="6" t="inlineStr"/>
       <c r="I325" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J325" s="2" t="inlineStr">
@@ -15771,7 +15771,7 @@
     <row r="326" ht="22" customHeight="1">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>4d4013d19591d2a5</t>
+          <t>a5bd833e8b837d34</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
@@ -15781,16 +15781,16 @@
       </c>
       <c r="C326" s="3" t="inlineStr">
         <is>
-          <t>Especialista en Salud y Seguridad en el trabajo con especialización en medio Ambiente</t>
+          <t>Residente en seguridad y salud en el trabajo</t>
         </is>
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>DEXTERA S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E326" s="8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="F326" s="2" t="inlineStr">
         <is>
@@ -15798,13 +15798,13 @@
         </is>
       </c>
       <c r="G326" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-especialista-en-salud-y-seguridad-en-el-trabajo-con-especializacion-en-medio-ambiente-en-bogota-dc-68C95C2F64D6648561373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/residente-en-seguridad-y-salud-en-el-trabajo-sst-1886762728", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H326" s="6" t="inlineStr"/>
       <c r="I326" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J326" s="2" t="inlineStr">
@@ -15817,7 +15817,7 @@
     <row r="327" ht="22" customHeight="1">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>cf70d2ca6e5c25de</t>
+          <t>55e7967f3b4afa02</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
@@ -15827,16 +15827,16 @@
       </c>
       <c r="C327" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero civil</t>
+          <t>Tecnólogo/a en Seguridad y Salud en el Trabajo</t>
         </is>
       </c>
       <c r="D327" s="3" t="inlineStr">
         <is>
-          <t>Importante empresa del sector</t>
+          <t>EOSOL</t>
         </is>
       </c>
       <c r="E327" s="8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="F327" s="2" t="inlineStr">
         <is>
@@ -15844,17 +15844,13 @@
         </is>
       </c>
       <c r="G327" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-con-experiencia-en-sistemas-fotovoltaicos-en-bogota-dc-8BCBCD7DF8FE589C61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H327" s="6" t="inlineStr">
-        <is>
-          <t>$ 3.300.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/tecn%C3%B3logo-a-en-seguridad-y-salud-en-el-trabajo-sst-at-eosol-4464868638", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H327" s="6" t="inlineStr"/>
       <c r="I327" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J327" s="2" t="inlineStr">
@@ -15867,7 +15863,7 @@
     <row r="328" ht="22" customHeight="1">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>bb8237cc7ed8d56b</t>
+          <t>6df905e482fe09b1</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
@@ -15877,16 +15873,16 @@
       </c>
       <c r="C328" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de Proyectos Mejoramientos de Vivienda</t>
+          <t>Aprendiz SENA - Técnico(a) de Salud Ocupacional o Seguridad y Salud en el Trabajo - Ginebra</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>Socya</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="E328" s="8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="F328" s="2" t="inlineStr">
         <is>
@@ -15894,13 +15890,13 @@
         </is>
       </c>
       <c r="G328" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-de-proyectos-mejoramientos-de-vivienda-medellin-antioquia-en-medellin-7E29781CFFD4058961373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-sena-t%C3%A9cnico-a-de-salud-ocupacional-o-seguridad-y-salud-en-el-trabajo-ginebra-at-cargill-4466994159", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H328" s="6" t="inlineStr"/>
       <c r="I328" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J328" s="2" t="inlineStr">
@@ -15913,7 +15909,7 @@
     <row r="329" ht="22" customHeight="1">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>c41dc091e876cb10</t>
+          <t>06656fbb2d452086</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
@@ -15923,16 +15919,16 @@
       </c>
       <c r="C329" s="3" t="inlineStr">
         <is>
-          <t>Especialista de Milk Collection</t>
+          <t>Residente de Seguridad y Salud en el trabajo</t>
         </is>
       </c>
       <c r="D329" s="3" t="inlineStr">
         <is>
-          <t>LACTALIS</t>
+          <t>Grupo Cal y Mayor</t>
         </is>
       </c>
       <c r="E329" s="8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="F329" s="2" t="inlineStr">
         <is>
@@ -15940,17 +15936,13 @@
         </is>
       </c>
       <c r="G329" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-especialista-de-milk-collection-optimizacion-y-analisis-de-datos-en-bogota-dc-B007F5172FEA6F6461373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H329" s="6" t="inlineStr">
-        <is>
-          <t>$ 6.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/residente-de-seguridad-y-salud-en-el-trabajo-sst-at-cal-y-mayor-4468610572", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H329" s="6" t="inlineStr"/>
       <c r="I329" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J329" s="2" t="inlineStr">
@@ -15963,7 +15955,7 @@
     <row r="330" ht="22" customHeight="1">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>4f38d6c20430e4bb</t>
+          <t>7796e088dce85b5a</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
@@ -15973,12 +15965,12 @@
       </c>
       <c r="C330" s="3" t="inlineStr">
         <is>
-          <t>ingeniero civil</t>
+          <t>Civil Engineer (Fire Sprinkler Design))</t>
         </is>
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>EVALTEC S.A.S.</t>
+          <t>Hyremote</t>
         </is>
       </c>
       <c r="E330" s="8" t="n">
@@ -15990,10 +15982,14 @@
         </is>
       </c>
       <c r="G330" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-o-areas-afines-en-medellin-0E02F682AB12631061373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H330" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-civil-engineer-fire-sprinkler-design-english-c1-remote-en-bogota-dc-A2EE61A321FC0D3361373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H330" s="6" t="inlineStr">
+        <is>
+          <t>$ 4.499.993,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I330" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -16009,7 +16005,7 @@
     <row r="331" ht="22" customHeight="1">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>af38dd28fbbad8f4</t>
+          <t>48463526ca7c8ada</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
@@ -16019,12 +16015,12 @@
       </c>
       <c r="C331" s="3" t="inlineStr">
         <is>
-          <t>Tecnólogo Auxiliar Civil</t>
+          <t>Ingeniero Civil Especialista en Hidrología e Hidráulica</t>
         </is>
       </c>
       <c r="D331" s="3" t="inlineStr">
         <is>
-          <t>Importante empresa del sector</t>
+          <t>ATLAS INFRASTRUCTURE DESIGN LIMITED</t>
         </is>
       </c>
       <c r="E331" s="8" t="n">
@@ -16036,10 +16032,14 @@
         </is>
       </c>
       <c r="G331" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-tecnologo-auxiliar-civil-antioquia-en-liborina-B380460DDA9F98D061373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H331" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-especialista-en-hidrologia-e-hidraulica-tiempo-completo-en-remoto-y-de-larga-duracion-en-colombia-027FB718364F4C7761373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H331" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I331" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -16055,7 +16055,7 @@
     <row r="332" ht="22" customHeight="1">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>19e74768ce848880</t>
+          <t>2d406567ceb21bf8</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
@@ -16065,12 +16065,12 @@
       </c>
       <c r="C332" s="3" t="inlineStr">
         <is>
-          <t>Coordinador HSEQ</t>
+          <t>Ingeniero Civil de Diseño</t>
         </is>
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>Agencia de empleo de Comfenalco Cartagena</t>
+          <t>ATLAS INFRASTRUCTURE DESIGN LIMITED</t>
         </is>
       </c>
       <c r="E332" s="8" t="n">
@@ -16082,17 +16082,17 @@
         </is>
       </c>
       <c r="G332" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-hseq-especialista-en-seguridad-y-salud-en-el-trabajo-salud-ocupacional-en-cartagena-de-indias-1EAF6570FC054C2661373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-de-diseno-tiempo-completo-en-remoto-en-colombia-4CB8F30B6D8FBF7261373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H332" s="6" t="inlineStr">
         <is>
-          <t>$ 2.500.000,00 (Mensual)</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="I332" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J332" s="2" t="inlineStr">
@@ -16105,7 +16105,7 @@
     <row r="333" ht="22" customHeight="1">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>38c9a9481706de58</t>
+          <t>4d4013d19591d2a5</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
@@ -16115,12 +16115,12 @@
       </c>
       <c r="C333" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de seguridad vial y monitoreo</t>
+          <t>Especialista en Salud y Seguridad en el trabajo con especialización en medio Ambiente</t>
         </is>
       </c>
       <c r="D333" s="3" t="inlineStr">
         <is>
-          <t>MEGACOMERCIAL S.A.S</t>
+          <t>DEXTERA S.A.S</t>
         </is>
       </c>
       <c r="E333" s="8" t="n">
@@ -16132,17 +16132,13 @@
         </is>
       </c>
       <c r="G333" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-de-seguridad-vial-y-monitoreo-abierto-a-nivel-nacional-en-bogota-dc-B9B593A780889F2A61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H333" s="6" t="inlineStr">
-        <is>
-          <t>$ 5.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-especialista-en-salud-y-seguridad-en-el-trabajo-con-especializacion-en-medio-ambiente-en-bogota-dc-68C95C2F64D6648561373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H333" s="6" t="inlineStr"/>
       <c r="I333" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J333" s="2" t="inlineStr">
@@ -16155,7 +16151,7 @@
     <row r="334" ht="22" customHeight="1">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>aecc6c18fdd71383</t>
+          <t>cf70d2ca6e5c25de</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
@@ -16165,12 +16161,12 @@
       </c>
       <c r="C334" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de PESV</t>
+          <t>Ingeniero civil</t>
         </is>
       </c>
       <c r="D334" s="3" t="inlineStr">
         <is>
-          <t>Agencia de Empleo de Comfenalco Antioquia</t>
+          <t>Importante empresa del sector</t>
         </is>
       </c>
       <c r="E334" s="8" t="n">
@@ -16182,17 +16178,17 @@
         </is>
       </c>
       <c r="G334" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-de-pesv-en-medellin-67C3B78E9A85885161373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-con-experiencia-en-sistemas-fotovoltaicos-en-bogota-dc-8BCBCD7DF8FE589C61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H334" s="6" t="inlineStr">
         <is>
-          <t>$ 2.800.000,00 (Mensual)</t>
+          <t>$ 3.300.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I334" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J334" s="2" t="inlineStr">
@@ -16205,7 +16201,7 @@
     <row r="335" ht="22" customHeight="1">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>1558fc20863bdd35</t>
+          <t>bb8237cc7ed8d56b</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
@@ -16215,12 +16211,12 @@
       </c>
       <c r="C335" s="3" t="inlineStr">
         <is>
-          <t>Coordinador HSEQ</t>
+          <t>Coordinador de Proyectos Mejoramientos de Vivienda</t>
         </is>
       </c>
       <c r="D335" s="3" t="inlineStr">
         <is>
-          <t>COMPAÑIA DE INGENIEROS CONSTRUCTORES S.A.S.</t>
+          <t>Socya</t>
         </is>
       </c>
       <c r="E335" s="8" t="n">
@@ -16232,13 +16228,13 @@
         </is>
       </c>
       <c r="G335" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-hseq-en-barranquilla-F4898EBB71CAF3ED61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-de-proyectos-mejoramientos-de-vivienda-medellin-antioquia-en-medellin-7E29781CFFD4058961373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H335" s="6" t="inlineStr"/>
       <c r="I335" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J335" s="2" t="inlineStr">
@@ -16251,7 +16247,7 @@
     <row r="336" ht="22" customHeight="1">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>0bf63022dc93885b</t>
+          <t>c41dc091e876cb10</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
@@ -16261,12 +16257,12 @@
       </c>
       <c r="C336" s="3" t="inlineStr">
         <is>
-          <t>ingeniero civil</t>
+          <t>Especialista de Milk Collection</t>
         </is>
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>FRANCISCO ANGULO M INGENIEROS S.A.S.</t>
+          <t>LACTALIS</t>
         </is>
       </c>
       <c r="E336" s="8" t="n">
@@ -16278,10 +16274,14 @@
         </is>
       </c>
       <c r="G336" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-residente-de-interventoria-yo-supervision-tecnica-en-cali-D2AE78FA9B23778161373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H336" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-especialista-de-milk-collection-optimizacion-y-analisis-de-datos-en-bogota-dc-B007F5172FEA6F6461373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H336" s="6" t="inlineStr">
+        <is>
+          <t>$ 6.000.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I336" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -16297,7 +16297,7 @@
     <row r="337" ht="22" customHeight="1">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>baa61a6e15a2de77</t>
+          <t>4f38d6c20430e4bb</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
@@ -16307,12 +16307,12 @@
       </c>
       <c r="C337" s="3" t="inlineStr">
         <is>
-          <t>Arquitecto(a) / Ingeniero(a) Civil</t>
+          <t>ingeniero civil</t>
         </is>
       </c>
       <c r="D337" s="3" t="inlineStr">
         <is>
-          <t>Importante empresa del sector</t>
+          <t>EVALTEC S.A.S.</t>
         </is>
       </c>
       <c r="E337" s="8" t="n">
@@ -16324,7 +16324,7 @@
         </is>
       </c>
       <c r="G337" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-arquitectoa-ingenieroa-civil-en-bucaramanga-8D15AF34F304555F61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-o-areas-afines-en-medellin-0E02F682AB12631061373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H337" s="6" t="inlineStr"/>
@@ -16343,7 +16343,7 @@
     <row r="338" ht="22" customHeight="1">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>448d93b15d9b7dec</t>
+          <t>af38dd28fbbad8f4</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
@@ -16353,12 +16353,12 @@
       </c>
       <c r="C338" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero especialista fortinet</t>
+          <t>Tecnólogo Auxiliar Civil</t>
         </is>
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>ATCG DE COLOMBIA S.A.S</t>
+          <t>Importante empresa del sector</t>
         </is>
       </c>
       <c r="E338" s="8" t="n">
@@ -16370,7 +16370,7 @@
         </is>
       </c>
       <c r="G338" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-especialista-fortinet-1886742914", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-tecnologo-auxiliar-civil-antioquia-en-liborina-B380460DDA9F98D061373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H338" s="6" t="inlineStr"/>
@@ -16389,7 +16389,7 @@
     <row r="339" ht="22" customHeight="1">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>f2fc6f9471f81665</t>
+          <t>19e74768ce848880</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
@@ -16399,12 +16399,12 @@
       </c>
       <c r="C339" s="3" t="inlineStr">
         <is>
-          <t>Coordinador/a nacional de redes e infraestructura de ti - presencial bucaramanga</t>
+          <t>Coordinador HSEQ</t>
         </is>
       </c>
       <c r="D339" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Agencia de empleo de Comfenalco Cartagena</t>
         </is>
       </c>
       <c r="E339" s="8" t="n">
@@ -16416,13 +16416,17 @@
         </is>
       </c>
       <c r="G339" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-a-nacional-de-redes-e-infraestructura-de-ti-presencial-bucaramanga-1886769481", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H339" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-hseq-especialista-en-seguridad-y-salud-en-el-trabajo-salud-ocupacional-en-cartagena-de-indias-1EAF6570FC054C2661373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H339" s="6" t="inlineStr">
+        <is>
+          <t>$ 2.500.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I339" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J339" s="2" t="inlineStr">
@@ -16435,7 +16439,7 @@
     <row r="340" ht="22" customHeight="1">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>53e1a775996a36c5</t>
+          <t>38c9a9481706de58</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
@@ -16445,12 +16449,12 @@
       </c>
       <c r="C340" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero civil</t>
+          <t>Coordinador de seguridad vial y monitoreo</t>
         </is>
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>Proyectos de Diseño y Construccion sas</t>
+          <t>MEGACOMERCIAL S.A.S</t>
         </is>
       </c>
       <c r="E340" s="8" t="n">
@@ -16462,13 +16466,17 @@
         </is>
       </c>
       <c r="G340" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-1886757049", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H340" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-de-seguridad-vial-y-monitoreo-abierto-a-nivel-nacional-en-bogota-dc-B9B593A780889F2A61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H340" s="6" t="inlineStr">
+        <is>
+          <t>$ 5.000.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I340" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J340" s="2" t="inlineStr">
@@ -16481,7 +16489,7 @@
     <row r="341" ht="22" customHeight="1">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>1072d76e2f18ea50</t>
+          <t>aecc6c18fdd71383</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
@@ -16491,12 +16499,12 @@
       </c>
       <c r="C341" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero civil</t>
+          <t>Coordinador de PESV</t>
         </is>
       </c>
       <c r="D341" s="3" t="inlineStr">
         <is>
-          <t>R2P SOLUCIONES Y CONSTRUCCIONES SAS</t>
+          <t>Agencia de Empleo de Comfenalco Antioquia</t>
         </is>
       </c>
       <c r="E341" s="8" t="n">
@@ -16508,13 +16516,17 @@
         </is>
       </c>
       <c r="G341" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-1886758475", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H341" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-de-pesv-en-medellin-67C3B78E9A85885161373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H341" s="6" t="inlineStr">
+        <is>
+          <t>$ 2.800.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I341" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J341" s="2" t="inlineStr">
@@ -16527,7 +16539,7 @@
     <row r="342" ht="22" customHeight="1">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>2c943591cc334f5a</t>
+          <t>1558fc20863bdd35</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
@@ -16537,12 +16549,12 @@
       </c>
       <c r="C342" s="3" t="inlineStr">
         <is>
-          <t>Ejecutivo/ade ingeniera</t>
+          <t>Coordinador HSEQ</t>
         </is>
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>COMPAÑIA DE INGENIEROS CONSTRUCTORES S.A.S.</t>
         </is>
       </c>
       <c r="E342" s="8" t="n">
@@ -16554,13 +16566,13 @@
         </is>
       </c>
       <c r="G342" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-ade-ingeniera-1886752134", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-hseq-en-barranquilla-F4898EBB71CAF3ED61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H342" s="6" t="inlineStr"/>
       <c r="I342" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J342" s="2" t="inlineStr">
@@ -16573,7 +16585,7 @@
     <row r="343" ht="22" customHeight="1">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>7d4067502e572780</t>
+          <t>0bf63022dc93885b</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
@@ -16583,12 +16595,12 @@
       </c>
       <c r="C343" s="3" t="inlineStr">
         <is>
-          <t>Ingeniera de ventas - cali</t>
+          <t>ingeniero civil</t>
         </is>
       </c>
       <c r="D343" s="3" t="inlineStr">
         <is>
-          <t>PIPOL EXPERT SAS</t>
+          <t>FRANCISCO ANGULO M INGENIEROS S.A.S.</t>
         </is>
       </c>
       <c r="E343" s="8" t="n">
@@ -16600,7 +16612,7 @@
         </is>
       </c>
       <c r="G343" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-de-ventas-cali-1886754430", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-residente-de-interventoria-yo-supervision-tecnica-en-cali-D2AE78FA9B23778161373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H343" s="6" t="inlineStr"/>
@@ -16619,7 +16631,7 @@
     <row r="344" ht="22" customHeight="1">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>a3a688084650de1c</t>
+          <t>baa61a6e15a2de77</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
@@ -16629,12 +16641,12 @@
       </c>
       <c r="C344" s="3" t="inlineStr">
         <is>
-          <t>Ingeniera comercial electrica - cali</t>
+          <t>Arquitecto(a) / Ingeniero(a) Civil</t>
         </is>
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>PIPOL EXPERT SAS</t>
+          <t>Importante empresa del sector</t>
         </is>
       </c>
       <c r="E344" s="8" t="n">
@@ -16646,7 +16658,7 @@
         </is>
       </c>
       <c r="G344" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-comercial-electrica-cali-1886752104", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-arquitectoa-ingenieroa-civil-en-bucaramanga-8D15AF34F304555F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H344" s="6" t="inlineStr"/>
@@ -16665,7 +16677,7 @@
     <row r="345" ht="22" customHeight="1">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>359d47915a2e74e6</t>
+          <t>448d93b15d9b7dec</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
@@ -16675,12 +16687,12 @@
       </c>
       <c r="C345" s="3" t="inlineStr">
         <is>
-          <t>Supervisor civil - obra</t>
+          <t>Ingeniero especialista fortinet</t>
         </is>
       </c>
       <c r="D345" s="3" t="inlineStr">
         <is>
-          <t>CONCONCRETO S.A.</t>
+          <t>ATCG DE COLOMBIA S.A.S</t>
         </is>
       </c>
       <c r="E345" s="8" t="n">
@@ -16692,7 +16704,7 @@
         </is>
       </c>
       <c r="G345" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/supervisor-civil-obra-1886750435", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-especialista-fortinet-1886742914", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H345" s="6" t="inlineStr"/>
@@ -16711,7 +16723,7 @@
     <row r="346" ht="22" customHeight="1">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>78244d2897084f6a</t>
+          <t>f2fc6f9471f81665</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
@@ -16721,12 +16733,12 @@
       </c>
       <c r="C346" s="3" t="inlineStr">
         <is>
-          <t>Ingeniera comercial sector industrial - cali</t>
+          <t>Coordinador/a nacional de redes e infraestructura de ti - presencial bucaramanga</t>
         </is>
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>PIPOL EXPERT SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E346" s="8" t="n">
@@ -16738,13 +16750,13 @@
         </is>
       </c>
       <c r="G346" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-comercial-sector-industrial-cali-1886753949", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-a-nacional-de-redes-e-infraestructura-de-ti-presencial-bucaramanga-1886769481", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H346" s="6" t="inlineStr"/>
       <c r="I346" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J346" s="2" t="inlineStr">
@@ -16757,7 +16769,7 @@
     <row r="347" ht="22" customHeight="1">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>a4d1239b8910f7cf</t>
+          <t>53e1a775996a36c5</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
@@ -16767,12 +16779,12 @@
       </c>
       <c r="C347" s="3" t="inlineStr">
         <is>
-          <t>Ingeniera electrica comercial - bogotá</t>
+          <t>Ingeniero civil</t>
         </is>
       </c>
       <c r="D347" s="3" t="inlineStr">
         <is>
-          <t>PIPOL EXPERT SAS</t>
+          <t>Proyectos de Diseño y Construccion sas</t>
         </is>
       </c>
       <c r="E347" s="8" t="n">
@@ -16784,7 +16796,7 @@
         </is>
       </c>
       <c r="G347" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-electrica-comercial-bogota-1886756984", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-1886757049", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H347" s="6" t="inlineStr"/>
@@ -16803,7 +16815,7 @@
     <row r="348" ht="22" customHeight="1">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>366f049dd1eaf173</t>
+          <t>1072d76e2f18ea50</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
@@ -16813,12 +16825,12 @@
       </c>
       <c r="C348" s="3" t="inlineStr">
         <is>
-          <t>Civil engineering-in-training</t>
+          <t>Ingeniero civil</t>
         </is>
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>WSP COLOMBIA SAS</t>
+          <t>R2P SOLUCIONES Y CONSTRUCCIONES SAS</t>
         </is>
       </c>
       <c r="E348" s="8" t="n">
@@ -16830,7 +16842,7 @@
         </is>
       </c>
       <c r="G348" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/civil-engineeringintraining-1886759044", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-1886758475", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H348" s="6" t="inlineStr"/>
@@ -16849,7 +16861,7 @@
     <row r="349" ht="22" customHeight="1">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>555a755e56fc6a80</t>
+          <t>2c943591cc334f5a</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
@@ -16859,12 +16871,12 @@
       </c>
       <c r="C349" s="3" t="inlineStr">
         <is>
-          <t>Civil engineering-in-training</t>
+          <t>Ejecutivo/ade ingeniera</t>
         </is>
       </c>
       <c r="D349" s="3" t="inlineStr">
         <is>
-          <t>WSP COLOMBIA SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E349" s="8" t="n">
@@ -16876,7 +16888,7 @@
         </is>
       </c>
       <c r="G349" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/civil-engineeringintraining-1886758755", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-ade-ingeniera-1886752134", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H349" s="6" t="inlineStr"/>
@@ -16895,7 +16907,7 @@
     <row r="350" ht="22" customHeight="1">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>776483d4ec602e40</t>
+          <t>7d4067502e572780</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
@@ -16905,12 +16917,12 @@
       </c>
       <c r="C350" s="3" t="inlineStr">
         <is>
-          <t>Consultor senior sap pm - remoto colombia</t>
+          <t>Ingeniera de ventas - cali</t>
         </is>
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>TALYCAP GLOBAL SAS</t>
+          <t>PIPOL EXPERT SAS</t>
         </is>
       </c>
       <c r="E350" s="8" t="n">
@@ -16922,7 +16934,7 @@
         </is>
       </c>
       <c r="G350" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultor-senior-sap-pm-remoto-colombia-1886747903", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-de-ventas-cali-1886754430", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H350" s="6" t="inlineStr"/>
@@ -16941,7 +16953,7 @@
     <row r="351" ht="22" customHeight="1">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>b1cfe269bbc00011</t>
+          <t>a3a688084650de1c</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
@@ -16951,12 +16963,12 @@
       </c>
       <c r="C351" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de interventoría</t>
+          <t>Ingeniera comercial electrica - cali</t>
         </is>
       </c>
       <c r="D351" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>PIPOL EXPERT SAS</t>
         </is>
       </c>
       <c r="E351" s="8" t="n">
@@ -16968,7 +16980,7 @@
         </is>
       </c>
       <c r="G351" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-interventoria-1886751671", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-comercial-electrica-cali-1886752104", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H351" s="6" t="inlineStr"/>
@@ -16987,7 +16999,7 @@
     <row r="352" ht="22" customHeight="1">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>b7a3423e1ee1e624</t>
+          <t>359d47915a2e74e6</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
@@ -16997,12 +17009,12 @@
       </c>
       <c r="C352" s="3" t="inlineStr">
         <is>
-          <t>Especialista en urbanismo - proyecto vial</t>
+          <t>Supervisor civil - obra</t>
         </is>
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>INGEPLAN.CO SAS EMPRESA DE BENEFICIO E INTERES COLECTIVO BIC</t>
+          <t>CONCONCRETO S.A.</t>
         </is>
       </c>
       <c r="E352" s="8" t="n">
@@ -17014,7 +17026,7 @@
         </is>
       </c>
       <c r="G352" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-urbanismo-proyecto-vial-1886755827", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/supervisor-civil-obra-1886750435", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H352" s="6" t="inlineStr"/>
@@ -17033,7 +17045,7 @@
     <row r="353" ht="22" customHeight="1">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>fcb39d755657052e</t>
+          <t>78244d2897084f6a</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
@@ -17043,12 +17055,12 @@
       </c>
       <c r="C353" s="3" t="inlineStr">
         <is>
-          <t>Coordinador hseq</t>
+          <t>Ingeniera comercial sector industrial - cali</t>
         </is>
       </c>
       <c r="D353" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>PIPOL EXPERT SAS</t>
         </is>
       </c>
       <c r="E353" s="8" t="n">
@@ -17060,13 +17072,13 @@
         </is>
       </c>
       <c r="G353" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-1886747304", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-comercial-sector-industrial-cali-1886753949", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H353" s="6" t="inlineStr"/>
       <c r="I353" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J353" s="2" t="inlineStr">
@@ -17079,7 +17091,7 @@
     <row r="354" ht="22" customHeight="1">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>9e2f0c16f1a50983</t>
+          <t>a4d1239b8910f7cf</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
@@ -17089,12 +17101,12 @@
       </c>
       <c r="C354" s="3" t="inlineStr">
         <is>
-          <t>Coordinador hseq</t>
+          <t>Ingeniera electrica comercial - bogotá</t>
         </is>
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>PIPOL EXPERT SAS</t>
         </is>
       </c>
       <c r="E354" s="8" t="n">
@@ -17106,13 +17118,13 @@
         </is>
       </c>
       <c r="G354" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-1886764155", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-electrica-comercial-bogota-1886756984", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H354" s="6" t="inlineStr"/>
       <c r="I354" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J354" s="2" t="inlineStr">
@@ -17125,7 +17137,7 @@
     <row r="355" ht="22" customHeight="1">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>9d4d87a631d5e8b8</t>
+          <t>366f049dd1eaf173</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
@@ -17135,12 +17147,12 @@
       </c>
       <c r="C355" s="3" t="inlineStr">
         <is>
-          <t>Coordinador hseq</t>
+          <t>Civil engineering-in-training</t>
         </is>
       </c>
       <c r="D355" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>WSP COLOMBIA SAS</t>
         </is>
       </c>
       <c r="E355" s="8" t="n">
@@ -17152,13 +17164,13 @@
         </is>
       </c>
       <c r="G355" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-1886760733", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/civil-engineeringintraining-1886759044", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H355" s="6" t="inlineStr"/>
       <c r="I355" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J355" s="2" t="inlineStr">
@@ -17171,7 +17183,7 @@
     <row r="356" ht="22" customHeight="1">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>62d6690ef260f268</t>
+          <t>555a755e56fc6a80</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
@@ -17181,12 +17193,12 @@
       </c>
       <c r="C356" s="3" t="inlineStr">
         <is>
-          <t>Coordinador hseq cartagena</t>
+          <t>Civil engineering-in-training</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>APPLUS NORCONTROL COLOMBIA LTDA</t>
+          <t>WSP COLOMBIA SAS</t>
         </is>
       </c>
       <c r="E356" s="8" t="n">
@@ -17198,13 +17210,13 @@
         </is>
       </c>
       <c r="G356" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-cartagena-1886754661", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/civil-engineeringintraining-1886758755", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H356" s="6" t="inlineStr"/>
       <c r="I356" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J356" s="2" t="inlineStr">
@@ -17217,7 +17229,7 @@
     <row r="357" ht="22" customHeight="1">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>6e57e2acbfc11d12</t>
+          <t>776483d4ec602e40</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
@@ -17227,12 +17239,12 @@
       </c>
       <c r="C357" s="3" t="inlineStr">
         <is>
-          <t>Especialista sig</t>
+          <t>Consultor senior sap pm - remoto colombia</t>
         </is>
       </c>
       <c r="D357" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>TALYCAP GLOBAL SAS</t>
         </is>
       </c>
       <c r="E357" s="8" t="n">
@@ -17244,7 +17256,7 @@
         </is>
       </c>
       <c r="G357" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-sig-1886757094", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultor-senior-sap-pm-remoto-colombia-1886747903", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H357" s="6" t="inlineStr"/>
@@ -17263,7 +17275,7 @@
     <row r="358" ht="22" customHeight="1">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>11494a184e6f9290</t>
+          <t>b1cfe269bbc00011</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
@@ -17273,7 +17285,7 @@
       </c>
       <c r="C358" s="3" t="inlineStr">
         <is>
-          <t>Especialista en ingeniería civil - coordinador técnico</t>
+          <t>Coordinador de interventoría</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
@@ -17290,7 +17302,7 @@
         </is>
       </c>
       <c r="G358" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-ingenieria-civil-coordinador-tecnico-honduras-1886745304", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-interventoria-1886751671", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H358" s="6" t="inlineStr"/>
@@ -17309,7 +17321,7 @@
     <row r="359" ht="22" customHeight="1">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>327c6d2b54619849</t>
+          <t>b7a3423e1ee1e624</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
@@ -17319,12 +17331,12 @@
       </c>
       <c r="C359" s="3" t="inlineStr">
         <is>
-          <t>Especialista en psiquiatría</t>
+          <t>Especialista en urbanismo - proyecto vial</t>
         </is>
       </c>
       <c r="D359" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>INGEPLAN.CO SAS EMPRESA DE BENEFICIO E INTERES COLECTIVO BIC</t>
         </is>
       </c>
       <c r="E359" s="8" t="n">
@@ -17336,7 +17348,7 @@
         </is>
       </c>
       <c r="G359" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-psiquiatria-1886757353", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-urbanismo-proyecto-vial-1886755827", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H359" s="6" t="inlineStr"/>
@@ -17355,7 +17367,7 @@
     <row r="360" ht="22" customHeight="1">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>b637f33f588eb5ae</t>
+          <t>fcb39d755657052e</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
@@ -17365,7 +17377,7 @@
       </c>
       <c r="C360" s="3" t="inlineStr">
         <is>
-          <t>Especialista en diseño hospitalario</t>
+          <t>Coordinador hseq</t>
         </is>
       </c>
       <c r="D360" s="3" t="inlineStr">
@@ -17382,13 +17394,13 @@
         </is>
       </c>
       <c r="G360" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-diseno-hospitalario-disponibilidad-viajar-a-peru-1886747220", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-1886747304", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H360" s="6" t="inlineStr"/>
       <c r="I360" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J360" s="2" t="inlineStr">
@@ -17401,7 +17413,7 @@
     <row r="361" ht="22" customHeight="1">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>adcc2b47284b5d4d</t>
+          <t>9e2f0c16f1a50983</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
@@ -17411,12 +17423,12 @@
       </c>
       <c r="C361" s="3" t="inlineStr">
         <is>
-          <t>Analista de diseño e ingeniería de empaque - sector farmaceutico</t>
+          <t>Coordinador hseq</t>
         </is>
       </c>
       <c r="D361" s="3" t="inlineStr">
         <is>
-          <t>LABORATORIOS BUSSIE</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E361" s="8" t="n">
@@ -17428,13 +17440,13 @@
         </is>
       </c>
       <c r="G361" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-diseno-e-ingenieria-de-empaque-sector-farmaceutico-1886755492", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-1886764155", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H361" s="6" t="inlineStr"/>
       <c r="I361" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J361" s="2" t="inlineStr">
@@ -17447,7 +17459,7 @@
     <row r="362" ht="22" customHeight="1">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>3ec3d2d34753ff04</t>
+          <t>9d4d87a631d5e8b8</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
@@ -17457,12 +17469,12 @@
       </c>
       <c r="C362" s="3" t="inlineStr">
         <is>
-          <t>Especialista de diseño y arquitectura</t>
+          <t>Coordinador hseq</t>
         </is>
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>INTER RAPIDISIMO</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E362" s="8" t="n">
@@ -17474,13 +17486,13 @@
         </is>
       </c>
       <c r="G362" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-de-diseno-y-arquitectura-1886761909", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-1886760733", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H362" s="6" t="inlineStr"/>
       <c r="I362" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J362" s="2" t="inlineStr">
@@ -17493,7 +17505,7 @@
     <row r="363" ht="22" customHeight="1">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>4e917305e90b3efa</t>
+          <t>62d6690ef260f268</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
@@ -17503,12 +17515,12 @@
       </c>
       <c r="C363" s="3" t="inlineStr">
         <is>
-          <t>Especialista en geología</t>
+          <t>Coordinador hseq cartagena</t>
         </is>
       </c>
       <c r="D363" s="3" t="inlineStr">
         <is>
-          <t>INGEPLAN.CO SAS EMPRESA DE BENEFICIO E INTERES COLECTIVO BIC</t>
+          <t>APPLUS NORCONTROL COLOMBIA LTDA</t>
         </is>
       </c>
       <c r="E363" s="8" t="n">
@@ -17520,13 +17532,13 @@
         </is>
       </c>
       <c r="G363" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-geologia-1886761263", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-cartagena-1886754661", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H363" s="6" t="inlineStr"/>
       <c r="I363" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J363" s="2" t="inlineStr">
@@ -17539,7 +17551,7 @@
     <row r="364" ht="22" customHeight="1">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>1aef5476d70bbe42</t>
+          <t>6e57e2acbfc11d12</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
@@ -17549,12 +17561,12 @@
       </c>
       <c r="C364" s="3" t="inlineStr">
         <is>
-          <t>Especialista en geología</t>
+          <t>Especialista sig</t>
         </is>
       </c>
       <c r="D364" s="3" t="inlineStr">
         <is>
-          <t>INGEPLAN.CO SAS EMPRESA DE BENEFICIO E INTERES COLECTIVO BIC</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E364" s="8" t="n">
@@ -17566,7 +17578,7 @@
         </is>
       </c>
       <c r="G364" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-geologia-1886755729", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-sig-1886757094", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H364" s="6" t="inlineStr"/>
@@ -17585,7 +17597,7 @@
     <row r="365" ht="22" customHeight="1">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>b46df3b678599255</t>
+          <t>11494a184e6f9290</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
@@ -17595,7 +17607,7 @@
       </c>
       <c r="C365" s="3" t="inlineStr">
         <is>
-          <t>Especialista en estructuras</t>
+          <t>Especialista en ingeniería civil - coordinador técnico</t>
         </is>
       </c>
       <c r="D365" s="3" t="inlineStr">
@@ -17612,7 +17624,7 @@
         </is>
       </c>
       <c r="G365" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-estructuras-1886757080", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-ingenieria-civil-coordinador-tecnico-honduras-1886745304", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H365" s="6" t="inlineStr"/>
@@ -17631,7 +17643,7 @@
     <row r="366" ht="22" customHeight="1">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>935035bdfa2ae0b7</t>
+          <t>327c6d2b54619849</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
@@ -17641,12 +17653,12 @@
       </c>
       <c r="C366" s="3" t="inlineStr">
         <is>
-          <t>Especialista en gestión del riesgo</t>
+          <t>Especialista en psiquiatría</t>
         </is>
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>INGEPLAN.CO SAS EMPRESA DE BENEFICIO E INTERES COLECTIVO BIC</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E366" s="8" t="n">
@@ -17658,7 +17670,7 @@
         </is>
       </c>
       <c r="G366" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-gestion-del-riesgo-1886755709", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-psiquiatria-1886757353", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H366" s="6" t="inlineStr"/>
@@ -17677,7 +17689,7 @@
     <row r="367" ht="22" customHeight="1">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>14a1c964238340ba</t>
+          <t>b637f33f588eb5ae</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
@@ -17687,7 +17699,7 @@
       </c>
       <c r="C367" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero civil nivel v</t>
+          <t>Especialista en diseño hospitalario</t>
         </is>
       </c>
       <c r="D367" s="3" t="inlineStr">
@@ -17704,7 +17716,7 @@
         </is>
       </c>
       <c r="G367" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-nivel-v-1886758046", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-diseno-hospitalario-disponibilidad-viajar-a-peru-1886747220", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H367" s="6" t="inlineStr"/>
@@ -17723,7 +17735,7 @@
     <row r="368" ht="22" customHeight="1">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>740f61bdbaa69d0e</t>
+          <t>adcc2b47284b5d4d</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
@@ -17733,12 +17745,12 @@
       </c>
       <c r="C368" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de proyectos bilingüe</t>
+          <t>Analista de diseño e ingeniería de empaque - sector farmaceutico</t>
         </is>
       </c>
       <c r="D368" s="3" t="inlineStr">
         <is>
-          <t>EyS IT SAS</t>
+          <t>LABORATORIOS BUSSIE</t>
         </is>
       </c>
       <c r="E368" s="8" t="n">
@@ -17750,7 +17762,7 @@
         </is>
       </c>
       <c r="G368" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-bilingue-1886749343", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-diseno-e-ingenieria-de-empaque-sector-farmaceutico-1886755492", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H368" s="6" t="inlineStr"/>
@@ -17769,7 +17781,7 @@
     <row r="369" ht="22" customHeight="1">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>63ef229552018ccd</t>
+          <t>3ec3d2d34753ff04</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
@@ -17779,12 +17791,12 @@
       </c>
       <c r="C369" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de proyectos</t>
+          <t>Especialista de diseño y arquitectura</t>
         </is>
       </c>
       <c r="D369" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>INTER RAPIDISIMO</t>
         </is>
       </c>
       <c r="E369" s="8" t="n">
@@ -17796,7 +17808,7 @@
         </is>
       </c>
       <c r="G369" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-1886748647", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-de-diseno-y-arquitectura-1886761909", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H369" s="6" t="inlineStr"/>
@@ -17815,7 +17827,7 @@
     <row r="370" ht="22" customHeight="1">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>03750e25a7e1c016</t>
+          <t>4e917305e90b3efa</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
@@ -17825,12 +17837,12 @@
       </c>
       <c r="C370" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de proyectos inmobiliarios</t>
+          <t>Especialista en geología</t>
         </is>
       </c>
       <c r="D370" s="3" t="inlineStr">
         <is>
-          <t>GRUPO AR S.A.</t>
+          <t>INGEPLAN.CO SAS EMPRESA DE BENEFICIO E INTERES COLECTIVO BIC</t>
         </is>
       </c>
       <c r="E370" s="8" t="n">
@@ -17842,7 +17854,7 @@
         </is>
       </c>
       <c r="G370" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-inmobiliarios-1886745877", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-geologia-1886761263", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H370" s="6" t="inlineStr"/>
@@ -17861,7 +17873,7 @@
     <row r="371" ht="22" customHeight="1">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>5627e52731a73f27</t>
+          <t>1aef5476d70bbe42</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
@@ -17871,12 +17883,12 @@
       </c>
       <c r="C371" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de proyectos inmobiliarios</t>
+          <t>Especialista en geología</t>
         </is>
       </c>
       <c r="D371" s="3" t="inlineStr">
         <is>
-          <t>GRUPO AR S.A.</t>
+          <t>INGEPLAN.CO SAS EMPRESA DE BENEFICIO E INTERES COLECTIVO BIC</t>
         </is>
       </c>
       <c r="E371" s="8" t="n">
@@ -17888,7 +17900,7 @@
         </is>
       </c>
       <c r="G371" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-inmobiliarios-1886704948", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-geologia-1886755729", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H371" s="6" t="inlineStr"/>
@@ -17907,7 +17919,7 @@
     <row r="372" ht="22" customHeight="1">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>b6af0024900baff6</t>
+          <t>b46df3b678599255</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
@@ -17917,12 +17929,12 @@
       </c>
       <c r="C372" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero residente - ingeniero civil-cordoba</t>
+          <t>Especialista en estructuras</t>
         </is>
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
-          <t>OBCIPOL SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E372" s="8" t="n">
@@ -17934,7 +17946,7 @@
         </is>
       </c>
       <c r="G372" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-residente-ingeniero-civilcordoba-1886763488", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-estructuras-1886757080", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H372" s="6" t="inlineStr"/>
@@ -17953,7 +17965,7 @@
     <row r="373" ht="22" customHeight="1">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>2a0453695fa88728</t>
+          <t>935035bdfa2ae0b7</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
@@ -17963,12 +17975,12 @@
       </c>
       <c r="C373" s="3" t="inlineStr">
         <is>
-          <t>Profesional ingenieria mecanica</t>
+          <t>Especialista en gestión del riesgo</t>
         </is>
       </c>
       <c r="D373" s="3" t="inlineStr">
         <is>
-          <t>INZIGNIA CONSTRUCTION S.A</t>
+          <t>INGEPLAN.CO SAS EMPRESA DE BENEFICIO E INTERES COLECTIVO BIC</t>
         </is>
       </c>
       <c r="E373" s="8" t="n">
@@ -17980,7 +17992,7 @@
         </is>
       </c>
       <c r="G373" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/profesional-ingenieria-mecanica-1886767282", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-gestion-del-riesgo-1886755709", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H373" s="6" t="inlineStr"/>
@@ -17999,7 +18011,7 @@
     <row r="374" ht="22" customHeight="1">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>edfe98c543194667</t>
+          <t>14a1c964238340ba</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
@@ -18009,12 +18021,12 @@
       </c>
       <c r="C374" s="3" t="inlineStr">
         <is>
-          <t>Jefe de sst - nemocón - 1625991634-135</t>
+          <t>Ingeniero civil nivel v</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E374" s="8" t="n">
@@ -18026,13 +18038,13 @@
         </is>
       </c>
       <c r="G374" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/jefe-de-sst-nemocon-1625991634135-1886754873", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-nivel-v-1886758046", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H374" s="6" t="inlineStr"/>
       <c r="I374" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J374" s="2" t="inlineStr">
@@ -18045,7 +18057,7 @@
     <row r="375" ht="22" customHeight="1">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>6233e93ceb1dbeed</t>
+          <t>740f61bdbaa69d0e</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
@@ -18055,12 +18067,12 @@
       </c>
       <c r="C375" s="3" t="inlineStr">
         <is>
-          <t>Jefe de sst- nemocón</t>
+          <t>Coordinador de proyectos bilingüe</t>
         </is>
       </c>
       <c r="D375" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>EyS IT SAS</t>
         </is>
       </c>
       <c r="E375" s="8" t="n">
@@ -18072,13 +18084,13 @@
         </is>
       </c>
       <c r="G375" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/jefe-de-sst-nemocon-1886757757", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-bilingue-1886749343", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H375" s="6" t="inlineStr"/>
       <c r="I375" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J375" s="2" t="inlineStr">
@@ -18091,7 +18103,7 @@
     <row r="376" ht="22" customHeight="1">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>ce75aab7a32f36a3</t>
+          <t>63ef229552018ccd</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
@@ -18101,12 +18113,12 @@
       </c>
       <c r="C376" s="3" t="inlineStr">
         <is>
-          <t>Coordinador talento humano y sst - bogota- 1626427532-7</t>
+          <t>Coordinador de proyectos</t>
         </is>
       </c>
       <c r="D376" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E376" s="8" t="n">
@@ -18118,13 +18130,13 @@
         </is>
       </c>
       <c r="G376" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-talento-humano-y-sst-bogota-16264275327-1886753531", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-1886748647", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H376" s="6" t="inlineStr"/>
       <c r="I376" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J376" s="2" t="inlineStr">
@@ -18137,7 +18149,7 @@
     <row r="377" ht="22" customHeight="1">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>850731f7bb6cd73f</t>
+          <t>03750e25a7e1c016</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
@@ -18147,12 +18159,12 @@
       </c>
       <c r="C377" s="3" t="inlineStr">
         <is>
-          <t>Coordinador(a) de sst y medio ambiente</t>
+          <t>Coordinador de proyectos inmobiliarios</t>
         </is>
       </c>
       <c r="D377" s="3" t="inlineStr">
         <is>
-          <t>ATIEMPO S.A.S</t>
+          <t>GRUPO AR S.A.</t>
         </is>
       </c>
       <c r="E377" s="8" t="n">
@@ -18164,13 +18176,13 @@
         </is>
       </c>
       <c r="G377" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinadora-de-sst-y-medio-ambiente-1886759848", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-inmobiliarios-1886745877", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H377" s="6" t="inlineStr"/>
       <c r="I377" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J377" s="2" t="inlineStr">
@@ -18183,7 +18195,7 @@
     <row r="378" ht="22" customHeight="1">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>abaf8e513787b3f3</t>
+          <t>5627e52731a73f27</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
@@ -18193,12 +18205,12 @@
       </c>
       <c r="C378" s="3" t="inlineStr">
         <is>
-          <t>Coordinador pesv</t>
+          <t>Coordinador de proyectos inmobiliarios</t>
         </is>
       </c>
       <c r="D378" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>GRUPO AR S.A.</t>
         </is>
       </c>
       <c r="E378" s="8" t="n">
@@ -18210,13 +18222,13 @@
         </is>
       </c>
       <c r="G378" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-pesv-1886769643", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-inmobiliarios-1886704948", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H378" s="6" t="inlineStr"/>
       <c r="I378" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J378" s="2" t="inlineStr">
@@ -18229,7 +18241,7 @@
     <row r="379" ht="22" customHeight="1">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>9dcdf501e5912b88</t>
+          <t>b6af0024900baff6</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
@@ -18239,12 +18251,12 @@
       </c>
       <c r="C379" s="3" t="inlineStr">
         <is>
-          <t>Tecnico de obras civiles /girardot ref. 339166-82241</t>
+          <t>Ingeniero residente - ingeniero civil-cordoba</t>
         </is>
       </c>
       <c r="D379" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>OBCIPOL SAS</t>
         </is>
       </c>
       <c r="E379" s="8" t="n">
@@ -18256,7 +18268,7 @@
         </is>
       </c>
       <c r="G379" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/tecnico-de-obras-civiles-girardot-ref-33916682241-1886747302", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-residente-ingeniero-civilcordoba-1886763488", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H379" s="6" t="inlineStr"/>
@@ -18275,7 +18287,7 @@
     <row r="380" ht="22" customHeight="1">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>693b8a076a888f67</t>
+          <t>2a0453695fa88728</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
@@ -18285,12 +18297,12 @@
       </c>
       <c r="C380" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero civil - especializacion en estructuras</t>
+          <t>Profesional ingenieria mecanica</t>
         </is>
       </c>
       <c r="D380" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>INZIGNIA CONSTRUCTION S.A</t>
         </is>
       </c>
       <c r="E380" s="8" t="n">
@@ -18302,7 +18314,7 @@
         </is>
       </c>
       <c r="G380" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-especializacion-en-estructuras-1886766956", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/profesional-ingenieria-mecanica-1886767282", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H380" s="6" t="inlineStr"/>
@@ -18321,7 +18333,7 @@
     <row r="381" ht="22" customHeight="1">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>13bc527565632878</t>
+          <t>edfe98c543194667</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
@@ -18331,12 +18343,12 @@
       </c>
       <c r="C381" s="3" t="inlineStr">
         <is>
-          <t>Tecnico en contratacion de obra civil bogota</t>
+          <t>Jefe de sst - nemocón - 1625991634-135</t>
         </is>
       </c>
       <c r="D381" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E381" s="8" t="n">
@@ -18348,13 +18360,13 @@
         </is>
       </c>
       <c r="G381" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/tecnico-en-contratacion-de-obra-civil-bogota-1886759693", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/jefe-de-sst-nemocon-1625991634135-1886754873", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H381" s="6" t="inlineStr"/>
       <c r="I381" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J381" s="2" t="inlineStr">
@@ -18367,7 +18379,7 @@
     <row r="382" ht="22" customHeight="1">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>6ccccd3a1ba05f7f</t>
+          <t>6233e93ceb1dbeed</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
@@ -18377,12 +18389,12 @@
       </c>
       <c r="C382" s="3" t="inlineStr">
         <is>
-          <t>14561-especialista interventoria-bogota</t>
+          <t>Jefe de sst- nemocón</t>
         </is>
       </c>
       <c r="D382" s="3" t="inlineStr">
         <is>
-          <t>APPLUS NORCONTROL COLOMBIA LTDA</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E382" s="8" t="n">
@@ -18394,13 +18406,13 @@
         </is>
       </c>
       <c r="G382" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/14561especialista-interventoriabogota-1886768886", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/jefe-de-sst-nemocon-1886757757", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H382" s="6" t="inlineStr"/>
       <c r="I382" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J382" s="2" t="inlineStr">
@@ -18413,7 +18425,7 @@
     <row r="383" ht="22" customHeight="1">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>8ad0c11c4f07472e</t>
+          <t>ce75aab7a32f36a3</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
@@ -18423,12 +18435,12 @@
       </c>
       <c r="C383" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero Civil / Terracerías</t>
+          <t>Coordinador talento humano y sst - bogota- 1626427532-7</t>
         </is>
       </c>
       <c r="D383" s="3" t="inlineStr">
         <is>
-          <t>EOSOL</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E383" s="8" t="n">
@@ -18440,13 +18452,13 @@
         </is>
       </c>
       <c r="G383" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-civil-terracer%C3%ADas-at-eosol-4445793534", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-talento-humano-y-sst-bogota-16264275327-1886753531", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H383" s="6" t="inlineStr"/>
       <c r="I383" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J383" s="2" t="inlineStr">
@@ -18459,7 +18471,7 @@
     <row r="384" ht="22" customHeight="1">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>ed46085f88d06bf5</t>
+          <t>850731f7bb6cd73f</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
@@ -18469,12 +18481,12 @@
       </c>
       <c r="C384" s="3" t="inlineStr">
         <is>
-          <t>Supervisor Civil</t>
+          <t>Coordinador(a) de sst y medio ambiente</t>
         </is>
       </c>
       <c r="D384" s="3" t="inlineStr">
         <is>
-          <t>EOSOL</t>
+          <t>ATIEMPO S.A.S</t>
         </is>
       </c>
       <c r="E384" s="8" t="n">
@@ -18486,13 +18498,13 @@
         </is>
       </c>
       <c r="G384" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/supervisor-civil-at-eosol-4442238964", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinadora-de-sst-y-medio-ambiente-1886759848", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H384" s="6" t="inlineStr"/>
       <c r="I384" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J384" s="2" t="inlineStr">
@@ -18505,7 +18517,7 @@
     <row r="385" ht="22" customHeight="1">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>dc949850c44ae2c9</t>
+          <t>abaf8e513787b3f3</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
@@ -18515,12 +18527,12 @@
       </c>
       <c r="C385" s="3" t="inlineStr">
         <is>
-          <t>Civil Engineer</t>
+          <t>Coordinador pesv</t>
         </is>
       </c>
       <c r="D385" s="3" t="inlineStr">
         <is>
-          <t>Cresta</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E385" s="8" t="n">
@@ -18532,13 +18544,13 @@
         </is>
       </c>
       <c r="G385" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineer-at-cresta-4465582487", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-pesv-1886769643", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H385" s="6" t="inlineStr"/>
       <c r="I385" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J385" s="2" t="inlineStr">
@@ -18551,7 +18563,7 @@
     <row r="386" ht="22" customHeight="1">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>4ad1a5acabdb8ad3</t>
+          <t>9dcdf501e5912b88</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
@@ -18561,12 +18573,12 @@
       </c>
       <c r="C386" s="3" t="inlineStr">
         <is>
-          <t>Civil BIM Specialist</t>
+          <t>Tecnico de obras civiles /girardot ref. 339166-82241</t>
         </is>
       </c>
       <c r="D386" s="3" t="inlineStr">
         <is>
-          <t>ENG</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E386" s="8" t="n">
@@ -18578,7 +18590,7 @@
         </is>
       </c>
       <c r="G386" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-bim-specialist-at-eng-4469886677", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/tecnico-de-obras-civiles-girardot-ref-33916682241-1886747302", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H386" s="6" t="inlineStr"/>
@@ -18597,7 +18609,7 @@
     <row r="387" ht="22" customHeight="1">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>5ebaba0a0c9927fb</t>
+          <t>693b8a076a888f67</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
@@ -18607,12 +18619,12 @@
       </c>
       <c r="C387" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero/a Civil-Estructuras Hormigón/Acero</t>
+          <t>Ingeniero civil - especializacion en estructuras</t>
         </is>
       </c>
       <c r="D387" s="3" t="inlineStr">
         <is>
-          <t>IDOM Consulting, Engineering, Architecture</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E387" s="8" t="n">
@@ -18624,7 +18636,7 @@
         </is>
       </c>
       <c r="G387" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-civil-estructuras-hormig%C3%B3n-acero-at-idom-consulting-engineering-architecture-4462998187", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-especializacion-en-estructuras-1886766956", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H387" s="6" t="inlineStr"/>
@@ -18643,7 +18655,7 @@
     <row r="388" ht="22" customHeight="1">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>5c954c66c2c9d655</t>
+          <t>13bc527565632878</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
@@ -18653,12 +18665,12 @@
       </c>
       <c r="C388" s="3" t="inlineStr">
         <is>
-          <t>Civil Engineering-in-Training</t>
+          <t>Tecnico en contratacion de obra civil bogota</t>
         </is>
       </c>
       <c r="D388" s="3" t="inlineStr">
         <is>
-          <t>WSP en Colombia</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E388" s="8" t="n">
@@ -18670,7 +18682,7 @@
         </is>
       </c>
       <c r="G388" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineering-in-training-french-at-wsp-en-colombia-4458430104", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/tecnico-en-contratacion-de-obra-civil-bogota-1886759693", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H388" s="6" t="inlineStr"/>
@@ -18689,7 +18701,7 @@
     <row r="389" ht="22" customHeight="1">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>571ae2aa81fa07b5</t>
+          <t>6ccccd3a1ba05f7f</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
@@ -18699,12 +18711,12 @@
       </c>
       <c r="C389" s="3" t="inlineStr">
         <is>
-          <t>Civil Engineering-in-Training</t>
+          <t>14561-especialista interventoria-bogota</t>
         </is>
       </c>
       <c r="D389" s="3" t="inlineStr">
         <is>
-          <t>WSP en Colombia</t>
+          <t>APPLUS NORCONTROL COLOMBIA LTDA</t>
         </is>
       </c>
       <c r="E389" s="8" t="n">
@@ -18716,7 +18728,7 @@
         </is>
       </c>
       <c r="G389" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineering-in-training-at-wsp-en-colombia-4458027784", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/14561especialista-interventoriabogota-1886768886", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H389" s="6" t="inlineStr"/>
@@ -18735,7 +18747,7 @@
     <row r="390" ht="22" customHeight="1">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>d94bcf92627b7b99</t>
+          <t>8ad0c11c4f07472e</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
@@ -18745,12 +18757,12 @@
       </c>
       <c r="C390" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero civil</t>
+          <t>Ingeniero Civil / Terracerías</t>
         </is>
       </c>
       <c r="D390" s="3" t="inlineStr">
         <is>
-          <t>HMV Ingenieros</t>
+          <t>EOSOL</t>
         </is>
       </c>
       <c r="E390" s="8" t="n">
@@ -18762,7 +18774,7 @@
         </is>
       </c>
       <c r="G390" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-civil-at-hmv-ingenieros-4461715824", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-civil-terracer%C3%ADas-at-eosol-4445793534", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H390" s="6" t="inlineStr"/>
@@ -18781,7 +18793,7 @@
     <row r="391" ht="22" customHeight="1">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>1be0a8e56fa4736b</t>
+          <t>ed46085f88d06bf5</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
@@ -18791,12 +18803,12 @@
       </c>
       <c r="C391" s="3" t="inlineStr">
         <is>
-          <t>Civil Engineer</t>
+          <t>Supervisor Civil</t>
         </is>
       </c>
       <c r="D391" s="3" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>EOSOL</t>
         </is>
       </c>
       <c r="E391" s="8" t="n">
@@ -18808,7 +18820,7 @@
         </is>
       </c>
       <c r="G391" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineer-at-wood-4418961778", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/supervisor-civil-at-eosol-4442238964", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H391" s="6" t="inlineStr"/>
@@ -18827,7 +18839,7 @@
     <row r="392" ht="22" customHeight="1">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>825c4e246cbd6b6b</t>
+          <t>dc949850c44ae2c9</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
@@ -18837,12 +18849,12 @@
       </c>
       <c r="C392" s="3" t="inlineStr">
         <is>
-          <t>Civil Engineering Expert</t>
+          <t>Civil Engineer</t>
         </is>
       </c>
       <c r="D392" s="3" t="inlineStr">
         <is>
-          <t>Anyone AI</t>
+          <t>Cresta</t>
         </is>
       </c>
       <c r="E392" s="8" t="n">
@@ -18854,7 +18866,7 @@
         </is>
       </c>
       <c r="G392" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineering-expert-at-anyone-ai-4462461832", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineer-at-cresta-4465582487", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H392" s="6" t="inlineStr"/>
@@ -18873,7 +18885,7 @@
     <row r="393" ht="22" customHeight="1">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>76740179a82340ae</t>
+          <t>4ad1a5acabdb8ad3</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
@@ -18883,12 +18895,12 @@
       </c>
       <c r="C393" s="3" t="inlineStr">
         <is>
-          <t>Profesional en Ingeniería Civil</t>
+          <t>Civil BIM Specialist</t>
         </is>
       </c>
       <c r="D393" s="3" t="inlineStr">
         <is>
-          <t>CMH Colombia</t>
+          <t>ENG</t>
         </is>
       </c>
       <c r="E393" s="8" t="n">
@@ -18900,7 +18912,7 @@
         </is>
       </c>
       <c r="G393" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/profesional-en-ingenier%C3%ADa-civil-at-minerales-c%C3%B3rdoba-4450022471", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-bim-specialist-at-eng-4469886677", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H393" s="6" t="inlineStr"/>
@@ -18919,7 +18931,7 @@
     <row r="394" ht="22" customHeight="1">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>5bea04b9e734c2fc</t>
+          <t>5ebaba0a0c9927fb</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
@@ -18929,12 +18941,12 @@
       </c>
       <c r="C394" s="3" t="inlineStr">
         <is>
-          <t>Coordinador HSEQ</t>
+          <t>Ingeniero/a Civil-Estructuras Hormigón/Acero</t>
         </is>
       </c>
       <c r="D394" s="3" t="inlineStr">
         <is>
-          <t>ASSEMTEC</t>
+          <t>IDOM Consulting, Engineering, Architecture</t>
         </is>
       </c>
       <c r="E394" s="8" t="n">
@@ -18946,13 +18958,13 @@
         </is>
       </c>
       <c r="G394" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-hseq-at-assemtec-4457664932", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-civil-estructuras-hormig%C3%B3n-acero-at-idom-consulting-engineering-architecture-4462998187", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H394" s="6" t="inlineStr"/>
       <c r="I394" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J394" s="2" t="inlineStr">
@@ -18965,7 +18977,7 @@
     <row r="395" ht="22" customHeight="1">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>6ba6bae2d7bfb226</t>
+          <t>5c954c66c2c9d655</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
@@ -18975,12 +18987,12 @@
       </c>
       <c r="C395" s="3" t="inlineStr">
         <is>
-          <t>Inspector SST con Licencia, Coordinador de Alturas</t>
+          <t>Civil Engineering-in-Training</t>
         </is>
       </c>
       <c r="D395" s="3" t="inlineStr">
         <is>
-          <t>Asertempo Colombia S.A.S</t>
+          <t>WSP en Colombia</t>
         </is>
       </c>
       <c r="E395" s="8" t="n">
@@ -18992,13 +19004,13 @@
         </is>
       </c>
       <c r="G395" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/inspector-sst-con-licencia-coordinador-de-alturas-at-asertempo-colombia-s-a-s-4464408367", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineering-in-training-french-at-wsp-en-colombia-4458430104", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H395" s="6" t="inlineStr"/>
       <c r="I395" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J395" s="2" t="inlineStr">
@@ -19011,7 +19023,7 @@
     <row r="396" ht="22" customHeight="1">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>0df4a63a82189896</t>
+          <t>571ae2aa81fa07b5</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
@@ -19021,12 +19033,12 @@
       </c>
       <c r="C396" s="3" t="inlineStr">
         <is>
-          <t>Especialista en Salud y Seguridad en el trabajo con especialización en medio Ambiente</t>
+          <t>Civil Engineering-in-Training</t>
         </is>
       </c>
       <c r="D396" s="3" t="inlineStr">
         <is>
-          <t>Dextera IT Services</t>
+          <t>WSP en Colombia</t>
         </is>
       </c>
       <c r="E396" s="8" t="n">
@@ -19038,7 +19050,7 @@
         </is>
       </c>
       <c r="G396" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/especialista-en-salud-y-seguridad-en-el-trabajo-con-especializaci%C3%B3n-en-medio-ambiente-at-dextera-it-services-4464024362", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineering-in-training-at-wsp-en-colombia-4458027784", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H396" s="6" t="inlineStr"/>
@@ -19057,7 +19069,7 @@
     <row r="397" ht="22" customHeight="1">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>e8e3c75915d1945c</t>
+          <t>d94bcf92627b7b99</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
@@ -19067,12 +19079,12 @@
       </c>
       <c r="C397" s="3" t="inlineStr">
         <is>
-          <t>Coordinador (a) profesional HSEQ</t>
+          <t>Ingeniero civil</t>
         </is>
       </c>
       <c r="D397" s="3" t="inlineStr">
         <is>
-          <t>SD SAS</t>
+          <t>HMV Ingenieros</t>
         </is>
       </c>
       <c r="E397" s="8" t="n">
@@ -19084,13 +19096,13 @@
         </is>
       </c>
       <c r="G397" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-profesional-hseq-at-sd-sas-4444939872", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-civil-at-hmv-ingenieros-4461715824", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H397" s="6" t="inlineStr"/>
       <c r="I397" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J397" s="2" t="inlineStr">
@@ -19103,7 +19115,7 @@
     <row r="398" ht="22" customHeight="1">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>fb37fc1bf485e650</t>
+          <t>1be0a8e56fa4736b</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
@@ -19113,12 +19125,12 @@
       </c>
       <c r="C398" s="3" t="inlineStr">
         <is>
-          <t>Técnico de trazado especialista en ISTRAM</t>
+          <t>Civil Engineer</t>
         </is>
       </c>
       <c r="D398" s="3" t="inlineStr">
         <is>
-          <t>EADIC</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="E398" s="8" t="n">
@@ -19130,7 +19142,7 @@
         </is>
       </c>
       <c r="G398" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/t%C3%A9cnico-de-trazado-especialista-en-istram-at-eadic-4468780158", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineer-at-wood-4418961778", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H398" s="6" t="inlineStr"/>
@@ -19149,7 +19161,7 @@
     <row r="399" ht="22" customHeight="1">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>0f01a66eb85a1ffd</t>
+          <t>825c4e246cbd6b6b</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
@@ -19159,12 +19171,12 @@
       </c>
       <c r="C399" s="3" t="inlineStr">
         <is>
-          <t>AUXILIAR MODELADOR BIM Y DIBUJANTE EN INGENIERÍA CIVIL</t>
+          <t>Civil Engineering Expert</t>
         </is>
       </c>
       <c r="D399" s="3" t="inlineStr">
         <is>
-          <t>Antea Group España y Latinoamérica</t>
+          <t>Anyone AI</t>
         </is>
       </c>
       <c r="E399" s="8" t="n">
@@ -19176,7 +19188,7 @@
         </is>
       </c>
       <c r="G399" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-modelador-bim-y-dibujante-en-ingenier%C3%ADa-civil-at-antea-group-espa%C3%B1a-y-latinoam%C3%A9rica-4467605615", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineering-expert-at-anyone-ai-4462461832", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H399" s="6" t="inlineStr"/>
@@ -19195,7 +19207,7 @@
     <row r="400" ht="22" customHeight="1">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>cba614af5ce1fc3a</t>
+          <t>76740179a82340ae</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
@@ -19205,12 +19217,12 @@
       </c>
       <c r="C400" s="3" t="inlineStr">
         <is>
-          <t>Principal Pavement Engineer - Linear Infrastructure &amp; Site Civils</t>
+          <t>Profesional en Ingeniería Civil</t>
         </is>
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>CMH Colombia</t>
         </is>
       </c>
       <c r="E400" s="8" t="n">
@@ -19222,7 +19234,7 @@
         </is>
       </c>
       <c r="G400" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/principal-pavement-engineer-linear-infrastructure-site-civils-at-aecom-4403657428", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/profesional-en-ingenier%C3%ADa-civil-at-minerales-c%C3%B3rdoba-4450022471", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H400" s="6" t="inlineStr"/>
@@ -19241,7 +19253,7 @@
     <row r="401" ht="22" customHeight="1">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>2bafc4e5eb29746b</t>
+          <t>5bea04b9e734c2fc</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
@@ -19251,12 +19263,12 @@
       </c>
       <c r="C401" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero/a Geotécnico/a Senior</t>
+          <t>Coordinador HSEQ</t>
         </is>
       </c>
       <c r="D401" s="3" t="inlineStr">
         <is>
-          <t>IDOM Consulting, Engineering, Architecture</t>
+          <t>ASSEMTEC</t>
         </is>
       </c>
       <c r="E401" s="8" t="n">
@@ -19268,13 +19280,13 @@
         </is>
       </c>
       <c r="G401" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-geot%C3%A9cnico-a-senior-at-idom-consulting-engineering-architecture-4467729578", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-hseq-at-assemtec-4457664932", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H401" s="6" t="inlineStr"/>
       <c r="I401" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J401" s="2" t="inlineStr">
@@ -19287,7 +19299,7 @@
     <row r="402" ht="22" customHeight="1">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>f3290f3c2a2d0061</t>
+          <t>6ba6bae2d7bfb226</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
@@ -19297,12 +19309,12 @@
       </c>
       <c r="C402" s="3" t="inlineStr">
         <is>
-          <t>Engenheiro Civil - Lisboa</t>
+          <t>Inspector SST con Licencia, Coordinador de Alturas</t>
         </is>
       </c>
       <c r="D402" s="3" t="inlineStr">
         <is>
-          <t>DDN GERENCIAMENTO</t>
+          <t>Asertempo Colombia S.A.S</t>
         </is>
       </c>
       <c r="E402" s="8" t="n">
@@ -19314,13 +19326,13 @@
         </is>
       </c>
       <c r="G402" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/engenheiro-civil-lisboa-at-ddn-gerenciamento-4468408791", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/inspector-sst-con-licencia-coordinador-de-alturas-at-asertempo-colombia-s-a-s-4464408367", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H402" s="6" t="inlineStr"/>
       <c r="I402" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J402" s="2" t="inlineStr">
@@ -19333,7 +19345,7 @@
     <row r="403" ht="22" customHeight="1">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>d2feccf91b9b1f0b</t>
+          <t>0df4a63a82189896</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
@@ -19343,12 +19355,12 @@
       </c>
       <c r="C403" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero/a Civil especialista en Talleres y Patios Ferroviarios</t>
+          <t>Especialista en Salud y Seguridad en el trabajo con especialización en medio Ambiente</t>
         </is>
       </c>
       <c r="D403" s="3" t="inlineStr">
         <is>
-          <t>IDOM Consulting, Engineering, Architecture</t>
+          <t>Dextera IT Services</t>
         </is>
       </c>
       <c r="E403" s="8" t="n">
@@ -19360,7 +19372,7 @@
         </is>
       </c>
       <c r="G403" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-civil-especialista-en-talleres-y-patios-ferroviarios-at-idom-consulting-engineering-architecture-4443713908", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/especialista-en-salud-y-seguridad-en-el-trabajo-con-especializaci%C3%B3n-en-medio-ambiente-at-dextera-it-services-4464024362", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H403" s="6" t="inlineStr"/>
@@ -19379,7 +19391,7 @@
     <row r="404" ht="22" customHeight="1">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>152ea7f07f195fc8</t>
+          <t>e8e3c75915d1945c</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
@@ -19389,12 +19401,12 @@
       </c>
       <c r="C404" s="3" t="inlineStr">
         <is>
-          <t>COORDINADOR DE INTERVENTORÍA-NIVEL 1 SECTOR HIDROCARBUROS</t>
+          <t>Coordinador (a) profesional HSEQ</t>
         </is>
       </c>
       <c r="D404" s="3" t="inlineStr">
         <is>
-          <t>Centro de Empleo y Talento</t>
+          <t>SD SAS</t>
         </is>
       </c>
       <c r="E404" s="8" t="n">
@@ -19406,13 +19418,13 @@
         </is>
       </c>
       <c r="G404" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-de-interventor%C3%ADa-nivel-1-sector-hidrocarburos-at-centro-de-empleo-y-talento-4468030406", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-profesional-hseq-at-sd-sas-4444939872", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H404" s="6" t="inlineStr"/>
       <c r="I404" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J404" s="2" t="inlineStr">
@@ -19425,7 +19437,7 @@
     <row r="405" ht="22" customHeight="1">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>b3dd7e9d8f53fb27</t>
+          <t>fb37fc1bf485e650</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
@@ -19435,12 +19447,12 @@
       </c>
       <c r="C405" s="3" t="inlineStr">
         <is>
-          <t>Consultor (Desarrollador) Senior Appian</t>
+          <t>Técnico de trazado especialista en ISTRAM</t>
         </is>
       </c>
       <c r="D405" s="3" t="inlineStr">
         <is>
-          <t>VASS LATAM</t>
+          <t>EADIC</t>
         </is>
       </c>
       <c r="E405" s="8" t="n">
@@ -19452,7 +19464,7 @@
         </is>
       </c>
       <c r="G405" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/consultor-desarrollador-senior-appian-at-vass-latam-4458249659", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/t%C3%A9cnico-de-trazado-especialista-en-istram-at-eadic-4468780158", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H405" s="6" t="inlineStr"/>
@@ -19471,7 +19483,7 @@
     <row r="406" ht="22" customHeight="1">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>0f895f69320d7d8d</t>
+          <t>0f01a66eb85a1ffd</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
@@ -19481,12 +19493,12 @@
       </c>
       <c r="C406" s="3" t="inlineStr">
         <is>
-          <t>Coordinador hse Cartagena</t>
+          <t>AUXILIAR MODELADOR BIM Y DIBUJANTE EN INGENIERÍA CIVIL</t>
         </is>
       </c>
       <c r="D406" s="3" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONTEJO SAS</t>
+          <t>Antea Group España y Latinoamérica</t>
         </is>
       </c>
       <c r="E406" s="8" t="n">
@@ -19498,13 +19510,13 @@
         </is>
       </c>
       <c r="G406" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-hse-cartagena-at-transportes-montejo-sas-4458746462", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-modelador-bim-y-dibujante-en-ingenier%C3%ADa-civil-at-antea-group-espa%C3%B1a-y-latinoam%C3%A9rica-4467605615", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H406" s="6" t="inlineStr"/>
       <c r="I406" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J406" s="2" t="inlineStr">
@@ -19517,7 +19529,7 @@
     <row r="407" ht="22" customHeight="1">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>b86d50ad2dd5f642</t>
+          <t>cba614af5ce1fc3a</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
@@ -19527,12 +19539,12 @@
       </c>
       <c r="C407" s="3" t="inlineStr">
         <is>
-          <t>Coordinador Regional SIG/ SST</t>
+          <t>Principal Pavement Engineer - Linear Infrastructure &amp; Site Civils</t>
         </is>
       </c>
       <c r="D407" s="3" t="inlineStr">
         <is>
-          <t>Interaseo S.A.S. E.S.P.</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="E407" s="8" t="n">
@@ -19544,13 +19556,13 @@
         </is>
       </c>
       <c r="G407" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-regional-sig-sst-at-interaseo-s-a-s-e-s-p-4459088040", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/principal-pavement-engineer-linear-infrastructure-site-civils-at-aecom-4403657428", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H407" s="6" t="inlineStr"/>
       <c r="I407" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J407" s="2" t="inlineStr">
@@ -19563,7 +19575,7 @@
     <row r="408" ht="22" customHeight="1">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>506296811a5a9cbb</t>
+          <t>2bafc4e5eb29746b</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
@@ -19573,12 +19585,12 @@
       </c>
       <c r="C408" s="3" t="inlineStr">
         <is>
-          <t>Coordinador/a de SST</t>
+          <t>Ingeniero/a Geotécnico/a Senior</t>
         </is>
       </c>
       <c r="D408" s="3" t="inlineStr">
         <is>
-          <t>Estelar Food S.A.S</t>
+          <t>IDOM Consulting, Engineering, Architecture</t>
         </is>
       </c>
       <c r="E408" s="8" t="n">
@@ -19590,13 +19602,13 @@
         </is>
       </c>
       <c r="G408" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-de-sst-at-estelar-food-s-a-s-4462115593", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-geot%C3%A9cnico-a-senior-at-idom-consulting-engineering-architecture-4467729578", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H408" s="6" t="inlineStr"/>
       <c r="I408" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J408" s="2" t="inlineStr">
@@ -19609,7 +19621,7 @@
     <row r="409" ht="22" customHeight="1">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>0e4b8eed7f32714e</t>
+          <t>f3290f3c2a2d0061</t>
         </is>
       </c>
       <c r="B409" s="2" t="inlineStr">
@@ -19619,12 +19631,12 @@
       </c>
       <c r="C409" s="3" t="inlineStr">
         <is>
-          <t>coordinador de Seguridad y Salud en el Trabajo</t>
+          <t>Engenheiro Civil - Lisboa</t>
         </is>
       </c>
       <c r="D409" s="3" t="inlineStr">
         <is>
-          <t>Asertempo Colombia S.A.S</t>
+          <t>DDN GERENCIAMENTO</t>
         </is>
       </c>
       <c r="E409" s="8" t="n">
@@ -19636,13 +19648,13 @@
         </is>
       </c>
       <c r="G409" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-de-seguridad-y-salud-en-el-trabajo-at-asertempo-colombia-s-a-s-4461723686", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/engenheiro-civil-lisboa-at-ddn-gerenciamento-4468408791", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H409" s="6" t="inlineStr"/>
       <c r="I409" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J409" s="2" t="inlineStr">
@@ -19655,7 +19667,7 @@
     <row r="410" ht="22" customHeight="1">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>aa2882af3c61095b</t>
+          <t>d2feccf91b9b1f0b</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
@@ -19665,12 +19677,12 @@
       </c>
       <c r="C410" s="3" t="inlineStr">
         <is>
-          <t>Coordinador (a) SST / APH - Marmato</t>
+          <t>Ingeniero/a Civil especialista en Talleres y Patios Ferroviarios</t>
         </is>
       </c>
       <c r="D410" s="3" t="inlineStr">
         <is>
-          <t>Aris Mining Colombia</t>
+          <t>IDOM Consulting, Engineering, Architecture</t>
         </is>
       </c>
       <c r="E410" s="8" t="n">
@@ -19682,13 +19694,13 @@
         </is>
       </c>
       <c r="G410" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-sst-aph-marmato-at-aris-mining-colombia-4448929810", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-civil-especialista-en-talleres-y-patios-ferroviarios-at-idom-consulting-engineering-architecture-4443713908", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H410" s="6" t="inlineStr"/>
       <c r="I410" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J410" s="2" t="inlineStr">
@@ -19701,7 +19713,7 @@
     <row r="411" ht="22" customHeight="1">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>26cff43f13982962</t>
+          <t>152ea7f07f195fc8</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
@@ -19711,12 +19723,12 @@
       </c>
       <c r="C411" s="3" t="inlineStr">
         <is>
-          <t>Consultor(a) Senior SOX TI</t>
+          <t>COORDINADOR DE INTERVENTORÍA-NIVEL 1 SECTOR HIDROCARBUROS</t>
         </is>
       </c>
       <c r="D411" s="3" t="inlineStr">
         <is>
-          <t>Hitss Colombia</t>
+          <t>Centro de Empleo y Talento</t>
         </is>
       </c>
       <c r="E411" s="8" t="n">
@@ -19728,7 +19740,7 @@
         </is>
       </c>
       <c r="G411" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/consultor-a-senior-sox-ti-at-hitss-colombia-4460766744", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-de-interventor%C3%ADa-nivel-1-sector-hidrocarburos-at-centro-de-empleo-y-talento-4468030406", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H411" s="6" t="inlineStr"/>
@@ -19747,7 +19759,7 @@
     <row r="412" ht="22" customHeight="1">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>87e367215ed55502</t>
+          <t>b3dd7e9d8f53fb27</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
@@ -19757,12 +19769,12 @@
       </c>
       <c r="C412" s="3" t="inlineStr">
         <is>
-          <t>Consultor(a) Senior Auditoría Interna</t>
+          <t>Consultor (Desarrollador) Senior Appian</t>
         </is>
       </c>
       <c r="D412" s="3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>VASS LATAM</t>
         </is>
       </c>
       <c r="E412" s="8" t="n">
@@ -19774,7 +19786,7 @@
         </is>
       </c>
       <c r="G412" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/consultor-a-senior-auditor%C3%ADa-interna-at-deloitte-4462090075", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/consultor-desarrollador-senior-appian-at-vass-latam-4458249659", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H412" s="6" t="inlineStr"/>
@@ -19793,7 +19805,7 @@
     <row r="413" ht="22" customHeight="1">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>e2e525b51bbd0e5e</t>
+          <t>0f895f69320d7d8d</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
@@ -19803,12 +19815,12 @@
       </c>
       <c r="C413" s="3" t="inlineStr">
         <is>
-          <t>Coordinador/a de Salud y Bienestar (HSE) Latam</t>
+          <t>Coordinador hse Cartagena</t>
         </is>
       </c>
       <c r="D413" s="3" t="inlineStr">
         <is>
-          <t>Aqualia</t>
+          <t>TRANSPORTES MONTEJO SAS</t>
         </is>
       </c>
       <c r="E413" s="8" t="n">
@@ -19820,7 +19832,7 @@
         </is>
       </c>
       <c r="G413" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-de-salud-y-bienestar-hse-latam-at-aqualia-4463977352", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-hse-cartagena-at-transportes-montejo-sas-4458746462", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H413" s="6" t="inlineStr"/>
@@ -19839,7 +19851,7 @@
     <row r="414" ht="22" customHeight="1">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>8ef614b651dfe9d9</t>
+          <t>b86d50ad2dd5f642</t>
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
@@ -19849,12 +19861,12 @@
       </c>
       <c r="C414" s="3" t="inlineStr">
         <is>
-          <t>Lead Civil Site Engineer</t>
+          <t>Coordinador Regional SIG/ SST</t>
         </is>
       </c>
       <c r="D414" s="3" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Interaseo S.A.S. E.S.P.</t>
         </is>
       </c>
       <c r="E414" s="8" t="n">
@@ -19866,13 +19878,13 @@
         </is>
       </c>
       <c r="G414" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/lead-civil-site-engineer-at-aecom-4468059409", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-regional-sig-sst-at-interaseo-s-a-s-e-s-p-4459088040", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H414" s="6" t="inlineStr"/>
       <c r="I414" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J414" s="2" t="inlineStr">
@@ -19885,7 +19897,7 @@
     <row r="415" ht="22" customHeight="1">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>b339389a0d32a94f</t>
+          <t>506296811a5a9cbb</t>
         </is>
       </c>
       <c r="B415" s="2" t="inlineStr">
@@ -19895,12 +19907,12 @@
       </c>
       <c r="C415" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero civil</t>
+          <t>Coordinador/a de SST</t>
         </is>
       </c>
       <c r="D415" s="3" t="inlineStr">
         <is>
-          <t>constructora cumbrera</t>
+          <t>Estelar Food S.A.S</t>
         </is>
       </c>
       <c r="E415" s="8" t="n">
@@ -19912,13 +19924,13 @@
         </is>
       </c>
       <c r="G415" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-civil-4463108593", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-de-sst-at-estelar-food-s-a-s-4462115593", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H415" s="6" t="inlineStr"/>
       <c r="I415" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J415" s="2" t="inlineStr">
@@ -19931,7 +19943,7 @@
     <row r="416" ht="22" customHeight="1">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>93623c0212e39cb9</t>
+          <t>0e4b8eed7f32714e</t>
         </is>
       </c>
       <c r="B416" s="2" t="inlineStr">
@@ -19941,12 +19953,12 @@
       </c>
       <c r="C416" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero(a) Civil</t>
+          <t>coordinador de Seguridad y Salud en el Trabajo</t>
         </is>
       </c>
       <c r="D416" s="3" t="inlineStr">
         <is>
-          <t>CMH Colombia</t>
+          <t>Asertempo Colombia S.A.S</t>
         </is>
       </c>
       <c r="E416" s="8" t="n">
@@ -19958,13 +19970,13 @@
         </is>
       </c>
       <c r="G416" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-civil-at-minerales-c%C3%B3rdoba-4417533007", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-de-seguridad-y-salud-en-el-trabajo-at-asertempo-colombia-s-a-s-4461723686", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H416" s="6" t="inlineStr"/>
       <c r="I416" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J416" s="2" t="inlineStr">
@@ -19977,7 +19989,7 @@
     <row r="417" ht="22" customHeight="1">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>cd06fbe3d5b74888</t>
+          <t>aa2882af3c61095b</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
@@ -19987,12 +19999,12 @@
       </c>
       <c r="C417" s="3" t="inlineStr">
         <is>
-          <t>Oficial Obra Civil</t>
+          <t>Coordinador (a) SST / APH - Marmato</t>
         </is>
       </c>
       <c r="D417" s="3" t="inlineStr">
         <is>
-          <t>Equans Colombia</t>
+          <t>Aris Mining Colombia</t>
         </is>
       </c>
       <c r="E417" s="8" t="n">
@@ -20004,25 +20016,347 @@
         </is>
       </c>
       <c r="G417" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/oficial-obra-civil-bogota-y-cundinamarca-at-equans-colombia-4470218146", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-sst-aph-marmato-at-aris-mining-colombia-4448929810", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H417" s="6" t="inlineStr"/>
       <c r="I417" s="3" t="inlineStr">
         <is>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J417" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K417" s="3" t="inlineStr"/>
+    </row>
+    <row r="418" ht="22" customHeight="1">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>26cff43f13982962</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 05:09</t>
+        </is>
+      </c>
+      <c r="C418" s="3" t="inlineStr">
+        <is>
+          <t>Consultor(a) Senior SOX TI</t>
+        </is>
+      </c>
+      <c r="D418" s="3" t="inlineStr">
+        <is>
+          <t>Hitss Colombia</t>
+        </is>
+      </c>
+      <c r="E418" s="8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F418" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G418" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/consultor-a-senior-sox-ti-at-hitss-colombia-4460766744", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H418" s="6" t="inlineStr"/>
+      <c r="I418" s="3" t="inlineStr">
+        <is>
           <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
-      <c r="J417" s="2" t="inlineStr">
-        <is>
-          <t>Nueva</t>
-        </is>
-      </c>
-      <c r="K417" s="3" t="inlineStr"/>
+      <c r="J418" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K418" s="3" t="inlineStr"/>
+    </row>
+    <row r="419" ht="22" customHeight="1">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>87e367215ed55502</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 05:09</t>
+        </is>
+      </c>
+      <c r="C419" s="3" t="inlineStr">
+        <is>
+          <t>Consultor(a) Senior Auditoría Interna</t>
+        </is>
+      </c>
+      <c r="D419" s="3" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="E419" s="8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F419" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G419" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/consultor-a-senior-auditor%C3%ADa-interna-at-deloitte-4462090075", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H419" s="6" t="inlineStr"/>
+      <c r="I419" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J419" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K419" s="3" t="inlineStr"/>
+    </row>
+    <row r="420" ht="22" customHeight="1">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>e2e525b51bbd0e5e</t>
+        </is>
+      </c>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 05:09</t>
+        </is>
+      </c>
+      <c r="C420" s="3" t="inlineStr">
+        <is>
+          <t>Coordinador/a de Salud y Bienestar (HSE) Latam</t>
+        </is>
+      </c>
+      <c r="D420" s="3" t="inlineStr">
+        <is>
+          <t>Aqualia</t>
+        </is>
+      </c>
+      <c r="E420" s="8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F420" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G420" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-de-salud-y-bienestar-hse-latam-at-aqualia-4463977352", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H420" s="6" t="inlineStr"/>
+      <c r="I420" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J420" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K420" s="3" t="inlineStr"/>
+    </row>
+    <row r="421" ht="22" customHeight="1">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>8ef614b651dfe9d9</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 05:09</t>
+        </is>
+      </c>
+      <c r="C421" s="3" t="inlineStr">
+        <is>
+          <t>Lead Civil Site Engineer</t>
+        </is>
+      </c>
+      <c r="D421" s="3" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E421" s="8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F421" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G421" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/lead-civil-site-engineer-at-aecom-4468059409", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H421" s="6" t="inlineStr"/>
+      <c r="I421" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J421" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K421" s="3" t="inlineStr"/>
+    </row>
+    <row r="422" ht="22" customHeight="1">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>b339389a0d32a94f</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 05:09</t>
+        </is>
+      </c>
+      <c r="C422" s="3" t="inlineStr">
+        <is>
+          <t>Ingeniero civil</t>
+        </is>
+      </c>
+      <c r="D422" s="3" t="inlineStr">
+        <is>
+          <t>constructora cumbrera</t>
+        </is>
+      </c>
+      <c r="E422" s="8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F422" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G422" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-civil-4463108593", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H422" s="6" t="inlineStr"/>
+      <c r="I422" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J422" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K422" s="3" t="inlineStr"/>
+    </row>
+    <row r="423" ht="22" customHeight="1">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>93623c0212e39cb9</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 05:09</t>
+        </is>
+      </c>
+      <c r="C423" s="3" t="inlineStr">
+        <is>
+          <t>Ingeniero(a) Civil</t>
+        </is>
+      </c>
+      <c r="D423" s="3" t="inlineStr">
+        <is>
+          <t>CMH Colombia</t>
+        </is>
+      </c>
+      <c r="E423" s="8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F423" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G423" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-civil-at-minerales-c%C3%B3rdoba-4417533007", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H423" s="6" t="inlineStr"/>
+      <c r="I423" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J423" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K423" s="3" t="inlineStr"/>
+    </row>
+    <row r="424" ht="22" customHeight="1">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>cd06fbe3d5b74888</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 05:09</t>
+        </is>
+      </c>
+      <c r="C424" s="3" t="inlineStr">
+        <is>
+          <t>Oficial Obra Civil</t>
+        </is>
+      </c>
+      <c r="D424" s="3" t="inlineStr">
+        <is>
+          <t>Equans Colombia</t>
+        </is>
+      </c>
+      <c r="E424" s="8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F424" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G424" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/oficial-obra-civil-bogota-y-cundinamarca-at-equans-colombia-4470218146", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H424" s="6" t="inlineStr"/>
+      <c r="I424" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J424" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K424" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J616" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J623" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Nueva,Por revisar,Postulado,Descartado,Entrevista"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/profile_1_civil_vias_sst_tracker.xlsx
+++ b/output/profile_1_civil_vias_sst_tracker.xlsx
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K637"/>
+  <dimension ref="A1:K640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -25399,26 +25399,26 @@
     <row r="530" ht="22" customHeight="1">
       <c r="A530" s="2" t="inlineStr">
         <is>
-          <t>4426b2c17306f519</t>
+          <t>b55954435d797fc0</t>
         </is>
       </c>
       <c r="B530" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 05:09</t>
+          <t>2026-10-18 14:24</t>
         </is>
       </c>
       <c r="C530" s="3" t="inlineStr">
         <is>
-          <t>Residente de Seguridad y Salud en el trabajo</t>
+          <t>Proyectista civil - semi senior</t>
         </is>
       </c>
       <c r="D530" s="3" t="inlineStr">
         <is>
-          <t>Cal y Mayor y Asociados S.C</t>
-        </is>
-      </c>
-      <c r="E530" s="8" t="n">
-        <v>0.48</v>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E530" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="F530" s="2" t="inlineStr">
         <is>
@@ -25426,17 +25426,13 @@
         </is>
       </c>
       <c r="G530" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-residente-de-seguridad-y-salud-en-el-trabajo-sst-sst-en-bogota-dc-D67E64C3D53E0D6961373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H530" s="6" t="inlineStr">
-        <is>
-          <t>$ 4.200.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/proyectista-civil-semi-senior-1886736963", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H530" s="6" t="inlineStr"/>
       <c r="I530" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J530" s="2" t="inlineStr">
@@ -25449,26 +25445,26 @@
     <row r="531" ht="22" customHeight="1">
       <c r="A531" s="2" t="inlineStr">
         <is>
-          <t>83015d6afb890f1d</t>
+          <t>eaecdc7883c5c946</t>
         </is>
       </c>
       <c r="B531" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 05:09</t>
+          <t>2026-10-18 14:24</t>
         </is>
       </c>
       <c r="C531" s="3" t="inlineStr">
         <is>
-          <t>Analista/profesional HSEQ / SST Sesquile o Alrededores</t>
+          <t>Analista de aplicaciones e infraestructura ti</t>
         </is>
       </c>
       <c r="D531" s="3" t="inlineStr">
         <is>
-          <t>ACTIVOS S A S</t>
-        </is>
-      </c>
-      <c r="E531" s="8" t="n">
-        <v>0.48</v>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E531" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="F531" s="2" t="inlineStr">
         <is>
@@ -25476,17 +25472,13 @@
         </is>
       </c>
       <c r="G531" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analistaprofesional-hseq-sst-sesquile-o-alrededores-sector-consumo-masivo-en-sesquile-632A9566338A59E361373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H531" s="6" t="inlineStr">
-        <is>
-          <t>$ 4.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aplicaciones-e-infraestructura-ti-1886763122", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H531" s="6" t="inlineStr"/>
       <c r="I531" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J531" s="2" t="inlineStr">
@@ -25499,26 +25491,26 @@
     <row r="532" ht="22" customHeight="1">
       <c r="A532" s="2" t="inlineStr">
         <is>
-          <t>bc0b38b5129e0905</t>
+          <t>94e5a72874057837</t>
         </is>
       </c>
       <c r="B532" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 05:09</t>
+          <t>2026-10-18 14:24</t>
         </is>
       </c>
       <c r="C532" s="3" t="inlineStr">
         <is>
-          <t>Profesional en seguridad y salud en el trabajo SST</t>
+          <t>Analista de seguridad y salud en el trabajo</t>
         </is>
       </c>
       <c r="D532" s="3" t="inlineStr">
         <is>
-          <t>Seguridad y Vigilancia Exito de Colombia</t>
-        </is>
-      </c>
-      <c r="E532" s="8" t="n">
-        <v>0.48</v>
+          <t>COMFACUNDI</t>
+        </is>
+      </c>
+      <c r="E532" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="F532" s="2" t="inlineStr">
         <is>
@@ -25526,17 +25518,13 @@
         </is>
       </c>
       <c r="G532" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-profesional-en-seguridad-y-salud-en-el-trabajo-sst-con-experiencia-y-conocimiento-en-pesv-en-bogota-dc-A7CA6F8805D1C53B61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H532" s="6" t="inlineStr">
-        <is>
-          <t>$ 3.200.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-seguridad-y-salud-en-el-trabajo-1886762763", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H532" s="6" t="inlineStr"/>
       <c r="I532" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J532" s="2" t="inlineStr">
@@ -25549,7 +25537,7 @@
     <row r="533" ht="22" customHeight="1">
       <c r="A533" s="2" t="inlineStr">
         <is>
-          <t>e15ce00dbe5c21b5</t>
+          <t>4426b2c17306f519</t>
         </is>
       </c>
       <c r="B533" s="2" t="inlineStr">
@@ -25559,12 +25547,12 @@
       </c>
       <c r="C533" s="3" t="inlineStr">
         <is>
-          <t>Tecnólogo HSEQ / Seguridad y Salud en el Trabajo</t>
+          <t>Residente de Seguridad y Salud en el trabajo</t>
         </is>
       </c>
       <c r="D533" s="3" t="inlineStr">
         <is>
-          <t>Lighgen Ingeniería Ltda</t>
+          <t>Cal y Mayor y Asociados S.C</t>
         </is>
       </c>
       <c r="E533" s="8" t="n">
@@ -25576,10 +25564,14 @@
         </is>
       </c>
       <c r="G533" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-tecnologo-hseq-seguridad-y-salud-en-el-trabajo-con-experiencia-2-anos-en-bogota-dc-87DB3FCAFEA8E12861373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H533" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-residente-de-seguridad-y-salud-en-el-trabajo-sst-sst-en-bogota-dc-D67E64C3D53E0D6961373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H533" s="6" t="inlineStr">
+        <is>
+          <t>$ 4.200.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I533" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -25595,7 +25587,7 @@
     <row r="534" ht="22" customHeight="1">
       <c r="A534" s="2" t="inlineStr">
         <is>
-          <t>1f3bf8b16a58f0b4</t>
+          <t>83015d6afb890f1d</t>
         </is>
       </c>
       <c r="B534" s="2" t="inlineStr">
@@ -25605,12 +25597,12 @@
       </c>
       <c r="C534" s="3" t="inlineStr">
         <is>
-          <t>Inspector (a) de vias y urbanismo</t>
+          <t>Analista/profesional HSEQ / SST Sesquile o Alrededores</t>
         </is>
       </c>
       <c r="D534" s="3" t="inlineStr">
         <is>
-          <t>METRO LINEA 1 S.A.S.</t>
+          <t>ACTIVOS S A S</t>
         </is>
       </c>
       <c r="E534" s="8" t="n">
@@ -25622,13 +25614,17 @@
         </is>
       </c>
       <c r="G534" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/inspector-a-de-vias-y-urbanismo-1886728733", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H534" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analistaprofesional-hseq-sst-sesquile-o-alrededores-sector-consumo-masivo-en-sesquile-632A9566338A59E361373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H534" s="6" t="inlineStr">
+        <is>
+          <t>$ 4.000.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I534" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J534" s="2" t="inlineStr">
@@ -25641,7 +25637,7 @@
     <row r="535" ht="22" customHeight="1">
       <c r="A535" s="2" t="inlineStr">
         <is>
-          <t>8fd843a922654d9e</t>
+          <t>bc0b38b5129e0905</t>
         </is>
       </c>
       <c r="B535" s="2" t="inlineStr">
@@ -25651,12 +25647,12 @@
       </c>
       <c r="C535" s="3" t="inlineStr">
         <is>
-          <t>Oficial de obra</t>
+          <t>Profesional en seguridad y salud en el trabajo SST</t>
         </is>
       </c>
       <c r="D535" s="3" t="inlineStr">
         <is>
-          <t>TERMOTECNICA COINDUSTRIAL SAS</t>
+          <t>Seguridad y Vigilancia Exito de Colombia</t>
         </is>
       </c>
       <c r="E535" s="8" t="n">
@@ -25668,13 +25664,17 @@
         </is>
       </c>
       <c r="G535" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/oficial-de-obra-puentevias-1886766237", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H535" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-profesional-en-seguridad-y-salud-en-el-trabajo-sst-con-experiencia-y-conocimiento-en-pesv-en-bogota-dc-A7CA6F8805D1C53B61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H535" s="6" t="inlineStr">
+        <is>
+          <t>$ 3.200.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I535" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J535" s="2" t="inlineStr">
@@ -25687,7 +25687,7 @@
     <row r="536" ht="22" customHeight="1">
       <c r="A536" s="2" t="inlineStr">
         <is>
-          <t>03eab73111095faa</t>
+          <t>e15ce00dbe5c21b5</t>
         </is>
       </c>
       <c r="B536" s="2" t="inlineStr">
@@ -25697,12 +25697,12 @@
       </c>
       <c r="C536" s="3" t="inlineStr">
         <is>
-          <t>Residente estructuras</t>
+          <t>Tecnólogo HSEQ / Seguridad y Salud en el Trabajo</t>
         </is>
       </c>
       <c r="D536" s="3" t="inlineStr">
         <is>
-          <t>CONCONCRETO S.A.</t>
+          <t>Lighgen Ingeniería Ltda</t>
         </is>
       </c>
       <c r="E536" s="8" t="n">
@@ -25714,13 +25714,13 @@
         </is>
       </c>
       <c r="G536" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/residente-estructuras-experiencia-en-infraestructura-vial-y-talud-1886757305", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-tecnologo-hseq-seguridad-y-salud-en-el-trabajo-con-experiencia-2-anos-en-bogota-dc-87DB3FCAFEA8E12861373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H536" s="6" t="inlineStr"/>
       <c r="I536" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J536" s="2" t="inlineStr">
@@ -25733,7 +25733,7 @@
     <row r="537" ht="22" customHeight="1">
       <c r="A537" s="2" t="inlineStr">
         <is>
-          <t>c5911c7562546e3c</t>
+          <t>1f3bf8b16a58f0b4</t>
         </is>
       </c>
       <c r="B537" s="2" t="inlineStr">
@@ -25743,12 +25743,12 @@
       </c>
       <c r="C537" s="3" t="inlineStr">
         <is>
-          <t>Profesional con experiencia en el sector de transporte marítimo y/o por vías navegables</t>
+          <t>Inspector (a) de vias y urbanismo</t>
         </is>
       </c>
       <c r="D537" s="3" t="inlineStr">
         <is>
-          <t>ICONTEC</t>
+          <t>METRO LINEA 1 S.A.S.</t>
         </is>
       </c>
       <c r="E537" s="8" t="n">
@@ -25760,7 +25760,7 @@
         </is>
       </c>
       <c r="G537" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/profesional-con-experiencia-en-el-sector-de-transporte-maritimo-y-o-por-vias-navegables-1886761682", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/inspector-a-de-vias-y-urbanismo-1886728733", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H537" s="6" t="inlineStr"/>
@@ -25779,7 +25779,7 @@
     <row r="538" ht="22" customHeight="1">
       <c r="A538" s="2" t="inlineStr">
         <is>
-          <t>c2903e245a44de39</t>
+          <t>8fd843a922654d9e</t>
         </is>
       </c>
       <c r="B538" s="2" t="inlineStr">
@@ -25789,7 +25789,7 @@
       </c>
       <c r="C538" s="3" t="inlineStr">
         <is>
-          <t>Encargado de obra</t>
+          <t>Oficial de obra</t>
         </is>
       </c>
       <c r="D538" s="3" t="inlineStr">
@@ -25806,7 +25806,7 @@
         </is>
       </c>
       <c r="G538" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/encargado-de-obra-puentes-vias-1886762620", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/oficial-de-obra-puentevias-1886766237", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H538" s="6" t="inlineStr"/>
@@ -25825,7 +25825,7 @@
     <row r="539" ht="22" customHeight="1">
       <c r="A539" s="2" t="inlineStr">
         <is>
-          <t>a5bd833e8b837d34</t>
+          <t>03eab73111095faa</t>
         </is>
       </c>
       <c r="B539" s="2" t="inlineStr">
@@ -25835,12 +25835,12 @@
       </c>
       <c r="C539" s="3" t="inlineStr">
         <is>
-          <t>Residente en seguridad y salud en el trabajo</t>
+          <t>Residente estructuras</t>
         </is>
       </c>
       <c r="D539" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>CONCONCRETO S.A.</t>
         </is>
       </c>
       <c r="E539" s="8" t="n">
@@ -25852,13 +25852,13 @@
         </is>
       </c>
       <c r="G539" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/residente-en-seguridad-y-salud-en-el-trabajo-sst-1886762728", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/residente-estructuras-experiencia-en-infraestructura-vial-y-talud-1886757305", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H539" s="6" t="inlineStr"/>
       <c r="I539" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J539" s="2" t="inlineStr">
@@ -25871,7 +25871,7 @@
     <row r="540" ht="22" customHeight="1">
       <c r="A540" s="2" t="inlineStr">
         <is>
-          <t>55e7967f3b4afa02</t>
+          <t>c5911c7562546e3c</t>
         </is>
       </c>
       <c r="B540" s="2" t="inlineStr">
@@ -25881,12 +25881,12 @@
       </c>
       <c r="C540" s="3" t="inlineStr">
         <is>
-          <t>Tecnólogo/a en Seguridad y Salud en el Trabajo</t>
+          <t>Profesional con experiencia en el sector de transporte marítimo y/o por vías navegables</t>
         </is>
       </c>
       <c r="D540" s="3" t="inlineStr">
         <is>
-          <t>EOSOL</t>
+          <t>ICONTEC</t>
         </is>
       </c>
       <c r="E540" s="8" t="n">
@@ -25898,13 +25898,13 @@
         </is>
       </c>
       <c r="G540" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/tecn%C3%B3logo-a-en-seguridad-y-salud-en-el-trabajo-sst-at-eosol-4464868638", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/profesional-con-experiencia-en-el-sector-de-transporte-maritimo-y-o-por-vias-navegables-1886761682", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H540" s="6" t="inlineStr"/>
       <c r="I540" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J540" s="2" t="inlineStr">
@@ -25917,7 +25917,7 @@
     <row r="541" ht="22" customHeight="1">
       <c r="A541" s="2" t="inlineStr">
         <is>
-          <t>6df905e482fe09b1</t>
+          <t>c2903e245a44de39</t>
         </is>
       </c>
       <c r="B541" s="2" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="C541" s="3" t="inlineStr">
         <is>
-          <t>Aprendiz SENA - Técnico(a) de Salud Ocupacional o Seguridad y Salud en el Trabajo - Ginebra</t>
+          <t>Encargado de obra</t>
         </is>
       </c>
       <c r="D541" s="3" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>TERMOTECNICA COINDUSTRIAL SAS</t>
         </is>
       </c>
       <c r="E541" s="8" t="n">
@@ -25944,13 +25944,13 @@
         </is>
       </c>
       <c r="G541" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-sena-t%C3%A9cnico-a-de-salud-ocupacional-o-seguridad-y-salud-en-el-trabajo-ginebra-at-cargill-4466994159", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/encargado-de-obra-puentes-vias-1886762620", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H541" s="6" t="inlineStr"/>
       <c r="I541" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J541" s="2" t="inlineStr">
@@ -25963,7 +25963,7 @@
     <row r="542" ht="22" customHeight="1">
       <c r="A542" s="2" t="inlineStr">
         <is>
-          <t>06656fbb2d452086</t>
+          <t>a5bd833e8b837d34</t>
         </is>
       </c>
       <c r="B542" s="2" t="inlineStr">
@@ -25973,12 +25973,12 @@
       </c>
       <c r="C542" s="3" t="inlineStr">
         <is>
-          <t>Residente de Seguridad y Salud en el trabajo</t>
+          <t>Residente en seguridad y salud en el trabajo</t>
         </is>
       </c>
       <c r="D542" s="3" t="inlineStr">
         <is>
-          <t>Grupo Cal y Mayor</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E542" s="8" t="n">
@@ -25990,7 +25990,7 @@
         </is>
       </c>
       <c r="G542" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/residente-de-seguridad-y-salud-en-el-trabajo-sst-at-cal-y-mayor-4468610572", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/residente-en-seguridad-y-salud-en-el-trabajo-sst-1886762728", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H542" s="6" t="inlineStr"/>
@@ -26009,7 +26009,7 @@
     <row r="543" ht="22" customHeight="1">
       <c r="A543" s="2" t="inlineStr">
         <is>
-          <t>7796e088dce85b5a</t>
+          <t>55e7967f3b4afa02</t>
         </is>
       </c>
       <c r="B543" s="2" t="inlineStr">
@@ -26019,16 +26019,16 @@
       </c>
       <c r="C543" s="3" t="inlineStr">
         <is>
-          <t>Civil Engineer (Fire Sprinkler Design))</t>
+          <t>Tecnólogo/a en Seguridad y Salud en el Trabajo</t>
         </is>
       </c>
       <c r="D543" s="3" t="inlineStr">
         <is>
-          <t>Hyremote</t>
+          <t>EOSOL</t>
         </is>
       </c>
       <c r="E543" s="8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="F543" s="2" t="inlineStr">
         <is>
@@ -26036,17 +26036,13 @@
         </is>
       </c>
       <c r="G543" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-civil-engineer-fire-sprinkler-design-english-c1-remote-en-bogota-dc-A2EE61A321FC0D3361373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H543" s="6" t="inlineStr">
-        <is>
-          <t>$ 4.499.993,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/tecn%C3%B3logo-a-en-seguridad-y-salud-en-el-trabajo-sst-at-eosol-4464868638", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H543" s="6" t="inlineStr"/>
       <c r="I543" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J543" s="2" t="inlineStr">
@@ -26059,7 +26055,7 @@
     <row r="544" ht="22" customHeight="1">
       <c r="A544" s="2" t="inlineStr">
         <is>
-          <t>48463526ca7c8ada</t>
+          <t>6df905e482fe09b1</t>
         </is>
       </c>
       <c r="B544" s="2" t="inlineStr">
@@ -26069,16 +26065,16 @@
       </c>
       <c r="C544" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero Civil Especialista en Hidrología e Hidráulica</t>
+          <t>Aprendiz SENA - Técnico(a) de Salud Ocupacional o Seguridad y Salud en el Trabajo - Ginebra</t>
         </is>
       </c>
       <c r="D544" s="3" t="inlineStr">
         <is>
-          <t>ATLAS INFRASTRUCTURE DESIGN LIMITED</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="E544" s="8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="F544" s="2" t="inlineStr">
         <is>
@@ -26086,17 +26082,13 @@
         </is>
       </c>
       <c r="G544" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-especialista-en-hidrologia-e-hidraulica-tiempo-completo-en-remoto-y-de-larga-duracion-en-colombia-027FB718364F4C7761373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H544" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-sena-t%C3%A9cnico-a-de-salud-ocupacional-o-seguridad-y-salud-en-el-trabajo-ginebra-at-cargill-4466994159", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H544" s="6" t="inlineStr"/>
       <c r="I544" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J544" s="2" t="inlineStr">
@@ -26109,7 +26101,7 @@
     <row r="545" ht="22" customHeight="1">
       <c r="A545" s="2" t="inlineStr">
         <is>
-          <t>2d406567ceb21bf8</t>
+          <t>06656fbb2d452086</t>
         </is>
       </c>
       <c r="B545" s="2" t="inlineStr">
@@ -26119,16 +26111,16 @@
       </c>
       <c r="C545" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero Civil de Diseño</t>
+          <t>Residente de Seguridad y Salud en el trabajo</t>
         </is>
       </c>
       <c r="D545" s="3" t="inlineStr">
         <is>
-          <t>ATLAS INFRASTRUCTURE DESIGN LIMITED</t>
+          <t>Grupo Cal y Mayor</t>
         </is>
       </c>
       <c r="E545" s="8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="F545" s="2" t="inlineStr">
         <is>
@@ -26136,17 +26128,13 @@
         </is>
       </c>
       <c r="G545" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-de-diseno-tiempo-completo-en-remoto-en-colombia-4CB8F30B6D8FBF7261373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H545" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/residente-de-seguridad-y-salud-en-el-trabajo-sst-at-cal-y-mayor-4468610572", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H545" s="6" t="inlineStr"/>
       <c r="I545" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J545" s="2" t="inlineStr">
@@ -26159,7 +26147,7 @@
     <row r="546" ht="22" customHeight="1">
       <c r="A546" s="2" t="inlineStr">
         <is>
-          <t>4d4013d19591d2a5</t>
+          <t>7796e088dce85b5a</t>
         </is>
       </c>
       <c r="B546" s="2" t="inlineStr">
@@ -26169,12 +26157,12 @@
       </c>
       <c r="C546" s="3" t="inlineStr">
         <is>
-          <t>Especialista en Salud y Seguridad en el trabajo con especialización en medio Ambiente</t>
+          <t>Civil Engineer (Fire Sprinkler Design))</t>
         </is>
       </c>
       <c r="D546" s="3" t="inlineStr">
         <is>
-          <t>DEXTERA S.A.S</t>
+          <t>Hyremote</t>
         </is>
       </c>
       <c r="E546" s="8" t="n">
@@ -26186,10 +26174,14 @@
         </is>
       </c>
       <c r="G546" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-especialista-en-salud-y-seguridad-en-el-trabajo-con-especializacion-en-medio-ambiente-en-bogota-dc-68C95C2F64D6648561373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H546" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-civil-engineer-fire-sprinkler-design-english-c1-remote-en-bogota-dc-A2EE61A321FC0D3361373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H546" s="6" t="inlineStr">
+        <is>
+          <t>$ 4.499.993,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I546" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -26205,7 +26197,7 @@
     <row r="547" ht="22" customHeight="1">
       <c r="A547" s="2" t="inlineStr">
         <is>
-          <t>cf70d2ca6e5c25de</t>
+          <t>48463526ca7c8ada</t>
         </is>
       </c>
       <c r="B547" s="2" t="inlineStr">
@@ -26215,12 +26207,12 @@
       </c>
       <c r="C547" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero civil</t>
+          <t>Ingeniero Civil Especialista en Hidrología e Hidráulica</t>
         </is>
       </c>
       <c r="D547" s="3" t="inlineStr">
         <is>
-          <t>Importante empresa del sector</t>
+          <t>ATLAS INFRASTRUCTURE DESIGN LIMITED</t>
         </is>
       </c>
       <c r="E547" s="8" t="n">
@@ -26232,12 +26224,12 @@
         </is>
       </c>
       <c r="G547" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-con-experiencia-en-sistemas-fotovoltaicos-en-bogota-dc-8BCBCD7DF8FE589C61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-especialista-en-hidrologia-e-hidraulica-tiempo-completo-en-remoto-y-de-larga-duracion-en-colombia-027FB718364F4C7761373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H547" s="6" t="inlineStr">
         <is>
-          <t>$ 3.300.000,00 (Mensual)</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="I547" s="3" t="inlineStr">
@@ -26255,7 +26247,7 @@
     <row r="548" ht="22" customHeight="1">
       <c r="A548" s="2" t="inlineStr">
         <is>
-          <t>bb8237cc7ed8d56b</t>
+          <t>2d406567ceb21bf8</t>
         </is>
       </c>
       <c r="B548" s="2" t="inlineStr">
@@ -26265,12 +26257,12 @@
       </c>
       <c r="C548" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de Proyectos Mejoramientos de Vivienda</t>
+          <t>Ingeniero Civil de Diseño</t>
         </is>
       </c>
       <c r="D548" s="3" t="inlineStr">
         <is>
-          <t>Socya</t>
+          <t>ATLAS INFRASTRUCTURE DESIGN LIMITED</t>
         </is>
       </c>
       <c r="E548" s="8" t="n">
@@ -26282,10 +26274,14 @@
         </is>
       </c>
       <c r="G548" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-de-proyectos-mejoramientos-de-vivienda-medellin-antioquia-en-medellin-7E29781CFFD4058961373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H548" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-de-diseno-tiempo-completo-en-remoto-en-colombia-4CB8F30B6D8FBF7261373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H548" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I548" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -26301,7 +26297,7 @@
     <row r="549" ht="22" customHeight="1">
       <c r="A549" s="2" t="inlineStr">
         <is>
-          <t>c41dc091e876cb10</t>
+          <t>4d4013d19591d2a5</t>
         </is>
       </c>
       <c r="B549" s="2" t="inlineStr">
@@ -26311,12 +26307,12 @@
       </c>
       <c r="C549" s="3" t="inlineStr">
         <is>
-          <t>Especialista de Milk Collection</t>
+          <t>Especialista en Salud y Seguridad en el trabajo con especialización en medio Ambiente</t>
         </is>
       </c>
       <c r="D549" s="3" t="inlineStr">
         <is>
-          <t>LACTALIS</t>
+          <t>DEXTERA S.A.S</t>
         </is>
       </c>
       <c r="E549" s="8" t="n">
@@ -26328,14 +26324,10 @@
         </is>
       </c>
       <c r="G549" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-especialista-de-milk-collection-optimizacion-y-analisis-de-datos-en-bogota-dc-B007F5172FEA6F6461373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H549" s="6" t="inlineStr">
-        <is>
-          <t>$ 6.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-especialista-en-salud-y-seguridad-en-el-trabajo-con-especializacion-en-medio-ambiente-en-bogota-dc-68C95C2F64D6648561373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H549" s="6" t="inlineStr"/>
       <c r="I549" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -26351,7 +26343,7 @@
     <row r="550" ht="22" customHeight="1">
       <c r="A550" s="2" t="inlineStr">
         <is>
-          <t>4f38d6c20430e4bb</t>
+          <t>cf70d2ca6e5c25de</t>
         </is>
       </c>
       <c r="B550" s="2" t="inlineStr">
@@ -26361,12 +26353,12 @@
       </c>
       <c r="C550" s="3" t="inlineStr">
         <is>
-          <t>ingeniero civil</t>
+          <t>Ingeniero civil</t>
         </is>
       </c>
       <c r="D550" s="3" t="inlineStr">
         <is>
-          <t>EVALTEC S.A.S.</t>
+          <t>Importante empresa del sector</t>
         </is>
       </c>
       <c r="E550" s="8" t="n">
@@ -26378,10 +26370,14 @@
         </is>
       </c>
       <c r="G550" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-o-areas-afines-en-medellin-0E02F682AB12631061373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H550" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-con-experiencia-en-sistemas-fotovoltaicos-en-bogota-dc-8BCBCD7DF8FE589C61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H550" s="6" t="inlineStr">
+        <is>
+          <t>$ 3.300.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I550" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -26397,7 +26393,7 @@
     <row r="551" ht="22" customHeight="1">
       <c r="A551" s="2" t="inlineStr">
         <is>
-          <t>af38dd28fbbad8f4</t>
+          <t>bb8237cc7ed8d56b</t>
         </is>
       </c>
       <c r="B551" s="2" t="inlineStr">
@@ -26407,12 +26403,12 @@
       </c>
       <c r="C551" s="3" t="inlineStr">
         <is>
-          <t>Tecnólogo Auxiliar Civil</t>
+          <t>Coordinador de Proyectos Mejoramientos de Vivienda</t>
         </is>
       </c>
       <c r="D551" s="3" t="inlineStr">
         <is>
-          <t>Importante empresa del sector</t>
+          <t>Socya</t>
         </is>
       </c>
       <c r="E551" s="8" t="n">
@@ -26424,7 +26420,7 @@
         </is>
       </c>
       <c r="G551" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-tecnologo-auxiliar-civil-antioquia-en-liborina-B380460DDA9F98D061373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-de-proyectos-mejoramientos-de-vivienda-medellin-antioquia-en-medellin-7E29781CFFD4058961373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H551" s="6" t="inlineStr"/>
@@ -26443,7 +26439,7 @@
     <row r="552" ht="22" customHeight="1">
       <c r="A552" s="2" t="inlineStr">
         <is>
-          <t>19e74768ce848880</t>
+          <t>c41dc091e876cb10</t>
         </is>
       </c>
       <c r="B552" s="2" t="inlineStr">
@@ -26453,12 +26449,12 @@
       </c>
       <c r="C552" s="3" t="inlineStr">
         <is>
-          <t>Coordinador HSEQ</t>
+          <t>Especialista de Milk Collection</t>
         </is>
       </c>
       <c r="D552" s="3" t="inlineStr">
         <is>
-          <t>Agencia de empleo de Comfenalco Cartagena</t>
+          <t>LACTALIS</t>
         </is>
       </c>
       <c r="E552" s="8" t="n">
@@ -26470,17 +26466,17 @@
         </is>
       </c>
       <c r="G552" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-hseq-especialista-en-seguridad-y-salud-en-el-trabajo-salud-ocupacional-en-cartagena-de-indias-1EAF6570FC054C2661373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-especialista-de-milk-collection-optimizacion-y-analisis-de-datos-en-bogota-dc-B007F5172FEA6F6461373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H552" s="6" t="inlineStr">
         <is>
-          <t>$ 2.500.000,00 (Mensual)</t>
+          <t>$ 6.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I552" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J552" s="2" t="inlineStr">
@@ -26493,7 +26489,7 @@
     <row r="553" ht="22" customHeight="1">
       <c r="A553" s="2" t="inlineStr">
         <is>
-          <t>38c9a9481706de58</t>
+          <t>4f38d6c20430e4bb</t>
         </is>
       </c>
       <c r="B553" s="2" t="inlineStr">
@@ -26503,12 +26499,12 @@
       </c>
       <c r="C553" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de seguridad vial y monitoreo</t>
+          <t>ingeniero civil</t>
         </is>
       </c>
       <c r="D553" s="3" t="inlineStr">
         <is>
-          <t>MEGACOMERCIAL S.A.S</t>
+          <t>EVALTEC S.A.S.</t>
         </is>
       </c>
       <c r="E553" s="8" t="n">
@@ -26520,17 +26516,13 @@
         </is>
       </c>
       <c r="G553" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-de-seguridad-vial-y-monitoreo-abierto-a-nivel-nacional-en-bogota-dc-B9B593A780889F2A61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H553" s="6" t="inlineStr">
-        <is>
-          <t>$ 5.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-o-areas-afines-en-medellin-0E02F682AB12631061373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H553" s="6" t="inlineStr"/>
       <c r="I553" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J553" s="2" t="inlineStr">
@@ -26543,7 +26535,7 @@
     <row r="554" ht="22" customHeight="1">
       <c r="A554" s="2" t="inlineStr">
         <is>
-          <t>aecc6c18fdd71383</t>
+          <t>af38dd28fbbad8f4</t>
         </is>
       </c>
       <c r="B554" s="2" t="inlineStr">
@@ -26553,12 +26545,12 @@
       </c>
       <c r="C554" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de PESV</t>
+          <t>Tecnólogo Auxiliar Civil</t>
         </is>
       </c>
       <c r="D554" s="3" t="inlineStr">
         <is>
-          <t>Agencia de Empleo de Comfenalco Antioquia</t>
+          <t>Importante empresa del sector</t>
         </is>
       </c>
       <c r="E554" s="8" t="n">
@@ -26570,17 +26562,13 @@
         </is>
       </c>
       <c r="G554" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-de-pesv-en-medellin-67C3B78E9A85885161373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H554" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.800.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-tecnologo-auxiliar-civil-antioquia-en-liborina-B380460DDA9F98D061373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H554" s="6" t="inlineStr"/>
       <c r="I554" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J554" s="2" t="inlineStr">
@@ -26593,7 +26581,7 @@
     <row r="555" ht="22" customHeight="1">
       <c r="A555" s="2" t="inlineStr">
         <is>
-          <t>1558fc20863bdd35</t>
+          <t>19e74768ce848880</t>
         </is>
       </c>
       <c r="B555" s="2" t="inlineStr">
@@ -26608,7 +26596,7 @@
       </c>
       <c r="D555" s="3" t="inlineStr">
         <is>
-          <t>COMPAÑIA DE INGENIEROS CONSTRUCTORES S.A.S.</t>
+          <t>Agencia de empleo de Comfenalco Cartagena</t>
         </is>
       </c>
       <c r="E555" s="8" t="n">
@@ -26620,10 +26608,14 @@
         </is>
       </c>
       <c r="G555" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-hseq-en-barranquilla-F4898EBB71CAF3ED61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H555" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-hseq-especialista-en-seguridad-y-salud-en-el-trabajo-salud-ocupacional-en-cartagena-de-indias-1EAF6570FC054C2661373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H555" s="6" t="inlineStr">
+        <is>
+          <t>$ 2.500.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I555" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -26639,7 +26631,7 @@
     <row r="556" ht="22" customHeight="1">
       <c r="A556" s="2" t="inlineStr">
         <is>
-          <t>0bf63022dc93885b</t>
+          <t>38c9a9481706de58</t>
         </is>
       </c>
       <c r="B556" s="2" t="inlineStr">
@@ -26649,12 +26641,12 @@
       </c>
       <c r="C556" s="3" t="inlineStr">
         <is>
-          <t>ingeniero civil</t>
+          <t>Coordinador de seguridad vial y monitoreo</t>
         </is>
       </c>
       <c r="D556" s="3" t="inlineStr">
         <is>
-          <t>FRANCISCO ANGULO M INGENIEROS S.A.S.</t>
+          <t>MEGACOMERCIAL S.A.S</t>
         </is>
       </c>
       <c r="E556" s="8" t="n">
@@ -26666,13 +26658,17 @@
         </is>
       </c>
       <c r="G556" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-residente-de-interventoria-yo-supervision-tecnica-en-cali-D2AE78FA9B23778161373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H556" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-de-seguridad-vial-y-monitoreo-abierto-a-nivel-nacional-en-bogota-dc-B9B593A780889F2A61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H556" s="6" t="inlineStr">
+        <is>
+          <t>$ 5.000.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I556" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J556" s="2" t="inlineStr">
@@ -26685,7 +26681,7 @@
     <row r="557" ht="22" customHeight="1">
       <c r="A557" s="2" t="inlineStr">
         <is>
-          <t>baa61a6e15a2de77</t>
+          <t>aecc6c18fdd71383</t>
         </is>
       </c>
       <c r="B557" s="2" t="inlineStr">
@@ -26695,12 +26691,12 @@
       </c>
       <c r="C557" s="3" t="inlineStr">
         <is>
-          <t>Arquitecto(a) / Ingeniero(a) Civil</t>
+          <t>Coordinador de PESV</t>
         </is>
       </c>
       <c r="D557" s="3" t="inlineStr">
         <is>
-          <t>Importante empresa del sector</t>
+          <t>Agencia de Empleo de Comfenalco Antioquia</t>
         </is>
       </c>
       <c r="E557" s="8" t="n">
@@ -26712,13 +26708,17 @@
         </is>
       </c>
       <c r="G557" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-arquitectoa-ingenieroa-civil-en-bucaramanga-8D15AF34F304555F61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H557" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-de-pesv-en-medellin-67C3B78E9A85885161373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H557" s="6" t="inlineStr">
+        <is>
+          <t>$ 2.800.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I557" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J557" s="2" t="inlineStr">
@@ -26731,7 +26731,7 @@
     <row r="558" ht="22" customHeight="1">
       <c r="A558" s="2" t="inlineStr">
         <is>
-          <t>448d93b15d9b7dec</t>
+          <t>1558fc20863bdd35</t>
         </is>
       </c>
       <c r="B558" s="2" t="inlineStr">
@@ -26741,12 +26741,12 @@
       </c>
       <c r="C558" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero especialista fortinet</t>
+          <t>Coordinador HSEQ</t>
         </is>
       </c>
       <c r="D558" s="3" t="inlineStr">
         <is>
-          <t>ATCG DE COLOMBIA S.A.S</t>
+          <t>COMPAÑIA DE INGENIEROS CONSTRUCTORES S.A.S.</t>
         </is>
       </c>
       <c r="E558" s="8" t="n">
@@ -26758,13 +26758,13 @@
         </is>
       </c>
       <c r="G558" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-especialista-fortinet-1886742914", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-hseq-en-barranquilla-F4898EBB71CAF3ED61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H558" s="6" t="inlineStr"/>
       <c r="I558" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J558" s="2" t="inlineStr">
@@ -26777,7 +26777,7 @@
     <row r="559" ht="22" customHeight="1">
       <c r="A559" s="2" t="inlineStr">
         <is>
-          <t>f2fc6f9471f81665</t>
+          <t>0bf63022dc93885b</t>
         </is>
       </c>
       <c r="B559" s="2" t="inlineStr">
@@ -26787,12 +26787,12 @@
       </c>
       <c r="C559" s="3" t="inlineStr">
         <is>
-          <t>Coordinador/a nacional de redes e infraestructura de ti - presencial bucaramanga</t>
+          <t>ingeniero civil</t>
         </is>
       </c>
       <c r="D559" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FRANCISCO ANGULO M INGENIEROS S.A.S.</t>
         </is>
       </c>
       <c r="E559" s="8" t="n">
@@ -26804,13 +26804,13 @@
         </is>
       </c>
       <c r="G559" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-a-nacional-de-redes-e-infraestructura-de-ti-presencial-bucaramanga-1886769481", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-residente-de-interventoria-yo-supervision-tecnica-en-cali-D2AE78FA9B23778161373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H559" s="6" t="inlineStr"/>
       <c r="I559" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J559" s="2" t="inlineStr">
@@ -26823,7 +26823,7 @@
     <row r="560" ht="22" customHeight="1">
       <c r="A560" s="2" t="inlineStr">
         <is>
-          <t>53e1a775996a36c5</t>
+          <t>baa61a6e15a2de77</t>
         </is>
       </c>
       <c r="B560" s="2" t="inlineStr">
@@ -26833,12 +26833,12 @@
       </c>
       <c r="C560" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero civil</t>
+          <t>Arquitecto(a) / Ingeniero(a) Civil</t>
         </is>
       </c>
       <c r="D560" s="3" t="inlineStr">
         <is>
-          <t>Proyectos de Diseño y Construccion sas</t>
+          <t>Importante empresa del sector</t>
         </is>
       </c>
       <c r="E560" s="8" t="n">
@@ -26850,7 +26850,7 @@
         </is>
       </c>
       <c r="G560" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-1886757049", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-arquitectoa-ingenieroa-civil-en-bucaramanga-8D15AF34F304555F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H560" s="6" t="inlineStr"/>
@@ -26869,7 +26869,7 @@
     <row r="561" ht="22" customHeight="1">
       <c r="A561" s="2" t="inlineStr">
         <is>
-          <t>1072d76e2f18ea50</t>
+          <t>448d93b15d9b7dec</t>
         </is>
       </c>
       <c r="B561" s="2" t="inlineStr">
@@ -26879,12 +26879,12 @@
       </c>
       <c r="C561" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero civil</t>
+          <t>Ingeniero especialista fortinet</t>
         </is>
       </c>
       <c r="D561" s="3" t="inlineStr">
         <is>
-          <t>R2P SOLUCIONES Y CONSTRUCCIONES SAS</t>
+          <t>ATCG DE COLOMBIA S.A.S</t>
         </is>
       </c>
       <c r="E561" s="8" t="n">
@@ -26896,7 +26896,7 @@
         </is>
       </c>
       <c r="G561" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-1886758475", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-especialista-fortinet-1886742914", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H561" s="6" t="inlineStr"/>
@@ -26915,7 +26915,7 @@
     <row r="562" ht="22" customHeight="1">
       <c r="A562" s="2" t="inlineStr">
         <is>
-          <t>2c943591cc334f5a</t>
+          <t>f2fc6f9471f81665</t>
         </is>
       </c>
       <c r="B562" s="2" t="inlineStr">
@@ -26925,7 +26925,7 @@
       </c>
       <c r="C562" s="3" t="inlineStr">
         <is>
-          <t>Ejecutivo/ade ingeniera</t>
+          <t>Coordinador/a nacional de redes e infraestructura de ti - presencial bucaramanga</t>
         </is>
       </c>
       <c r="D562" s="3" t="inlineStr">
@@ -26942,13 +26942,13 @@
         </is>
       </c>
       <c r="G562" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-ade-ingeniera-1886752134", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-a-nacional-de-redes-e-infraestructura-de-ti-presencial-bucaramanga-1886769481", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H562" s="6" t="inlineStr"/>
       <c r="I562" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J562" s="2" t="inlineStr">
@@ -26961,7 +26961,7 @@
     <row r="563" ht="22" customHeight="1">
       <c r="A563" s="2" t="inlineStr">
         <is>
-          <t>7d4067502e572780</t>
+          <t>53e1a775996a36c5</t>
         </is>
       </c>
       <c r="B563" s="2" t="inlineStr">
@@ -26971,12 +26971,12 @@
       </c>
       <c r="C563" s="3" t="inlineStr">
         <is>
-          <t>Ingeniera de ventas - cali</t>
+          <t>Ingeniero civil</t>
         </is>
       </c>
       <c r="D563" s="3" t="inlineStr">
         <is>
-          <t>PIPOL EXPERT SAS</t>
+          <t>Proyectos de Diseño y Construccion sas</t>
         </is>
       </c>
       <c r="E563" s="8" t="n">
@@ -26988,7 +26988,7 @@
         </is>
       </c>
       <c r="G563" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-de-ventas-cali-1886754430", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-1886757049", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H563" s="6" t="inlineStr"/>
@@ -27007,7 +27007,7 @@
     <row r="564" ht="22" customHeight="1">
       <c r="A564" s="2" t="inlineStr">
         <is>
-          <t>a3a688084650de1c</t>
+          <t>1072d76e2f18ea50</t>
         </is>
       </c>
       <c r="B564" s="2" t="inlineStr">
@@ -27017,12 +27017,12 @@
       </c>
       <c r="C564" s="3" t="inlineStr">
         <is>
-          <t>Ingeniera comercial electrica - cali</t>
+          <t>Ingeniero civil</t>
         </is>
       </c>
       <c r="D564" s="3" t="inlineStr">
         <is>
-          <t>PIPOL EXPERT SAS</t>
+          <t>R2P SOLUCIONES Y CONSTRUCCIONES SAS</t>
         </is>
       </c>
       <c r="E564" s="8" t="n">
@@ -27034,7 +27034,7 @@
         </is>
       </c>
       <c r="G564" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-comercial-electrica-cali-1886752104", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-1886758475", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H564" s="6" t="inlineStr"/>
@@ -27053,7 +27053,7 @@
     <row r="565" ht="22" customHeight="1">
       <c r="A565" s="2" t="inlineStr">
         <is>
-          <t>359d47915a2e74e6</t>
+          <t>2c943591cc334f5a</t>
         </is>
       </c>
       <c r="B565" s="2" t="inlineStr">
@@ -27063,12 +27063,12 @@
       </c>
       <c r="C565" s="3" t="inlineStr">
         <is>
-          <t>Supervisor civil - obra</t>
+          <t>Ejecutivo/ade ingeniera</t>
         </is>
       </c>
       <c r="D565" s="3" t="inlineStr">
         <is>
-          <t>CONCONCRETO S.A.</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E565" s="8" t="n">
@@ -27080,7 +27080,7 @@
         </is>
       </c>
       <c r="G565" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/supervisor-civil-obra-1886750435", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-ade-ingeniera-1886752134", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H565" s="6" t="inlineStr"/>
@@ -27099,7 +27099,7 @@
     <row r="566" ht="22" customHeight="1">
       <c r="A566" s="2" t="inlineStr">
         <is>
-          <t>78244d2897084f6a</t>
+          <t>7d4067502e572780</t>
         </is>
       </c>
       <c r="B566" s="2" t="inlineStr">
@@ -27109,7 +27109,7 @@
       </c>
       <c r="C566" s="3" t="inlineStr">
         <is>
-          <t>Ingeniera comercial sector industrial - cali</t>
+          <t>Ingeniera de ventas - cali</t>
         </is>
       </c>
       <c r="D566" s="3" t="inlineStr">
@@ -27126,7 +27126,7 @@
         </is>
       </c>
       <c r="G566" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-comercial-sector-industrial-cali-1886753949", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-de-ventas-cali-1886754430", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H566" s="6" t="inlineStr"/>
@@ -27145,7 +27145,7 @@
     <row r="567" ht="22" customHeight="1">
       <c r="A567" s="2" t="inlineStr">
         <is>
-          <t>a4d1239b8910f7cf</t>
+          <t>a3a688084650de1c</t>
         </is>
       </c>
       <c r="B567" s="2" t="inlineStr">
@@ -27155,7 +27155,7 @@
       </c>
       <c r="C567" s="3" t="inlineStr">
         <is>
-          <t>Ingeniera electrica comercial - bogotá</t>
+          <t>Ingeniera comercial electrica - cali</t>
         </is>
       </c>
       <c r="D567" s="3" t="inlineStr">
@@ -27172,7 +27172,7 @@
         </is>
       </c>
       <c r="G567" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-electrica-comercial-bogota-1886756984", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-comercial-electrica-cali-1886752104", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H567" s="6" t="inlineStr"/>
@@ -27191,7 +27191,7 @@
     <row r="568" ht="22" customHeight="1">
       <c r="A568" s="2" t="inlineStr">
         <is>
-          <t>366f049dd1eaf173</t>
+          <t>359d47915a2e74e6</t>
         </is>
       </c>
       <c r="B568" s="2" t="inlineStr">
@@ -27201,12 +27201,12 @@
       </c>
       <c r="C568" s="3" t="inlineStr">
         <is>
-          <t>Civil engineering-in-training</t>
+          <t>Supervisor civil - obra</t>
         </is>
       </c>
       <c r="D568" s="3" t="inlineStr">
         <is>
-          <t>WSP COLOMBIA SAS</t>
+          <t>CONCONCRETO S.A.</t>
         </is>
       </c>
       <c r="E568" s="8" t="n">
@@ -27218,7 +27218,7 @@
         </is>
       </c>
       <c r="G568" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/civil-engineeringintraining-1886759044", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/supervisor-civil-obra-1886750435", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H568" s="6" t="inlineStr"/>
@@ -27237,7 +27237,7 @@
     <row r="569" ht="22" customHeight="1">
       <c r="A569" s="2" t="inlineStr">
         <is>
-          <t>555a755e56fc6a80</t>
+          <t>78244d2897084f6a</t>
         </is>
       </c>
       <c r="B569" s="2" t="inlineStr">
@@ -27247,12 +27247,12 @@
       </c>
       <c r="C569" s="3" t="inlineStr">
         <is>
-          <t>Civil engineering-in-training</t>
+          <t>Ingeniera comercial sector industrial - cali</t>
         </is>
       </c>
       <c r="D569" s="3" t="inlineStr">
         <is>
-          <t>WSP COLOMBIA SAS</t>
+          <t>PIPOL EXPERT SAS</t>
         </is>
       </c>
       <c r="E569" s="8" t="n">
@@ -27264,7 +27264,7 @@
         </is>
       </c>
       <c r="G569" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/civil-engineeringintraining-1886758755", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-comercial-sector-industrial-cali-1886753949", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H569" s="6" t="inlineStr"/>
@@ -27283,7 +27283,7 @@
     <row r="570" ht="22" customHeight="1">
       <c r="A570" s="2" t="inlineStr">
         <is>
-          <t>776483d4ec602e40</t>
+          <t>a4d1239b8910f7cf</t>
         </is>
       </c>
       <c r="B570" s="2" t="inlineStr">
@@ -27293,12 +27293,12 @@
       </c>
       <c r="C570" s="3" t="inlineStr">
         <is>
-          <t>Consultor senior sap pm - remoto colombia</t>
+          <t>Ingeniera electrica comercial - bogotá</t>
         </is>
       </c>
       <c r="D570" s="3" t="inlineStr">
         <is>
-          <t>TALYCAP GLOBAL SAS</t>
+          <t>PIPOL EXPERT SAS</t>
         </is>
       </c>
       <c r="E570" s="8" t="n">
@@ -27310,7 +27310,7 @@
         </is>
       </c>
       <c r="G570" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultor-senior-sap-pm-remoto-colombia-1886747903", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-electrica-comercial-bogota-1886756984", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H570" s="6" t="inlineStr"/>
@@ -27329,7 +27329,7 @@
     <row r="571" ht="22" customHeight="1">
       <c r="A571" s="2" t="inlineStr">
         <is>
-          <t>b1cfe269bbc00011</t>
+          <t>366f049dd1eaf173</t>
         </is>
       </c>
       <c r="B571" s="2" t="inlineStr">
@@ -27339,12 +27339,12 @@
       </c>
       <c r="C571" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de interventoría</t>
+          <t>Civil engineering-in-training</t>
         </is>
       </c>
       <c r="D571" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>WSP COLOMBIA SAS</t>
         </is>
       </c>
       <c r="E571" s="8" t="n">
@@ -27356,7 +27356,7 @@
         </is>
       </c>
       <c r="G571" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-interventoria-1886751671", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/civil-engineeringintraining-1886759044", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H571" s="6" t="inlineStr"/>
@@ -27375,7 +27375,7 @@
     <row r="572" ht="22" customHeight="1">
       <c r="A572" s="2" t="inlineStr">
         <is>
-          <t>b7a3423e1ee1e624</t>
+          <t>555a755e56fc6a80</t>
         </is>
       </c>
       <c r="B572" s="2" t="inlineStr">
@@ -27385,12 +27385,12 @@
       </c>
       <c r="C572" s="3" t="inlineStr">
         <is>
-          <t>Especialista en urbanismo - proyecto vial</t>
+          <t>Civil engineering-in-training</t>
         </is>
       </c>
       <c r="D572" s="3" t="inlineStr">
         <is>
-          <t>INGEPLAN.CO SAS EMPRESA DE BENEFICIO E INTERES COLECTIVO BIC</t>
+          <t>WSP COLOMBIA SAS</t>
         </is>
       </c>
       <c r="E572" s="8" t="n">
@@ -27402,7 +27402,7 @@
         </is>
       </c>
       <c r="G572" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-urbanismo-proyecto-vial-1886755827", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/civil-engineeringintraining-1886758755", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H572" s="6" t="inlineStr"/>
@@ -27421,7 +27421,7 @@
     <row r="573" ht="22" customHeight="1">
       <c r="A573" s="2" t="inlineStr">
         <is>
-          <t>fcb39d755657052e</t>
+          <t>776483d4ec602e40</t>
         </is>
       </c>
       <c r="B573" s="2" t="inlineStr">
@@ -27431,12 +27431,12 @@
       </c>
       <c r="C573" s="3" t="inlineStr">
         <is>
-          <t>Coordinador hseq</t>
+          <t>Consultor senior sap pm - remoto colombia</t>
         </is>
       </c>
       <c r="D573" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>TALYCAP GLOBAL SAS</t>
         </is>
       </c>
       <c r="E573" s="8" t="n">
@@ -27448,13 +27448,13 @@
         </is>
       </c>
       <c r="G573" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-1886747304", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultor-senior-sap-pm-remoto-colombia-1886747903", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H573" s="6" t="inlineStr"/>
       <c r="I573" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J573" s="2" t="inlineStr">
@@ -27467,7 +27467,7 @@
     <row r="574" ht="22" customHeight="1">
       <c r="A574" s="2" t="inlineStr">
         <is>
-          <t>9e2f0c16f1a50983</t>
+          <t>b1cfe269bbc00011</t>
         </is>
       </c>
       <c r="B574" s="2" t="inlineStr">
@@ -27477,7 +27477,7 @@
       </c>
       <c r="C574" s="3" t="inlineStr">
         <is>
-          <t>Coordinador hseq</t>
+          <t>Coordinador de interventoría</t>
         </is>
       </c>
       <c r="D574" s="3" t="inlineStr">
@@ -27494,13 +27494,13 @@
         </is>
       </c>
       <c r="G574" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-1886764155", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-interventoria-1886751671", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H574" s="6" t="inlineStr"/>
       <c r="I574" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J574" s="2" t="inlineStr">
@@ -27513,7 +27513,7 @@
     <row r="575" ht="22" customHeight="1">
       <c r="A575" s="2" t="inlineStr">
         <is>
-          <t>9d4d87a631d5e8b8</t>
+          <t>b7a3423e1ee1e624</t>
         </is>
       </c>
       <c r="B575" s="2" t="inlineStr">
@@ -27523,12 +27523,12 @@
       </c>
       <c r="C575" s="3" t="inlineStr">
         <is>
-          <t>Coordinador hseq</t>
+          <t>Especialista en urbanismo - proyecto vial</t>
         </is>
       </c>
       <c r="D575" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>INGEPLAN.CO SAS EMPRESA DE BENEFICIO E INTERES COLECTIVO BIC</t>
         </is>
       </c>
       <c r="E575" s="8" t="n">
@@ -27540,13 +27540,13 @@
         </is>
       </c>
       <c r="G575" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-1886760733", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-urbanismo-proyecto-vial-1886755827", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H575" s="6" t="inlineStr"/>
       <c r="I575" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J575" s="2" t="inlineStr">
@@ -27559,7 +27559,7 @@
     <row r="576" ht="22" customHeight="1">
       <c r="A576" s="2" t="inlineStr">
         <is>
-          <t>62d6690ef260f268</t>
+          <t>fcb39d755657052e</t>
         </is>
       </c>
       <c r="B576" s="2" t="inlineStr">
@@ -27569,12 +27569,12 @@
       </c>
       <c r="C576" s="3" t="inlineStr">
         <is>
-          <t>Coordinador hseq cartagena</t>
+          <t>Coordinador hseq</t>
         </is>
       </c>
       <c r="D576" s="3" t="inlineStr">
         <is>
-          <t>APPLUS NORCONTROL COLOMBIA LTDA</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E576" s="8" t="n">
@@ -27586,7 +27586,7 @@
         </is>
       </c>
       <c r="G576" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-cartagena-1886754661", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-1886747304", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H576" s="6" t="inlineStr"/>
@@ -27605,7 +27605,7 @@
     <row r="577" ht="22" customHeight="1">
       <c r="A577" s="2" t="inlineStr">
         <is>
-          <t>6e57e2acbfc11d12</t>
+          <t>9e2f0c16f1a50983</t>
         </is>
       </c>
       <c r="B577" s="2" t="inlineStr">
@@ -27615,7 +27615,7 @@
       </c>
       <c r="C577" s="3" t="inlineStr">
         <is>
-          <t>Especialista sig</t>
+          <t>Coordinador hseq</t>
         </is>
       </c>
       <c r="D577" s="3" t="inlineStr">
@@ -27632,13 +27632,13 @@
         </is>
       </c>
       <c r="G577" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-sig-1886757094", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-1886764155", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H577" s="6" t="inlineStr"/>
       <c r="I577" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J577" s="2" t="inlineStr">
@@ -27651,7 +27651,7 @@
     <row r="578" ht="22" customHeight="1">
       <c r="A578" s="2" t="inlineStr">
         <is>
-          <t>11494a184e6f9290</t>
+          <t>9d4d87a631d5e8b8</t>
         </is>
       </c>
       <c r="B578" s="2" t="inlineStr">
@@ -27661,7 +27661,7 @@
       </c>
       <c r="C578" s="3" t="inlineStr">
         <is>
-          <t>Especialista en ingeniería civil - coordinador técnico</t>
+          <t>Coordinador hseq</t>
         </is>
       </c>
       <c r="D578" s="3" t="inlineStr">
@@ -27678,13 +27678,13 @@
         </is>
       </c>
       <c r="G578" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-ingenieria-civil-coordinador-tecnico-honduras-1886745304", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-1886760733", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H578" s="6" t="inlineStr"/>
       <c r="I578" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J578" s="2" t="inlineStr">
@@ -27697,7 +27697,7 @@
     <row r="579" ht="22" customHeight="1">
       <c r="A579" s="2" t="inlineStr">
         <is>
-          <t>327c6d2b54619849</t>
+          <t>62d6690ef260f268</t>
         </is>
       </c>
       <c r="B579" s="2" t="inlineStr">
@@ -27707,12 +27707,12 @@
       </c>
       <c r="C579" s="3" t="inlineStr">
         <is>
-          <t>Especialista en psiquiatría</t>
+          <t>Coordinador hseq cartagena</t>
         </is>
       </c>
       <c r="D579" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>APPLUS NORCONTROL COLOMBIA LTDA</t>
         </is>
       </c>
       <c r="E579" s="8" t="n">
@@ -27724,13 +27724,13 @@
         </is>
       </c>
       <c r="G579" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-psiquiatria-1886757353", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-cartagena-1886754661", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H579" s="6" t="inlineStr"/>
       <c r="I579" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J579" s="2" t="inlineStr">
@@ -27743,7 +27743,7 @@
     <row r="580" ht="22" customHeight="1">
       <c r="A580" s="2" t="inlineStr">
         <is>
-          <t>b637f33f588eb5ae</t>
+          <t>6e57e2acbfc11d12</t>
         </is>
       </c>
       <c r="B580" s="2" t="inlineStr">
@@ -27753,7 +27753,7 @@
       </c>
       <c r="C580" s="3" t="inlineStr">
         <is>
-          <t>Especialista en diseño hospitalario</t>
+          <t>Especialista sig</t>
         </is>
       </c>
       <c r="D580" s="3" t="inlineStr">
@@ -27770,7 +27770,7 @@
         </is>
       </c>
       <c r="G580" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-diseno-hospitalario-disponibilidad-viajar-a-peru-1886747220", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-sig-1886757094", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H580" s="6" t="inlineStr"/>
@@ -27789,7 +27789,7 @@
     <row r="581" ht="22" customHeight="1">
       <c r="A581" s="2" t="inlineStr">
         <is>
-          <t>adcc2b47284b5d4d</t>
+          <t>11494a184e6f9290</t>
         </is>
       </c>
       <c r="B581" s="2" t="inlineStr">
@@ -27799,12 +27799,12 @@
       </c>
       <c r="C581" s="3" t="inlineStr">
         <is>
-          <t>Analista de diseño e ingeniería de empaque - sector farmaceutico</t>
+          <t>Especialista en ingeniería civil - coordinador técnico</t>
         </is>
       </c>
       <c r="D581" s="3" t="inlineStr">
         <is>
-          <t>LABORATORIOS BUSSIE</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E581" s="8" t="n">
@@ -27816,7 +27816,7 @@
         </is>
       </c>
       <c r="G581" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-diseno-e-ingenieria-de-empaque-sector-farmaceutico-1886755492", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-ingenieria-civil-coordinador-tecnico-honduras-1886745304", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H581" s="6" t="inlineStr"/>
@@ -27835,7 +27835,7 @@
     <row r="582" ht="22" customHeight="1">
       <c r="A582" s="2" t="inlineStr">
         <is>
-          <t>3ec3d2d34753ff04</t>
+          <t>327c6d2b54619849</t>
         </is>
       </c>
       <c r="B582" s="2" t="inlineStr">
@@ -27845,12 +27845,12 @@
       </c>
       <c r="C582" s="3" t="inlineStr">
         <is>
-          <t>Especialista de diseño y arquitectura</t>
+          <t>Especialista en psiquiatría</t>
         </is>
       </c>
       <c r="D582" s="3" t="inlineStr">
         <is>
-          <t>INTER RAPIDISIMO</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E582" s="8" t="n">
@@ -27862,7 +27862,7 @@
         </is>
       </c>
       <c r="G582" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-de-diseno-y-arquitectura-1886761909", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-psiquiatria-1886757353", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H582" s="6" t="inlineStr"/>
@@ -27881,7 +27881,7 @@
     <row r="583" ht="22" customHeight="1">
       <c r="A583" s="2" t="inlineStr">
         <is>
-          <t>4e917305e90b3efa</t>
+          <t>b637f33f588eb5ae</t>
         </is>
       </c>
       <c r="B583" s="2" t="inlineStr">
@@ -27891,12 +27891,12 @@
       </c>
       <c r="C583" s="3" t="inlineStr">
         <is>
-          <t>Especialista en geología</t>
+          <t>Especialista en diseño hospitalario</t>
         </is>
       </c>
       <c r="D583" s="3" t="inlineStr">
         <is>
-          <t>INGEPLAN.CO SAS EMPRESA DE BENEFICIO E INTERES COLECTIVO BIC</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E583" s="8" t="n">
@@ -27908,7 +27908,7 @@
         </is>
       </c>
       <c r="G583" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-geologia-1886761263", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-diseno-hospitalario-disponibilidad-viajar-a-peru-1886747220", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H583" s="6" t="inlineStr"/>
@@ -27927,7 +27927,7 @@
     <row r="584" ht="22" customHeight="1">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>1aef5476d70bbe42</t>
+          <t>adcc2b47284b5d4d</t>
         </is>
       </c>
       <c r="B584" s="2" t="inlineStr">
@@ -27937,12 +27937,12 @@
       </c>
       <c r="C584" s="3" t="inlineStr">
         <is>
-          <t>Especialista en geología</t>
+          <t>Analista de diseño e ingeniería de empaque - sector farmaceutico</t>
         </is>
       </c>
       <c r="D584" s="3" t="inlineStr">
         <is>
-          <t>INGEPLAN.CO SAS EMPRESA DE BENEFICIO E INTERES COLECTIVO BIC</t>
+          <t>LABORATORIOS BUSSIE</t>
         </is>
       </c>
       <c r="E584" s="8" t="n">
@@ -27954,7 +27954,7 @@
         </is>
       </c>
       <c r="G584" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-geologia-1886755729", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-diseno-e-ingenieria-de-empaque-sector-farmaceutico-1886755492", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H584" s="6" t="inlineStr"/>
@@ -27973,7 +27973,7 @@
     <row r="585" ht="22" customHeight="1">
       <c r="A585" s="2" t="inlineStr">
         <is>
-          <t>b46df3b678599255</t>
+          <t>3ec3d2d34753ff04</t>
         </is>
       </c>
       <c r="B585" s="2" t="inlineStr">
@@ -27983,12 +27983,12 @@
       </c>
       <c r="C585" s="3" t="inlineStr">
         <is>
-          <t>Especialista en estructuras</t>
+          <t>Especialista de diseño y arquitectura</t>
         </is>
       </c>
       <c r="D585" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>INTER RAPIDISIMO</t>
         </is>
       </c>
       <c r="E585" s="8" t="n">
@@ -28000,7 +28000,7 @@
         </is>
       </c>
       <c r="G585" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-estructuras-1886757080", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-de-diseno-y-arquitectura-1886761909", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H585" s="6" t="inlineStr"/>
@@ -28019,7 +28019,7 @@
     <row r="586" ht="22" customHeight="1">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>935035bdfa2ae0b7</t>
+          <t>4e917305e90b3efa</t>
         </is>
       </c>
       <c r="B586" s="2" t="inlineStr">
@@ -28029,7 +28029,7 @@
       </c>
       <c r="C586" s="3" t="inlineStr">
         <is>
-          <t>Especialista en gestión del riesgo</t>
+          <t>Especialista en geología</t>
         </is>
       </c>
       <c r="D586" s="3" t="inlineStr">
@@ -28046,7 +28046,7 @@
         </is>
       </c>
       <c r="G586" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-gestion-del-riesgo-1886755709", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-geologia-1886761263", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H586" s="6" t="inlineStr"/>
@@ -28065,7 +28065,7 @@
     <row r="587" ht="22" customHeight="1">
       <c r="A587" s="2" t="inlineStr">
         <is>
-          <t>14a1c964238340ba</t>
+          <t>1aef5476d70bbe42</t>
         </is>
       </c>
       <c r="B587" s="2" t="inlineStr">
@@ -28075,12 +28075,12 @@
       </c>
       <c r="C587" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero civil nivel v</t>
+          <t>Especialista en geología</t>
         </is>
       </c>
       <c r="D587" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>INGEPLAN.CO SAS EMPRESA DE BENEFICIO E INTERES COLECTIVO BIC</t>
         </is>
       </c>
       <c r="E587" s="8" t="n">
@@ -28092,7 +28092,7 @@
         </is>
       </c>
       <c r="G587" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-nivel-v-1886758046", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-geologia-1886755729", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H587" s="6" t="inlineStr"/>
@@ -28111,7 +28111,7 @@
     <row r="588" ht="22" customHeight="1">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>740f61bdbaa69d0e</t>
+          <t>b46df3b678599255</t>
         </is>
       </c>
       <c r="B588" s="2" t="inlineStr">
@@ -28121,12 +28121,12 @@
       </c>
       <c r="C588" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de proyectos bilingüe</t>
+          <t>Especialista en estructuras</t>
         </is>
       </c>
       <c r="D588" s="3" t="inlineStr">
         <is>
-          <t>EyS IT SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E588" s="8" t="n">
@@ -28138,7 +28138,7 @@
         </is>
       </c>
       <c r="G588" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-bilingue-1886749343", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-estructuras-1886757080", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H588" s="6" t="inlineStr"/>
@@ -28157,7 +28157,7 @@
     <row r="589" ht="22" customHeight="1">
       <c r="A589" s="2" t="inlineStr">
         <is>
-          <t>63ef229552018ccd</t>
+          <t>935035bdfa2ae0b7</t>
         </is>
       </c>
       <c r="B589" s="2" t="inlineStr">
@@ -28167,12 +28167,12 @@
       </c>
       <c r="C589" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de proyectos</t>
+          <t>Especialista en gestión del riesgo</t>
         </is>
       </c>
       <c r="D589" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>INGEPLAN.CO SAS EMPRESA DE BENEFICIO E INTERES COLECTIVO BIC</t>
         </is>
       </c>
       <c r="E589" s="8" t="n">
@@ -28184,7 +28184,7 @@
         </is>
       </c>
       <c r="G589" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-1886748647", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-gestion-del-riesgo-1886755709", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H589" s="6" t="inlineStr"/>
@@ -28203,7 +28203,7 @@
     <row r="590" ht="22" customHeight="1">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>03750e25a7e1c016</t>
+          <t>14a1c964238340ba</t>
         </is>
       </c>
       <c r="B590" s="2" t="inlineStr">
@@ -28213,12 +28213,12 @@
       </c>
       <c r="C590" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de proyectos inmobiliarios</t>
+          <t>Ingeniero civil nivel v</t>
         </is>
       </c>
       <c r="D590" s="3" t="inlineStr">
         <is>
-          <t>GRUPO AR S.A.</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E590" s="8" t="n">
@@ -28230,7 +28230,7 @@
         </is>
       </c>
       <c r="G590" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-inmobiliarios-1886745877", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-nivel-v-1886758046", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H590" s="6" t="inlineStr"/>
@@ -28249,7 +28249,7 @@
     <row r="591" ht="22" customHeight="1">
       <c r="A591" s="2" t="inlineStr">
         <is>
-          <t>5627e52731a73f27</t>
+          <t>740f61bdbaa69d0e</t>
         </is>
       </c>
       <c r="B591" s="2" t="inlineStr">
@@ -28259,12 +28259,12 @@
       </c>
       <c r="C591" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de proyectos inmobiliarios</t>
+          <t>Coordinador de proyectos bilingüe</t>
         </is>
       </c>
       <c r="D591" s="3" t="inlineStr">
         <is>
-          <t>GRUPO AR S.A.</t>
+          <t>EyS IT SAS</t>
         </is>
       </c>
       <c r="E591" s="8" t="n">
@@ -28276,7 +28276,7 @@
         </is>
       </c>
       <c r="G591" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-inmobiliarios-1886704948", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-bilingue-1886749343", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H591" s="6" t="inlineStr"/>
@@ -28295,7 +28295,7 @@
     <row r="592" ht="22" customHeight="1">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>b6af0024900baff6</t>
+          <t>63ef229552018ccd</t>
         </is>
       </c>
       <c r="B592" s="2" t="inlineStr">
@@ -28305,12 +28305,12 @@
       </c>
       <c r="C592" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero residente - ingeniero civil-cordoba</t>
+          <t>Coordinador de proyectos</t>
         </is>
       </c>
       <c r="D592" s="3" t="inlineStr">
         <is>
-          <t>OBCIPOL SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E592" s="8" t="n">
@@ -28322,7 +28322,7 @@
         </is>
       </c>
       <c r="G592" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-residente-ingeniero-civilcordoba-1886763488", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-1886748647", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H592" s="6" t="inlineStr"/>
@@ -28341,7 +28341,7 @@
     <row r="593" ht="22" customHeight="1">
       <c r="A593" s="2" t="inlineStr">
         <is>
-          <t>2a0453695fa88728</t>
+          <t>03750e25a7e1c016</t>
         </is>
       </c>
       <c r="B593" s="2" t="inlineStr">
@@ -28351,12 +28351,12 @@
       </c>
       <c r="C593" s="3" t="inlineStr">
         <is>
-          <t>Profesional ingenieria mecanica</t>
+          <t>Coordinador de proyectos inmobiliarios</t>
         </is>
       </c>
       <c r="D593" s="3" t="inlineStr">
         <is>
-          <t>INZIGNIA CONSTRUCTION S.A</t>
+          <t>GRUPO AR S.A.</t>
         </is>
       </c>
       <c r="E593" s="8" t="n">
@@ -28368,7 +28368,7 @@
         </is>
       </c>
       <c r="G593" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/profesional-ingenieria-mecanica-1886767282", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-inmobiliarios-1886745877", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H593" s="6" t="inlineStr"/>
@@ -28387,7 +28387,7 @@
     <row r="594" ht="22" customHeight="1">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>edfe98c543194667</t>
+          <t>5627e52731a73f27</t>
         </is>
       </c>
       <c r="B594" s="2" t="inlineStr">
@@ -28397,12 +28397,12 @@
       </c>
       <c r="C594" s="3" t="inlineStr">
         <is>
-          <t>Jefe de sst - nemocón - 1625991634-135</t>
+          <t>Coordinador de proyectos inmobiliarios</t>
         </is>
       </c>
       <c r="D594" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>GRUPO AR S.A.</t>
         </is>
       </c>
       <c r="E594" s="8" t="n">
@@ -28414,13 +28414,13 @@
         </is>
       </c>
       <c r="G594" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/jefe-de-sst-nemocon-1625991634135-1886754873", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-inmobiliarios-1886704948", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H594" s="6" t="inlineStr"/>
       <c r="I594" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J594" s="2" t="inlineStr">
@@ -28433,7 +28433,7 @@
     <row r="595" ht="22" customHeight="1">
       <c r="A595" s="2" t="inlineStr">
         <is>
-          <t>6233e93ceb1dbeed</t>
+          <t>b6af0024900baff6</t>
         </is>
       </c>
       <c r="B595" s="2" t="inlineStr">
@@ -28443,12 +28443,12 @@
       </c>
       <c r="C595" s="3" t="inlineStr">
         <is>
-          <t>Jefe de sst- nemocón</t>
+          <t>Ingeniero residente - ingeniero civil-cordoba</t>
         </is>
       </c>
       <c r="D595" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>OBCIPOL SAS</t>
         </is>
       </c>
       <c r="E595" s="8" t="n">
@@ -28460,13 +28460,13 @@
         </is>
       </c>
       <c r="G595" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/jefe-de-sst-nemocon-1886757757", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-residente-ingeniero-civilcordoba-1886763488", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H595" s="6" t="inlineStr"/>
       <c r="I595" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J595" s="2" t="inlineStr">
@@ -28479,7 +28479,7 @@
     <row r="596" ht="22" customHeight="1">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>ce75aab7a32f36a3</t>
+          <t>2a0453695fa88728</t>
         </is>
       </c>
       <c r="B596" s="2" t="inlineStr">
@@ -28489,12 +28489,12 @@
       </c>
       <c r="C596" s="3" t="inlineStr">
         <is>
-          <t>Coordinador talento humano y sst - bogota- 1626427532-7</t>
+          <t>Profesional ingenieria mecanica</t>
         </is>
       </c>
       <c r="D596" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>INZIGNIA CONSTRUCTION S.A</t>
         </is>
       </c>
       <c r="E596" s="8" t="n">
@@ -28506,13 +28506,13 @@
         </is>
       </c>
       <c r="G596" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-talento-humano-y-sst-bogota-16264275327-1886753531", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/profesional-ingenieria-mecanica-1886767282", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H596" s="6" t="inlineStr"/>
       <c r="I596" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J596" s="2" t="inlineStr">
@@ -28525,7 +28525,7 @@
     <row r="597" ht="22" customHeight="1">
       <c r="A597" s="2" t="inlineStr">
         <is>
-          <t>850731f7bb6cd73f</t>
+          <t>edfe98c543194667</t>
         </is>
       </c>
       <c r="B597" s="2" t="inlineStr">
@@ -28535,12 +28535,12 @@
       </c>
       <c r="C597" s="3" t="inlineStr">
         <is>
-          <t>Coordinador(a) de sst y medio ambiente</t>
+          <t>Jefe de sst - nemocón - 1625991634-135</t>
         </is>
       </c>
       <c r="D597" s="3" t="inlineStr">
         <is>
-          <t>ATIEMPO S.A.S</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E597" s="8" t="n">
@@ -28552,7 +28552,7 @@
         </is>
       </c>
       <c r="G597" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinadora-de-sst-y-medio-ambiente-1886759848", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/jefe-de-sst-nemocon-1625991634135-1886754873", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H597" s="6" t="inlineStr"/>
@@ -28571,7 +28571,7 @@
     <row r="598" ht="22" customHeight="1">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>abaf8e513787b3f3</t>
+          <t>6233e93ceb1dbeed</t>
         </is>
       </c>
       <c r="B598" s="2" t="inlineStr">
@@ -28581,7 +28581,7 @@
       </c>
       <c r="C598" s="3" t="inlineStr">
         <is>
-          <t>Coordinador pesv</t>
+          <t>Jefe de sst- nemocón</t>
         </is>
       </c>
       <c r="D598" s="3" t="inlineStr">
@@ -28598,13 +28598,13 @@
         </is>
       </c>
       <c r="G598" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-pesv-1886769643", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/jefe-de-sst-nemocon-1886757757", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H598" s="6" t="inlineStr"/>
       <c r="I598" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J598" s="2" t="inlineStr">
@@ -28617,7 +28617,7 @@
     <row r="599" ht="22" customHeight="1">
       <c r="A599" s="2" t="inlineStr">
         <is>
-          <t>9dcdf501e5912b88</t>
+          <t>ce75aab7a32f36a3</t>
         </is>
       </c>
       <c r="B599" s="2" t="inlineStr">
@@ -28627,7 +28627,7 @@
       </c>
       <c r="C599" s="3" t="inlineStr">
         <is>
-          <t>Tecnico de obras civiles /girardot ref. 339166-82241</t>
+          <t>Coordinador talento humano y sst - bogota- 1626427532-7</t>
         </is>
       </c>
       <c r="D599" s="3" t="inlineStr">
@@ -28644,13 +28644,13 @@
         </is>
       </c>
       <c r="G599" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/tecnico-de-obras-civiles-girardot-ref-33916682241-1886747302", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-talento-humano-y-sst-bogota-16264275327-1886753531", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H599" s="6" t="inlineStr"/>
       <c r="I599" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J599" s="2" t="inlineStr">
@@ -28663,7 +28663,7 @@
     <row r="600" ht="22" customHeight="1">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>693b8a076a888f67</t>
+          <t>850731f7bb6cd73f</t>
         </is>
       </c>
       <c r="B600" s="2" t="inlineStr">
@@ -28673,12 +28673,12 @@
       </c>
       <c r="C600" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero civil - especializacion en estructuras</t>
+          <t>Coordinador(a) de sst y medio ambiente</t>
         </is>
       </c>
       <c r="D600" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ATIEMPO S.A.S</t>
         </is>
       </c>
       <c r="E600" s="8" t="n">
@@ -28690,13 +28690,13 @@
         </is>
       </c>
       <c r="G600" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-especializacion-en-estructuras-1886766956", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinadora-de-sst-y-medio-ambiente-1886759848", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H600" s="6" t="inlineStr"/>
       <c r="I600" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J600" s="2" t="inlineStr">
@@ -28709,7 +28709,7 @@
     <row r="601" ht="22" customHeight="1">
       <c r="A601" s="2" t="inlineStr">
         <is>
-          <t>13bc527565632878</t>
+          <t>abaf8e513787b3f3</t>
         </is>
       </c>
       <c r="B601" s="2" t="inlineStr">
@@ -28719,7 +28719,7 @@
       </c>
       <c r="C601" s="3" t="inlineStr">
         <is>
-          <t>Tecnico en contratacion de obra civil bogota</t>
+          <t>Coordinador pesv</t>
         </is>
       </c>
       <c r="D601" s="3" t="inlineStr">
@@ -28736,13 +28736,13 @@
         </is>
       </c>
       <c r="G601" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/tecnico-en-contratacion-de-obra-civil-bogota-1886759693", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-pesv-1886769643", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H601" s="6" t="inlineStr"/>
       <c r="I601" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J601" s="2" t="inlineStr">
@@ -28755,7 +28755,7 @@
     <row r="602" ht="22" customHeight="1">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>6ccccd3a1ba05f7f</t>
+          <t>9dcdf501e5912b88</t>
         </is>
       </c>
       <c r="B602" s="2" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="C602" s="3" t="inlineStr">
         <is>
-          <t>14561-especialista interventoria-bogota</t>
+          <t>Tecnico de obras civiles /girardot ref. 339166-82241</t>
         </is>
       </c>
       <c r="D602" s="3" t="inlineStr">
         <is>
-          <t>APPLUS NORCONTROL COLOMBIA LTDA</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E602" s="8" t="n">
@@ -28782,7 +28782,7 @@
         </is>
       </c>
       <c r="G602" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/14561especialista-interventoriabogota-1886768886", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/tecnico-de-obras-civiles-girardot-ref-33916682241-1886747302", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H602" s="6" t="inlineStr"/>
@@ -28801,7 +28801,7 @@
     <row r="603" ht="22" customHeight="1">
       <c r="A603" s="2" t="inlineStr">
         <is>
-          <t>8ad0c11c4f07472e</t>
+          <t>693b8a076a888f67</t>
         </is>
       </c>
       <c r="B603" s="2" t="inlineStr">
@@ -28811,12 +28811,12 @@
       </c>
       <c r="C603" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero Civil / Terracerías</t>
+          <t>Ingeniero civil - especializacion en estructuras</t>
         </is>
       </c>
       <c r="D603" s="3" t="inlineStr">
         <is>
-          <t>EOSOL</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E603" s="8" t="n">
@@ -28828,7 +28828,7 @@
         </is>
       </c>
       <c r="G603" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-civil-terracer%C3%ADas-at-eosol-4445793534", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-especializacion-en-estructuras-1886766956", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H603" s="6" t="inlineStr"/>
@@ -28847,7 +28847,7 @@
     <row r="604" ht="22" customHeight="1">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>ed46085f88d06bf5</t>
+          <t>13bc527565632878</t>
         </is>
       </c>
       <c r="B604" s="2" t="inlineStr">
@@ -28857,12 +28857,12 @@
       </c>
       <c r="C604" s="3" t="inlineStr">
         <is>
-          <t>Supervisor Civil</t>
+          <t>Tecnico en contratacion de obra civil bogota</t>
         </is>
       </c>
       <c r="D604" s="3" t="inlineStr">
         <is>
-          <t>EOSOL</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E604" s="8" t="n">
@@ -28874,7 +28874,7 @@
         </is>
       </c>
       <c r="G604" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/supervisor-civil-at-eosol-4442238964", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/tecnico-en-contratacion-de-obra-civil-bogota-1886759693", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H604" s="6" t="inlineStr"/>
@@ -28893,7 +28893,7 @@
     <row r="605" ht="22" customHeight="1">
       <c r="A605" s="2" t="inlineStr">
         <is>
-          <t>dc949850c44ae2c9</t>
+          <t>6ccccd3a1ba05f7f</t>
         </is>
       </c>
       <c r="B605" s="2" t="inlineStr">
@@ -28903,12 +28903,12 @@
       </c>
       <c r="C605" s="3" t="inlineStr">
         <is>
-          <t>Civil Engineer</t>
+          <t>14561-especialista interventoria-bogota</t>
         </is>
       </c>
       <c r="D605" s="3" t="inlineStr">
         <is>
-          <t>Cresta</t>
+          <t>APPLUS NORCONTROL COLOMBIA LTDA</t>
         </is>
       </c>
       <c r="E605" s="8" t="n">
@@ -28920,7 +28920,7 @@
         </is>
       </c>
       <c r="G605" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineer-at-cresta-4465582487", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/14561especialista-interventoriabogota-1886768886", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H605" s="6" t="inlineStr"/>
@@ -28939,7 +28939,7 @@
     <row r="606" ht="22" customHeight="1">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>4ad1a5acabdb8ad3</t>
+          <t>8ad0c11c4f07472e</t>
         </is>
       </c>
       <c r="B606" s="2" t="inlineStr">
@@ -28949,12 +28949,12 @@
       </c>
       <c r="C606" s="3" t="inlineStr">
         <is>
-          <t>Civil BIM Specialist</t>
+          <t>Ingeniero Civil / Terracerías</t>
         </is>
       </c>
       <c r="D606" s="3" t="inlineStr">
         <is>
-          <t>ENG</t>
+          <t>EOSOL</t>
         </is>
       </c>
       <c r="E606" s="8" t="n">
@@ -28966,7 +28966,7 @@
         </is>
       </c>
       <c r="G606" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-bim-specialist-at-eng-4469886677", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-civil-terracer%C3%ADas-at-eosol-4445793534", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H606" s="6" t="inlineStr"/>
@@ -28985,7 +28985,7 @@
     <row r="607" ht="22" customHeight="1">
       <c r="A607" s="2" t="inlineStr">
         <is>
-          <t>5ebaba0a0c9927fb</t>
+          <t>ed46085f88d06bf5</t>
         </is>
       </c>
       <c r="B607" s="2" t="inlineStr">
@@ -28995,12 +28995,12 @@
       </c>
       <c r="C607" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero/a Civil-Estructuras Hormigón/Acero</t>
+          <t>Supervisor Civil</t>
         </is>
       </c>
       <c r="D607" s="3" t="inlineStr">
         <is>
-          <t>IDOM Consulting, Engineering, Architecture</t>
+          <t>EOSOL</t>
         </is>
       </c>
       <c r="E607" s="8" t="n">
@@ -29012,7 +29012,7 @@
         </is>
       </c>
       <c r="G607" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-civil-estructuras-hormig%C3%B3n-acero-at-idom-consulting-engineering-architecture-4462998187", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/supervisor-civil-at-eosol-4442238964", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H607" s="6" t="inlineStr"/>
@@ -29031,7 +29031,7 @@
     <row r="608" ht="22" customHeight="1">
       <c r="A608" s="2" t="inlineStr">
         <is>
-          <t>5c954c66c2c9d655</t>
+          <t>dc949850c44ae2c9</t>
         </is>
       </c>
       <c r="B608" s="2" t="inlineStr">
@@ -29041,12 +29041,12 @@
       </c>
       <c r="C608" s="3" t="inlineStr">
         <is>
-          <t>Civil Engineering-in-Training</t>
+          <t>Civil Engineer</t>
         </is>
       </c>
       <c r="D608" s="3" t="inlineStr">
         <is>
-          <t>WSP en Colombia</t>
+          <t>Cresta</t>
         </is>
       </c>
       <c r="E608" s="8" t="n">
@@ -29058,7 +29058,7 @@
         </is>
       </c>
       <c r="G608" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineering-in-training-french-at-wsp-en-colombia-4458430104", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineer-at-cresta-4465582487", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H608" s="6" t="inlineStr"/>
@@ -29077,7 +29077,7 @@
     <row r="609" ht="22" customHeight="1">
       <c r="A609" s="2" t="inlineStr">
         <is>
-          <t>571ae2aa81fa07b5</t>
+          <t>4ad1a5acabdb8ad3</t>
         </is>
       </c>
       <c r="B609" s="2" t="inlineStr">
@@ -29087,12 +29087,12 @@
       </c>
       <c r="C609" s="3" t="inlineStr">
         <is>
-          <t>Civil Engineering-in-Training</t>
+          <t>Civil BIM Specialist</t>
         </is>
       </c>
       <c r="D609" s="3" t="inlineStr">
         <is>
-          <t>WSP en Colombia</t>
+          <t>ENG</t>
         </is>
       </c>
       <c r="E609" s="8" t="n">
@@ -29104,7 +29104,7 @@
         </is>
       </c>
       <c r="G609" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineering-in-training-at-wsp-en-colombia-4458027784", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-bim-specialist-at-eng-4469886677", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H609" s="6" t="inlineStr"/>
@@ -29123,7 +29123,7 @@
     <row r="610" ht="22" customHeight="1">
       <c r="A610" s="2" t="inlineStr">
         <is>
-          <t>d94bcf92627b7b99</t>
+          <t>5ebaba0a0c9927fb</t>
         </is>
       </c>
       <c r="B610" s="2" t="inlineStr">
@@ -29133,12 +29133,12 @@
       </c>
       <c r="C610" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero civil</t>
+          <t>Ingeniero/a Civil-Estructuras Hormigón/Acero</t>
         </is>
       </c>
       <c r="D610" s="3" t="inlineStr">
         <is>
-          <t>HMV Ingenieros</t>
+          <t>IDOM Consulting, Engineering, Architecture</t>
         </is>
       </c>
       <c r="E610" s="8" t="n">
@@ -29150,7 +29150,7 @@
         </is>
       </c>
       <c r="G610" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-civil-at-hmv-ingenieros-4461715824", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-civil-estructuras-hormig%C3%B3n-acero-at-idom-consulting-engineering-architecture-4462998187", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H610" s="6" t="inlineStr"/>
@@ -29169,7 +29169,7 @@
     <row r="611" ht="22" customHeight="1">
       <c r="A611" s="2" t="inlineStr">
         <is>
-          <t>1be0a8e56fa4736b</t>
+          <t>5c954c66c2c9d655</t>
         </is>
       </c>
       <c r="B611" s="2" t="inlineStr">
@@ -29179,12 +29179,12 @@
       </c>
       <c r="C611" s="3" t="inlineStr">
         <is>
-          <t>Civil Engineer</t>
+          <t>Civil Engineering-in-Training</t>
         </is>
       </c>
       <c r="D611" s="3" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>WSP en Colombia</t>
         </is>
       </c>
       <c r="E611" s="8" t="n">
@@ -29196,7 +29196,7 @@
         </is>
       </c>
       <c r="G611" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineer-at-wood-4418961778", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineering-in-training-french-at-wsp-en-colombia-4458430104", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H611" s="6" t="inlineStr"/>
@@ -29215,7 +29215,7 @@
     <row r="612" ht="22" customHeight="1">
       <c r="A612" s="2" t="inlineStr">
         <is>
-          <t>825c4e246cbd6b6b</t>
+          <t>571ae2aa81fa07b5</t>
         </is>
       </c>
       <c r="B612" s="2" t="inlineStr">
@@ -29225,12 +29225,12 @@
       </c>
       <c r="C612" s="3" t="inlineStr">
         <is>
-          <t>Civil Engineering Expert</t>
+          <t>Civil Engineering-in-Training</t>
         </is>
       </c>
       <c r="D612" s="3" t="inlineStr">
         <is>
-          <t>Anyone AI</t>
+          <t>WSP en Colombia</t>
         </is>
       </c>
       <c r="E612" s="8" t="n">
@@ -29242,7 +29242,7 @@
         </is>
       </c>
       <c r="G612" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineering-expert-at-anyone-ai-4462461832", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineering-in-training-at-wsp-en-colombia-4458027784", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H612" s="6" t="inlineStr"/>
@@ -29261,7 +29261,7 @@
     <row r="613" ht="22" customHeight="1">
       <c r="A613" s="2" t="inlineStr">
         <is>
-          <t>76740179a82340ae</t>
+          <t>d94bcf92627b7b99</t>
         </is>
       </c>
       <c r="B613" s="2" t="inlineStr">
@@ -29271,12 +29271,12 @@
       </c>
       <c r="C613" s="3" t="inlineStr">
         <is>
-          <t>Profesional en Ingeniería Civil</t>
+          <t>Ingeniero civil</t>
         </is>
       </c>
       <c r="D613" s="3" t="inlineStr">
         <is>
-          <t>CMH Colombia</t>
+          <t>HMV Ingenieros</t>
         </is>
       </c>
       <c r="E613" s="8" t="n">
@@ -29288,7 +29288,7 @@
         </is>
       </c>
       <c r="G613" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/profesional-en-ingenier%C3%ADa-civil-at-minerales-c%C3%B3rdoba-4450022471", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-civil-at-hmv-ingenieros-4461715824", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H613" s="6" t="inlineStr"/>
@@ -29307,7 +29307,7 @@
     <row r="614" ht="22" customHeight="1">
       <c r="A614" s="2" t="inlineStr">
         <is>
-          <t>5bea04b9e734c2fc</t>
+          <t>1be0a8e56fa4736b</t>
         </is>
       </c>
       <c r="B614" s="2" t="inlineStr">
@@ -29317,12 +29317,12 @@
       </c>
       <c r="C614" s="3" t="inlineStr">
         <is>
-          <t>Coordinador HSEQ</t>
+          <t>Civil Engineer</t>
         </is>
       </c>
       <c r="D614" s="3" t="inlineStr">
         <is>
-          <t>ASSEMTEC</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="E614" s="8" t="n">
@@ -29334,13 +29334,13 @@
         </is>
       </c>
       <c r="G614" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-hseq-at-assemtec-4457664932", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineer-at-wood-4418961778", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H614" s="6" t="inlineStr"/>
       <c r="I614" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J614" s="2" t="inlineStr">
@@ -29353,7 +29353,7 @@
     <row r="615" ht="22" customHeight="1">
       <c r="A615" s="2" t="inlineStr">
         <is>
-          <t>6ba6bae2d7bfb226</t>
+          <t>825c4e246cbd6b6b</t>
         </is>
       </c>
       <c r="B615" s="2" t="inlineStr">
@@ -29363,12 +29363,12 @@
       </c>
       <c r="C615" s="3" t="inlineStr">
         <is>
-          <t>Inspector SST con Licencia, Coordinador de Alturas</t>
+          <t>Civil Engineering Expert</t>
         </is>
       </c>
       <c r="D615" s="3" t="inlineStr">
         <is>
-          <t>Asertempo Colombia S.A.S</t>
+          <t>Anyone AI</t>
         </is>
       </c>
       <c r="E615" s="8" t="n">
@@ -29380,13 +29380,13 @@
         </is>
       </c>
       <c r="G615" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/inspector-sst-con-licencia-coordinador-de-alturas-at-asertempo-colombia-s-a-s-4464408367", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineering-expert-at-anyone-ai-4462461832", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H615" s="6" t="inlineStr"/>
       <c r="I615" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J615" s="2" t="inlineStr">
@@ -29399,7 +29399,7 @@
     <row r="616" ht="22" customHeight="1">
       <c r="A616" s="2" t="inlineStr">
         <is>
-          <t>0df4a63a82189896</t>
+          <t>76740179a82340ae</t>
         </is>
       </c>
       <c r="B616" s="2" t="inlineStr">
@@ -29409,12 +29409,12 @@
       </c>
       <c r="C616" s="3" t="inlineStr">
         <is>
-          <t>Especialista en Salud y Seguridad en el trabajo con especialización en medio Ambiente</t>
+          <t>Profesional en Ingeniería Civil</t>
         </is>
       </c>
       <c r="D616" s="3" t="inlineStr">
         <is>
-          <t>Dextera IT Services</t>
+          <t>CMH Colombia</t>
         </is>
       </c>
       <c r="E616" s="8" t="n">
@@ -29426,7 +29426,7 @@
         </is>
       </c>
       <c r="G616" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/especialista-en-salud-y-seguridad-en-el-trabajo-con-especializaci%C3%B3n-en-medio-ambiente-at-dextera-it-services-4464024362", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/profesional-en-ingenier%C3%ADa-civil-at-minerales-c%C3%B3rdoba-4450022471", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H616" s="6" t="inlineStr"/>
@@ -29445,7 +29445,7 @@
     <row r="617" ht="22" customHeight="1">
       <c r="A617" s="2" t="inlineStr">
         <is>
-          <t>e8e3c75915d1945c</t>
+          <t>5bea04b9e734c2fc</t>
         </is>
       </c>
       <c r="B617" s="2" t="inlineStr">
@@ -29455,12 +29455,12 @@
       </c>
       <c r="C617" s="3" t="inlineStr">
         <is>
-          <t>Coordinador (a) profesional HSEQ</t>
+          <t>Coordinador HSEQ</t>
         </is>
       </c>
       <c r="D617" s="3" t="inlineStr">
         <is>
-          <t>SD SAS</t>
+          <t>ASSEMTEC</t>
         </is>
       </c>
       <c r="E617" s="8" t="n">
@@ -29472,7 +29472,7 @@
         </is>
       </c>
       <c r="G617" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-profesional-hseq-at-sd-sas-4444939872", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-hseq-at-assemtec-4457664932", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H617" s="6" t="inlineStr"/>
@@ -29491,7 +29491,7 @@
     <row r="618" ht="22" customHeight="1">
       <c r="A618" s="2" t="inlineStr">
         <is>
-          <t>fb37fc1bf485e650</t>
+          <t>6ba6bae2d7bfb226</t>
         </is>
       </c>
       <c r="B618" s="2" t="inlineStr">
@@ -29501,12 +29501,12 @@
       </c>
       <c r="C618" s="3" t="inlineStr">
         <is>
-          <t>Técnico de trazado especialista en ISTRAM</t>
+          <t>Inspector SST con Licencia, Coordinador de Alturas</t>
         </is>
       </c>
       <c r="D618" s="3" t="inlineStr">
         <is>
-          <t>EADIC</t>
+          <t>Asertempo Colombia S.A.S</t>
         </is>
       </c>
       <c r="E618" s="8" t="n">
@@ -29518,13 +29518,13 @@
         </is>
       </c>
       <c r="G618" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/t%C3%A9cnico-de-trazado-especialista-en-istram-at-eadic-4468780158", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/inspector-sst-con-licencia-coordinador-de-alturas-at-asertempo-colombia-s-a-s-4464408367", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H618" s="6" t="inlineStr"/>
       <c r="I618" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J618" s="2" t="inlineStr">
@@ -29537,7 +29537,7 @@
     <row r="619" ht="22" customHeight="1">
       <c r="A619" s="2" t="inlineStr">
         <is>
-          <t>0f01a66eb85a1ffd</t>
+          <t>0df4a63a82189896</t>
         </is>
       </c>
       <c r="B619" s="2" t="inlineStr">
@@ -29547,12 +29547,12 @@
       </c>
       <c r="C619" s="3" t="inlineStr">
         <is>
-          <t>AUXILIAR MODELADOR BIM Y DIBUJANTE EN INGENIERÍA CIVIL</t>
+          <t>Especialista en Salud y Seguridad en el trabajo con especialización en medio Ambiente</t>
         </is>
       </c>
       <c r="D619" s="3" t="inlineStr">
         <is>
-          <t>Antea Group España y Latinoamérica</t>
+          <t>Dextera IT Services</t>
         </is>
       </c>
       <c r="E619" s="8" t="n">
@@ -29564,7 +29564,7 @@
         </is>
       </c>
       <c r="G619" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-modelador-bim-y-dibujante-en-ingenier%C3%ADa-civil-at-antea-group-espa%C3%B1a-y-latinoam%C3%A9rica-4467605615", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/especialista-en-salud-y-seguridad-en-el-trabajo-con-especializaci%C3%B3n-en-medio-ambiente-at-dextera-it-services-4464024362", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H619" s="6" t="inlineStr"/>
@@ -29583,7 +29583,7 @@
     <row r="620" ht="22" customHeight="1">
       <c r="A620" s="2" t="inlineStr">
         <is>
-          <t>cba614af5ce1fc3a</t>
+          <t>e8e3c75915d1945c</t>
         </is>
       </c>
       <c r="B620" s="2" t="inlineStr">
@@ -29593,12 +29593,12 @@
       </c>
       <c r="C620" s="3" t="inlineStr">
         <is>
-          <t>Principal Pavement Engineer - Linear Infrastructure &amp; Site Civils</t>
+          <t>Coordinador (a) profesional HSEQ</t>
         </is>
       </c>
       <c r="D620" s="3" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>SD SAS</t>
         </is>
       </c>
       <c r="E620" s="8" t="n">
@@ -29610,13 +29610,13 @@
         </is>
       </c>
       <c r="G620" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/principal-pavement-engineer-linear-infrastructure-site-civils-at-aecom-4403657428", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-profesional-hseq-at-sd-sas-4444939872", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H620" s="6" t="inlineStr"/>
       <c r="I620" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J620" s="2" t="inlineStr">
@@ -29629,7 +29629,7 @@
     <row r="621" ht="22" customHeight="1">
       <c r="A621" s="2" t="inlineStr">
         <is>
-          <t>2bafc4e5eb29746b</t>
+          <t>fb37fc1bf485e650</t>
         </is>
       </c>
       <c r="B621" s="2" t="inlineStr">
@@ -29639,12 +29639,12 @@
       </c>
       <c r="C621" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero/a Geotécnico/a Senior</t>
+          <t>Técnico de trazado especialista en ISTRAM</t>
         </is>
       </c>
       <c r="D621" s="3" t="inlineStr">
         <is>
-          <t>IDOM Consulting, Engineering, Architecture</t>
+          <t>EADIC</t>
         </is>
       </c>
       <c r="E621" s="8" t="n">
@@ -29656,7 +29656,7 @@
         </is>
       </c>
       <c r="G621" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-geot%C3%A9cnico-a-senior-at-idom-consulting-engineering-architecture-4467729578", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/t%C3%A9cnico-de-trazado-especialista-en-istram-at-eadic-4468780158", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H621" s="6" t="inlineStr"/>
@@ -29675,7 +29675,7 @@
     <row r="622" ht="22" customHeight="1">
       <c r="A622" s="2" t="inlineStr">
         <is>
-          <t>f3290f3c2a2d0061</t>
+          <t>0f01a66eb85a1ffd</t>
         </is>
       </c>
       <c r="B622" s="2" t="inlineStr">
@@ -29685,12 +29685,12 @@
       </c>
       <c r="C622" s="3" t="inlineStr">
         <is>
-          <t>Engenheiro Civil - Lisboa</t>
+          <t>AUXILIAR MODELADOR BIM Y DIBUJANTE EN INGENIERÍA CIVIL</t>
         </is>
       </c>
       <c r="D622" s="3" t="inlineStr">
         <is>
-          <t>DDN GERENCIAMENTO</t>
+          <t>Antea Group España y Latinoamérica</t>
         </is>
       </c>
       <c r="E622" s="8" t="n">
@@ -29702,7 +29702,7 @@
         </is>
       </c>
       <c r="G622" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/engenheiro-civil-lisboa-at-ddn-gerenciamento-4468408791", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-modelador-bim-y-dibujante-en-ingenier%C3%ADa-civil-at-antea-group-espa%C3%B1a-y-latinoam%C3%A9rica-4467605615", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H622" s="6" t="inlineStr"/>
@@ -29721,7 +29721,7 @@
     <row r="623" ht="22" customHeight="1">
       <c r="A623" s="2" t="inlineStr">
         <is>
-          <t>d2feccf91b9b1f0b</t>
+          <t>cba614af5ce1fc3a</t>
         </is>
       </c>
       <c r="B623" s="2" t="inlineStr">
@@ -29731,12 +29731,12 @@
       </c>
       <c r="C623" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero/a Civil especialista en Talleres y Patios Ferroviarios</t>
+          <t>Principal Pavement Engineer - Linear Infrastructure &amp; Site Civils</t>
         </is>
       </c>
       <c r="D623" s="3" t="inlineStr">
         <is>
-          <t>IDOM Consulting, Engineering, Architecture</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="E623" s="8" t="n">
@@ -29748,7 +29748,7 @@
         </is>
       </c>
       <c r="G623" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-civil-especialista-en-talleres-y-patios-ferroviarios-at-idom-consulting-engineering-architecture-4443713908", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/principal-pavement-engineer-linear-infrastructure-site-civils-at-aecom-4403657428", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H623" s="6" t="inlineStr"/>
@@ -29767,7 +29767,7 @@
     <row r="624" ht="22" customHeight="1">
       <c r="A624" s="2" t="inlineStr">
         <is>
-          <t>152ea7f07f195fc8</t>
+          <t>2bafc4e5eb29746b</t>
         </is>
       </c>
       <c r="B624" s="2" t="inlineStr">
@@ -29777,12 +29777,12 @@
       </c>
       <c r="C624" s="3" t="inlineStr">
         <is>
-          <t>COORDINADOR DE INTERVENTORÍA-NIVEL 1 SECTOR HIDROCARBUROS</t>
+          <t>Ingeniero/a Geotécnico/a Senior</t>
         </is>
       </c>
       <c r="D624" s="3" t="inlineStr">
         <is>
-          <t>Centro de Empleo y Talento</t>
+          <t>IDOM Consulting, Engineering, Architecture</t>
         </is>
       </c>
       <c r="E624" s="8" t="n">
@@ -29794,7 +29794,7 @@
         </is>
       </c>
       <c r="G624" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-de-interventor%C3%ADa-nivel-1-sector-hidrocarburos-at-centro-de-empleo-y-talento-4468030406", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-geot%C3%A9cnico-a-senior-at-idom-consulting-engineering-architecture-4467729578", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H624" s="6" t="inlineStr"/>
@@ -29813,7 +29813,7 @@
     <row r="625" ht="22" customHeight="1">
       <c r="A625" s="2" t="inlineStr">
         <is>
-          <t>b3dd7e9d8f53fb27</t>
+          <t>f3290f3c2a2d0061</t>
         </is>
       </c>
       <c r="B625" s="2" t="inlineStr">
@@ -29823,12 +29823,12 @@
       </c>
       <c r="C625" s="3" t="inlineStr">
         <is>
-          <t>Consultor (Desarrollador) Senior Appian</t>
+          <t>Engenheiro Civil - Lisboa</t>
         </is>
       </c>
       <c r="D625" s="3" t="inlineStr">
         <is>
-          <t>VASS LATAM</t>
+          <t>DDN GERENCIAMENTO</t>
         </is>
       </c>
       <c r="E625" s="8" t="n">
@@ -29840,7 +29840,7 @@
         </is>
       </c>
       <c r="G625" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/consultor-desarrollador-senior-appian-at-vass-latam-4458249659", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/engenheiro-civil-lisboa-at-ddn-gerenciamento-4468408791", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H625" s="6" t="inlineStr"/>
@@ -29859,7 +29859,7 @@
     <row r="626" ht="22" customHeight="1">
       <c r="A626" s="2" t="inlineStr">
         <is>
-          <t>0f895f69320d7d8d</t>
+          <t>d2feccf91b9b1f0b</t>
         </is>
       </c>
       <c r="B626" s="2" t="inlineStr">
@@ -29869,12 +29869,12 @@
       </c>
       <c r="C626" s="3" t="inlineStr">
         <is>
-          <t>Coordinador hse Cartagena</t>
+          <t>Ingeniero/a Civil especialista en Talleres y Patios Ferroviarios</t>
         </is>
       </c>
       <c r="D626" s="3" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONTEJO SAS</t>
+          <t>IDOM Consulting, Engineering, Architecture</t>
         </is>
       </c>
       <c r="E626" s="8" t="n">
@@ -29886,13 +29886,13 @@
         </is>
       </c>
       <c r="G626" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-hse-cartagena-at-transportes-montejo-sas-4458746462", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-civil-especialista-en-talleres-y-patios-ferroviarios-at-idom-consulting-engineering-architecture-4443713908", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H626" s="6" t="inlineStr"/>
       <c r="I626" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J626" s="2" t="inlineStr">
@@ -29905,7 +29905,7 @@
     <row r="627" ht="22" customHeight="1">
       <c r="A627" s="2" t="inlineStr">
         <is>
-          <t>b86d50ad2dd5f642</t>
+          <t>152ea7f07f195fc8</t>
         </is>
       </c>
       <c r="B627" s="2" t="inlineStr">
@@ -29915,12 +29915,12 @@
       </c>
       <c r="C627" s="3" t="inlineStr">
         <is>
-          <t>Coordinador Regional SIG/ SST</t>
+          <t>COORDINADOR DE INTERVENTORÍA-NIVEL 1 SECTOR HIDROCARBUROS</t>
         </is>
       </c>
       <c r="D627" s="3" t="inlineStr">
         <is>
-          <t>Interaseo S.A.S. E.S.P.</t>
+          <t>Centro de Empleo y Talento</t>
         </is>
       </c>
       <c r="E627" s="8" t="n">
@@ -29932,13 +29932,13 @@
         </is>
       </c>
       <c r="G627" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-regional-sig-sst-at-interaseo-s-a-s-e-s-p-4459088040", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-de-interventor%C3%ADa-nivel-1-sector-hidrocarburos-at-centro-de-empleo-y-talento-4468030406", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H627" s="6" t="inlineStr"/>
       <c r="I627" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J627" s="2" t="inlineStr">
@@ -29951,7 +29951,7 @@
     <row r="628" ht="22" customHeight="1">
       <c r="A628" s="2" t="inlineStr">
         <is>
-          <t>506296811a5a9cbb</t>
+          <t>b3dd7e9d8f53fb27</t>
         </is>
       </c>
       <c r="B628" s="2" t="inlineStr">
@@ -29961,12 +29961,12 @@
       </c>
       <c r="C628" s="3" t="inlineStr">
         <is>
-          <t>Coordinador/a de SST</t>
+          <t>Consultor (Desarrollador) Senior Appian</t>
         </is>
       </c>
       <c r="D628" s="3" t="inlineStr">
         <is>
-          <t>Estelar Food S.A.S</t>
+          <t>VASS LATAM</t>
         </is>
       </c>
       <c r="E628" s="8" t="n">
@@ -29978,13 +29978,13 @@
         </is>
       </c>
       <c r="G628" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-de-sst-at-estelar-food-s-a-s-4462115593", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/consultor-desarrollador-senior-appian-at-vass-latam-4458249659", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H628" s="6" t="inlineStr"/>
       <c r="I628" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J628" s="2" t="inlineStr">
@@ -29997,7 +29997,7 @@
     <row r="629" ht="22" customHeight="1">
       <c r="A629" s="2" t="inlineStr">
         <is>
-          <t>0e4b8eed7f32714e</t>
+          <t>0f895f69320d7d8d</t>
         </is>
       </c>
       <c r="B629" s="2" t="inlineStr">
@@ -30007,12 +30007,12 @@
       </c>
       <c r="C629" s="3" t="inlineStr">
         <is>
-          <t>coordinador de Seguridad y Salud en el Trabajo</t>
+          <t>Coordinador hse Cartagena</t>
         </is>
       </c>
       <c r="D629" s="3" t="inlineStr">
         <is>
-          <t>Asertempo Colombia S.A.S</t>
+          <t>TRANSPORTES MONTEJO SAS</t>
         </is>
       </c>
       <c r="E629" s="8" t="n">
@@ -30024,7 +30024,7 @@
         </is>
       </c>
       <c r="G629" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-de-seguridad-y-salud-en-el-trabajo-at-asertempo-colombia-s-a-s-4461723686", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-hse-cartagena-at-transportes-montejo-sas-4458746462", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H629" s="6" t="inlineStr"/>
@@ -30043,7 +30043,7 @@
     <row r="630" ht="22" customHeight="1">
       <c r="A630" s="2" t="inlineStr">
         <is>
-          <t>aa2882af3c61095b</t>
+          <t>b86d50ad2dd5f642</t>
         </is>
       </c>
       <c r="B630" s="2" t="inlineStr">
@@ -30053,12 +30053,12 @@
       </c>
       <c r="C630" s="3" t="inlineStr">
         <is>
-          <t>Coordinador (a) SST / APH - Marmato</t>
+          <t>Coordinador Regional SIG/ SST</t>
         </is>
       </c>
       <c r="D630" s="3" t="inlineStr">
         <is>
-          <t>Aris Mining Colombia</t>
+          <t>Interaseo S.A.S. E.S.P.</t>
         </is>
       </c>
       <c r="E630" s="8" t="n">
@@ -30070,7 +30070,7 @@
         </is>
       </c>
       <c r="G630" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-sst-aph-marmato-at-aris-mining-colombia-4448929810", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-regional-sig-sst-at-interaseo-s-a-s-e-s-p-4459088040", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H630" s="6" t="inlineStr"/>
@@ -30089,7 +30089,7 @@
     <row r="631" ht="22" customHeight="1">
       <c r="A631" s="2" t="inlineStr">
         <is>
-          <t>26cff43f13982962</t>
+          <t>506296811a5a9cbb</t>
         </is>
       </c>
       <c r="B631" s="2" t="inlineStr">
@@ -30099,12 +30099,12 @@
       </c>
       <c r="C631" s="3" t="inlineStr">
         <is>
-          <t>Consultor(a) Senior SOX TI</t>
+          <t>Coordinador/a de SST</t>
         </is>
       </c>
       <c r="D631" s="3" t="inlineStr">
         <is>
-          <t>Hitss Colombia</t>
+          <t>Estelar Food S.A.S</t>
         </is>
       </c>
       <c r="E631" s="8" t="n">
@@ -30116,13 +30116,13 @@
         </is>
       </c>
       <c r="G631" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/consultor-a-senior-sox-ti-at-hitss-colombia-4460766744", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-de-sst-at-estelar-food-s-a-s-4462115593", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H631" s="6" t="inlineStr"/>
       <c r="I631" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J631" s="2" t="inlineStr">
@@ -30135,7 +30135,7 @@
     <row r="632" ht="22" customHeight="1">
       <c r="A632" s="2" t="inlineStr">
         <is>
-          <t>87e367215ed55502</t>
+          <t>0e4b8eed7f32714e</t>
         </is>
       </c>
       <c r="B632" s="2" t="inlineStr">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="C632" s="3" t="inlineStr">
         <is>
-          <t>Consultor(a) Senior Auditoría Interna</t>
+          <t>coordinador de Seguridad y Salud en el Trabajo</t>
         </is>
       </c>
       <c r="D632" s="3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Asertempo Colombia S.A.S</t>
         </is>
       </c>
       <c r="E632" s="8" t="n">
@@ -30162,13 +30162,13 @@
         </is>
       </c>
       <c r="G632" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/consultor-a-senior-auditor%C3%ADa-interna-at-deloitte-4462090075", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-de-seguridad-y-salud-en-el-trabajo-at-asertempo-colombia-s-a-s-4461723686", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H632" s="6" t="inlineStr"/>
       <c r="I632" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J632" s="2" t="inlineStr">
@@ -30181,7 +30181,7 @@
     <row r="633" ht="22" customHeight="1">
       <c r="A633" s="2" t="inlineStr">
         <is>
-          <t>e2e525b51bbd0e5e</t>
+          <t>aa2882af3c61095b</t>
         </is>
       </c>
       <c r="B633" s="2" t="inlineStr">
@@ -30191,12 +30191,12 @@
       </c>
       <c r="C633" s="3" t="inlineStr">
         <is>
-          <t>Coordinador/a de Salud y Bienestar (HSE) Latam</t>
+          <t>Coordinador (a) SST / APH - Marmato</t>
         </is>
       </c>
       <c r="D633" s="3" t="inlineStr">
         <is>
-          <t>Aqualia</t>
+          <t>Aris Mining Colombia</t>
         </is>
       </c>
       <c r="E633" s="8" t="n">
@@ -30208,7 +30208,7 @@
         </is>
       </c>
       <c r="G633" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-de-salud-y-bienestar-hse-latam-at-aqualia-4463977352", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-sst-aph-marmato-at-aris-mining-colombia-4448929810", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H633" s="6" t="inlineStr"/>
@@ -30227,7 +30227,7 @@
     <row r="634" ht="22" customHeight="1">
       <c r="A634" s="2" t="inlineStr">
         <is>
-          <t>8ef614b651dfe9d9</t>
+          <t>26cff43f13982962</t>
         </is>
       </c>
       <c r="B634" s="2" t="inlineStr">
@@ -30237,12 +30237,12 @@
       </c>
       <c r="C634" s="3" t="inlineStr">
         <is>
-          <t>Lead Civil Site Engineer</t>
+          <t>Consultor(a) Senior SOX TI</t>
         </is>
       </c>
       <c r="D634" s="3" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Hitss Colombia</t>
         </is>
       </c>
       <c r="E634" s="8" t="n">
@@ -30254,7 +30254,7 @@
         </is>
       </c>
       <c r="G634" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/lead-civil-site-engineer-at-aecom-4468059409", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/consultor-a-senior-sox-ti-at-hitss-colombia-4460766744", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H634" s="6" t="inlineStr"/>
@@ -30273,7 +30273,7 @@
     <row r="635" ht="22" customHeight="1">
       <c r="A635" s="2" t="inlineStr">
         <is>
-          <t>b339389a0d32a94f</t>
+          <t>87e367215ed55502</t>
         </is>
       </c>
       <c r="B635" s="2" t="inlineStr">
@@ -30283,12 +30283,12 @@
       </c>
       <c r="C635" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero civil</t>
+          <t>Consultor(a) Senior Auditoría Interna</t>
         </is>
       </c>
       <c r="D635" s="3" t="inlineStr">
         <is>
-          <t>constructora cumbrera</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="E635" s="8" t="n">
@@ -30300,7 +30300,7 @@
         </is>
       </c>
       <c r="G635" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-civil-4463108593", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/consultor-a-senior-auditor%C3%ADa-interna-at-deloitte-4462090075", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H635" s="6" t="inlineStr"/>
@@ -30319,7 +30319,7 @@
     <row r="636" ht="22" customHeight="1">
       <c r="A636" s="2" t="inlineStr">
         <is>
-          <t>93623c0212e39cb9</t>
+          <t>e2e525b51bbd0e5e</t>
         </is>
       </c>
       <c r="B636" s="2" t="inlineStr">
@@ -30329,12 +30329,12 @@
       </c>
       <c r="C636" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero(a) Civil</t>
+          <t>Coordinador/a de Salud y Bienestar (HSE) Latam</t>
         </is>
       </c>
       <c r="D636" s="3" t="inlineStr">
         <is>
-          <t>CMH Colombia</t>
+          <t>Aqualia</t>
         </is>
       </c>
       <c r="E636" s="8" t="n">
@@ -30346,13 +30346,13 @@
         </is>
       </c>
       <c r="G636" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-civil-at-minerales-c%C3%B3rdoba-4417533007", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-de-salud-y-bienestar-hse-latam-at-aqualia-4463977352", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H636" s="6" t="inlineStr"/>
       <c r="I636" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J636" s="2" t="inlineStr">
@@ -30365,7 +30365,7 @@
     <row r="637" ht="22" customHeight="1">
       <c r="A637" s="2" t="inlineStr">
         <is>
-          <t>cd06fbe3d5b74888</t>
+          <t>8ef614b651dfe9d9</t>
         </is>
       </c>
       <c r="B637" s="2" t="inlineStr">
@@ -30375,12 +30375,12 @@
       </c>
       <c r="C637" s="3" t="inlineStr">
         <is>
-          <t>Oficial Obra Civil</t>
+          <t>Lead Civil Site Engineer</t>
         </is>
       </c>
       <c r="D637" s="3" t="inlineStr">
         <is>
-          <t>Equans Colombia</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="E637" s="8" t="n">
@@ -30392,7 +30392,7 @@
         </is>
       </c>
       <c r="G637" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/oficial-obra-civil-bogota-y-cundinamarca-at-equans-colombia-4470218146", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/lead-civil-site-engineer-at-aecom-4468059409", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H637" s="6" t="inlineStr"/>
@@ -30408,9 +30408,147 @@
       </c>
       <c r="K637" s="3" t="inlineStr"/>
     </row>
+    <row r="638" ht="22" customHeight="1">
+      <c r="A638" s="2" t="inlineStr">
+        <is>
+          <t>b339389a0d32a94f</t>
+        </is>
+      </c>
+      <c r="B638" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 05:09</t>
+        </is>
+      </c>
+      <c r="C638" s="3" t="inlineStr">
+        <is>
+          <t>Ingeniero civil</t>
+        </is>
+      </c>
+      <c r="D638" s="3" t="inlineStr">
+        <is>
+          <t>constructora cumbrera</t>
+        </is>
+      </c>
+      <c r="E638" s="8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F638" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G638" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-civil-4463108593", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H638" s="6" t="inlineStr"/>
+      <c r="I638" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J638" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K638" s="3" t="inlineStr"/>
+    </row>
+    <row r="639" ht="22" customHeight="1">
+      <c r="A639" s="2" t="inlineStr">
+        <is>
+          <t>93623c0212e39cb9</t>
+        </is>
+      </c>
+      <c r="B639" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 05:09</t>
+        </is>
+      </c>
+      <c r="C639" s="3" t="inlineStr">
+        <is>
+          <t>Ingeniero(a) Civil</t>
+        </is>
+      </c>
+      <c r="D639" s="3" t="inlineStr">
+        <is>
+          <t>CMH Colombia</t>
+        </is>
+      </c>
+      <c r="E639" s="8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F639" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G639" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-civil-at-minerales-c%C3%B3rdoba-4417533007", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H639" s="6" t="inlineStr"/>
+      <c r="I639" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J639" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K639" s="3" t="inlineStr"/>
+    </row>
+    <row r="640" ht="22" customHeight="1">
+      <c r="A640" s="2" t="inlineStr">
+        <is>
+          <t>cd06fbe3d5b74888</t>
+        </is>
+      </c>
+      <c r="B640" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 05:09</t>
+        </is>
+      </c>
+      <c r="C640" s="3" t="inlineStr">
+        <is>
+          <t>Oficial Obra Civil</t>
+        </is>
+      </c>
+      <c r="D640" s="3" t="inlineStr">
+        <is>
+          <t>Equans Colombia</t>
+        </is>
+      </c>
+      <c r="E640" s="8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F640" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G640" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/oficial-obra-civil-bogota-y-cundinamarca-at-equans-colombia-4470218146", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H640" s="6" t="inlineStr"/>
+      <c r="I640" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J640" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K640" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J836" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J839" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Nueva,Por revisar,Postulado,Descartado,Entrevista"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/profile_1_civil_vias_sst_tracker.xlsx
+++ b/output/profile_1_civil_vias_sst_tracker.xlsx
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K640"/>
+  <dimension ref="A1:K648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -25537,26 +25537,26 @@
     <row r="533" ht="22" customHeight="1">
       <c r="A533" s="2" t="inlineStr">
         <is>
-          <t>4426b2c17306f519</t>
+          <t>f77356fba7f7ea68</t>
         </is>
       </c>
       <c r="B533" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 05:09</t>
+          <t>2026-10-19 17:27</t>
         </is>
       </c>
       <c r="C533" s="3" t="inlineStr">
         <is>
-          <t>Residente de Seguridad y Salud en el trabajo</t>
+          <t>Analista de Seguridad y Salud en el Trabajo</t>
         </is>
       </c>
       <c r="D533" s="3" t="inlineStr">
         <is>
-          <t>Cal y Mayor y Asociados S.C</t>
-        </is>
-      </c>
-      <c r="E533" s="8" t="n">
-        <v>0.48</v>
+          <t>Takami S.A</t>
+        </is>
+      </c>
+      <c r="E533" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="F533" s="2" t="inlineStr">
         <is>
@@ -25564,17 +25564,13 @@
         </is>
       </c>
       <c r="G533" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-residente-de-seguridad-y-salud-en-el-trabajo-sst-sst-en-bogota-dc-D67E64C3D53E0D6961373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H533" s="6" t="inlineStr">
-        <is>
-          <t>$ 4.200.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-seguridad-y-salud-en-el-trabajo-analista-sst-en-bogota-dc-0FC1FA07D486E6FB61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H533" s="6" t="inlineStr"/>
       <c r="I533" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J533" s="2" t="inlineStr">
@@ -25587,26 +25583,26 @@
     <row r="534" ht="22" customHeight="1">
       <c r="A534" s="2" t="inlineStr">
         <is>
-          <t>83015d6afb890f1d</t>
+          <t>23251498ce710db0</t>
         </is>
       </c>
       <c r="B534" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 05:09</t>
+          <t>2026-10-19 17:27</t>
         </is>
       </c>
       <c r="C534" s="3" t="inlineStr">
         <is>
-          <t>Analista/profesional HSEQ / SST Sesquile o Alrededores</t>
+          <t>Director de Proyecto</t>
         </is>
       </c>
       <c r="D534" s="3" t="inlineStr">
         <is>
-          <t>ACTIVOS S A S</t>
-        </is>
-      </c>
-      <c r="E534" s="8" t="n">
-        <v>0.48</v>
+          <t>GESTION DE RECURSOS TEMPORALES S.A.S. "GR TEMPORALES S.A.S."</t>
+        </is>
+      </c>
+      <c r="E534" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="F534" s="2" t="inlineStr">
         <is>
@@ -25614,17 +25610,17 @@
         </is>
       </c>
       <c r="G534" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analistaprofesional-hseq-sst-sesquile-o-alrededores-sector-consumo-masivo-en-sesquile-632A9566338A59E361373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-director-de-proyecto-obras-y-montajes-en-medellin-109E3C7C5CB623BA61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H534" s="6" t="inlineStr">
         <is>
-          <t>$ 4.000.000,00 (Mensual)</t>
+          <t>$ 5.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I534" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J534" s="2" t="inlineStr">
@@ -25637,26 +25633,26 @@
     <row r="535" ht="22" customHeight="1">
       <c r="A535" s="2" t="inlineStr">
         <is>
-          <t>bc0b38b5129e0905</t>
+          <t>c3249bf92df00c21</t>
         </is>
       </c>
       <c r="B535" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 05:09</t>
+          <t>2026-10-19 17:27</t>
         </is>
       </c>
       <c r="C535" s="3" t="inlineStr">
         <is>
-          <t>Profesional en seguridad y salud en el trabajo SST</t>
+          <t>Analista de seguridad y salud en el trabajo</t>
         </is>
       </c>
       <c r="D535" s="3" t="inlineStr">
         <is>
-          <t>Seguridad y Vigilancia Exito de Colombia</t>
-        </is>
-      </c>
-      <c r="E535" s="8" t="n">
-        <v>0.48</v>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E535" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="F535" s="2" t="inlineStr">
         <is>
@@ -25664,17 +25660,13 @@
         </is>
       </c>
       <c r="G535" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-profesional-en-seguridad-y-salud-en-el-trabajo-sst-con-experiencia-y-conocimiento-en-pesv-en-bogota-dc-A7CA6F8805D1C53B61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H535" s="6" t="inlineStr">
-        <is>
-          <t>$ 3.200.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-seguridad-y-salud-en-el-trabajo-1886781980", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H535" s="6" t="inlineStr"/>
       <c r="I535" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J535" s="2" t="inlineStr">
@@ -25687,26 +25679,26 @@
     <row r="536" ht="22" customHeight="1">
       <c r="A536" s="2" t="inlineStr">
         <is>
-          <t>e15ce00dbe5c21b5</t>
+          <t>172a040b143ea0cf</t>
         </is>
       </c>
       <c r="B536" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 05:09</t>
+          <t>2026-10-19 17:27</t>
         </is>
       </c>
       <c r="C536" s="3" t="inlineStr">
         <is>
-          <t>Tecnólogo HSEQ / Seguridad y Salud en el Trabajo</t>
+          <t>Analista sst</t>
         </is>
       </c>
       <c r="D536" s="3" t="inlineStr">
         <is>
-          <t>Lighgen Ingeniería Ltda</t>
-        </is>
-      </c>
-      <c r="E536" s="8" t="n">
-        <v>0.48</v>
+          <t>Diseños y Aplicaciones de Ingeniería civil sas</t>
+        </is>
+      </c>
+      <c r="E536" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="F536" s="2" t="inlineStr">
         <is>
@@ -25714,13 +25706,13 @@
         </is>
       </c>
       <c r="G536" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-tecnologo-hseq-seguridad-y-salud-en-el-trabajo-con-experiencia-2-anos-en-bogota-dc-87DB3FCAFEA8E12861373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-sst-1886779165", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H536" s="6" t="inlineStr"/>
       <c r="I536" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J536" s="2" t="inlineStr">
@@ -25733,26 +25725,26 @@
     <row r="537" ht="22" customHeight="1">
       <c r="A537" s="2" t="inlineStr">
         <is>
-          <t>1f3bf8b16a58f0b4</t>
+          <t>718395b7e6fbf0fd</t>
         </is>
       </c>
       <c r="B537" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 05:09</t>
+          <t>2026-10-19 17:27</t>
         </is>
       </c>
       <c r="C537" s="3" t="inlineStr">
         <is>
-          <t>Inspector (a) de vias y urbanismo</t>
+          <t>Lider calidad y sst</t>
         </is>
       </c>
       <c r="D537" s="3" t="inlineStr">
         <is>
-          <t>METRO LINEA 1 S.A.S.</t>
-        </is>
-      </c>
-      <c r="E537" s="8" t="n">
-        <v>0.48</v>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E537" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="F537" s="2" t="inlineStr">
         <is>
@@ -25760,13 +25752,13 @@
         </is>
       </c>
       <c r="G537" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/inspector-a-de-vias-y-urbanismo-1886728733", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/lider-calidad-y-sst-1886780115", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H537" s="6" t="inlineStr"/>
       <c r="I537" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J537" s="2" t="inlineStr">
@@ -25779,26 +25771,26 @@
     <row r="538" ht="22" customHeight="1">
       <c r="A538" s="2" t="inlineStr">
         <is>
-          <t>8fd843a922654d9e</t>
+          <t>c7d5298917a12bd3</t>
         </is>
       </c>
       <c r="B538" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 05:09</t>
+          <t>2026-10-19 17:27</t>
         </is>
       </c>
       <c r="C538" s="3" t="inlineStr">
         <is>
-          <t>Oficial de obra</t>
+          <t>Analista SST</t>
         </is>
       </c>
       <c r="D538" s="3" t="inlineStr">
         <is>
-          <t>TERMOTECNICA COINDUSTRIAL SAS</t>
-        </is>
-      </c>
-      <c r="E538" s="8" t="n">
-        <v>0.48</v>
+          <t>Grupo Núcleos de Madera</t>
+        </is>
+      </c>
+      <c r="E538" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="F538" s="2" t="inlineStr">
         <is>
@@ -25806,13 +25798,13 @@
         </is>
       </c>
       <c r="G538" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/oficial-de-obra-puentevias-1886766237", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-sst-at-grupo-n%C3%BAcleos-de-madera-4480993859", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H538" s="6" t="inlineStr"/>
       <c r="I538" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J538" s="2" t="inlineStr">
@@ -25825,26 +25817,26 @@
     <row r="539" ht="22" customHeight="1">
       <c r="A539" s="2" t="inlineStr">
         <is>
-          <t>03eab73111095faa</t>
+          <t>4a81f35509c76a9b</t>
         </is>
       </c>
       <c r="B539" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 05:09</t>
+          <t>2026-10-19 17:27</t>
         </is>
       </c>
       <c r="C539" s="3" t="inlineStr">
         <is>
-          <t>Residente estructuras</t>
+          <t>LIDER HSE</t>
         </is>
       </c>
       <c r="D539" s="3" t="inlineStr">
         <is>
-          <t>CONCONCRETO S.A.</t>
-        </is>
-      </c>
-      <c r="E539" s="8" t="n">
-        <v>0.48</v>
+          <t>Atento</t>
+        </is>
+      </c>
+      <c r="E539" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="F539" s="2" t="inlineStr">
         <is>
@@ -25852,13 +25844,13 @@
         </is>
       </c>
       <c r="G539" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/residente-estructuras-experiencia-en-infraestructura-vial-y-talud-1886757305", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/lider-hse-at-atento-4478228863", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H539" s="6" t="inlineStr"/>
       <c r="I539" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J539" s="2" t="inlineStr">
@@ -25871,26 +25863,26 @@
     <row r="540" ht="22" customHeight="1">
       <c r="A540" s="2" t="inlineStr">
         <is>
-          <t>c5911c7562546e3c</t>
+          <t>ee66cc010a275e08</t>
         </is>
       </c>
       <c r="B540" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 05:09</t>
+          <t>2026-10-19 17:27</t>
         </is>
       </c>
       <c r="C540" s="3" t="inlineStr">
         <is>
-          <t>Profesional con experiencia en el sector de transporte marítimo y/o por vías navegables</t>
+          <t>Senior Civil Engineer</t>
         </is>
       </c>
       <c r="D540" s="3" t="inlineStr">
         <is>
-          <t>ICONTEC</t>
-        </is>
-      </c>
-      <c r="E540" s="8" t="n">
-        <v>0.48</v>
+          <t>WSP Chile y Argentina</t>
+        </is>
+      </c>
+      <c r="E540" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="F540" s="2" t="inlineStr">
         <is>
@@ -25898,13 +25890,13 @@
         </is>
       </c>
       <c r="G540" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/profesional-con-experiencia-en-el-sector-de-transporte-maritimo-y-o-por-vias-navegables-1886761682", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/senior-civil-engineer-at-wsp-chile-y-argentina-4480250388", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H540" s="6" t="inlineStr"/>
       <c r="I540" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J540" s="2" t="inlineStr">
@@ -25917,7 +25909,7 @@
     <row r="541" ht="22" customHeight="1">
       <c r="A541" s="2" t="inlineStr">
         <is>
-          <t>c2903e245a44de39</t>
+          <t>4426b2c17306f519</t>
         </is>
       </c>
       <c r="B541" s="2" t="inlineStr">
@@ -25927,12 +25919,12 @@
       </c>
       <c r="C541" s="3" t="inlineStr">
         <is>
-          <t>Encargado de obra</t>
+          <t>Residente de Seguridad y Salud en el trabajo</t>
         </is>
       </c>
       <c r="D541" s="3" t="inlineStr">
         <is>
-          <t>TERMOTECNICA COINDUSTRIAL SAS</t>
+          <t>Cal y Mayor y Asociados S.C</t>
         </is>
       </c>
       <c r="E541" s="8" t="n">
@@ -25944,13 +25936,17 @@
         </is>
       </c>
       <c r="G541" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/encargado-de-obra-puentes-vias-1886762620", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H541" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-residente-de-seguridad-y-salud-en-el-trabajo-sst-sst-en-bogota-dc-D67E64C3D53E0D6961373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H541" s="6" t="inlineStr">
+        <is>
+          <t>$ 4.200.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I541" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J541" s="2" t="inlineStr">
@@ -25963,7 +25959,7 @@
     <row r="542" ht="22" customHeight="1">
       <c r="A542" s="2" t="inlineStr">
         <is>
-          <t>a5bd833e8b837d34</t>
+          <t>83015d6afb890f1d</t>
         </is>
       </c>
       <c r="B542" s="2" t="inlineStr">
@@ -25973,12 +25969,12 @@
       </c>
       <c r="C542" s="3" t="inlineStr">
         <is>
-          <t>Residente en seguridad y salud en el trabajo</t>
+          <t>Analista/profesional HSEQ / SST Sesquile o Alrededores</t>
         </is>
       </c>
       <c r="D542" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ACTIVOS S A S</t>
         </is>
       </c>
       <c r="E542" s="8" t="n">
@@ -25990,10 +25986,14 @@
         </is>
       </c>
       <c r="G542" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/residente-en-seguridad-y-salud-en-el-trabajo-sst-1886762728", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H542" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analistaprofesional-hseq-sst-sesquile-o-alrededores-sector-consumo-masivo-en-sesquile-632A9566338A59E361373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H542" s="6" t="inlineStr">
+        <is>
+          <t>$ 4.000.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I542" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -26009,7 +26009,7 @@
     <row r="543" ht="22" customHeight="1">
       <c r="A543" s="2" t="inlineStr">
         <is>
-          <t>55e7967f3b4afa02</t>
+          <t>bc0b38b5129e0905</t>
         </is>
       </c>
       <c r="B543" s="2" t="inlineStr">
@@ -26019,12 +26019,12 @@
       </c>
       <c r="C543" s="3" t="inlineStr">
         <is>
-          <t>Tecnólogo/a en Seguridad y Salud en el Trabajo</t>
+          <t>Profesional en seguridad y salud en el trabajo SST</t>
         </is>
       </c>
       <c r="D543" s="3" t="inlineStr">
         <is>
-          <t>EOSOL</t>
+          <t>Seguridad y Vigilancia Exito de Colombia</t>
         </is>
       </c>
       <c r="E543" s="8" t="n">
@@ -26036,10 +26036,14 @@
         </is>
       </c>
       <c r="G543" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/tecn%C3%B3logo-a-en-seguridad-y-salud-en-el-trabajo-sst-at-eosol-4464868638", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H543" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-profesional-en-seguridad-y-salud-en-el-trabajo-sst-con-experiencia-y-conocimiento-en-pesv-en-bogota-dc-A7CA6F8805D1C53B61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H543" s="6" t="inlineStr">
+        <is>
+          <t>$ 3.200.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I543" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -26055,7 +26059,7 @@
     <row r="544" ht="22" customHeight="1">
       <c r="A544" s="2" t="inlineStr">
         <is>
-          <t>6df905e482fe09b1</t>
+          <t>e15ce00dbe5c21b5</t>
         </is>
       </c>
       <c r="B544" s="2" t="inlineStr">
@@ -26065,12 +26069,12 @@
       </c>
       <c r="C544" s="3" t="inlineStr">
         <is>
-          <t>Aprendiz SENA - Técnico(a) de Salud Ocupacional o Seguridad y Salud en el Trabajo - Ginebra</t>
+          <t>Tecnólogo HSEQ / Seguridad y Salud en el Trabajo</t>
         </is>
       </c>
       <c r="D544" s="3" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Lighgen Ingeniería Ltda</t>
         </is>
       </c>
       <c r="E544" s="8" t="n">
@@ -26082,7 +26086,7 @@
         </is>
       </c>
       <c r="G544" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-sena-t%C3%A9cnico-a-de-salud-ocupacional-o-seguridad-y-salud-en-el-trabajo-ginebra-at-cargill-4466994159", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-tecnologo-hseq-seguridad-y-salud-en-el-trabajo-con-experiencia-2-anos-en-bogota-dc-87DB3FCAFEA8E12861373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H544" s="6" t="inlineStr"/>
@@ -26101,7 +26105,7 @@
     <row r="545" ht="22" customHeight="1">
       <c r="A545" s="2" t="inlineStr">
         <is>
-          <t>06656fbb2d452086</t>
+          <t>1f3bf8b16a58f0b4</t>
         </is>
       </c>
       <c r="B545" s="2" t="inlineStr">
@@ -26111,12 +26115,12 @@
       </c>
       <c r="C545" s="3" t="inlineStr">
         <is>
-          <t>Residente de Seguridad y Salud en el trabajo</t>
+          <t>Inspector (a) de vias y urbanismo</t>
         </is>
       </c>
       <c r="D545" s="3" t="inlineStr">
         <is>
-          <t>Grupo Cal y Mayor</t>
+          <t>METRO LINEA 1 S.A.S.</t>
         </is>
       </c>
       <c r="E545" s="8" t="n">
@@ -26128,13 +26132,13 @@
         </is>
       </c>
       <c r="G545" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/residente-de-seguridad-y-salud-en-el-trabajo-sst-at-cal-y-mayor-4468610572", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/inspector-a-de-vias-y-urbanismo-1886728733", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H545" s="6" t="inlineStr"/>
       <c r="I545" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J545" s="2" t="inlineStr">
@@ -26147,7 +26151,7 @@
     <row r="546" ht="22" customHeight="1">
       <c r="A546" s="2" t="inlineStr">
         <is>
-          <t>7796e088dce85b5a</t>
+          <t>8fd843a922654d9e</t>
         </is>
       </c>
       <c r="B546" s="2" t="inlineStr">
@@ -26157,16 +26161,16 @@
       </c>
       <c r="C546" s="3" t="inlineStr">
         <is>
-          <t>Civil Engineer (Fire Sprinkler Design))</t>
+          <t>Oficial de obra</t>
         </is>
       </c>
       <c r="D546" s="3" t="inlineStr">
         <is>
-          <t>Hyremote</t>
+          <t>TERMOTECNICA COINDUSTRIAL SAS</t>
         </is>
       </c>
       <c r="E546" s="8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="F546" s="2" t="inlineStr">
         <is>
@@ -26174,17 +26178,13 @@
         </is>
       </c>
       <c r="G546" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-civil-engineer-fire-sprinkler-design-english-c1-remote-en-bogota-dc-A2EE61A321FC0D3361373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H546" s="6" t="inlineStr">
-        <is>
-          <t>$ 4.499.993,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/oficial-de-obra-puentevias-1886766237", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H546" s="6" t="inlineStr"/>
       <c r="I546" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J546" s="2" t="inlineStr">
@@ -26197,7 +26197,7 @@
     <row r="547" ht="22" customHeight="1">
       <c r="A547" s="2" t="inlineStr">
         <is>
-          <t>48463526ca7c8ada</t>
+          <t>03eab73111095faa</t>
         </is>
       </c>
       <c r="B547" s="2" t="inlineStr">
@@ -26207,16 +26207,16 @@
       </c>
       <c r="C547" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero Civil Especialista en Hidrología e Hidráulica</t>
+          <t>Residente estructuras</t>
         </is>
       </c>
       <c r="D547" s="3" t="inlineStr">
         <is>
-          <t>ATLAS INFRASTRUCTURE DESIGN LIMITED</t>
+          <t>CONCONCRETO S.A.</t>
         </is>
       </c>
       <c r="E547" s="8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="F547" s="2" t="inlineStr">
         <is>
@@ -26224,17 +26224,13 @@
         </is>
       </c>
       <c r="G547" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-especialista-en-hidrologia-e-hidraulica-tiempo-completo-en-remoto-y-de-larga-duracion-en-colombia-027FB718364F4C7761373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H547" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/residente-estructuras-experiencia-en-infraestructura-vial-y-talud-1886757305", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H547" s="6" t="inlineStr"/>
       <c r="I547" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J547" s="2" t="inlineStr">
@@ -26247,7 +26243,7 @@
     <row r="548" ht="22" customHeight="1">
       <c r="A548" s="2" t="inlineStr">
         <is>
-          <t>2d406567ceb21bf8</t>
+          <t>c5911c7562546e3c</t>
         </is>
       </c>
       <c r="B548" s="2" t="inlineStr">
@@ -26257,16 +26253,16 @@
       </c>
       <c r="C548" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero Civil de Diseño</t>
+          <t>Profesional con experiencia en el sector de transporte marítimo y/o por vías navegables</t>
         </is>
       </c>
       <c r="D548" s="3" t="inlineStr">
         <is>
-          <t>ATLAS INFRASTRUCTURE DESIGN LIMITED</t>
+          <t>ICONTEC</t>
         </is>
       </c>
       <c r="E548" s="8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="F548" s="2" t="inlineStr">
         <is>
@@ -26274,17 +26270,13 @@
         </is>
       </c>
       <c r="G548" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-de-diseno-tiempo-completo-en-remoto-en-colombia-4CB8F30B6D8FBF7261373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H548" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/profesional-con-experiencia-en-el-sector-de-transporte-maritimo-y-o-por-vias-navegables-1886761682", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H548" s="6" t="inlineStr"/>
       <c r="I548" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J548" s="2" t="inlineStr">
@@ -26297,7 +26289,7 @@
     <row r="549" ht="22" customHeight="1">
       <c r="A549" s="2" t="inlineStr">
         <is>
-          <t>4d4013d19591d2a5</t>
+          <t>c2903e245a44de39</t>
         </is>
       </c>
       <c r="B549" s="2" t="inlineStr">
@@ -26307,16 +26299,16 @@
       </c>
       <c r="C549" s="3" t="inlineStr">
         <is>
-          <t>Especialista en Salud y Seguridad en el trabajo con especialización en medio Ambiente</t>
+          <t>Encargado de obra</t>
         </is>
       </c>
       <c r="D549" s="3" t="inlineStr">
         <is>
-          <t>DEXTERA S.A.S</t>
+          <t>TERMOTECNICA COINDUSTRIAL SAS</t>
         </is>
       </c>
       <c r="E549" s="8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="F549" s="2" t="inlineStr">
         <is>
@@ -26324,13 +26316,13 @@
         </is>
       </c>
       <c r="G549" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-especialista-en-salud-y-seguridad-en-el-trabajo-con-especializacion-en-medio-ambiente-en-bogota-dc-68C95C2F64D6648561373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/encargado-de-obra-puentes-vias-1886762620", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H549" s="6" t="inlineStr"/>
       <c r="I549" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia técnica en infraestructura vial, diseño geométrico y pavimentos. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J549" s="2" t="inlineStr">
@@ -26343,7 +26335,7 @@
     <row r="550" ht="22" customHeight="1">
       <c r="A550" s="2" t="inlineStr">
         <is>
-          <t>cf70d2ca6e5c25de</t>
+          <t>a5bd833e8b837d34</t>
         </is>
       </c>
       <c r="B550" s="2" t="inlineStr">
@@ -26353,16 +26345,16 @@
       </c>
       <c r="C550" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero civil</t>
+          <t>Residente en seguridad y salud en el trabajo</t>
         </is>
       </c>
       <c r="D550" s="3" t="inlineStr">
         <is>
-          <t>Importante empresa del sector</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E550" s="8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="F550" s="2" t="inlineStr">
         <is>
@@ -26370,17 +26362,13 @@
         </is>
       </c>
       <c r="G550" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-con-experiencia-en-sistemas-fotovoltaicos-en-bogota-dc-8BCBCD7DF8FE589C61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H550" s="6" t="inlineStr">
-        <is>
-          <t>$ 3.300.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/residente-en-seguridad-y-salud-en-el-trabajo-sst-1886762728", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H550" s="6" t="inlineStr"/>
       <c r="I550" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J550" s="2" t="inlineStr">
@@ -26393,7 +26381,7 @@
     <row r="551" ht="22" customHeight="1">
       <c r="A551" s="2" t="inlineStr">
         <is>
-          <t>bb8237cc7ed8d56b</t>
+          <t>55e7967f3b4afa02</t>
         </is>
       </c>
       <c r="B551" s="2" t="inlineStr">
@@ -26403,16 +26391,16 @@
       </c>
       <c r="C551" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de Proyectos Mejoramientos de Vivienda</t>
+          <t>Tecnólogo/a en Seguridad y Salud en el Trabajo</t>
         </is>
       </c>
       <c r="D551" s="3" t="inlineStr">
         <is>
-          <t>Socya</t>
+          <t>EOSOL</t>
         </is>
       </c>
       <c r="E551" s="8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="F551" s="2" t="inlineStr">
         <is>
@@ -26420,13 +26408,13 @@
         </is>
       </c>
       <c r="G551" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-de-proyectos-mejoramientos-de-vivienda-medellin-antioquia-en-medellin-7E29781CFFD4058961373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/tecn%C3%B3logo-a-en-seguridad-y-salud-en-el-trabajo-sst-at-eosol-4464868638", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H551" s="6" t="inlineStr"/>
       <c r="I551" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J551" s="2" t="inlineStr">
@@ -26439,7 +26427,7 @@
     <row r="552" ht="22" customHeight="1">
       <c r="A552" s="2" t="inlineStr">
         <is>
-          <t>c41dc091e876cb10</t>
+          <t>6df905e482fe09b1</t>
         </is>
       </c>
       <c r="B552" s="2" t="inlineStr">
@@ -26449,16 +26437,16 @@
       </c>
       <c r="C552" s="3" t="inlineStr">
         <is>
-          <t>Especialista de Milk Collection</t>
+          <t>Aprendiz SENA - Técnico(a) de Salud Ocupacional o Seguridad y Salud en el Trabajo - Ginebra</t>
         </is>
       </c>
       <c r="D552" s="3" t="inlineStr">
         <is>
-          <t>LACTALIS</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="E552" s="8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="F552" s="2" t="inlineStr">
         <is>
@@ -26466,17 +26454,13 @@
         </is>
       </c>
       <c r="G552" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-especialista-de-milk-collection-optimizacion-y-analisis-de-datos-en-bogota-dc-B007F5172FEA6F6461373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H552" s="6" t="inlineStr">
-        <is>
-          <t>$ 6.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-sena-t%C3%A9cnico-a-de-salud-ocupacional-o-seguridad-y-salud-en-el-trabajo-ginebra-at-cargill-4466994159", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H552" s="6" t="inlineStr"/>
       <c r="I552" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J552" s="2" t="inlineStr">
@@ -26489,7 +26473,7 @@
     <row r="553" ht="22" customHeight="1">
       <c r="A553" s="2" t="inlineStr">
         <is>
-          <t>4f38d6c20430e4bb</t>
+          <t>06656fbb2d452086</t>
         </is>
       </c>
       <c r="B553" s="2" t="inlineStr">
@@ -26499,16 +26483,16 @@
       </c>
       <c r="C553" s="3" t="inlineStr">
         <is>
-          <t>ingeniero civil</t>
+          <t>Residente de Seguridad y Salud en el trabajo</t>
         </is>
       </c>
       <c r="D553" s="3" t="inlineStr">
         <is>
-          <t>EVALTEC S.A.S.</t>
+          <t>Grupo Cal y Mayor</t>
         </is>
       </c>
       <c r="E553" s="8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="F553" s="2" t="inlineStr">
         <is>
@@ -26516,13 +26500,13 @@
         </is>
       </c>
       <c r="G553" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-o-areas-afines-en-medellin-0E02F682AB12631061373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/residente-de-seguridad-y-salud-en-el-trabajo-sst-at-cal-y-mayor-4468610572", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H553" s="6" t="inlineStr"/>
       <c r="I553" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 48/100 - Baja Afinidad] Alta coincidencia en gestión de Seguridad y Salud en el Trabajo (SST). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J553" s="2" t="inlineStr">
@@ -26535,7 +26519,7 @@
     <row r="554" ht="22" customHeight="1">
       <c r="A554" s="2" t="inlineStr">
         <is>
-          <t>af38dd28fbbad8f4</t>
+          <t>7796e088dce85b5a</t>
         </is>
       </c>
       <c r="B554" s="2" t="inlineStr">
@@ -26545,12 +26529,12 @@
       </c>
       <c r="C554" s="3" t="inlineStr">
         <is>
-          <t>Tecnólogo Auxiliar Civil</t>
+          <t>Civil Engineer (Fire Sprinkler Design))</t>
         </is>
       </c>
       <c r="D554" s="3" t="inlineStr">
         <is>
-          <t>Importante empresa del sector</t>
+          <t>Hyremote</t>
         </is>
       </c>
       <c r="E554" s="8" t="n">
@@ -26562,10 +26546,14 @@
         </is>
       </c>
       <c r="G554" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-tecnologo-auxiliar-civil-antioquia-en-liborina-B380460DDA9F98D061373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H554" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-civil-engineer-fire-sprinkler-design-english-c1-remote-en-bogota-dc-A2EE61A321FC0D3361373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H554" s="6" t="inlineStr">
+        <is>
+          <t>$ 4.499.993,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I554" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -26581,7 +26569,7 @@
     <row r="555" ht="22" customHeight="1">
       <c r="A555" s="2" t="inlineStr">
         <is>
-          <t>19e74768ce848880</t>
+          <t>48463526ca7c8ada</t>
         </is>
       </c>
       <c r="B555" s="2" t="inlineStr">
@@ -26591,12 +26579,12 @@
       </c>
       <c r="C555" s="3" t="inlineStr">
         <is>
-          <t>Coordinador HSEQ</t>
+          <t>Ingeniero Civil Especialista en Hidrología e Hidráulica</t>
         </is>
       </c>
       <c r="D555" s="3" t="inlineStr">
         <is>
-          <t>Agencia de empleo de Comfenalco Cartagena</t>
+          <t>ATLAS INFRASTRUCTURE DESIGN LIMITED</t>
         </is>
       </c>
       <c r="E555" s="8" t="n">
@@ -26608,17 +26596,17 @@
         </is>
       </c>
       <c r="G555" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-hseq-especialista-en-seguridad-y-salud-en-el-trabajo-salud-ocupacional-en-cartagena-de-indias-1EAF6570FC054C2661373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-especialista-en-hidrologia-e-hidraulica-tiempo-completo-en-remoto-y-de-larga-duracion-en-colombia-027FB718364F4C7761373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H555" s="6" t="inlineStr">
         <is>
-          <t>$ 2.500.000,00 (Mensual)</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="I555" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J555" s="2" t="inlineStr">
@@ -26631,7 +26619,7 @@
     <row r="556" ht="22" customHeight="1">
       <c r="A556" s="2" t="inlineStr">
         <is>
-          <t>38c9a9481706de58</t>
+          <t>2d406567ceb21bf8</t>
         </is>
       </c>
       <c r="B556" s="2" t="inlineStr">
@@ -26641,12 +26629,12 @@
       </c>
       <c r="C556" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de seguridad vial y monitoreo</t>
+          <t>Ingeniero Civil de Diseño</t>
         </is>
       </c>
       <c r="D556" s="3" t="inlineStr">
         <is>
-          <t>MEGACOMERCIAL S.A.S</t>
+          <t>ATLAS INFRASTRUCTURE DESIGN LIMITED</t>
         </is>
       </c>
       <c r="E556" s="8" t="n">
@@ -26658,17 +26646,17 @@
         </is>
       </c>
       <c r="G556" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-de-seguridad-vial-y-monitoreo-abierto-a-nivel-nacional-en-bogota-dc-B9B593A780889F2A61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-de-diseno-tiempo-completo-en-remoto-en-colombia-4CB8F30B6D8FBF7261373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H556" s="6" t="inlineStr">
         <is>
-          <t>$ 5.000.000,00 (Mensual)</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="I556" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J556" s="2" t="inlineStr">
@@ -26681,7 +26669,7 @@
     <row r="557" ht="22" customHeight="1">
       <c r="A557" s="2" t="inlineStr">
         <is>
-          <t>aecc6c18fdd71383</t>
+          <t>4d4013d19591d2a5</t>
         </is>
       </c>
       <c r="B557" s="2" t="inlineStr">
@@ -26691,12 +26679,12 @@
       </c>
       <c r="C557" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de PESV</t>
+          <t>Especialista en Salud y Seguridad en el trabajo con especialización en medio Ambiente</t>
         </is>
       </c>
       <c r="D557" s="3" t="inlineStr">
         <is>
-          <t>Agencia de Empleo de Comfenalco Antioquia</t>
+          <t>DEXTERA S.A.S</t>
         </is>
       </c>
       <c r="E557" s="8" t="n">
@@ -26708,17 +26696,13 @@
         </is>
       </c>
       <c r="G557" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-de-pesv-en-medellin-67C3B78E9A85885161373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H557" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.800.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-especialista-en-salud-y-seguridad-en-el-trabajo-con-especializacion-en-medio-ambiente-en-bogota-dc-68C95C2F64D6648561373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H557" s="6" t="inlineStr"/>
       <c r="I557" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J557" s="2" t="inlineStr">
@@ -26731,7 +26715,7 @@
     <row r="558" ht="22" customHeight="1">
       <c r="A558" s="2" t="inlineStr">
         <is>
-          <t>1558fc20863bdd35</t>
+          <t>cf70d2ca6e5c25de</t>
         </is>
       </c>
       <c r="B558" s="2" t="inlineStr">
@@ -26741,12 +26725,12 @@
       </c>
       <c r="C558" s="3" t="inlineStr">
         <is>
-          <t>Coordinador HSEQ</t>
+          <t>Ingeniero civil</t>
         </is>
       </c>
       <c r="D558" s="3" t="inlineStr">
         <is>
-          <t>COMPAÑIA DE INGENIEROS CONSTRUCTORES S.A.S.</t>
+          <t>Importante empresa del sector</t>
         </is>
       </c>
       <c r="E558" s="8" t="n">
@@ -26758,13 +26742,17 @@
         </is>
       </c>
       <c r="G558" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-hseq-en-barranquilla-F4898EBB71CAF3ED61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H558" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-con-experiencia-en-sistemas-fotovoltaicos-en-bogota-dc-8BCBCD7DF8FE589C61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H558" s="6" t="inlineStr">
+        <is>
+          <t>$ 3.300.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I558" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J558" s="2" t="inlineStr">
@@ -26777,7 +26765,7 @@
     <row r="559" ht="22" customHeight="1">
       <c r="A559" s="2" t="inlineStr">
         <is>
-          <t>0bf63022dc93885b</t>
+          <t>bb8237cc7ed8d56b</t>
         </is>
       </c>
       <c r="B559" s="2" t="inlineStr">
@@ -26787,12 +26775,12 @@
       </c>
       <c r="C559" s="3" t="inlineStr">
         <is>
-          <t>ingeniero civil</t>
+          <t>Coordinador de Proyectos Mejoramientos de Vivienda</t>
         </is>
       </c>
       <c r="D559" s="3" t="inlineStr">
         <is>
-          <t>FRANCISCO ANGULO M INGENIEROS S.A.S.</t>
+          <t>Socya</t>
         </is>
       </c>
       <c r="E559" s="8" t="n">
@@ -26804,7 +26792,7 @@
         </is>
       </c>
       <c r="G559" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-residente-de-interventoria-yo-supervision-tecnica-en-cali-D2AE78FA9B23778161373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-de-proyectos-mejoramientos-de-vivienda-medellin-antioquia-en-medellin-7E29781CFFD4058961373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H559" s="6" t="inlineStr"/>
@@ -26823,7 +26811,7 @@
     <row r="560" ht="22" customHeight="1">
       <c r="A560" s="2" t="inlineStr">
         <is>
-          <t>baa61a6e15a2de77</t>
+          <t>c41dc091e876cb10</t>
         </is>
       </c>
       <c r="B560" s="2" t="inlineStr">
@@ -26833,12 +26821,12 @@
       </c>
       <c r="C560" s="3" t="inlineStr">
         <is>
-          <t>Arquitecto(a) / Ingeniero(a) Civil</t>
+          <t>Especialista de Milk Collection</t>
         </is>
       </c>
       <c r="D560" s="3" t="inlineStr">
         <is>
-          <t>Importante empresa del sector</t>
+          <t>LACTALIS</t>
         </is>
       </c>
       <c r="E560" s="8" t="n">
@@ -26850,10 +26838,14 @@
         </is>
       </c>
       <c r="G560" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-arquitectoa-ingenieroa-civil-en-bucaramanga-8D15AF34F304555F61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H560" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-especialista-de-milk-collection-optimizacion-y-analisis-de-datos-en-bogota-dc-B007F5172FEA6F6461373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H560" s="6" t="inlineStr">
+        <is>
+          <t>$ 6.000.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I560" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -26869,7 +26861,7 @@
     <row r="561" ht="22" customHeight="1">
       <c r="A561" s="2" t="inlineStr">
         <is>
-          <t>448d93b15d9b7dec</t>
+          <t>4f38d6c20430e4bb</t>
         </is>
       </c>
       <c r="B561" s="2" t="inlineStr">
@@ -26879,12 +26871,12 @@
       </c>
       <c r="C561" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero especialista fortinet</t>
+          <t>ingeniero civil</t>
         </is>
       </c>
       <c r="D561" s="3" t="inlineStr">
         <is>
-          <t>ATCG DE COLOMBIA S.A.S</t>
+          <t>EVALTEC S.A.S.</t>
         </is>
       </c>
       <c r="E561" s="8" t="n">
@@ -26896,7 +26888,7 @@
         </is>
       </c>
       <c r="G561" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-especialista-fortinet-1886742914", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-o-areas-afines-en-medellin-0E02F682AB12631061373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H561" s="6" t="inlineStr"/>
@@ -26915,7 +26907,7 @@
     <row r="562" ht="22" customHeight="1">
       <c r="A562" s="2" t="inlineStr">
         <is>
-          <t>f2fc6f9471f81665</t>
+          <t>af38dd28fbbad8f4</t>
         </is>
       </c>
       <c r="B562" s="2" t="inlineStr">
@@ -26925,12 +26917,12 @@
       </c>
       <c r="C562" s="3" t="inlineStr">
         <is>
-          <t>Coordinador/a nacional de redes e infraestructura de ti - presencial bucaramanga</t>
+          <t>Tecnólogo Auxiliar Civil</t>
         </is>
       </c>
       <c r="D562" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Importante empresa del sector</t>
         </is>
       </c>
       <c r="E562" s="8" t="n">
@@ -26942,13 +26934,13 @@
         </is>
       </c>
       <c r="G562" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-a-nacional-de-redes-e-infraestructura-de-ti-presencial-bucaramanga-1886769481", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-tecnologo-auxiliar-civil-antioquia-en-liborina-B380460DDA9F98D061373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H562" s="6" t="inlineStr"/>
       <c r="I562" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J562" s="2" t="inlineStr">
@@ -26961,7 +26953,7 @@
     <row r="563" ht="22" customHeight="1">
       <c r="A563" s="2" t="inlineStr">
         <is>
-          <t>53e1a775996a36c5</t>
+          <t>19e74768ce848880</t>
         </is>
       </c>
       <c r="B563" s="2" t="inlineStr">
@@ -26971,12 +26963,12 @@
       </c>
       <c r="C563" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero civil</t>
+          <t>Coordinador HSEQ</t>
         </is>
       </c>
       <c r="D563" s="3" t="inlineStr">
         <is>
-          <t>Proyectos de Diseño y Construccion sas</t>
+          <t>Agencia de empleo de Comfenalco Cartagena</t>
         </is>
       </c>
       <c r="E563" s="8" t="n">
@@ -26988,13 +26980,17 @@
         </is>
       </c>
       <c r="G563" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-1886757049", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H563" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-hseq-especialista-en-seguridad-y-salud-en-el-trabajo-salud-ocupacional-en-cartagena-de-indias-1EAF6570FC054C2661373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H563" s="6" t="inlineStr">
+        <is>
+          <t>$ 2.500.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I563" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J563" s="2" t="inlineStr">
@@ -27007,7 +27003,7 @@
     <row r="564" ht="22" customHeight="1">
       <c r="A564" s="2" t="inlineStr">
         <is>
-          <t>1072d76e2f18ea50</t>
+          <t>38c9a9481706de58</t>
         </is>
       </c>
       <c r="B564" s="2" t="inlineStr">
@@ -27017,12 +27013,12 @@
       </c>
       <c r="C564" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero civil</t>
+          <t>Coordinador de seguridad vial y monitoreo</t>
         </is>
       </c>
       <c r="D564" s="3" t="inlineStr">
         <is>
-          <t>R2P SOLUCIONES Y CONSTRUCCIONES SAS</t>
+          <t>MEGACOMERCIAL S.A.S</t>
         </is>
       </c>
       <c r="E564" s="8" t="n">
@@ -27034,13 +27030,17 @@
         </is>
       </c>
       <c r="G564" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-1886758475", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H564" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-de-seguridad-vial-y-monitoreo-abierto-a-nivel-nacional-en-bogota-dc-B9B593A780889F2A61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H564" s="6" t="inlineStr">
+        <is>
+          <t>$ 5.000.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I564" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J564" s="2" t="inlineStr">
@@ -27053,7 +27053,7 @@
     <row r="565" ht="22" customHeight="1">
       <c r="A565" s="2" t="inlineStr">
         <is>
-          <t>2c943591cc334f5a</t>
+          <t>aecc6c18fdd71383</t>
         </is>
       </c>
       <c r="B565" s="2" t="inlineStr">
@@ -27063,12 +27063,12 @@
       </c>
       <c r="C565" s="3" t="inlineStr">
         <is>
-          <t>Ejecutivo/ade ingeniera</t>
+          <t>Coordinador de PESV</t>
         </is>
       </c>
       <c r="D565" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Agencia de Empleo de Comfenalco Antioquia</t>
         </is>
       </c>
       <c r="E565" s="8" t="n">
@@ -27080,13 +27080,17 @@
         </is>
       </c>
       <c r="G565" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-ade-ingeniera-1886752134", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H565" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-de-pesv-en-medellin-67C3B78E9A85885161373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H565" s="6" t="inlineStr">
+        <is>
+          <t>$ 2.800.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I565" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J565" s="2" t="inlineStr">
@@ -27099,7 +27103,7 @@
     <row r="566" ht="22" customHeight="1">
       <c r="A566" s="2" t="inlineStr">
         <is>
-          <t>7d4067502e572780</t>
+          <t>1558fc20863bdd35</t>
         </is>
       </c>
       <c r="B566" s="2" t="inlineStr">
@@ -27109,12 +27113,12 @@
       </c>
       <c r="C566" s="3" t="inlineStr">
         <is>
-          <t>Ingeniera de ventas - cali</t>
+          <t>Coordinador HSEQ</t>
         </is>
       </c>
       <c r="D566" s="3" t="inlineStr">
         <is>
-          <t>PIPOL EXPERT SAS</t>
+          <t>COMPAÑIA DE INGENIEROS CONSTRUCTORES S.A.S.</t>
         </is>
       </c>
       <c r="E566" s="8" t="n">
@@ -27126,13 +27130,13 @@
         </is>
       </c>
       <c r="G566" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-de-ventas-cali-1886754430", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-coordinador-hseq-en-barranquilla-F4898EBB71CAF3ED61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H566" s="6" t="inlineStr"/>
       <c r="I566" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J566" s="2" t="inlineStr">
@@ -27145,7 +27149,7 @@
     <row r="567" ht="22" customHeight="1">
       <c r="A567" s="2" t="inlineStr">
         <is>
-          <t>a3a688084650de1c</t>
+          <t>0bf63022dc93885b</t>
         </is>
       </c>
       <c r="B567" s="2" t="inlineStr">
@@ -27155,12 +27159,12 @@
       </c>
       <c r="C567" s="3" t="inlineStr">
         <is>
-          <t>Ingeniera comercial electrica - cali</t>
+          <t>ingeniero civil</t>
         </is>
       </c>
       <c r="D567" s="3" t="inlineStr">
         <is>
-          <t>PIPOL EXPERT SAS</t>
+          <t>FRANCISCO ANGULO M INGENIEROS S.A.S.</t>
         </is>
       </c>
       <c r="E567" s="8" t="n">
@@ -27172,7 +27176,7 @@
         </is>
       </c>
       <c r="G567" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-comercial-electrica-cali-1886752104", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-ingeniero-civil-residente-de-interventoria-yo-supervision-tecnica-en-cali-D2AE78FA9B23778161373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H567" s="6" t="inlineStr"/>
@@ -27191,7 +27195,7 @@
     <row r="568" ht="22" customHeight="1">
       <c r="A568" s="2" t="inlineStr">
         <is>
-          <t>359d47915a2e74e6</t>
+          <t>baa61a6e15a2de77</t>
         </is>
       </c>
       <c r="B568" s="2" t="inlineStr">
@@ -27201,12 +27205,12 @@
       </c>
       <c r="C568" s="3" t="inlineStr">
         <is>
-          <t>Supervisor civil - obra</t>
+          <t>Arquitecto(a) / Ingeniero(a) Civil</t>
         </is>
       </c>
       <c r="D568" s="3" t="inlineStr">
         <is>
-          <t>CONCONCRETO S.A.</t>
+          <t>Importante empresa del sector</t>
         </is>
       </c>
       <c r="E568" s="8" t="n">
@@ -27218,7 +27222,7 @@
         </is>
       </c>
       <c r="G568" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/supervisor-civil-obra-1886750435", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-arquitectoa-ingenieroa-civil-en-bucaramanga-8D15AF34F304555F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H568" s="6" t="inlineStr"/>
@@ -27237,7 +27241,7 @@
     <row r="569" ht="22" customHeight="1">
       <c r="A569" s="2" t="inlineStr">
         <is>
-          <t>78244d2897084f6a</t>
+          <t>448d93b15d9b7dec</t>
         </is>
       </c>
       <c r="B569" s="2" t="inlineStr">
@@ -27247,12 +27251,12 @@
       </c>
       <c r="C569" s="3" t="inlineStr">
         <is>
-          <t>Ingeniera comercial sector industrial - cali</t>
+          <t>Ingeniero especialista fortinet</t>
         </is>
       </c>
       <c r="D569" s="3" t="inlineStr">
         <is>
-          <t>PIPOL EXPERT SAS</t>
+          <t>ATCG DE COLOMBIA S.A.S</t>
         </is>
       </c>
       <c r="E569" s="8" t="n">
@@ -27264,7 +27268,7 @@
         </is>
       </c>
       <c r="G569" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-comercial-sector-industrial-cali-1886753949", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-especialista-fortinet-1886742914", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H569" s="6" t="inlineStr"/>
@@ -27283,7 +27287,7 @@
     <row r="570" ht="22" customHeight="1">
       <c r="A570" s="2" t="inlineStr">
         <is>
-          <t>a4d1239b8910f7cf</t>
+          <t>f2fc6f9471f81665</t>
         </is>
       </c>
       <c r="B570" s="2" t="inlineStr">
@@ -27293,12 +27297,12 @@
       </c>
       <c r="C570" s="3" t="inlineStr">
         <is>
-          <t>Ingeniera electrica comercial - bogotá</t>
+          <t>Coordinador/a nacional de redes e infraestructura de ti - presencial bucaramanga</t>
         </is>
       </c>
       <c r="D570" s="3" t="inlineStr">
         <is>
-          <t>PIPOL EXPERT SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E570" s="8" t="n">
@@ -27310,13 +27314,13 @@
         </is>
       </c>
       <c r="G570" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-electrica-comercial-bogota-1886756984", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-a-nacional-de-redes-e-infraestructura-de-ti-presencial-bucaramanga-1886769481", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H570" s="6" t="inlineStr"/>
       <c r="I570" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J570" s="2" t="inlineStr">
@@ -27329,7 +27333,7 @@
     <row r="571" ht="22" customHeight="1">
       <c r="A571" s="2" t="inlineStr">
         <is>
-          <t>366f049dd1eaf173</t>
+          <t>53e1a775996a36c5</t>
         </is>
       </c>
       <c r="B571" s="2" t="inlineStr">
@@ -27339,12 +27343,12 @@
       </c>
       <c r="C571" s="3" t="inlineStr">
         <is>
-          <t>Civil engineering-in-training</t>
+          <t>Ingeniero civil</t>
         </is>
       </c>
       <c r="D571" s="3" t="inlineStr">
         <is>
-          <t>WSP COLOMBIA SAS</t>
+          <t>Proyectos de Diseño y Construccion sas</t>
         </is>
       </c>
       <c r="E571" s="8" t="n">
@@ -27356,7 +27360,7 @@
         </is>
       </c>
       <c r="G571" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/civil-engineeringintraining-1886759044", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-1886757049", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H571" s="6" t="inlineStr"/>
@@ -27375,7 +27379,7 @@
     <row r="572" ht="22" customHeight="1">
       <c r="A572" s="2" t="inlineStr">
         <is>
-          <t>555a755e56fc6a80</t>
+          <t>1072d76e2f18ea50</t>
         </is>
       </c>
       <c r="B572" s="2" t="inlineStr">
@@ -27385,12 +27389,12 @@
       </c>
       <c r="C572" s="3" t="inlineStr">
         <is>
-          <t>Civil engineering-in-training</t>
+          <t>Ingeniero civil</t>
         </is>
       </c>
       <c r="D572" s="3" t="inlineStr">
         <is>
-          <t>WSP COLOMBIA SAS</t>
+          <t>R2P SOLUCIONES Y CONSTRUCCIONES SAS</t>
         </is>
       </c>
       <c r="E572" s="8" t="n">
@@ -27402,7 +27406,7 @@
         </is>
       </c>
       <c r="G572" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/civil-engineeringintraining-1886758755", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-1886758475", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H572" s="6" t="inlineStr"/>
@@ -27421,7 +27425,7 @@
     <row r="573" ht="22" customHeight="1">
       <c r="A573" s="2" t="inlineStr">
         <is>
-          <t>776483d4ec602e40</t>
+          <t>2c943591cc334f5a</t>
         </is>
       </c>
       <c r="B573" s="2" t="inlineStr">
@@ -27431,12 +27435,12 @@
       </c>
       <c r="C573" s="3" t="inlineStr">
         <is>
-          <t>Consultor senior sap pm - remoto colombia</t>
+          <t>Ejecutivo/ade ingeniera</t>
         </is>
       </c>
       <c r="D573" s="3" t="inlineStr">
         <is>
-          <t>TALYCAP GLOBAL SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E573" s="8" t="n">
@@ -27448,7 +27452,7 @@
         </is>
       </c>
       <c r="G573" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultor-senior-sap-pm-remoto-colombia-1886747903", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-ade-ingeniera-1886752134", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H573" s="6" t="inlineStr"/>
@@ -27467,7 +27471,7 @@
     <row r="574" ht="22" customHeight="1">
       <c r="A574" s="2" t="inlineStr">
         <is>
-          <t>b1cfe269bbc00011</t>
+          <t>7d4067502e572780</t>
         </is>
       </c>
       <c r="B574" s="2" t="inlineStr">
@@ -27477,12 +27481,12 @@
       </c>
       <c r="C574" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de interventoría</t>
+          <t>Ingeniera de ventas - cali</t>
         </is>
       </c>
       <c r="D574" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>PIPOL EXPERT SAS</t>
         </is>
       </c>
       <c r="E574" s="8" t="n">
@@ -27494,7 +27498,7 @@
         </is>
       </c>
       <c r="G574" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-interventoria-1886751671", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-de-ventas-cali-1886754430", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H574" s="6" t="inlineStr"/>
@@ -27513,7 +27517,7 @@
     <row r="575" ht="22" customHeight="1">
       <c r="A575" s="2" t="inlineStr">
         <is>
-          <t>b7a3423e1ee1e624</t>
+          <t>a3a688084650de1c</t>
         </is>
       </c>
       <c r="B575" s="2" t="inlineStr">
@@ -27523,12 +27527,12 @@
       </c>
       <c r="C575" s="3" t="inlineStr">
         <is>
-          <t>Especialista en urbanismo - proyecto vial</t>
+          <t>Ingeniera comercial electrica - cali</t>
         </is>
       </c>
       <c r="D575" s="3" t="inlineStr">
         <is>
-          <t>INGEPLAN.CO SAS EMPRESA DE BENEFICIO E INTERES COLECTIVO BIC</t>
+          <t>PIPOL EXPERT SAS</t>
         </is>
       </c>
       <c r="E575" s="8" t="n">
@@ -27540,7 +27544,7 @@
         </is>
       </c>
       <c r="G575" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-urbanismo-proyecto-vial-1886755827", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-comercial-electrica-cali-1886752104", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H575" s="6" t="inlineStr"/>
@@ -27559,7 +27563,7 @@
     <row r="576" ht="22" customHeight="1">
       <c r="A576" s="2" t="inlineStr">
         <is>
-          <t>fcb39d755657052e</t>
+          <t>359d47915a2e74e6</t>
         </is>
       </c>
       <c r="B576" s="2" t="inlineStr">
@@ -27569,12 +27573,12 @@
       </c>
       <c r="C576" s="3" t="inlineStr">
         <is>
-          <t>Coordinador hseq</t>
+          <t>Supervisor civil - obra</t>
         </is>
       </c>
       <c r="D576" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>CONCONCRETO S.A.</t>
         </is>
       </c>
       <c r="E576" s="8" t="n">
@@ -27586,13 +27590,13 @@
         </is>
       </c>
       <c r="G576" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-1886747304", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/supervisor-civil-obra-1886750435", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H576" s="6" t="inlineStr"/>
       <c r="I576" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J576" s="2" t="inlineStr">
@@ -27605,7 +27609,7 @@
     <row r="577" ht="22" customHeight="1">
       <c r="A577" s="2" t="inlineStr">
         <is>
-          <t>9e2f0c16f1a50983</t>
+          <t>78244d2897084f6a</t>
         </is>
       </c>
       <c r="B577" s="2" t="inlineStr">
@@ -27615,12 +27619,12 @@
       </c>
       <c r="C577" s="3" t="inlineStr">
         <is>
-          <t>Coordinador hseq</t>
+          <t>Ingeniera comercial sector industrial - cali</t>
         </is>
       </c>
       <c r="D577" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>PIPOL EXPERT SAS</t>
         </is>
       </c>
       <c r="E577" s="8" t="n">
@@ -27632,13 +27636,13 @@
         </is>
       </c>
       <c r="G577" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-1886764155", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-comercial-sector-industrial-cali-1886753949", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H577" s="6" t="inlineStr"/>
       <c r="I577" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J577" s="2" t="inlineStr">
@@ -27651,7 +27655,7 @@
     <row r="578" ht="22" customHeight="1">
       <c r="A578" s="2" t="inlineStr">
         <is>
-          <t>9d4d87a631d5e8b8</t>
+          <t>a4d1239b8910f7cf</t>
         </is>
       </c>
       <c r="B578" s="2" t="inlineStr">
@@ -27661,12 +27665,12 @@
       </c>
       <c r="C578" s="3" t="inlineStr">
         <is>
-          <t>Coordinador hseq</t>
+          <t>Ingeniera electrica comercial - bogotá</t>
         </is>
       </c>
       <c r="D578" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>PIPOL EXPERT SAS</t>
         </is>
       </c>
       <c r="E578" s="8" t="n">
@@ -27678,13 +27682,13 @@
         </is>
       </c>
       <c r="G578" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-1886760733", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniera-electrica-comercial-bogota-1886756984", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H578" s="6" t="inlineStr"/>
       <c r="I578" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J578" s="2" t="inlineStr">
@@ -27697,7 +27701,7 @@
     <row r="579" ht="22" customHeight="1">
       <c r="A579" s="2" t="inlineStr">
         <is>
-          <t>62d6690ef260f268</t>
+          <t>366f049dd1eaf173</t>
         </is>
       </c>
       <c r="B579" s="2" t="inlineStr">
@@ -27707,12 +27711,12 @@
       </c>
       <c r="C579" s="3" t="inlineStr">
         <is>
-          <t>Coordinador hseq cartagena</t>
+          <t>Civil engineering-in-training</t>
         </is>
       </c>
       <c r="D579" s="3" t="inlineStr">
         <is>
-          <t>APPLUS NORCONTROL COLOMBIA LTDA</t>
+          <t>WSP COLOMBIA SAS</t>
         </is>
       </c>
       <c r="E579" s="8" t="n">
@@ -27724,13 +27728,13 @@
         </is>
       </c>
       <c r="G579" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-cartagena-1886754661", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/civil-engineeringintraining-1886759044", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H579" s="6" t="inlineStr"/>
       <c r="I579" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J579" s="2" t="inlineStr">
@@ -27743,7 +27747,7 @@
     <row r="580" ht="22" customHeight="1">
       <c r="A580" s="2" t="inlineStr">
         <is>
-          <t>6e57e2acbfc11d12</t>
+          <t>555a755e56fc6a80</t>
         </is>
       </c>
       <c r="B580" s="2" t="inlineStr">
@@ -27753,12 +27757,12 @@
       </c>
       <c r="C580" s="3" t="inlineStr">
         <is>
-          <t>Especialista sig</t>
+          <t>Civil engineering-in-training</t>
         </is>
       </c>
       <c r="D580" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>WSP COLOMBIA SAS</t>
         </is>
       </c>
       <c r="E580" s="8" t="n">
@@ -27770,7 +27774,7 @@
         </is>
       </c>
       <c r="G580" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-sig-1886757094", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/civil-engineeringintraining-1886758755", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H580" s="6" t="inlineStr"/>
@@ -27789,7 +27793,7 @@
     <row r="581" ht="22" customHeight="1">
       <c r="A581" s="2" t="inlineStr">
         <is>
-          <t>11494a184e6f9290</t>
+          <t>776483d4ec602e40</t>
         </is>
       </c>
       <c r="B581" s="2" t="inlineStr">
@@ -27799,12 +27803,12 @@
       </c>
       <c r="C581" s="3" t="inlineStr">
         <is>
-          <t>Especialista en ingeniería civil - coordinador técnico</t>
+          <t>Consultor senior sap pm - remoto colombia</t>
         </is>
       </c>
       <c r="D581" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>TALYCAP GLOBAL SAS</t>
         </is>
       </c>
       <c r="E581" s="8" t="n">
@@ -27816,7 +27820,7 @@
         </is>
       </c>
       <c r="G581" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-ingenieria-civil-coordinador-tecnico-honduras-1886745304", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultor-senior-sap-pm-remoto-colombia-1886747903", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H581" s="6" t="inlineStr"/>
@@ -27835,7 +27839,7 @@
     <row r="582" ht="22" customHeight="1">
       <c r="A582" s="2" t="inlineStr">
         <is>
-          <t>327c6d2b54619849</t>
+          <t>b1cfe269bbc00011</t>
         </is>
       </c>
       <c r="B582" s="2" t="inlineStr">
@@ -27845,7 +27849,7 @@
       </c>
       <c r="C582" s="3" t="inlineStr">
         <is>
-          <t>Especialista en psiquiatría</t>
+          <t>Coordinador de interventoría</t>
         </is>
       </c>
       <c r="D582" s="3" t="inlineStr">
@@ -27862,7 +27866,7 @@
         </is>
       </c>
       <c r="G582" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-psiquiatria-1886757353", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-interventoria-1886751671", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H582" s="6" t="inlineStr"/>
@@ -27881,7 +27885,7 @@
     <row r="583" ht="22" customHeight="1">
       <c r="A583" s="2" t="inlineStr">
         <is>
-          <t>b637f33f588eb5ae</t>
+          <t>b7a3423e1ee1e624</t>
         </is>
       </c>
       <c r="B583" s="2" t="inlineStr">
@@ -27891,12 +27895,12 @@
       </c>
       <c r="C583" s="3" t="inlineStr">
         <is>
-          <t>Especialista en diseño hospitalario</t>
+          <t>Especialista en urbanismo - proyecto vial</t>
         </is>
       </c>
       <c r="D583" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>INGEPLAN.CO SAS EMPRESA DE BENEFICIO E INTERES COLECTIVO BIC</t>
         </is>
       </c>
       <c r="E583" s="8" t="n">
@@ -27908,7 +27912,7 @@
         </is>
       </c>
       <c r="G583" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-diseno-hospitalario-disponibilidad-viajar-a-peru-1886747220", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-urbanismo-proyecto-vial-1886755827", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H583" s="6" t="inlineStr"/>
@@ -27927,7 +27931,7 @@
     <row r="584" ht="22" customHeight="1">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>adcc2b47284b5d4d</t>
+          <t>fcb39d755657052e</t>
         </is>
       </c>
       <c r="B584" s="2" t="inlineStr">
@@ -27937,12 +27941,12 @@
       </c>
       <c r="C584" s="3" t="inlineStr">
         <is>
-          <t>Analista de diseño e ingeniería de empaque - sector farmaceutico</t>
+          <t>Coordinador hseq</t>
         </is>
       </c>
       <c r="D584" s="3" t="inlineStr">
         <is>
-          <t>LABORATORIOS BUSSIE</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E584" s="8" t="n">
@@ -27954,13 +27958,13 @@
         </is>
       </c>
       <c r="G584" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-diseno-e-ingenieria-de-empaque-sector-farmaceutico-1886755492", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-1886747304", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H584" s="6" t="inlineStr"/>
       <c r="I584" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J584" s="2" t="inlineStr">
@@ -27973,7 +27977,7 @@
     <row r="585" ht="22" customHeight="1">
       <c r="A585" s="2" t="inlineStr">
         <is>
-          <t>3ec3d2d34753ff04</t>
+          <t>9e2f0c16f1a50983</t>
         </is>
       </c>
       <c r="B585" s="2" t="inlineStr">
@@ -27983,12 +27987,12 @@
       </c>
       <c r="C585" s="3" t="inlineStr">
         <is>
-          <t>Especialista de diseño y arquitectura</t>
+          <t>Coordinador hseq</t>
         </is>
       </c>
       <c r="D585" s="3" t="inlineStr">
         <is>
-          <t>INTER RAPIDISIMO</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E585" s="8" t="n">
@@ -28000,13 +28004,13 @@
         </is>
       </c>
       <c r="G585" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-de-diseno-y-arquitectura-1886761909", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-1886764155", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H585" s="6" t="inlineStr"/>
       <c r="I585" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J585" s="2" t="inlineStr">
@@ -28019,7 +28023,7 @@
     <row r="586" ht="22" customHeight="1">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>4e917305e90b3efa</t>
+          <t>9d4d87a631d5e8b8</t>
         </is>
       </c>
       <c r="B586" s="2" t="inlineStr">
@@ -28029,12 +28033,12 @@
       </c>
       <c r="C586" s="3" t="inlineStr">
         <is>
-          <t>Especialista en geología</t>
+          <t>Coordinador hseq</t>
         </is>
       </c>
       <c r="D586" s="3" t="inlineStr">
         <is>
-          <t>INGEPLAN.CO SAS EMPRESA DE BENEFICIO E INTERES COLECTIVO BIC</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E586" s="8" t="n">
@@ -28046,13 +28050,13 @@
         </is>
       </c>
       <c r="G586" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-geologia-1886761263", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-1886760733", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H586" s="6" t="inlineStr"/>
       <c r="I586" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J586" s="2" t="inlineStr">
@@ -28065,7 +28069,7 @@
     <row r="587" ht="22" customHeight="1">
       <c r="A587" s="2" t="inlineStr">
         <is>
-          <t>1aef5476d70bbe42</t>
+          <t>62d6690ef260f268</t>
         </is>
       </c>
       <c r="B587" s="2" t="inlineStr">
@@ -28075,12 +28079,12 @@
       </c>
       <c r="C587" s="3" t="inlineStr">
         <is>
-          <t>Especialista en geología</t>
+          <t>Coordinador hseq cartagena</t>
         </is>
       </c>
       <c r="D587" s="3" t="inlineStr">
         <is>
-          <t>INGEPLAN.CO SAS EMPRESA DE BENEFICIO E INTERES COLECTIVO BIC</t>
+          <t>APPLUS NORCONTROL COLOMBIA LTDA</t>
         </is>
       </c>
       <c r="E587" s="8" t="n">
@@ -28092,13 +28096,13 @@
         </is>
       </c>
       <c r="G587" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-geologia-1886755729", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-hseq-cartagena-1886754661", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H587" s="6" t="inlineStr"/>
       <c r="I587" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J587" s="2" t="inlineStr">
@@ -28111,7 +28115,7 @@
     <row r="588" ht="22" customHeight="1">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>b46df3b678599255</t>
+          <t>6e57e2acbfc11d12</t>
         </is>
       </c>
       <c r="B588" s="2" t="inlineStr">
@@ -28121,7 +28125,7 @@
       </c>
       <c r="C588" s="3" t="inlineStr">
         <is>
-          <t>Especialista en estructuras</t>
+          <t>Especialista sig</t>
         </is>
       </c>
       <c r="D588" s="3" t="inlineStr">
@@ -28138,7 +28142,7 @@
         </is>
       </c>
       <c r="G588" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-estructuras-1886757080", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-sig-1886757094", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H588" s="6" t="inlineStr"/>
@@ -28157,7 +28161,7 @@
     <row r="589" ht="22" customHeight="1">
       <c r="A589" s="2" t="inlineStr">
         <is>
-          <t>935035bdfa2ae0b7</t>
+          <t>11494a184e6f9290</t>
         </is>
       </c>
       <c r="B589" s="2" t="inlineStr">
@@ -28167,12 +28171,12 @@
       </c>
       <c r="C589" s="3" t="inlineStr">
         <is>
-          <t>Especialista en gestión del riesgo</t>
+          <t>Especialista en ingeniería civil - coordinador técnico</t>
         </is>
       </c>
       <c r="D589" s="3" t="inlineStr">
         <is>
-          <t>INGEPLAN.CO SAS EMPRESA DE BENEFICIO E INTERES COLECTIVO BIC</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E589" s="8" t="n">
@@ -28184,7 +28188,7 @@
         </is>
       </c>
       <c r="G589" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-gestion-del-riesgo-1886755709", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-ingenieria-civil-coordinador-tecnico-honduras-1886745304", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H589" s="6" t="inlineStr"/>
@@ -28203,7 +28207,7 @@
     <row r="590" ht="22" customHeight="1">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>14a1c964238340ba</t>
+          <t>327c6d2b54619849</t>
         </is>
       </c>
       <c r="B590" s="2" t="inlineStr">
@@ -28213,7 +28217,7 @@
       </c>
       <c r="C590" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero civil nivel v</t>
+          <t>Especialista en psiquiatría</t>
         </is>
       </c>
       <c r="D590" s="3" t="inlineStr">
@@ -28230,7 +28234,7 @@
         </is>
       </c>
       <c r="G590" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-nivel-v-1886758046", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-psiquiatria-1886757353", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H590" s="6" t="inlineStr"/>
@@ -28249,7 +28253,7 @@
     <row r="591" ht="22" customHeight="1">
       <c r="A591" s="2" t="inlineStr">
         <is>
-          <t>740f61bdbaa69d0e</t>
+          <t>b637f33f588eb5ae</t>
         </is>
       </c>
       <c r="B591" s="2" t="inlineStr">
@@ -28259,12 +28263,12 @@
       </c>
       <c r="C591" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de proyectos bilingüe</t>
+          <t>Especialista en diseño hospitalario</t>
         </is>
       </c>
       <c r="D591" s="3" t="inlineStr">
         <is>
-          <t>EyS IT SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E591" s="8" t="n">
@@ -28276,7 +28280,7 @@
         </is>
       </c>
       <c r="G591" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-bilingue-1886749343", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-diseno-hospitalario-disponibilidad-viajar-a-peru-1886747220", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H591" s="6" t="inlineStr"/>
@@ -28295,7 +28299,7 @@
     <row r="592" ht="22" customHeight="1">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>63ef229552018ccd</t>
+          <t>adcc2b47284b5d4d</t>
         </is>
       </c>
       <c r="B592" s="2" t="inlineStr">
@@ -28305,12 +28309,12 @@
       </c>
       <c r="C592" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de proyectos</t>
+          <t>Analista de diseño e ingeniería de empaque - sector farmaceutico</t>
         </is>
       </c>
       <c r="D592" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>LABORATORIOS BUSSIE</t>
         </is>
       </c>
       <c r="E592" s="8" t="n">
@@ -28322,7 +28326,7 @@
         </is>
       </c>
       <c r="G592" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-1886748647", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-diseno-e-ingenieria-de-empaque-sector-farmaceutico-1886755492", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H592" s="6" t="inlineStr"/>
@@ -28341,7 +28345,7 @@
     <row r="593" ht="22" customHeight="1">
       <c r="A593" s="2" t="inlineStr">
         <is>
-          <t>03750e25a7e1c016</t>
+          <t>3ec3d2d34753ff04</t>
         </is>
       </c>
       <c r="B593" s="2" t="inlineStr">
@@ -28351,12 +28355,12 @@
       </c>
       <c r="C593" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de proyectos inmobiliarios</t>
+          <t>Especialista de diseño y arquitectura</t>
         </is>
       </c>
       <c r="D593" s="3" t="inlineStr">
         <is>
-          <t>GRUPO AR S.A.</t>
+          <t>INTER RAPIDISIMO</t>
         </is>
       </c>
       <c r="E593" s="8" t="n">
@@ -28368,7 +28372,7 @@
         </is>
       </c>
       <c r="G593" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-inmobiliarios-1886745877", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-de-diseno-y-arquitectura-1886761909", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H593" s="6" t="inlineStr"/>
@@ -28387,7 +28391,7 @@
     <row r="594" ht="22" customHeight="1">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>5627e52731a73f27</t>
+          <t>4e917305e90b3efa</t>
         </is>
       </c>
       <c r="B594" s="2" t="inlineStr">
@@ -28397,12 +28401,12 @@
       </c>
       <c r="C594" s="3" t="inlineStr">
         <is>
-          <t>Coordinador de proyectos inmobiliarios</t>
+          <t>Especialista en geología</t>
         </is>
       </c>
       <c r="D594" s="3" t="inlineStr">
         <is>
-          <t>GRUPO AR S.A.</t>
+          <t>INGEPLAN.CO SAS EMPRESA DE BENEFICIO E INTERES COLECTIVO BIC</t>
         </is>
       </c>
       <c r="E594" s="8" t="n">
@@ -28414,7 +28418,7 @@
         </is>
       </c>
       <c r="G594" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-inmobiliarios-1886704948", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-geologia-1886761263", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H594" s="6" t="inlineStr"/>
@@ -28433,7 +28437,7 @@
     <row r="595" ht="22" customHeight="1">
       <c r="A595" s="2" t="inlineStr">
         <is>
-          <t>b6af0024900baff6</t>
+          <t>1aef5476d70bbe42</t>
         </is>
       </c>
       <c r="B595" s="2" t="inlineStr">
@@ -28443,12 +28447,12 @@
       </c>
       <c r="C595" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero residente - ingeniero civil-cordoba</t>
+          <t>Especialista en geología</t>
         </is>
       </c>
       <c r="D595" s="3" t="inlineStr">
         <is>
-          <t>OBCIPOL SAS</t>
+          <t>INGEPLAN.CO SAS EMPRESA DE BENEFICIO E INTERES COLECTIVO BIC</t>
         </is>
       </c>
       <c r="E595" s="8" t="n">
@@ -28460,7 +28464,7 @@
         </is>
       </c>
       <c r="G595" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-residente-ingeniero-civilcordoba-1886763488", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-geologia-1886755729", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H595" s="6" t="inlineStr"/>
@@ -28479,7 +28483,7 @@
     <row r="596" ht="22" customHeight="1">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>2a0453695fa88728</t>
+          <t>b46df3b678599255</t>
         </is>
       </c>
       <c r="B596" s="2" t="inlineStr">
@@ -28489,12 +28493,12 @@
       </c>
       <c r="C596" s="3" t="inlineStr">
         <is>
-          <t>Profesional ingenieria mecanica</t>
+          <t>Especialista en estructuras</t>
         </is>
       </c>
       <c r="D596" s="3" t="inlineStr">
         <is>
-          <t>INZIGNIA CONSTRUCTION S.A</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E596" s="8" t="n">
@@ -28506,7 +28510,7 @@
         </is>
       </c>
       <c r="G596" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/profesional-ingenieria-mecanica-1886767282", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-estructuras-1886757080", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H596" s="6" t="inlineStr"/>
@@ -28525,7 +28529,7 @@
     <row r="597" ht="22" customHeight="1">
       <c r="A597" s="2" t="inlineStr">
         <is>
-          <t>edfe98c543194667</t>
+          <t>935035bdfa2ae0b7</t>
         </is>
       </c>
       <c r="B597" s="2" t="inlineStr">
@@ -28535,12 +28539,12 @@
       </c>
       <c r="C597" s="3" t="inlineStr">
         <is>
-          <t>Jefe de sst - nemocón - 1625991634-135</t>
+          <t>Especialista en gestión del riesgo</t>
         </is>
       </c>
       <c r="D597" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>INGEPLAN.CO SAS EMPRESA DE BENEFICIO E INTERES COLECTIVO BIC</t>
         </is>
       </c>
       <c r="E597" s="8" t="n">
@@ -28552,13 +28556,13 @@
         </is>
       </c>
       <c r="G597" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/jefe-de-sst-nemocon-1625991634135-1886754873", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/especialista-en-gestion-del-riesgo-1886755709", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H597" s="6" t="inlineStr"/>
       <c r="I597" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J597" s="2" t="inlineStr">
@@ -28571,7 +28575,7 @@
     <row r="598" ht="22" customHeight="1">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>6233e93ceb1dbeed</t>
+          <t>14a1c964238340ba</t>
         </is>
       </c>
       <c r="B598" s="2" t="inlineStr">
@@ -28581,7 +28585,7 @@
       </c>
       <c r="C598" s="3" t="inlineStr">
         <is>
-          <t>Jefe de sst- nemocón</t>
+          <t>Ingeniero civil nivel v</t>
         </is>
       </c>
       <c r="D598" s="3" t="inlineStr">
@@ -28598,13 +28602,13 @@
         </is>
       </c>
       <c r="G598" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/jefe-de-sst-nemocon-1886757757", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-nivel-v-1886758046", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H598" s="6" t="inlineStr"/>
       <c r="I598" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J598" s="2" t="inlineStr">
@@ -28617,7 +28621,7 @@
     <row r="599" ht="22" customHeight="1">
       <c r="A599" s="2" t="inlineStr">
         <is>
-          <t>ce75aab7a32f36a3</t>
+          <t>740f61bdbaa69d0e</t>
         </is>
       </c>
       <c r="B599" s="2" t="inlineStr">
@@ -28627,12 +28631,12 @@
       </c>
       <c r="C599" s="3" t="inlineStr">
         <is>
-          <t>Coordinador talento humano y sst - bogota- 1626427532-7</t>
+          <t>Coordinador de proyectos bilingüe</t>
         </is>
       </c>
       <c r="D599" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>EyS IT SAS</t>
         </is>
       </c>
       <c r="E599" s="8" t="n">
@@ -28644,13 +28648,13 @@
         </is>
       </c>
       <c r="G599" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-talento-humano-y-sst-bogota-16264275327-1886753531", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-bilingue-1886749343", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H599" s="6" t="inlineStr"/>
       <c r="I599" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J599" s="2" t="inlineStr">
@@ -28663,7 +28667,7 @@
     <row r="600" ht="22" customHeight="1">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>850731f7bb6cd73f</t>
+          <t>63ef229552018ccd</t>
         </is>
       </c>
       <c r="B600" s="2" t="inlineStr">
@@ -28673,12 +28677,12 @@
       </c>
       <c r="C600" s="3" t="inlineStr">
         <is>
-          <t>Coordinador(a) de sst y medio ambiente</t>
+          <t>Coordinador de proyectos</t>
         </is>
       </c>
       <c r="D600" s="3" t="inlineStr">
         <is>
-          <t>ATIEMPO S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E600" s="8" t="n">
@@ -28690,13 +28694,13 @@
         </is>
       </c>
       <c r="G600" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinadora-de-sst-y-medio-ambiente-1886759848", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-1886748647", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H600" s="6" t="inlineStr"/>
       <c r="I600" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J600" s="2" t="inlineStr">
@@ -28709,7 +28713,7 @@
     <row r="601" ht="22" customHeight="1">
       <c r="A601" s="2" t="inlineStr">
         <is>
-          <t>abaf8e513787b3f3</t>
+          <t>03750e25a7e1c016</t>
         </is>
       </c>
       <c r="B601" s="2" t="inlineStr">
@@ -28719,12 +28723,12 @@
       </c>
       <c r="C601" s="3" t="inlineStr">
         <is>
-          <t>Coordinador pesv</t>
+          <t>Coordinador de proyectos inmobiliarios</t>
         </is>
       </c>
       <c r="D601" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>GRUPO AR S.A.</t>
         </is>
       </c>
       <c r="E601" s="8" t="n">
@@ -28736,13 +28740,13 @@
         </is>
       </c>
       <c r="G601" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-pesv-1886769643", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-inmobiliarios-1886745877", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H601" s="6" t="inlineStr"/>
       <c r="I601" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J601" s="2" t="inlineStr">
@@ -28755,7 +28759,7 @@
     <row r="602" ht="22" customHeight="1">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>9dcdf501e5912b88</t>
+          <t>5627e52731a73f27</t>
         </is>
       </c>
       <c r="B602" s="2" t="inlineStr">
@@ -28765,12 +28769,12 @@
       </c>
       <c r="C602" s="3" t="inlineStr">
         <is>
-          <t>Tecnico de obras civiles /girardot ref. 339166-82241</t>
+          <t>Coordinador de proyectos inmobiliarios</t>
         </is>
       </c>
       <c r="D602" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>GRUPO AR S.A.</t>
         </is>
       </c>
       <c r="E602" s="8" t="n">
@@ -28782,7 +28786,7 @@
         </is>
       </c>
       <c r="G602" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/tecnico-de-obras-civiles-girardot-ref-33916682241-1886747302", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-de-proyectos-inmobiliarios-1886704948", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H602" s="6" t="inlineStr"/>
@@ -28801,7 +28805,7 @@
     <row r="603" ht="22" customHeight="1">
       <c r="A603" s="2" t="inlineStr">
         <is>
-          <t>693b8a076a888f67</t>
+          <t>b6af0024900baff6</t>
         </is>
       </c>
       <c r="B603" s="2" t="inlineStr">
@@ -28811,12 +28815,12 @@
       </c>
       <c r="C603" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero civil - especializacion en estructuras</t>
+          <t>Ingeniero residente - ingeniero civil-cordoba</t>
         </is>
       </c>
       <c r="D603" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>OBCIPOL SAS</t>
         </is>
       </c>
       <c r="E603" s="8" t="n">
@@ -28828,7 +28832,7 @@
         </is>
       </c>
       <c r="G603" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-especializacion-en-estructuras-1886766956", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-residente-ingeniero-civilcordoba-1886763488", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H603" s="6" t="inlineStr"/>
@@ -28847,7 +28851,7 @@
     <row r="604" ht="22" customHeight="1">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>13bc527565632878</t>
+          <t>2a0453695fa88728</t>
         </is>
       </c>
       <c r="B604" s="2" t="inlineStr">
@@ -28857,12 +28861,12 @@
       </c>
       <c r="C604" s="3" t="inlineStr">
         <is>
-          <t>Tecnico en contratacion de obra civil bogota</t>
+          <t>Profesional ingenieria mecanica</t>
         </is>
       </c>
       <c r="D604" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>INZIGNIA CONSTRUCTION S.A</t>
         </is>
       </c>
       <c r="E604" s="8" t="n">
@@ -28874,7 +28878,7 @@
         </is>
       </c>
       <c r="G604" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/tecnico-en-contratacion-de-obra-civil-bogota-1886759693", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/profesional-ingenieria-mecanica-1886767282", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H604" s="6" t="inlineStr"/>
@@ -28893,7 +28897,7 @@
     <row r="605" ht="22" customHeight="1">
       <c r="A605" s="2" t="inlineStr">
         <is>
-          <t>6ccccd3a1ba05f7f</t>
+          <t>edfe98c543194667</t>
         </is>
       </c>
       <c r="B605" s="2" t="inlineStr">
@@ -28903,12 +28907,12 @@
       </c>
       <c r="C605" s="3" t="inlineStr">
         <is>
-          <t>14561-especialista interventoria-bogota</t>
+          <t>Jefe de sst - nemocón - 1625991634-135</t>
         </is>
       </c>
       <c r="D605" s="3" t="inlineStr">
         <is>
-          <t>APPLUS NORCONTROL COLOMBIA LTDA</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E605" s="8" t="n">
@@ -28920,13 +28924,13 @@
         </is>
       </c>
       <c r="G605" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/14561especialista-interventoriabogota-1886768886", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/jefe-de-sst-nemocon-1625991634135-1886754873", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H605" s="6" t="inlineStr"/>
       <c r="I605" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J605" s="2" t="inlineStr">
@@ -28939,7 +28943,7 @@
     <row r="606" ht="22" customHeight="1">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>8ad0c11c4f07472e</t>
+          <t>6233e93ceb1dbeed</t>
         </is>
       </c>
       <c r="B606" s="2" t="inlineStr">
@@ -28949,12 +28953,12 @@
       </c>
       <c r="C606" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero Civil / Terracerías</t>
+          <t>Jefe de sst- nemocón</t>
         </is>
       </c>
       <c r="D606" s="3" t="inlineStr">
         <is>
-          <t>EOSOL</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E606" s="8" t="n">
@@ -28966,13 +28970,13 @@
         </is>
       </c>
       <c r="G606" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-civil-terracer%C3%ADas-at-eosol-4445793534", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/jefe-de-sst-nemocon-1886757757", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H606" s="6" t="inlineStr"/>
       <c r="I606" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J606" s="2" t="inlineStr">
@@ -28985,7 +28989,7 @@
     <row r="607" ht="22" customHeight="1">
       <c r="A607" s="2" t="inlineStr">
         <is>
-          <t>ed46085f88d06bf5</t>
+          <t>ce75aab7a32f36a3</t>
         </is>
       </c>
       <c r="B607" s="2" t="inlineStr">
@@ -28995,12 +28999,12 @@
       </c>
       <c r="C607" s="3" t="inlineStr">
         <is>
-          <t>Supervisor Civil</t>
+          <t>Coordinador talento humano y sst - bogota- 1626427532-7</t>
         </is>
       </c>
       <c r="D607" s="3" t="inlineStr">
         <is>
-          <t>EOSOL</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E607" s="8" t="n">
@@ -29012,13 +29016,13 @@
         </is>
       </c>
       <c r="G607" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/supervisor-civil-at-eosol-4442238964", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-talento-humano-y-sst-bogota-16264275327-1886753531", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H607" s="6" t="inlineStr"/>
       <c r="I607" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J607" s="2" t="inlineStr">
@@ -29031,7 +29035,7 @@
     <row r="608" ht="22" customHeight="1">
       <c r="A608" s="2" t="inlineStr">
         <is>
-          <t>dc949850c44ae2c9</t>
+          <t>850731f7bb6cd73f</t>
         </is>
       </c>
       <c r="B608" s="2" t="inlineStr">
@@ -29041,12 +29045,12 @@
       </c>
       <c r="C608" s="3" t="inlineStr">
         <is>
-          <t>Civil Engineer</t>
+          <t>Coordinador(a) de sst y medio ambiente</t>
         </is>
       </c>
       <c r="D608" s="3" t="inlineStr">
         <is>
-          <t>Cresta</t>
+          <t>ATIEMPO S.A.S</t>
         </is>
       </c>
       <c r="E608" s="8" t="n">
@@ -29058,13 +29062,13 @@
         </is>
       </c>
       <c r="G608" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineer-at-cresta-4465582487", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinadora-de-sst-y-medio-ambiente-1886759848", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H608" s="6" t="inlineStr"/>
       <c r="I608" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J608" s="2" t="inlineStr">
@@ -29077,7 +29081,7 @@
     <row r="609" ht="22" customHeight="1">
       <c r="A609" s="2" t="inlineStr">
         <is>
-          <t>4ad1a5acabdb8ad3</t>
+          <t>abaf8e513787b3f3</t>
         </is>
       </c>
       <c r="B609" s="2" t="inlineStr">
@@ -29087,12 +29091,12 @@
       </c>
       <c r="C609" s="3" t="inlineStr">
         <is>
-          <t>Civil BIM Specialist</t>
+          <t>Coordinador pesv</t>
         </is>
       </c>
       <c r="D609" s="3" t="inlineStr">
         <is>
-          <t>ENG</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E609" s="8" t="n">
@@ -29104,13 +29108,13 @@
         </is>
       </c>
       <c r="G609" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-bim-specialist-at-eng-4469886677", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/coordinador-pesv-1886769643", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H609" s="6" t="inlineStr"/>
       <c r="I609" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en infraestructura vial y transporte. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J609" s="2" t="inlineStr">
@@ -29123,7 +29127,7 @@
     <row r="610" ht="22" customHeight="1">
       <c r="A610" s="2" t="inlineStr">
         <is>
-          <t>5ebaba0a0c9927fb</t>
+          <t>9dcdf501e5912b88</t>
         </is>
       </c>
       <c r="B610" s="2" t="inlineStr">
@@ -29133,12 +29137,12 @@
       </c>
       <c r="C610" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero/a Civil-Estructuras Hormigón/Acero</t>
+          <t>Tecnico de obras civiles /girardot ref. 339166-82241</t>
         </is>
       </c>
       <c r="D610" s="3" t="inlineStr">
         <is>
-          <t>IDOM Consulting, Engineering, Architecture</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E610" s="8" t="n">
@@ -29150,7 +29154,7 @@
         </is>
       </c>
       <c r="G610" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-civil-estructuras-hormig%C3%B3n-acero-at-idom-consulting-engineering-architecture-4462998187", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/tecnico-de-obras-civiles-girardot-ref-33916682241-1886747302", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H610" s="6" t="inlineStr"/>
@@ -29169,7 +29173,7 @@
     <row r="611" ht="22" customHeight="1">
       <c r="A611" s="2" t="inlineStr">
         <is>
-          <t>5c954c66c2c9d655</t>
+          <t>693b8a076a888f67</t>
         </is>
       </c>
       <c r="B611" s="2" t="inlineStr">
@@ -29179,12 +29183,12 @@
       </c>
       <c r="C611" s="3" t="inlineStr">
         <is>
-          <t>Civil Engineering-in-Training</t>
+          <t>Ingeniero civil - especializacion en estructuras</t>
         </is>
       </c>
       <c r="D611" s="3" t="inlineStr">
         <is>
-          <t>WSP en Colombia</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E611" s="8" t="n">
@@ -29196,7 +29200,7 @@
         </is>
       </c>
       <c r="G611" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineering-in-training-french-at-wsp-en-colombia-4458430104", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ingeniero-civil-especializacion-en-estructuras-1886766956", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H611" s="6" t="inlineStr"/>
@@ -29215,7 +29219,7 @@
     <row r="612" ht="22" customHeight="1">
       <c r="A612" s="2" t="inlineStr">
         <is>
-          <t>571ae2aa81fa07b5</t>
+          <t>13bc527565632878</t>
         </is>
       </c>
       <c r="B612" s="2" t="inlineStr">
@@ -29225,12 +29229,12 @@
       </c>
       <c r="C612" s="3" t="inlineStr">
         <is>
-          <t>Civil Engineering-in-Training</t>
+          <t>Tecnico en contratacion de obra civil bogota</t>
         </is>
       </c>
       <c r="D612" s="3" t="inlineStr">
         <is>
-          <t>WSP en Colombia</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E612" s="8" t="n">
@@ -29242,7 +29246,7 @@
         </is>
       </c>
       <c r="G612" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineering-in-training-at-wsp-en-colombia-4458027784", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/tecnico-en-contratacion-de-obra-civil-bogota-1886759693", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H612" s="6" t="inlineStr"/>
@@ -29261,7 +29265,7 @@
     <row r="613" ht="22" customHeight="1">
       <c r="A613" s="2" t="inlineStr">
         <is>
-          <t>d94bcf92627b7b99</t>
+          <t>6ccccd3a1ba05f7f</t>
         </is>
       </c>
       <c r="B613" s="2" t="inlineStr">
@@ -29271,12 +29275,12 @@
       </c>
       <c r="C613" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero civil</t>
+          <t>14561-especialista interventoria-bogota</t>
         </is>
       </c>
       <c r="D613" s="3" t="inlineStr">
         <is>
-          <t>HMV Ingenieros</t>
+          <t>APPLUS NORCONTROL COLOMBIA LTDA</t>
         </is>
       </c>
       <c r="E613" s="8" t="n">
@@ -29288,7 +29292,7 @@
         </is>
       </c>
       <c r="G613" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-civil-at-hmv-ingenieros-4461715824", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/14561especialista-interventoriabogota-1886768886", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H613" s="6" t="inlineStr"/>
@@ -29307,7 +29311,7 @@
     <row r="614" ht="22" customHeight="1">
       <c r="A614" s="2" t="inlineStr">
         <is>
-          <t>1be0a8e56fa4736b</t>
+          <t>8ad0c11c4f07472e</t>
         </is>
       </c>
       <c r="B614" s="2" t="inlineStr">
@@ -29317,12 +29321,12 @@
       </c>
       <c r="C614" s="3" t="inlineStr">
         <is>
-          <t>Civil Engineer</t>
+          <t>Ingeniero Civil / Terracerías</t>
         </is>
       </c>
       <c r="D614" s="3" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>EOSOL</t>
         </is>
       </c>
       <c r="E614" s="8" t="n">
@@ -29334,7 +29338,7 @@
         </is>
       </c>
       <c r="G614" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineer-at-wood-4418961778", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-civil-terracer%C3%ADas-at-eosol-4445793534", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H614" s="6" t="inlineStr"/>
@@ -29353,7 +29357,7 @@
     <row r="615" ht="22" customHeight="1">
       <c r="A615" s="2" t="inlineStr">
         <is>
-          <t>825c4e246cbd6b6b</t>
+          <t>ed46085f88d06bf5</t>
         </is>
       </c>
       <c r="B615" s="2" t="inlineStr">
@@ -29363,12 +29367,12 @@
       </c>
       <c r="C615" s="3" t="inlineStr">
         <is>
-          <t>Civil Engineering Expert</t>
+          <t>Supervisor Civil</t>
         </is>
       </c>
       <c r="D615" s="3" t="inlineStr">
         <is>
-          <t>Anyone AI</t>
+          <t>EOSOL</t>
         </is>
       </c>
       <c r="E615" s="8" t="n">
@@ -29380,7 +29384,7 @@
         </is>
       </c>
       <c r="G615" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineering-expert-at-anyone-ai-4462461832", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/supervisor-civil-at-eosol-4442238964", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H615" s="6" t="inlineStr"/>
@@ -29399,7 +29403,7 @@
     <row r="616" ht="22" customHeight="1">
       <c r="A616" s="2" t="inlineStr">
         <is>
-          <t>76740179a82340ae</t>
+          <t>dc949850c44ae2c9</t>
         </is>
       </c>
       <c r="B616" s="2" t="inlineStr">
@@ -29409,12 +29413,12 @@
       </c>
       <c r="C616" s="3" t="inlineStr">
         <is>
-          <t>Profesional en Ingeniería Civil</t>
+          <t>Civil Engineer</t>
         </is>
       </c>
       <c r="D616" s="3" t="inlineStr">
         <is>
-          <t>CMH Colombia</t>
+          <t>Cresta</t>
         </is>
       </c>
       <c r="E616" s="8" t="n">
@@ -29426,7 +29430,7 @@
         </is>
       </c>
       <c r="G616" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/profesional-en-ingenier%C3%ADa-civil-at-minerales-c%C3%B3rdoba-4450022471", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineer-at-cresta-4465582487", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H616" s="6" t="inlineStr"/>
@@ -29445,7 +29449,7 @@
     <row r="617" ht="22" customHeight="1">
       <c r="A617" s="2" t="inlineStr">
         <is>
-          <t>5bea04b9e734c2fc</t>
+          <t>4ad1a5acabdb8ad3</t>
         </is>
       </c>
       <c r="B617" s="2" t="inlineStr">
@@ -29455,12 +29459,12 @@
       </c>
       <c r="C617" s="3" t="inlineStr">
         <is>
-          <t>Coordinador HSEQ</t>
+          <t>Civil BIM Specialist</t>
         </is>
       </c>
       <c r="D617" s="3" t="inlineStr">
         <is>
-          <t>ASSEMTEC</t>
+          <t>ENG</t>
         </is>
       </c>
       <c r="E617" s="8" t="n">
@@ -29472,13 +29476,13 @@
         </is>
       </c>
       <c r="G617" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-hseq-at-assemtec-4457664932", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-bim-specialist-at-eng-4469886677", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H617" s="6" t="inlineStr"/>
       <c r="I617" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J617" s="2" t="inlineStr">
@@ -29491,7 +29495,7 @@
     <row r="618" ht="22" customHeight="1">
       <c r="A618" s="2" t="inlineStr">
         <is>
-          <t>6ba6bae2d7bfb226</t>
+          <t>5ebaba0a0c9927fb</t>
         </is>
       </c>
       <c r="B618" s="2" t="inlineStr">
@@ -29501,12 +29505,12 @@
       </c>
       <c r="C618" s="3" t="inlineStr">
         <is>
-          <t>Inspector SST con Licencia, Coordinador de Alturas</t>
+          <t>Ingeniero/a Civil-Estructuras Hormigón/Acero</t>
         </is>
       </c>
       <c r="D618" s="3" t="inlineStr">
         <is>
-          <t>Asertempo Colombia S.A.S</t>
+          <t>IDOM Consulting, Engineering, Architecture</t>
         </is>
       </c>
       <c r="E618" s="8" t="n">
@@ -29518,13 +29522,13 @@
         </is>
       </c>
       <c r="G618" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/inspector-sst-con-licencia-coordinador-de-alturas-at-asertempo-colombia-s-a-s-4464408367", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-civil-estructuras-hormig%C3%B3n-acero-at-idom-consulting-engineering-architecture-4462998187", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H618" s="6" t="inlineStr"/>
       <c r="I618" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J618" s="2" t="inlineStr">
@@ -29537,7 +29541,7 @@
     <row r="619" ht="22" customHeight="1">
       <c r="A619" s="2" t="inlineStr">
         <is>
-          <t>0df4a63a82189896</t>
+          <t>5c954c66c2c9d655</t>
         </is>
       </c>
       <c r="B619" s="2" t="inlineStr">
@@ -29547,12 +29551,12 @@
       </c>
       <c r="C619" s="3" t="inlineStr">
         <is>
-          <t>Especialista en Salud y Seguridad en el trabajo con especialización en medio Ambiente</t>
+          <t>Civil Engineering-in-Training</t>
         </is>
       </c>
       <c r="D619" s="3" t="inlineStr">
         <is>
-          <t>Dextera IT Services</t>
+          <t>WSP en Colombia</t>
         </is>
       </c>
       <c r="E619" s="8" t="n">
@@ -29564,7 +29568,7 @@
         </is>
       </c>
       <c r="G619" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/especialista-en-salud-y-seguridad-en-el-trabajo-con-especializaci%C3%B3n-en-medio-ambiente-at-dextera-it-services-4464024362", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineering-in-training-french-at-wsp-en-colombia-4458430104", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H619" s="6" t="inlineStr"/>
@@ -29583,7 +29587,7 @@
     <row r="620" ht="22" customHeight="1">
       <c r="A620" s="2" t="inlineStr">
         <is>
-          <t>e8e3c75915d1945c</t>
+          <t>571ae2aa81fa07b5</t>
         </is>
       </c>
       <c r="B620" s="2" t="inlineStr">
@@ -29593,12 +29597,12 @@
       </c>
       <c r="C620" s="3" t="inlineStr">
         <is>
-          <t>Coordinador (a) profesional HSEQ</t>
+          <t>Civil Engineering-in-Training</t>
         </is>
       </c>
       <c r="D620" s="3" t="inlineStr">
         <is>
-          <t>SD SAS</t>
+          <t>WSP en Colombia</t>
         </is>
       </c>
       <c r="E620" s="8" t="n">
@@ -29610,13 +29614,13 @@
         </is>
       </c>
       <c r="G620" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-profesional-hseq-at-sd-sas-4444939872", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineering-in-training-at-wsp-en-colombia-4458027784", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H620" s="6" t="inlineStr"/>
       <c r="I620" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J620" s="2" t="inlineStr">
@@ -29629,7 +29633,7 @@
     <row r="621" ht="22" customHeight="1">
       <c r="A621" s="2" t="inlineStr">
         <is>
-          <t>fb37fc1bf485e650</t>
+          <t>d94bcf92627b7b99</t>
         </is>
       </c>
       <c r="B621" s="2" t="inlineStr">
@@ -29639,12 +29643,12 @@
       </c>
       <c r="C621" s="3" t="inlineStr">
         <is>
-          <t>Técnico de trazado especialista en ISTRAM</t>
+          <t>Ingeniero civil</t>
         </is>
       </c>
       <c r="D621" s="3" t="inlineStr">
         <is>
-          <t>EADIC</t>
+          <t>HMV Ingenieros</t>
         </is>
       </c>
       <c r="E621" s="8" t="n">
@@ -29656,7 +29660,7 @@
         </is>
       </c>
       <c r="G621" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/t%C3%A9cnico-de-trazado-especialista-en-istram-at-eadic-4468780158", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-civil-at-hmv-ingenieros-4461715824", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H621" s="6" t="inlineStr"/>
@@ -29675,7 +29679,7 @@
     <row r="622" ht="22" customHeight="1">
       <c r="A622" s="2" t="inlineStr">
         <is>
-          <t>0f01a66eb85a1ffd</t>
+          <t>1be0a8e56fa4736b</t>
         </is>
       </c>
       <c r="B622" s="2" t="inlineStr">
@@ -29685,12 +29689,12 @@
       </c>
       <c r="C622" s="3" t="inlineStr">
         <is>
-          <t>AUXILIAR MODELADOR BIM Y DIBUJANTE EN INGENIERÍA CIVIL</t>
+          <t>Civil Engineer</t>
         </is>
       </c>
       <c r="D622" s="3" t="inlineStr">
         <is>
-          <t>Antea Group España y Latinoamérica</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="E622" s="8" t="n">
@@ -29702,7 +29706,7 @@
         </is>
       </c>
       <c r="G622" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-modelador-bim-y-dibujante-en-ingenier%C3%ADa-civil-at-antea-group-espa%C3%B1a-y-latinoam%C3%A9rica-4467605615", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineer-at-wood-4418961778", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H622" s="6" t="inlineStr"/>
@@ -29721,7 +29725,7 @@
     <row r="623" ht="22" customHeight="1">
       <c r="A623" s="2" t="inlineStr">
         <is>
-          <t>cba614af5ce1fc3a</t>
+          <t>825c4e246cbd6b6b</t>
         </is>
       </c>
       <c r="B623" s="2" t="inlineStr">
@@ -29731,12 +29735,12 @@
       </c>
       <c r="C623" s="3" t="inlineStr">
         <is>
-          <t>Principal Pavement Engineer - Linear Infrastructure &amp; Site Civils</t>
+          <t>Civil Engineering Expert</t>
         </is>
       </c>
       <c r="D623" s="3" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Anyone AI</t>
         </is>
       </c>
       <c r="E623" s="8" t="n">
@@ -29748,7 +29752,7 @@
         </is>
       </c>
       <c r="G623" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/principal-pavement-engineer-linear-infrastructure-site-civils-at-aecom-4403657428", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/civil-engineering-expert-at-anyone-ai-4462461832", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H623" s="6" t="inlineStr"/>
@@ -29767,7 +29771,7 @@
     <row r="624" ht="22" customHeight="1">
       <c r="A624" s="2" t="inlineStr">
         <is>
-          <t>2bafc4e5eb29746b</t>
+          <t>76740179a82340ae</t>
         </is>
       </c>
       <c r="B624" s="2" t="inlineStr">
@@ -29777,12 +29781,12 @@
       </c>
       <c r="C624" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero/a Geotécnico/a Senior</t>
+          <t>Profesional en Ingeniería Civil</t>
         </is>
       </c>
       <c r="D624" s="3" t="inlineStr">
         <is>
-          <t>IDOM Consulting, Engineering, Architecture</t>
+          <t>CMH Colombia</t>
         </is>
       </c>
       <c r="E624" s="8" t="n">
@@ -29794,7 +29798,7 @@
         </is>
       </c>
       <c r="G624" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-geot%C3%A9cnico-a-senior-at-idom-consulting-engineering-architecture-4467729578", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/profesional-en-ingenier%C3%ADa-civil-at-minerales-c%C3%B3rdoba-4450022471", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H624" s="6" t="inlineStr"/>
@@ -29813,7 +29817,7 @@
     <row r="625" ht="22" customHeight="1">
       <c r="A625" s="2" t="inlineStr">
         <is>
-          <t>f3290f3c2a2d0061</t>
+          <t>5bea04b9e734c2fc</t>
         </is>
       </c>
       <c r="B625" s="2" t="inlineStr">
@@ -29823,12 +29827,12 @@
       </c>
       <c r="C625" s="3" t="inlineStr">
         <is>
-          <t>Engenheiro Civil - Lisboa</t>
+          <t>Coordinador HSEQ</t>
         </is>
       </c>
       <c r="D625" s="3" t="inlineStr">
         <is>
-          <t>DDN GERENCIAMENTO</t>
+          <t>ASSEMTEC</t>
         </is>
       </c>
       <c r="E625" s="8" t="n">
@@ -29840,13 +29844,13 @@
         </is>
       </c>
       <c r="G625" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/engenheiro-civil-lisboa-at-ddn-gerenciamento-4468408791", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-hseq-at-assemtec-4457664932", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H625" s="6" t="inlineStr"/>
       <c r="I625" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J625" s="2" t="inlineStr">
@@ -29859,7 +29863,7 @@
     <row r="626" ht="22" customHeight="1">
       <c r="A626" s="2" t="inlineStr">
         <is>
-          <t>d2feccf91b9b1f0b</t>
+          <t>6ba6bae2d7bfb226</t>
         </is>
       </c>
       <c r="B626" s="2" t="inlineStr">
@@ -29869,12 +29873,12 @@
       </c>
       <c r="C626" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero/a Civil especialista en Talleres y Patios Ferroviarios</t>
+          <t>Inspector SST con Licencia, Coordinador de Alturas</t>
         </is>
       </c>
       <c r="D626" s="3" t="inlineStr">
         <is>
-          <t>IDOM Consulting, Engineering, Architecture</t>
+          <t>Asertempo Colombia S.A.S</t>
         </is>
       </c>
       <c r="E626" s="8" t="n">
@@ -29886,13 +29890,13 @@
         </is>
       </c>
       <c r="G626" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-civil-especialista-en-talleres-y-patios-ferroviarios-at-idom-consulting-engineering-architecture-4443713908", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/inspector-sst-con-licencia-coordinador-de-alturas-at-asertempo-colombia-s-a-s-4464408367", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H626" s="6" t="inlineStr"/>
       <c r="I626" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J626" s="2" t="inlineStr">
@@ -29905,7 +29909,7 @@
     <row r="627" ht="22" customHeight="1">
       <c r="A627" s="2" t="inlineStr">
         <is>
-          <t>152ea7f07f195fc8</t>
+          <t>0df4a63a82189896</t>
         </is>
       </c>
       <c r="B627" s="2" t="inlineStr">
@@ -29915,12 +29919,12 @@
       </c>
       <c r="C627" s="3" t="inlineStr">
         <is>
-          <t>COORDINADOR DE INTERVENTORÍA-NIVEL 1 SECTOR HIDROCARBUROS</t>
+          <t>Especialista en Salud y Seguridad en el trabajo con especialización en medio Ambiente</t>
         </is>
       </c>
       <c r="D627" s="3" t="inlineStr">
         <is>
-          <t>Centro de Empleo y Talento</t>
+          <t>Dextera IT Services</t>
         </is>
       </c>
       <c r="E627" s="8" t="n">
@@ -29932,7 +29936,7 @@
         </is>
       </c>
       <c r="G627" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-de-interventor%C3%ADa-nivel-1-sector-hidrocarburos-at-centro-de-empleo-y-talento-4468030406", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/especialista-en-salud-y-seguridad-en-el-trabajo-con-especializaci%C3%B3n-en-medio-ambiente-at-dextera-it-services-4464024362", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H627" s="6" t="inlineStr"/>
@@ -29951,7 +29955,7 @@
     <row r="628" ht="22" customHeight="1">
       <c r="A628" s="2" t="inlineStr">
         <is>
-          <t>b3dd7e9d8f53fb27</t>
+          <t>e8e3c75915d1945c</t>
         </is>
       </c>
       <c r="B628" s="2" t="inlineStr">
@@ -29961,12 +29965,12 @@
       </c>
       <c r="C628" s="3" t="inlineStr">
         <is>
-          <t>Consultor (Desarrollador) Senior Appian</t>
+          <t>Coordinador (a) profesional HSEQ</t>
         </is>
       </c>
       <c r="D628" s="3" t="inlineStr">
         <is>
-          <t>VASS LATAM</t>
+          <t>SD SAS</t>
         </is>
       </c>
       <c r="E628" s="8" t="n">
@@ -29978,13 +29982,13 @@
         </is>
       </c>
       <c r="G628" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/consultor-desarrollador-senior-appian-at-vass-latam-4458249659", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-profesional-hseq-at-sd-sas-4444939872", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H628" s="6" t="inlineStr"/>
       <c r="I628" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J628" s="2" t="inlineStr">
@@ -29997,7 +30001,7 @@
     <row r="629" ht="22" customHeight="1">
       <c r="A629" s="2" t="inlineStr">
         <is>
-          <t>0f895f69320d7d8d</t>
+          <t>fb37fc1bf485e650</t>
         </is>
       </c>
       <c r="B629" s="2" t="inlineStr">
@@ -30007,12 +30011,12 @@
       </c>
       <c r="C629" s="3" t="inlineStr">
         <is>
-          <t>Coordinador hse Cartagena</t>
+          <t>Técnico de trazado especialista en ISTRAM</t>
         </is>
       </c>
       <c r="D629" s="3" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONTEJO SAS</t>
+          <t>EADIC</t>
         </is>
       </c>
       <c r="E629" s="8" t="n">
@@ -30024,13 +30028,13 @@
         </is>
       </c>
       <c r="G629" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-hse-cartagena-at-transportes-montejo-sas-4458746462", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/t%C3%A9cnico-de-trazado-especialista-en-istram-at-eadic-4468780158", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H629" s="6" t="inlineStr"/>
       <c r="I629" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J629" s="2" t="inlineStr">
@@ -30043,7 +30047,7 @@
     <row r="630" ht="22" customHeight="1">
       <c r="A630" s="2" t="inlineStr">
         <is>
-          <t>b86d50ad2dd5f642</t>
+          <t>0f01a66eb85a1ffd</t>
         </is>
       </c>
       <c r="B630" s="2" t="inlineStr">
@@ -30053,12 +30057,12 @@
       </c>
       <c r="C630" s="3" t="inlineStr">
         <is>
-          <t>Coordinador Regional SIG/ SST</t>
+          <t>AUXILIAR MODELADOR BIM Y DIBUJANTE EN INGENIERÍA CIVIL</t>
         </is>
       </c>
       <c r="D630" s="3" t="inlineStr">
         <is>
-          <t>Interaseo S.A.S. E.S.P.</t>
+          <t>Antea Group España y Latinoamérica</t>
         </is>
       </c>
       <c r="E630" s="8" t="n">
@@ -30070,13 +30074,13 @@
         </is>
       </c>
       <c r="G630" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-regional-sig-sst-at-interaseo-s-a-s-e-s-p-4459088040", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-modelador-bim-y-dibujante-en-ingenier%C3%ADa-civil-at-antea-group-espa%C3%B1a-y-latinoam%C3%A9rica-4467605615", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H630" s="6" t="inlineStr"/>
       <c r="I630" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J630" s="2" t="inlineStr">
@@ -30089,7 +30093,7 @@
     <row r="631" ht="22" customHeight="1">
       <c r="A631" s="2" t="inlineStr">
         <is>
-          <t>506296811a5a9cbb</t>
+          <t>cba614af5ce1fc3a</t>
         </is>
       </c>
       <c r="B631" s="2" t="inlineStr">
@@ -30099,12 +30103,12 @@
       </c>
       <c r="C631" s="3" t="inlineStr">
         <is>
-          <t>Coordinador/a de SST</t>
+          <t>Principal Pavement Engineer - Linear Infrastructure &amp; Site Civils</t>
         </is>
       </c>
       <c r="D631" s="3" t="inlineStr">
         <is>
-          <t>Estelar Food S.A.S</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="E631" s="8" t="n">
@@ -30116,13 +30120,13 @@
         </is>
       </c>
       <c r="G631" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-de-sst-at-estelar-food-s-a-s-4462115593", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/principal-pavement-engineer-linear-infrastructure-site-civils-at-aecom-4403657428", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H631" s="6" t="inlineStr"/>
       <c r="I631" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J631" s="2" t="inlineStr">
@@ -30135,7 +30139,7 @@
     <row r="632" ht="22" customHeight="1">
       <c r="A632" s="2" t="inlineStr">
         <is>
-          <t>0e4b8eed7f32714e</t>
+          <t>2bafc4e5eb29746b</t>
         </is>
       </c>
       <c r="B632" s="2" t="inlineStr">
@@ -30145,12 +30149,12 @@
       </c>
       <c r="C632" s="3" t="inlineStr">
         <is>
-          <t>coordinador de Seguridad y Salud en el Trabajo</t>
+          <t>Ingeniero/a Geotécnico/a Senior</t>
         </is>
       </c>
       <c r="D632" s="3" t="inlineStr">
         <is>
-          <t>Asertempo Colombia S.A.S</t>
+          <t>IDOM Consulting, Engineering, Architecture</t>
         </is>
       </c>
       <c r="E632" s="8" t="n">
@@ -30162,13 +30166,13 @@
         </is>
       </c>
       <c r="G632" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-de-seguridad-y-salud-en-el-trabajo-at-asertempo-colombia-s-a-s-4461723686", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-geot%C3%A9cnico-a-senior-at-idom-consulting-engineering-architecture-4467729578", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H632" s="6" t="inlineStr"/>
       <c r="I632" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J632" s="2" t="inlineStr">
@@ -30181,7 +30185,7 @@
     <row r="633" ht="22" customHeight="1">
       <c r="A633" s="2" t="inlineStr">
         <is>
-          <t>aa2882af3c61095b</t>
+          <t>f3290f3c2a2d0061</t>
         </is>
       </c>
       <c r="B633" s="2" t="inlineStr">
@@ -30191,12 +30195,12 @@
       </c>
       <c r="C633" s="3" t="inlineStr">
         <is>
-          <t>Coordinador (a) SST / APH - Marmato</t>
+          <t>Engenheiro Civil - Lisboa</t>
         </is>
       </c>
       <c r="D633" s="3" t="inlineStr">
         <is>
-          <t>Aris Mining Colombia</t>
+          <t>DDN GERENCIAMENTO</t>
         </is>
       </c>
       <c r="E633" s="8" t="n">
@@ -30208,13 +30212,13 @@
         </is>
       </c>
       <c r="G633" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-sst-aph-marmato-at-aris-mining-colombia-4448929810", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/engenheiro-civil-lisboa-at-ddn-gerenciamento-4468408791", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H633" s="6" t="inlineStr"/>
       <c r="I633" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J633" s="2" t="inlineStr">
@@ -30227,7 +30231,7 @@
     <row r="634" ht="22" customHeight="1">
       <c r="A634" s="2" t="inlineStr">
         <is>
-          <t>26cff43f13982962</t>
+          <t>d2feccf91b9b1f0b</t>
         </is>
       </c>
       <c r="B634" s="2" t="inlineStr">
@@ -30237,12 +30241,12 @@
       </c>
       <c r="C634" s="3" t="inlineStr">
         <is>
-          <t>Consultor(a) Senior SOX TI</t>
+          <t>Ingeniero/a Civil especialista en Talleres y Patios Ferroviarios</t>
         </is>
       </c>
       <c r="D634" s="3" t="inlineStr">
         <is>
-          <t>Hitss Colombia</t>
+          <t>IDOM Consulting, Engineering, Architecture</t>
         </is>
       </c>
       <c r="E634" s="8" t="n">
@@ -30254,7 +30258,7 @@
         </is>
       </c>
       <c r="G634" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/consultor-a-senior-sox-ti-at-hitss-colombia-4460766744", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-civil-especialista-en-talleres-y-patios-ferroviarios-at-idom-consulting-engineering-architecture-4443713908", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H634" s="6" t="inlineStr"/>
@@ -30273,7 +30277,7 @@
     <row r="635" ht="22" customHeight="1">
       <c r="A635" s="2" t="inlineStr">
         <is>
-          <t>87e367215ed55502</t>
+          <t>152ea7f07f195fc8</t>
         </is>
       </c>
       <c r="B635" s="2" t="inlineStr">
@@ -30283,12 +30287,12 @@
       </c>
       <c r="C635" s="3" t="inlineStr">
         <is>
-          <t>Consultor(a) Senior Auditoría Interna</t>
+          <t>COORDINADOR DE INTERVENTORÍA-NIVEL 1 SECTOR HIDROCARBUROS</t>
         </is>
       </c>
       <c r="D635" s="3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Centro de Empleo y Talento</t>
         </is>
       </c>
       <c r="E635" s="8" t="n">
@@ -30300,7 +30304,7 @@
         </is>
       </c>
       <c r="G635" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/consultor-a-senior-auditor%C3%ADa-interna-at-deloitte-4462090075", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-de-interventor%C3%ADa-nivel-1-sector-hidrocarburos-at-centro-de-empleo-y-talento-4468030406", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H635" s="6" t="inlineStr"/>
@@ -30319,7 +30323,7 @@
     <row r="636" ht="22" customHeight="1">
       <c r="A636" s="2" t="inlineStr">
         <is>
-          <t>e2e525b51bbd0e5e</t>
+          <t>b3dd7e9d8f53fb27</t>
         </is>
       </c>
       <c r="B636" s="2" t="inlineStr">
@@ -30329,12 +30333,12 @@
       </c>
       <c r="C636" s="3" t="inlineStr">
         <is>
-          <t>Coordinador/a de Salud y Bienestar (HSE) Latam</t>
+          <t>Consultor (Desarrollador) Senior Appian</t>
         </is>
       </c>
       <c r="D636" s="3" t="inlineStr">
         <is>
-          <t>Aqualia</t>
+          <t>VASS LATAM</t>
         </is>
       </c>
       <c r="E636" s="8" t="n">
@@ -30346,13 +30350,13 @@
         </is>
       </c>
       <c r="G636" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-de-salud-y-bienestar-hse-latam-at-aqualia-4463977352", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/consultor-desarrollador-senior-appian-at-vass-latam-4458249659", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H636" s="6" t="inlineStr"/>
       <c r="I636" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J636" s="2" t="inlineStr">
@@ -30365,7 +30369,7 @@
     <row r="637" ht="22" customHeight="1">
       <c r="A637" s="2" t="inlineStr">
         <is>
-          <t>8ef614b651dfe9d9</t>
+          <t>0f895f69320d7d8d</t>
         </is>
       </c>
       <c r="B637" s="2" t="inlineStr">
@@ -30375,12 +30379,12 @@
       </c>
       <c r="C637" s="3" t="inlineStr">
         <is>
-          <t>Lead Civil Site Engineer</t>
+          <t>Coordinador hse Cartagena</t>
         </is>
       </c>
       <c r="D637" s="3" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>TRANSPORTES MONTEJO SAS</t>
         </is>
       </c>
       <c r="E637" s="8" t="n">
@@ -30392,13 +30396,13 @@
         </is>
       </c>
       <c r="G637" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/lead-civil-site-engineer-at-aecom-4468059409", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-hse-cartagena-at-transportes-montejo-sas-4458746462", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H637" s="6" t="inlineStr"/>
       <c r="I637" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J637" s="2" t="inlineStr">
@@ -30411,7 +30415,7 @@
     <row r="638" ht="22" customHeight="1">
       <c r="A638" s="2" t="inlineStr">
         <is>
-          <t>b339389a0d32a94f</t>
+          <t>b86d50ad2dd5f642</t>
         </is>
       </c>
       <c r="B638" s="2" t="inlineStr">
@@ -30421,12 +30425,12 @@
       </c>
       <c r="C638" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero civil</t>
+          <t>Coordinador Regional SIG/ SST</t>
         </is>
       </c>
       <c r="D638" s="3" t="inlineStr">
         <is>
-          <t>constructora cumbrera</t>
+          <t>Interaseo S.A.S. E.S.P.</t>
         </is>
       </c>
       <c r="E638" s="8" t="n">
@@ -30438,13 +30442,13 @@
         </is>
       </c>
       <c r="G638" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-civil-4463108593", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-regional-sig-sst-at-interaseo-s-a-s-e-s-p-4459088040", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H638" s="6" t="inlineStr"/>
       <c r="I638" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J638" s="2" t="inlineStr">
@@ -30457,7 +30461,7 @@
     <row r="639" ht="22" customHeight="1">
       <c r="A639" s="2" t="inlineStr">
         <is>
-          <t>93623c0212e39cb9</t>
+          <t>506296811a5a9cbb</t>
         </is>
       </c>
       <c r="B639" s="2" t="inlineStr">
@@ -30467,12 +30471,12 @@
       </c>
       <c r="C639" s="3" t="inlineStr">
         <is>
-          <t>Ingeniero(a) Civil</t>
+          <t>Coordinador/a de SST</t>
         </is>
       </c>
       <c r="D639" s="3" t="inlineStr">
         <is>
-          <t>CMH Colombia</t>
+          <t>Estelar Food S.A.S</t>
         </is>
       </c>
       <c r="E639" s="8" t="n">
@@ -30484,13 +30488,13 @@
         </is>
       </c>
       <c r="G639" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-civil-at-minerales-c%C3%B3rdoba-4417533007", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-de-sst-at-estelar-food-s-a-s-4462115593", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H639" s="6" t="inlineStr"/>
       <c r="I639" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J639" s="2" t="inlineStr">
@@ -30503,7 +30507,7 @@
     <row r="640" ht="22" customHeight="1">
       <c r="A640" s="2" t="inlineStr">
         <is>
-          <t>cd06fbe3d5b74888</t>
+          <t>0e4b8eed7f32714e</t>
         </is>
       </c>
       <c r="B640" s="2" t="inlineStr">
@@ -30513,12 +30517,12 @@
       </c>
       <c r="C640" s="3" t="inlineStr">
         <is>
-          <t>Oficial Obra Civil</t>
+          <t>coordinador de Seguridad y Salud en el Trabajo</t>
         </is>
       </c>
       <c r="D640" s="3" t="inlineStr">
         <is>
-          <t>Equans Colombia</t>
+          <t>Asertempo Colombia S.A.S</t>
         </is>
       </c>
       <c r="E640" s="8" t="n">
@@ -30530,25 +30534,393 @@
         </is>
       </c>
       <c r="G640" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/oficial-obra-civil-bogota-y-cundinamarca-at-equans-colombia-4470218146", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-de-seguridad-y-salud-en-el-trabajo-at-asertempo-colombia-s-a-s-4461723686", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H640" s="6" t="inlineStr"/>
       <c r="I640" s="3" t="inlineStr">
         <is>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J640" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K640" s="3" t="inlineStr"/>
+    </row>
+    <row r="641" ht="22" customHeight="1">
+      <c r="A641" s="2" t="inlineStr">
+        <is>
+          <t>aa2882af3c61095b</t>
+        </is>
+      </c>
+      <c r="B641" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 05:09</t>
+        </is>
+      </c>
+      <c r="C641" s="3" t="inlineStr">
+        <is>
+          <t>Coordinador (a) SST / APH - Marmato</t>
+        </is>
+      </c>
+      <c r="D641" s="3" t="inlineStr">
+        <is>
+          <t>Aris Mining Colombia</t>
+        </is>
+      </c>
+      <c r="E641" s="8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F641" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G641" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-sst-aph-marmato-at-aris-mining-colombia-4448929810", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H641" s="6" t="inlineStr"/>
+      <c r="I641" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J641" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K641" s="3" t="inlineStr"/>
+    </row>
+    <row r="642" ht="22" customHeight="1">
+      <c r="A642" s="2" t="inlineStr">
+        <is>
+          <t>26cff43f13982962</t>
+        </is>
+      </c>
+      <c r="B642" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 05:09</t>
+        </is>
+      </c>
+      <c r="C642" s="3" t="inlineStr">
+        <is>
+          <t>Consultor(a) Senior SOX TI</t>
+        </is>
+      </c>
+      <c r="D642" s="3" t="inlineStr">
+        <is>
+          <t>Hitss Colombia</t>
+        </is>
+      </c>
+      <c r="E642" s="8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F642" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G642" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/consultor-a-senior-sox-ti-at-hitss-colombia-4460766744", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H642" s="6" t="inlineStr"/>
+      <c r="I642" s="3" t="inlineStr">
+        <is>
           <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
-      <c r="J640" s="2" t="inlineStr">
-        <is>
-          <t>Nueva</t>
-        </is>
-      </c>
-      <c r="K640" s="3" t="inlineStr"/>
+      <c r="J642" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K642" s="3" t="inlineStr"/>
+    </row>
+    <row r="643" ht="22" customHeight="1">
+      <c r="A643" s="2" t="inlineStr">
+        <is>
+          <t>87e367215ed55502</t>
+        </is>
+      </c>
+      <c r="B643" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 05:09</t>
+        </is>
+      </c>
+      <c r="C643" s="3" t="inlineStr">
+        <is>
+          <t>Consultor(a) Senior Auditoría Interna</t>
+        </is>
+      </c>
+      <c r="D643" s="3" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="E643" s="8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F643" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G643" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/consultor-a-senior-auditor%C3%ADa-interna-at-deloitte-4462090075", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H643" s="6" t="inlineStr"/>
+      <c r="I643" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J643" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K643" s="3" t="inlineStr"/>
+    </row>
+    <row r="644" ht="22" customHeight="1">
+      <c r="A644" s="2" t="inlineStr">
+        <is>
+          <t>e2e525b51bbd0e5e</t>
+        </is>
+      </c>
+      <c r="B644" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 05:09</t>
+        </is>
+      </c>
+      <c r="C644" s="3" t="inlineStr">
+        <is>
+          <t>Coordinador/a de Salud y Bienestar (HSE) Latam</t>
+        </is>
+      </c>
+      <c r="D644" s="3" t="inlineStr">
+        <is>
+          <t>Aqualia</t>
+        </is>
+      </c>
+      <c r="E644" s="8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F644" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G644" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/coordinador-a-de-salud-y-bienestar-hse-latam-at-aqualia-4463977352", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H644" s="6" t="inlineStr"/>
+      <c r="I644" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad parcial en seguridad y salud ocupacional. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J644" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K644" s="3" t="inlineStr"/>
+    </row>
+    <row r="645" ht="22" customHeight="1">
+      <c r="A645" s="2" t="inlineStr">
+        <is>
+          <t>8ef614b651dfe9d9</t>
+        </is>
+      </c>
+      <c r="B645" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 05:09</t>
+        </is>
+      </c>
+      <c r="C645" s="3" t="inlineStr">
+        <is>
+          <t>Lead Civil Site Engineer</t>
+        </is>
+      </c>
+      <c r="D645" s="3" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E645" s="8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F645" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G645" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/lead-civil-site-engineer-at-aecom-4468059409", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H645" s="6" t="inlineStr"/>
+      <c r="I645" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J645" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K645" s="3" t="inlineStr"/>
+    </row>
+    <row r="646" ht="22" customHeight="1">
+      <c r="A646" s="2" t="inlineStr">
+        <is>
+          <t>b339389a0d32a94f</t>
+        </is>
+      </c>
+      <c r="B646" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 05:09</t>
+        </is>
+      </c>
+      <c r="C646" s="3" t="inlineStr">
+        <is>
+          <t>Ingeniero civil</t>
+        </is>
+      </c>
+      <c r="D646" s="3" t="inlineStr">
+        <is>
+          <t>constructora cumbrera</t>
+        </is>
+      </c>
+      <c r="E646" s="8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F646" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G646" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-civil-4463108593", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H646" s="6" t="inlineStr"/>
+      <c r="I646" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J646" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K646" s="3" t="inlineStr"/>
+    </row>
+    <row r="647" ht="22" customHeight="1">
+      <c r="A647" s="2" t="inlineStr">
+        <is>
+          <t>93623c0212e39cb9</t>
+        </is>
+      </c>
+      <c r="B647" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 05:09</t>
+        </is>
+      </c>
+      <c r="C647" s="3" t="inlineStr">
+        <is>
+          <t>Ingeniero(a) Civil</t>
+        </is>
+      </c>
+      <c r="D647" s="3" t="inlineStr">
+        <is>
+          <t>CMH Colombia</t>
+        </is>
+      </c>
+      <c r="E647" s="8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F647" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G647" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/ingeniero-a-civil-at-minerales-c%C3%B3rdoba-4417533007", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H647" s="6" t="inlineStr"/>
+      <c r="I647" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J647" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K647" s="3" t="inlineStr"/>
+    </row>
+    <row r="648" ht="22" customHeight="1">
+      <c r="A648" s="2" t="inlineStr">
+        <is>
+          <t>cd06fbe3d5b74888</t>
+        </is>
+      </c>
+      <c r="B648" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 05:09</t>
+        </is>
+      </c>
+      <c r="C648" s="3" t="inlineStr">
+        <is>
+          <t>Oficial Obra Civil</t>
+        </is>
+      </c>
+      <c r="D648" s="3" t="inlineStr">
+        <is>
+          <t>Equans Colombia</t>
+        </is>
+      </c>
+      <c r="E648" s="8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F648" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G648" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/oficial-obra-civil-bogota-y-cundinamarca-at-equans-colombia-4470218146", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H648" s="6" t="inlineStr"/>
+      <c r="I648" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 45/100 - Baja Afinidad] Afinidad en disciplina base (Ingeniera Civil Especialista en Vías y SST) sin especialidad directa en vías/SST. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J648" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K648" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J839" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J847" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Nueva,Por revisar,Postulado,Descartado,Entrevista"</formula1>
     </dataValidation>
   </dataValidations>
